--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="277">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -595,6 +595,18 @@
     <t>['19']</t>
   </si>
   <si>
+    <t>['24', '48']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['18', '25', '36', '79']</t>
+  </si>
+  <si>
+    <t>['23']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -827,6 +839,12 @@
   </si>
   <si>
     <t>['37', '49', '86']</t>
+  </si>
+  <si>
+    <t>['15', '17', '51', '67', '77', '90+2']</t>
+  </si>
+  <si>
+    <t>['1', '29', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP144"/>
+  <dimension ref="A1:BP150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1728,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1856,7 +1874,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2140,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ5">
         <v>1.08</v>
@@ -2474,7 +2492,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2555,7 +2573,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ7">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2758,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -2886,7 +2904,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -2967,7 +2985,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3170,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ10">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3298,7 +3316,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3376,10 +3394,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ11">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3504,7 +3522,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3710,7 +3728,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -3788,10 +3806,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ13">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3997,7 +4015,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR14">
         <v>2.04</v>
@@ -4122,7 +4140,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4200,7 +4218,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ15">
         <v>1.09</v>
@@ -4406,10 +4424,10 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ16">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>2.02</v>
@@ -4534,7 +4552,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4612,10 +4630,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR17">
         <v>1.07</v>
@@ -4818,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR18">
         <v>1.47</v>
@@ -5152,7 +5170,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5230,7 +5248,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ20">
         <v>1.08</v>
@@ -5358,7 +5376,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5564,7 +5582,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5645,7 +5663,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ22">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>1.66</v>
@@ -5976,7 +5994,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6057,7 +6075,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR24">
         <v>1.14</v>
@@ -6182,7 +6200,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6260,7 +6278,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ25">
         <v>1.08</v>
@@ -6675,7 +6693,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ27">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR27">
         <v>2.21</v>
@@ -6878,10 +6896,10 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ28">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR28">
         <v>0.85</v>
@@ -7212,7 +7230,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7290,7 +7308,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ30">
         <v>0.6899999999999999</v>
@@ -7624,7 +7642,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7705,7 +7723,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ32">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR32">
         <v>1.31</v>
@@ -7908,10 +7926,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ33">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR33">
         <v>0.87</v>
@@ -8036,7 +8054,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8117,7 +8135,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.25</v>
@@ -8242,7 +8260,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8320,10 +8338,10 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ35">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR35">
         <v>1.32</v>
@@ -8448,7 +8466,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8526,7 +8544,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
         <v>1.08</v>
@@ -8654,7 +8672,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8732,10 +8750,10 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ37">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -8860,7 +8878,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -8941,7 +8959,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ38">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR38">
         <v>1.42</v>
@@ -9144,7 +9162,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ39">
         <v>1.08</v>
@@ -9272,7 +9290,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9350,10 +9368,10 @@
         <v>1.67</v>
       </c>
       <c r="AP40">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ40">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR40">
         <v>0.9399999999999999</v>
@@ -9478,7 +9496,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9556,7 +9574,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -9684,7 +9702,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9762,7 +9780,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ42">
         <v>0.6899999999999999</v>
@@ -9890,7 +9908,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -9971,7 +9989,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ43">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR43">
         <v>1.4</v>
@@ -10096,7 +10114,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10177,7 +10195,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ44">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR44">
         <v>1.19</v>
@@ -10380,10 +10398,10 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ45">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR45">
         <v>1.85</v>
@@ -10508,7 +10526,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10589,7 +10607,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ46">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>2.16</v>
@@ -10714,7 +10732,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11126,7 +11144,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11204,7 +11222,7 @@
         <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ49">
         <v>1.09</v>
@@ -11413,7 +11431,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ50">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11616,7 +11634,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ51">
         <v>1.33</v>
@@ -11744,7 +11762,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11822,10 +11840,10 @@
         <v>0.8</v>
       </c>
       <c r="AP52">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ52">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -11950,7 +11968,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12237,7 +12255,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ54">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR54">
         <v>1.17</v>
@@ -12440,10 +12458,10 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ55">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR55">
         <v>1.27</v>
@@ -12568,7 +12586,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12646,10 +12664,10 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
@@ -12774,7 +12792,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -12852,7 +12870,7 @@
         <v>0.25</v>
       </c>
       <c r="AP57">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ57">
         <v>1.08</v>
@@ -12980,7 +12998,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13392,7 +13410,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13470,10 +13488,10 @@
         <v>1.17</v>
       </c>
       <c r="AP60">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ60">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR60">
         <v>1.06</v>
@@ -13598,7 +13616,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14010,7 +14028,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14216,7 +14234,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14297,7 +14315,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ64">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR64">
         <v>1.33</v>
@@ -14500,10 +14518,10 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ65">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR65">
         <v>1.13</v>
@@ -14628,7 +14646,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14706,7 +14724,7 @@
         <v>1.17</v>
       </c>
       <c r="AP66">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ66">
         <v>0.6899999999999999</v>
@@ -14834,7 +14852,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -14912,10 +14930,10 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ67">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR67">
         <v>1.3</v>
@@ -15121,7 +15139,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ68">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.22</v>
@@ -15246,7 +15264,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15324,7 +15342,7 @@
         <v>0.2</v>
       </c>
       <c r="AP69">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ69">
         <v>1.08</v>
@@ -15452,7 +15470,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15530,10 +15548,10 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ70">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR70">
         <v>1.19</v>
@@ -15658,7 +15676,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15864,7 +15882,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -15942,10 +15960,10 @@
         <v>3</v>
       </c>
       <c r="AP72">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ72">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR72">
         <v>1.22</v>
@@ -16148,10 +16166,10 @@
         <v>0.57</v>
       </c>
       <c r="AP73">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ73">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR73">
         <v>1.87</v>
@@ -16482,7 +16500,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16766,10 +16784,10 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ76">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR76">
         <v>1.75</v>
@@ -16894,7 +16912,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16972,10 +16990,10 @@
         <v>2.5</v>
       </c>
       <c r="AP77">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ77">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.13</v>
@@ -17100,7 +17118,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17178,7 +17196,7 @@
         <v>0.4</v>
       </c>
       <c r="AP78">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ78">
         <v>1.08</v>
@@ -17306,7 +17324,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17387,7 +17405,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR79">
         <v>1.56</v>
@@ -17512,7 +17530,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17590,10 +17608,10 @@
         <v>2</v>
       </c>
       <c r="AP80">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ80">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR80">
         <v>1.33</v>
@@ -17799,7 +17817,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ81">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>2.21</v>
@@ -18130,7 +18148,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18208,7 +18226,7 @@
         <v>0.83</v>
       </c>
       <c r="AP83">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ83">
         <v>1.09</v>
@@ -18336,7 +18354,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18414,7 +18432,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
         <v>1.08</v>
@@ -18542,7 +18560,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18748,7 +18766,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18829,7 +18847,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ86">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.56</v>
@@ -19032,7 +19050,7 @@
         <v>0.88</v>
       </c>
       <c r="AP87">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ87">
         <v>0.6899999999999999</v>
@@ -19238,7 +19256,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ88">
         <v>1</v>
@@ -19366,7 +19384,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19447,7 +19465,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ89">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19650,7 +19668,7 @@
         <v>1.29</v>
       </c>
       <c r="AP90">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -19859,7 +19877,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ91">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR91">
         <v>1.37</v>
@@ -20602,7 +20620,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20808,7 +20826,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21014,7 +21032,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21092,10 +21110,10 @@
         <v>0.43</v>
       </c>
       <c r="AP97">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ97">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.38</v>
@@ -21220,7 +21238,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21298,10 +21316,10 @@
         <v>1.43</v>
       </c>
       <c r="AP98">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ98">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR98">
         <v>1.21</v>
@@ -21504,10 +21522,10 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ99">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR99">
         <v>1.4</v>
@@ -21632,7 +21650,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21710,7 +21728,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ100">
         <v>0.6899999999999999</v>
@@ -21838,7 +21856,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22122,7 +22140,7 @@
         <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ102">
         <v>1.09</v>
@@ -22250,7 +22268,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22537,7 +22555,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR104">
         <v>1.42</v>
@@ -22743,7 +22761,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ105">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR105">
         <v>1.69</v>
@@ -22868,7 +22886,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23280,7 +23298,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23358,10 +23376,10 @@
         <v>0.38</v>
       </c>
       <c r="AP108">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ108">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR108">
         <v>1.38</v>
@@ -23564,10 +23582,10 @@
         <v>1.71</v>
       </c>
       <c r="AP109">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ109">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR109">
         <v>1.35</v>
@@ -23692,7 +23710,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23773,7 +23791,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ110">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR110">
         <v>1.25</v>
@@ -23976,7 +23994,7 @@
         <v>1.43</v>
       </c>
       <c r="AP111">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ111">
         <v>1.33</v>
@@ -24104,7 +24122,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24185,7 +24203,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ112">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR112">
         <v>1.24</v>
@@ -24391,7 +24409,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ113">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR113">
         <v>2.24</v>
@@ -24594,7 +24612,7 @@
         <v>0.82</v>
       </c>
       <c r="AP114">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ114">
         <v>0.6899999999999999</v>
@@ -24722,7 +24740,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24800,7 +24818,7 @@
         <v>1.25</v>
       </c>
       <c r="AP115">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ115">
         <v>1.33</v>
@@ -24928,7 +24946,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25006,7 +25024,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ116">
         <v>1.09</v>
@@ -25215,7 +25233,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ117">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR117">
         <v>1.33</v>
@@ -25418,10 +25436,10 @@
         <v>2.78</v>
       </c>
       <c r="AP118">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ118">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR118">
         <v>2.04</v>
@@ -26036,7 +26054,7 @@
         <v>1.11</v>
       </c>
       <c r="AP121">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ121">
         <v>1.08</v>
@@ -26164,7 +26182,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26245,7 +26263,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ122">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR122">
         <v>1.36</v>
@@ -26370,7 +26388,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26448,10 +26466,10 @@
         <v>1.44</v>
       </c>
       <c r="AP123">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ123">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR123">
         <v>1.36</v>
@@ -26576,7 +26594,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26654,7 +26672,7 @@
         <v>1.22</v>
       </c>
       <c r="AP124">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ124">
         <v>1.33</v>
@@ -26860,10 +26878,10 @@
         <v>1.33</v>
       </c>
       <c r="AP125">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ125">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR125">
         <v>1.17</v>
@@ -27194,7 +27212,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27275,7 +27293,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ127">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR127">
         <v>1.36</v>
@@ -27400,7 +27418,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27478,10 +27496,10 @@
         <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ128">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR128">
         <v>1.42</v>
@@ -27606,7 +27624,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -27890,7 +27908,7 @@
         <v>1.2</v>
       </c>
       <c r="AP130">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -28099,7 +28117,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ131">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR131">
         <v>2.28</v>
@@ -28302,7 +28320,7 @@
         <v>1.2</v>
       </c>
       <c r="AP132">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ132">
         <v>1.33</v>
@@ -28430,7 +28448,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28511,7 +28529,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ133">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR133">
         <v>1.25</v>
@@ -28714,10 +28732,10 @@
         <v>1.45</v>
       </c>
       <c r="AP134">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ134">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR134">
         <v>1.22</v>
@@ -28842,7 +28860,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -28920,7 +28938,7 @@
         <v>1.18</v>
       </c>
       <c r="AP135">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ135">
         <v>1</v>
@@ -29048,7 +29066,7 @@
         <v>187</v>
       </c>
       <c r="P136" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q136">
         <v>1.37</v>
@@ -29126,10 +29144,10 @@
         <v>0.73</v>
       </c>
       <c r="AP136">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ136">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR136">
         <v>2.05</v>
@@ -29335,7 +29353,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ137">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR137">
         <v>1.38</v>
@@ -29460,7 +29478,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29538,10 +29556,10 @@
         <v>2.55</v>
       </c>
       <c r="AP138">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ138">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR138">
         <v>1.32</v>
@@ -29744,10 +29762,10 @@
         <v>1.2</v>
       </c>
       <c r="AP139">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ139">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR139">
         <v>2</v>
@@ -29872,7 +29890,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30078,7 +30096,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30284,7 +30302,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30490,7 +30508,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30696,7 +30714,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30853,6 +30871,1242 @@
       </c>
       <c r="BP144">
         <v>1.73</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7480287</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F145">
+        <v>25</v>
+      </c>
+      <c r="G145" t="s">
+        <v>73</v>
+      </c>
+      <c r="H145" t="s">
+        <v>75</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>1</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145" t="s">
+        <v>82</v>
+      </c>
+      <c r="P145" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q145">
+        <v>2.5</v>
+      </c>
+      <c r="R145">
+        <v>2.2</v>
+      </c>
+      <c r="S145">
+        <v>4.75</v>
+      </c>
+      <c r="T145">
+        <v>1.4</v>
+      </c>
+      <c r="U145">
+        <v>2.75</v>
+      </c>
+      <c r="V145">
+        <v>2.75</v>
+      </c>
+      <c r="W145">
+        <v>1.4</v>
+      </c>
+      <c r="X145">
+        <v>8</v>
+      </c>
+      <c r="Y145">
+        <v>1.08</v>
+      </c>
+      <c r="Z145">
+        <v>1.78</v>
+      </c>
+      <c r="AA145">
+        <v>3.66</v>
+      </c>
+      <c r="AB145">
+        <v>4.2</v>
+      </c>
+      <c r="AC145">
+        <v>1.05</v>
+      </c>
+      <c r="AD145">
+        <v>9.5</v>
+      </c>
+      <c r="AE145">
+        <v>1.25</v>
+      </c>
+      <c r="AF145">
+        <v>3.8</v>
+      </c>
+      <c r="AG145">
+        <v>1.77</v>
+      </c>
+      <c r="AH145">
+        <v>1.98</v>
+      </c>
+      <c r="AI145">
+        <v>1.8</v>
+      </c>
+      <c r="AJ145">
+        <v>1.95</v>
+      </c>
+      <c r="AK145">
+        <v>1.22</v>
+      </c>
+      <c r="AL145">
+        <v>1.26</v>
+      </c>
+      <c r="AM145">
+        <v>1.98</v>
+      </c>
+      <c r="AN145">
+        <v>1.42</v>
+      </c>
+      <c r="AO145">
+        <v>0.67</v>
+      </c>
+      <c r="AP145">
+        <v>1.31</v>
+      </c>
+      <c r="AQ145">
+        <v>0.85</v>
+      </c>
+      <c r="AR145">
+        <v>1.26</v>
+      </c>
+      <c r="AS145">
+        <v>1</v>
+      </c>
+      <c r="AT145">
+        <v>2.26</v>
+      </c>
+      <c r="AU145">
+        <v>5</v>
+      </c>
+      <c r="AV145">
+        <v>5</v>
+      </c>
+      <c r="AW145">
+        <v>9</v>
+      </c>
+      <c r="AX145">
+        <v>1</v>
+      </c>
+      <c r="AY145">
+        <v>14</v>
+      </c>
+      <c r="AZ145">
+        <v>6</v>
+      </c>
+      <c r="BA145">
+        <v>5</v>
+      </c>
+      <c r="BB145">
+        <v>3</v>
+      </c>
+      <c r="BC145">
+        <v>8</v>
+      </c>
+      <c r="BD145">
+        <v>1.45</v>
+      </c>
+      <c r="BE145">
+        <v>7</v>
+      </c>
+      <c r="BF145">
+        <v>3.05</v>
+      </c>
+      <c r="BG145">
+        <v>1.21</v>
+      </c>
+      <c r="BH145">
+        <v>3.7</v>
+      </c>
+      <c r="BI145">
+        <v>1.38</v>
+      </c>
+      <c r="BJ145">
+        <v>2.75</v>
+      </c>
+      <c r="BK145">
+        <v>1.62</v>
+      </c>
+      <c r="BL145">
+        <v>2.14</v>
+      </c>
+      <c r="BM145">
+        <v>1.97</v>
+      </c>
+      <c r="BN145">
+        <v>1.73</v>
+      </c>
+      <c r="BO145">
+        <v>2.48</v>
+      </c>
+      <c r="BP145">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7480282</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F146">
+        <v>25</v>
+      </c>
+      <c r="G146" t="s">
+        <v>78</v>
+      </c>
+      <c r="H146" t="s">
+        <v>70</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>2</v>
+      </c>
+      <c r="K146">
+        <v>2</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>6</v>
+      </c>
+      <c r="N146">
+        <v>6</v>
+      </c>
+      <c r="O146" t="s">
+        <v>82</v>
+      </c>
+      <c r="P146" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q146">
+        <v>3.5</v>
+      </c>
+      <c r="R146">
+        <v>2.2</v>
+      </c>
+      <c r="S146">
+        <v>3</v>
+      </c>
+      <c r="T146">
+        <v>1.36</v>
+      </c>
+      <c r="U146">
+        <v>3</v>
+      </c>
+      <c r="V146">
+        <v>2.75</v>
+      </c>
+      <c r="W146">
+        <v>1.4</v>
+      </c>
+      <c r="X146">
+        <v>7</v>
+      </c>
+      <c r="Y146">
+        <v>1.1</v>
+      </c>
+      <c r="Z146">
+        <v>2.9</v>
+      </c>
+      <c r="AA146">
+        <v>3.34</v>
+      </c>
+      <c r="AB146">
+        <v>2.35</v>
+      </c>
+      <c r="AC146">
+        <v>1.05</v>
+      </c>
+      <c r="AD146">
+        <v>9.5</v>
+      </c>
+      <c r="AE146">
+        <v>1.25</v>
+      </c>
+      <c r="AF146">
+        <v>3.75</v>
+      </c>
+      <c r="AG146">
+        <v>1.82</v>
+      </c>
+      <c r="AH146">
+        <v>1.92</v>
+      </c>
+      <c r="AI146">
+        <v>1.67</v>
+      </c>
+      <c r="AJ146">
+        <v>2.1</v>
+      </c>
+      <c r="AK146">
+        <v>1.57</v>
+      </c>
+      <c r="AL146">
+        <v>1.28</v>
+      </c>
+      <c r="AM146">
+        <v>1.41</v>
+      </c>
+      <c r="AN146">
+        <v>1.25</v>
+      </c>
+      <c r="AO146">
+        <v>0.75</v>
+      </c>
+      <c r="AP146">
+        <v>1.15</v>
+      </c>
+      <c r="AQ146">
+        <v>0.92</v>
+      </c>
+      <c r="AR146">
+        <v>1.31</v>
+      </c>
+      <c r="AS146">
+        <v>1.16</v>
+      </c>
+      <c r="AT146">
+        <v>2.47</v>
+      </c>
+      <c r="AU146">
+        <v>4</v>
+      </c>
+      <c r="AV146">
+        <v>13</v>
+      </c>
+      <c r="AW146">
+        <v>5</v>
+      </c>
+      <c r="AX146">
+        <v>5</v>
+      </c>
+      <c r="AY146">
+        <v>9</v>
+      </c>
+      <c r="AZ146">
+        <v>18</v>
+      </c>
+      <c r="BA146">
+        <v>3</v>
+      </c>
+      <c r="BB146">
+        <v>9</v>
+      </c>
+      <c r="BC146">
+        <v>12</v>
+      </c>
+      <c r="BD146">
+        <v>1.98</v>
+      </c>
+      <c r="BE146">
+        <v>6.75</v>
+      </c>
+      <c r="BF146">
+        <v>1.97</v>
+      </c>
+      <c r="BG146">
+        <v>1.17</v>
+      </c>
+      <c r="BH146">
+        <v>4.3</v>
+      </c>
+      <c r="BI146">
+        <v>1.3</v>
+      </c>
+      <c r="BJ146">
+        <v>3.05</v>
+      </c>
+      <c r="BK146">
+        <v>1.52</v>
+      </c>
+      <c r="BL146">
+        <v>2.33</v>
+      </c>
+      <c r="BM146">
+        <v>1.8</v>
+      </c>
+      <c r="BN146">
+        <v>1.89</v>
+      </c>
+      <c r="BO146">
+        <v>2.23</v>
+      </c>
+      <c r="BP146">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="147" spans="1:68">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>7480283</v>
+      </c>
+      <c r="C147" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F147">
+        <v>25</v>
+      </c>
+      <c r="G147" t="s">
+        <v>79</v>
+      </c>
+      <c r="H147" t="s">
+        <v>80</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="L147">
+        <v>2</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>2</v>
+      </c>
+      <c r="O147" t="s">
+        <v>193</v>
+      </c>
+      <c r="P147" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q147">
+        <v>2.4</v>
+      </c>
+      <c r="R147">
+        <v>2.3</v>
+      </c>
+      <c r="S147">
+        <v>4.33</v>
+      </c>
+      <c r="T147">
+        <v>1.33</v>
+      </c>
+      <c r="U147">
+        <v>3.25</v>
+      </c>
+      <c r="V147">
+        <v>2.63</v>
+      </c>
+      <c r="W147">
+        <v>1.44</v>
+      </c>
+      <c r="X147">
+        <v>6.5</v>
+      </c>
+      <c r="Y147">
+        <v>1.11</v>
+      </c>
+      <c r="Z147">
+        <v>1.91</v>
+      </c>
+      <c r="AA147">
+        <v>3.53</v>
+      </c>
+      <c r="AB147">
+        <v>3.82</v>
+      </c>
+      <c r="AC147">
+        <v>1.05</v>
+      </c>
+      <c r="AD147">
+        <v>9.5</v>
+      </c>
+      <c r="AE147">
+        <v>1.25</v>
+      </c>
+      <c r="AF147">
+        <v>3.75</v>
+      </c>
+      <c r="AG147">
+        <v>1.8</v>
+      </c>
+      <c r="AH147">
+        <v>1.95</v>
+      </c>
+      <c r="AI147">
+        <v>1.67</v>
+      </c>
+      <c r="AJ147">
+        <v>2.1</v>
+      </c>
+      <c r="AK147">
+        <v>1.27</v>
+      </c>
+      <c r="AL147">
+        <v>1.26</v>
+      </c>
+      <c r="AM147">
+        <v>1.85</v>
+      </c>
+      <c r="AN147">
+        <v>1.42</v>
+      </c>
+      <c r="AO147">
+        <v>1.09</v>
+      </c>
+      <c r="AP147">
+        <v>1.54</v>
+      </c>
+      <c r="AQ147">
+        <v>1</v>
+      </c>
+      <c r="AR147">
+        <v>1.38</v>
+      </c>
+      <c r="AS147">
+        <v>1.17</v>
+      </c>
+      <c r="AT147">
+        <v>2.55</v>
+      </c>
+      <c r="AU147">
+        <v>6</v>
+      </c>
+      <c r="AV147">
+        <v>4</v>
+      </c>
+      <c r="AW147">
+        <v>4</v>
+      </c>
+      <c r="AX147">
+        <v>5</v>
+      </c>
+      <c r="AY147">
+        <v>10</v>
+      </c>
+      <c r="AZ147">
+        <v>9</v>
+      </c>
+      <c r="BA147">
+        <v>2</v>
+      </c>
+      <c r="BB147">
+        <v>8</v>
+      </c>
+      <c r="BC147">
+        <v>10</v>
+      </c>
+      <c r="BD147">
+        <v>1.57</v>
+      </c>
+      <c r="BE147">
+        <v>7</v>
+      </c>
+      <c r="BF147">
+        <v>2.6</v>
+      </c>
+      <c r="BG147">
+        <v>1.12</v>
+      </c>
+      <c r="BH147">
+        <v>5.1</v>
+      </c>
+      <c r="BI147">
+        <v>1.24</v>
+      </c>
+      <c r="BJ147">
+        <v>3.55</v>
+      </c>
+      <c r="BK147">
+        <v>1.4</v>
+      </c>
+      <c r="BL147">
+        <v>2.65</v>
+      </c>
+      <c r="BM147">
+        <v>1.64</v>
+      </c>
+      <c r="BN147">
+        <v>2.1</v>
+      </c>
+      <c r="BO147">
+        <v>1.97</v>
+      </c>
+      <c r="BP147">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7480284</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45689.61458333334</v>
+      </c>
+      <c r="F148">
+        <v>25</v>
+      </c>
+      <c r="G148" t="s">
+        <v>81</v>
+      </c>
+      <c r="H148" t="s">
+        <v>72</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>1</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>1</v>
+      </c>
+      <c r="O148" t="s">
+        <v>194</v>
+      </c>
+      <c r="P148" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q148">
+        <v>3.1</v>
+      </c>
+      <c r="R148">
+        <v>2.1</v>
+      </c>
+      <c r="S148">
+        <v>3.5</v>
+      </c>
+      <c r="T148">
+        <v>1.4</v>
+      </c>
+      <c r="U148">
+        <v>2.75</v>
+      </c>
+      <c r="V148">
+        <v>3</v>
+      </c>
+      <c r="W148">
+        <v>1.36</v>
+      </c>
+      <c r="X148">
+        <v>9</v>
+      </c>
+      <c r="Y148">
+        <v>1.07</v>
+      </c>
+      <c r="Z148">
+        <v>2.53</v>
+      </c>
+      <c r="AA148">
+        <v>3.47</v>
+      </c>
+      <c r="AB148">
+        <v>2.58</v>
+      </c>
+      <c r="AC148">
+        <v>1.05</v>
+      </c>
+      <c r="AD148">
+        <v>9</v>
+      </c>
+      <c r="AE148">
+        <v>1.3</v>
+      </c>
+      <c r="AF148">
+        <v>3.45</v>
+      </c>
+      <c r="AG148">
+        <v>1.91</v>
+      </c>
+      <c r="AH148">
+        <v>1.83</v>
+      </c>
+      <c r="AI148">
+        <v>1.8</v>
+      </c>
+      <c r="AJ148">
+        <v>1.95</v>
+      </c>
+      <c r="AK148">
+        <v>1.4</v>
+      </c>
+      <c r="AL148">
+        <v>1.3</v>
+      </c>
+      <c r="AM148">
+        <v>1.55</v>
+      </c>
+      <c r="AN148">
+        <v>1.45</v>
+      </c>
+      <c r="AO148">
+        <v>1.58</v>
+      </c>
+      <c r="AP148">
+        <v>1.58</v>
+      </c>
+      <c r="AQ148">
+        <v>1.46</v>
+      </c>
+      <c r="AR148">
+        <v>1.42</v>
+      </c>
+      <c r="AS148">
+        <v>1.24</v>
+      </c>
+      <c r="AT148">
+        <v>2.66</v>
+      </c>
+      <c r="AU148">
+        <v>5</v>
+      </c>
+      <c r="AV148">
+        <v>3</v>
+      </c>
+      <c r="AW148">
+        <v>6</v>
+      </c>
+      <c r="AX148">
+        <v>13</v>
+      </c>
+      <c r="AY148">
+        <v>11</v>
+      </c>
+      <c r="AZ148">
+        <v>16</v>
+      </c>
+      <c r="BA148">
+        <v>3</v>
+      </c>
+      <c r="BB148">
+        <v>4</v>
+      </c>
+      <c r="BC148">
+        <v>7</v>
+      </c>
+      <c r="BD148">
+        <v>1.77</v>
+      </c>
+      <c r="BE148">
+        <v>6.75</v>
+      </c>
+      <c r="BF148">
+        <v>2.23</v>
+      </c>
+      <c r="BG148">
+        <v>1.2</v>
+      </c>
+      <c r="BH148">
+        <v>3.9</v>
+      </c>
+      <c r="BI148">
+        <v>1.36</v>
+      </c>
+      <c r="BJ148">
+        <v>2.8</v>
+      </c>
+      <c r="BK148">
+        <v>1.58</v>
+      </c>
+      <c r="BL148">
+        <v>2.18</v>
+      </c>
+      <c r="BM148">
+        <v>1.94</v>
+      </c>
+      <c r="BN148">
+        <v>1.76</v>
+      </c>
+      <c r="BO148">
+        <v>2.4</v>
+      </c>
+      <c r="BP148">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7480286</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45690.5</v>
+      </c>
+      <c r="F149">
+        <v>25</v>
+      </c>
+      <c r="G149" t="s">
+        <v>76</v>
+      </c>
+      <c r="H149" t="s">
+        <v>77</v>
+      </c>
+      <c r="I149">
+        <v>3</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>3</v>
+      </c>
+      <c r="L149">
+        <v>4</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>4</v>
+      </c>
+      <c r="O149" t="s">
+        <v>195</v>
+      </c>
+      <c r="P149" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q149">
+        <v>1.5</v>
+      </c>
+      <c r="R149">
+        <v>3.1</v>
+      </c>
+      <c r="S149">
+        <v>11</v>
+      </c>
+      <c r="T149">
+        <v>1.2</v>
+      </c>
+      <c r="U149">
+        <v>4.33</v>
+      </c>
+      <c r="V149">
+        <v>2</v>
+      </c>
+      <c r="W149">
+        <v>1.73</v>
+      </c>
+      <c r="X149">
+        <v>4.33</v>
+      </c>
+      <c r="Y149">
+        <v>1.2</v>
+      </c>
+      <c r="Z149">
+        <v>1.16</v>
+      </c>
+      <c r="AA149">
+        <v>7.3</v>
+      </c>
+      <c r="AB149">
+        <v>14</v>
+      </c>
+      <c r="AC149">
+        <v>1.03</v>
+      </c>
+      <c r="AD149">
+        <v>11</v>
+      </c>
+      <c r="AE149">
+        <v>1.11</v>
+      </c>
+      <c r="AF149">
+        <v>6.25</v>
+      </c>
+      <c r="AG149">
+        <v>1.6</v>
+      </c>
+      <c r="AH149">
+        <v>2.25</v>
+      </c>
+      <c r="AI149">
+        <v>2.05</v>
+      </c>
+      <c r="AJ149">
+        <v>1.7</v>
+      </c>
+      <c r="AK149">
+        <v>1.02</v>
+      </c>
+      <c r="AL149">
+        <v>1.08</v>
+      </c>
+      <c r="AM149">
+        <v>5.25</v>
+      </c>
+      <c r="AN149">
+        <v>2.83</v>
+      </c>
+      <c r="AO149">
+        <v>1.09</v>
+      </c>
+      <c r="AP149">
+        <v>2.85</v>
+      </c>
+      <c r="AQ149">
+        <v>1</v>
+      </c>
+      <c r="AR149">
+        <v>2.11</v>
+      </c>
+      <c r="AS149">
+        <v>0.98</v>
+      </c>
+      <c r="AT149">
+        <v>3.09</v>
+      </c>
+      <c r="AU149">
+        <v>10</v>
+      </c>
+      <c r="AV149">
+        <v>2</v>
+      </c>
+      <c r="AW149">
+        <v>16</v>
+      </c>
+      <c r="AX149">
+        <v>1</v>
+      </c>
+      <c r="AY149">
+        <v>26</v>
+      </c>
+      <c r="AZ149">
+        <v>3</v>
+      </c>
+      <c r="BA149">
+        <v>8</v>
+      </c>
+      <c r="BB149">
+        <v>3</v>
+      </c>
+      <c r="BC149">
+        <v>11</v>
+      </c>
+      <c r="BD149">
+        <v>1.07</v>
+      </c>
+      <c r="BE149">
+        <v>13</v>
+      </c>
+      <c r="BF149">
+        <v>8</v>
+      </c>
+      <c r="BG149">
+        <v>1.12</v>
+      </c>
+      <c r="BH149">
+        <v>5.1</v>
+      </c>
+      <c r="BI149">
+        <v>1.21</v>
+      </c>
+      <c r="BJ149">
+        <v>3.7</v>
+      </c>
+      <c r="BK149">
+        <v>1.37</v>
+      </c>
+      <c r="BL149">
+        <v>2.8</v>
+      </c>
+      <c r="BM149">
+        <v>1.58</v>
+      </c>
+      <c r="BN149">
+        <v>2.18</v>
+      </c>
+      <c r="BO149">
+        <v>1.9</v>
+      </c>
+      <c r="BP149">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7480285</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45690.5</v>
+      </c>
+      <c r="F150">
+        <v>25</v>
+      </c>
+      <c r="G150" t="s">
+        <v>71</v>
+      </c>
+      <c r="H150" t="s">
+        <v>74</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="J150">
+        <v>2</v>
+      </c>
+      <c r="K150">
+        <v>3</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="M150">
+        <v>3</v>
+      </c>
+      <c r="N150">
+        <v>4</v>
+      </c>
+      <c r="O150" t="s">
+        <v>196</v>
+      </c>
+      <c r="P150" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q150">
+        <v>10</v>
+      </c>
+      <c r="R150">
+        <v>2.88</v>
+      </c>
+      <c r="S150">
+        <v>1.57</v>
+      </c>
+      <c r="T150">
+        <v>1.22</v>
+      </c>
+      <c r="U150">
+        <v>4</v>
+      </c>
+      <c r="V150">
+        <v>2.1</v>
+      </c>
+      <c r="W150">
+        <v>1.67</v>
+      </c>
+      <c r="X150">
+        <v>4.5</v>
+      </c>
+      <c r="Y150">
+        <v>1.18</v>
+      </c>
+      <c r="Z150">
+        <v>12</v>
+      </c>
+      <c r="AA150">
+        <v>6.7</v>
+      </c>
+      <c r="AB150">
+        <v>1.19</v>
+      </c>
+      <c r="AC150">
+        <v>1.01</v>
+      </c>
+      <c r="AD150">
+        <v>17</v>
+      </c>
+      <c r="AE150">
+        <v>1.12</v>
+      </c>
+      <c r="AF150">
+        <v>5.75</v>
+      </c>
+      <c r="AG150">
+        <v>1.41</v>
+      </c>
+      <c r="AH150">
+        <v>2.78</v>
+      </c>
+      <c r="AI150">
+        <v>2</v>
+      </c>
+      <c r="AJ150">
+        <v>1.75</v>
+      </c>
+      <c r="AK150">
+        <v>4.5</v>
+      </c>
+      <c r="AL150">
+        <v>1.1</v>
+      </c>
+      <c r="AM150">
+        <v>1.03</v>
+      </c>
+      <c r="AN150">
+        <v>1.64</v>
+      </c>
+      <c r="AO150">
+        <v>2.42</v>
+      </c>
+      <c r="AP150">
+        <v>1.5</v>
+      </c>
+      <c r="AQ150">
+        <v>2.46</v>
+      </c>
+      <c r="AR150">
+        <v>1.15</v>
+      </c>
+      <c r="AS150">
+        <v>1.83</v>
+      </c>
+      <c r="AT150">
+        <v>2.98</v>
+      </c>
+      <c r="AU150">
+        <v>2</v>
+      </c>
+      <c r="AV150">
+        <v>10</v>
+      </c>
+      <c r="AW150">
+        <v>1</v>
+      </c>
+      <c r="AX150">
+        <v>11</v>
+      </c>
+      <c r="AY150">
+        <v>3</v>
+      </c>
+      <c r="AZ150">
+        <v>21</v>
+      </c>
+      <c r="BA150">
+        <v>3</v>
+      </c>
+      <c r="BB150">
+        <v>10</v>
+      </c>
+      <c r="BC150">
+        <v>13</v>
+      </c>
+      <c r="BD150">
+        <v>5.8</v>
+      </c>
+      <c r="BE150">
+        <v>11</v>
+      </c>
+      <c r="BF150">
+        <v>1.13</v>
+      </c>
+      <c r="BG150">
+        <v>1.14</v>
+      </c>
+      <c r="BH150">
+        <v>4.8</v>
+      </c>
+      <c r="BI150">
+        <v>1.25</v>
+      </c>
+      <c r="BJ150">
+        <v>3.45</v>
+      </c>
+      <c r="BK150">
+        <v>1.41</v>
+      </c>
+      <c r="BL150">
+        <v>2.63</v>
+      </c>
+      <c r="BM150">
+        <v>1.65</v>
+      </c>
+      <c r="BN150">
+        <v>2.08</v>
+      </c>
+      <c r="BO150">
+        <v>1.98</v>
+      </c>
+      <c r="BP150">
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="278">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t>['23']</t>
+  </si>
+  <si>
+    <t>['18', '45+1', '55', '59', '71', '81']</t>
   </si>
   <si>
     <t>['18', '79']</t>
@@ -1206,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP150"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1874,7 +1877,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1955,7 +1958,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2364,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ6">
         <v>0.6899999999999999</v>
@@ -2492,7 +2495,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2904,7 +2907,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3316,7 +3319,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3522,7 +3525,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3728,7 +3731,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -4140,7 +4143,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4221,7 +4224,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ15">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0.53</v>
@@ -4552,7 +4555,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -5170,7 +5173,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5376,7 +5379,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5582,7 +5585,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5866,7 +5869,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ23">
         <v>1.33</v>
@@ -5994,7 +5997,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6200,7 +6203,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6690,7 +6693,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ27">
         <v>0.92</v>
@@ -7105,7 +7108,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ29">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>1.33</v>
@@ -7230,7 +7233,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7642,7 +7645,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8054,7 +8057,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8260,7 +8263,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8466,7 +8469,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8672,7 +8675,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8878,7 +8881,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9290,7 +9293,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9496,7 +9499,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9702,7 +9705,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9908,7 +9911,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10114,7 +10117,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10526,7 +10529,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10604,7 +10607,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -10732,7 +10735,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11144,7 +11147,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11225,7 +11228,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>1.3</v>
@@ -11762,7 +11765,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11968,7 +11971,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12586,7 +12589,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12792,7 +12795,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -12998,7 +13001,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13410,7 +13413,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13616,7 +13619,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13900,10 +13903,10 @@
         <v>1.25</v>
       </c>
       <c r="AP62">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ62">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>2.17</v>
@@ -14028,7 +14031,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14234,7 +14237,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14646,7 +14649,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14852,7 +14855,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15264,7 +15267,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15470,7 +15473,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15676,7 +15679,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15757,7 +15760,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ71">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>1.32</v>
@@ -15882,7 +15885,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16500,7 +16503,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16912,7 +16915,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17118,7 +17121,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17324,7 +17327,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17530,7 +17533,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17814,7 +17817,7 @@
         <v>0.5</v>
       </c>
       <c r="AP81">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -18148,7 +18151,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18229,7 +18232,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ83">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR83">
         <v>1.34</v>
@@ -18354,7 +18357,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18560,7 +18563,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18766,7 +18769,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19384,7 +19387,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -20080,7 +20083,7 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ92">
         <v>1.08</v>
@@ -20495,7 +20498,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ94">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.63</v>
@@ -20620,7 +20623,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20826,7 +20829,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21032,7 +21035,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21238,7 +21241,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21650,7 +21653,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21856,7 +21859,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22143,7 +22146,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ102">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR102">
         <v>2.07</v>
@@ -22268,7 +22271,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22886,7 +22889,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23170,7 +23173,7 @@
         <v>1.5</v>
       </c>
       <c r="AP107">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23298,7 +23301,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23710,7 +23713,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24122,7 +24125,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24406,7 +24409,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ113">
         <v>0.85</v>
@@ -24740,7 +24743,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24946,7 +24949,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25027,7 +25030,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ116">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR116">
         <v>1.2</v>
@@ -26182,7 +26185,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26388,7 +26391,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26594,7 +26597,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -27084,7 +27087,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ126">
         <v>1.08</v>
@@ -27212,7 +27215,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27418,7 +27421,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27624,7 +27627,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -27705,7 +27708,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ129">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR129">
         <v>1.19</v>
@@ -28114,7 +28117,7 @@
         <v>1.6</v>
       </c>
       <c r="AP131">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ131">
         <v>1.46</v>
@@ -28448,7 +28451,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28860,7 +28863,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29066,7 +29069,7 @@
         <v>187</v>
       </c>
       <c r="P136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q136">
         <v>1.37</v>
@@ -29478,7 +29481,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29890,7 +29893,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30096,7 +30099,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30302,7 +30305,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30508,7 +30511,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30714,7 +30717,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30920,7 +30923,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31126,7 +31129,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31950,7 +31953,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32107,6 +32110,212 @@
       </c>
       <c r="BP150">
         <v>1.72</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7480277</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45693.69791666666</v>
+      </c>
+      <c r="F151">
+        <v>24</v>
+      </c>
+      <c r="G151" t="s">
+        <v>74</v>
+      </c>
+      <c r="H151" t="s">
+        <v>78</v>
+      </c>
+      <c r="I151">
+        <v>2</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>2</v>
+      </c>
+      <c r="L151">
+        <v>6</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+      <c r="N151">
+        <v>6</v>
+      </c>
+      <c r="O151" t="s">
+        <v>197</v>
+      </c>
+      <c r="P151" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q151">
+        <v>1.38</v>
+      </c>
+      <c r="R151">
+        <v>3.4</v>
+      </c>
+      <c r="S151">
+        <v>11</v>
+      </c>
+      <c r="T151">
+        <v>1.15</v>
+      </c>
+      <c r="U151">
+        <v>4.8</v>
+      </c>
+      <c r="V151">
+        <v>1.72</v>
+      </c>
+      <c r="W151">
+        <v>1.98</v>
+      </c>
+      <c r="X151">
+        <v>3.25</v>
+      </c>
+      <c r="Y151">
+        <v>1.3</v>
+      </c>
+      <c r="Z151">
+        <v>1.13</v>
+      </c>
+      <c r="AA151">
+        <v>7.6</v>
+      </c>
+      <c r="AB151">
+        <v>17</v>
+      </c>
+      <c r="AC151">
+        <v>0</v>
+      </c>
+      <c r="AD151">
+        <v>0</v>
+      </c>
+      <c r="AE151">
+        <v>1.05</v>
+      </c>
+      <c r="AF151">
+        <v>9.5</v>
+      </c>
+      <c r="AG151">
+        <v>1.22</v>
+      </c>
+      <c r="AH151">
+        <v>4</v>
+      </c>
+      <c r="AI151">
+        <v>1.98</v>
+      </c>
+      <c r="AJ151">
+        <v>1.72</v>
+      </c>
+      <c r="AK151">
+        <v>1.01</v>
+      </c>
+      <c r="AL151">
+        <v>1.05</v>
+      </c>
+      <c r="AM151">
+        <v>7</v>
+      </c>
+      <c r="AN151">
+        <v>2.82</v>
+      </c>
+      <c r="AO151">
+        <v>1.09</v>
+      </c>
+      <c r="AP151">
+        <v>2.83</v>
+      </c>
+      <c r="AQ151">
+        <v>1</v>
+      </c>
+      <c r="AR151">
+        <v>2.26</v>
+      </c>
+      <c r="AS151">
+        <v>1.11</v>
+      </c>
+      <c r="AT151">
+        <v>3.37</v>
+      </c>
+      <c r="AU151">
+        <v>9</v>
+      </c>
+      <c r="AV151">
+        <v>0</v>
+      </c>
+      <c r="AW151">
+        <v>9</v>
+      </c>
+      <c r="AX151">
+        <v>6</v>
+      </c>
+      <c r="AY151">
+        <v>18</v>
+      </c>
+      <c r="AZ151">
+        <v>6</v>
+      </c>
+      <c r="BA151">
+        <v>6</v>
+      </c>
+      <c r="BB151">
+        <v>3</v>
+      </c>
+      <c r="BC151">
+        <v>9</v>
+      </c>
+      <c r="BD151">
+        <v>1.06</v>
+      </c>
+      <c r="BE151">
+        <v>14</v>
+      </c>
+      <c r="BF151">
+        <v>9.5</v>
+      </c>
+      <c r="BG151">
+        <v>1.09</v>
+      </c>
+      <c r="BH151">
+        <v>5.8</v>
+      </c>
+      <c r="BI151">
+        <v>1.17</v>
+      </c>
+      <c r="BJ151">
+        <v>4.3</v>
+      </c>
+      <c r="BK151">
+        <v>1.29</v>
+      </c>
+      <c r="BL151">
+        <v>3.15</v>
+      </c>
+      <c r="BM151">
+        <v>1.48</v>
+      </c>
+      <c r="BN151">
+        <v>2.43</v>
+      </c>
+      <c r="BO151">
+        <v>1.72</v>
+      </c>
+      <c r="BP151">
+        <v>1.98</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1749,10 +1749,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1955,10 +1955,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2367,10 +2367,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ6">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2573,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2773,25 +2773,25 @@
         <v>4.33</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP8">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU8">
         <v>10</v>
@@ -2979,25 +2979,25 @@
         <v>1.5</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ9">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU9">
         <v>6</v>
@@ -3185,25 +3185,25 @@
         <v>1.36</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AU10">
         <v>8</v>
@@ -3394,22 +3394,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ11">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AU11">
         <v>0</v>
@@ -3597,25 +3597,25 @@
         <v>1.95</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP12">
+        <v>1.4</v>
+      </c>
+      <c r="AQ12">
+        <v>1.2</v>
+      </c>
+      <c r="AR12">
         <v>1.77</v>
       </c>
-      <c r="AQ12">
-        <v>1.08</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AU12">
         <v>4</v>
@@ -3809,19 +3809,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ13">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU13">
         <v>3</v>
@@ -4012,22 +4012,22 @@
         <v>1</v>
       </c>
       <c r="AO14">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP14">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ14">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR14">
-        <v>2.04</v>
+        <v>1.54</v>
       </c>
       <c r="AS14">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AT14">
-        <v>3.54</v>
+        <v>2.98</v>
       </c>
       <c r="AU14">
         <v>3</v>
@@ -4218,22 +4218,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP15">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR15">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="AS15">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AT15">
-        <v>2.13</v>
+        <v>2.58</v>
       </c>
       <c r="AU15">
         <v>3</v>
@@ -4421,25 +4421,25 @@
         <v>4.5</v>
       </c>
       <c r="AN16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO16">
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR16">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AS16">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="AT16">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="AU16">
         <v>10</v>
@@ -4627,25 +4627,25 @@
         <v>1.02</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO17">
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ17">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR17">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AS17">
-        <v>1.65</v>
+        <v>2.38</v>
       </c>
       <c r="AT17">
-        <v>2.72</v>
+        <v>3.53</v>
       </c>
       <c r="AU17">
         <v>2</v>
@@ -4833,25 +4833,25 @@
         <v>1.4</v>
       </c>
       <c r="AN18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ18">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR18">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AS18">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AT18">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="AU18">
         <v>7</v>
@@ -5045,19 +5045,19 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ19">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AR19">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="AS19">
-        <v>0.6899999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AT19">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
       <c r="AU19">
         <v>4</v>
@@ -5245,25 +5245,25 @@
         <v>1.73</v>
       </c>
       <c r="AN20">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ20">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AR20">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AS20">
-        <v>1.22</v>
+        <v>0.91</v>
       </c>
       <c r="AT20">
-        <v>2.78</v>
+        <v>2.36</v>
       </c>
       <c r="AU20">
         <v>6</v>
@@ -5451,25 +5451,25 @@
         <v>1.42</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP21">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR21">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AS21">
-        <v>0.88</v>
+        <v>1.26</v>
       </c>
       <c r="AT21">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="AU21">
         <v>6</v>
@@ -5657,25 +5657,25 @@
         <v>1.3</v>
       </c>
       <c r="AN22">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO22">
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR22">
-        <v>1.66</v>
+        <v>1.12</v>
       </c>
       <c r="AS22">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AT22">
-        <v>3.43</v>
+        <v>2.46</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5866,22 +5866,22 @@
         <v>3</v>
       </c>
       <c r="AO23">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR23">
-        <v>3.1</v>
+        <v>2.22</v>
       </c>
       <c r="AS23">
-        <v>1.18</v>
+        <v>1.74</v>
       </c>
       <c r="AT23">
-        <v>4.28</v>
+        <v>3.96</v>
       </c>
       <c r="AU23">
         <v>5</v>
@@ -6069,25 +6069,25 @@
         <v>2</v>
       </c>
       <c r="AN24">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ24">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR24">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AS24">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AT24">
-        <v>2.19</v>
+        <v>2.47</v>
       </c>
       <c r="AU24">
         <v>3</v>
@@ -6278,22 +6278,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP25">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ25">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AR25">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="AS25">
-        <v>1.47</v>
+        <v>1.06</v>
       </c>
       <c r="AT25">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6484,22 +6484,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP26">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR26">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AS26">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AT26">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6690,22 +6690,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP27">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ27">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR27">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AS27">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AT27">
-        <v>3.36</v>
+        <v>3.19</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6896,22 +6896,22 @@
         <v>0.5</v>
       </c>
       <c r="AO28">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP28">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ28">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR28">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="AS28">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AT28">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -7102,22 +7102,22 @@
         <v>0.5</v>
       </c>
       <c r="AO29">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP29">
+        <v>1.04</v>
+      </c>
+      <c r="AQ29">
         <v>1.08</v>
       </c>
-      <c r="AQ29">
-        <v>1</v>
-      </c>
       <c r="AR29">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AS29">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AT29">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7305,25 +7305,25 @@
         <v>1.66</v>
       </c>
       <c r="AN30">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP30">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ30">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AR30">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
       <c r="AS30">
-        <v>0.85</v>
+        <v>1.09</v>
       </c>
       <c r="AT30">
-        <v>1.61</v>
+        <v>2.14</v>
       </c>
       <c r="AU30">
         <v>4</v>
@@ -7514,22 +7514,22 @@
         <v>2</v>
       </c>
       <c r="AO31">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP31">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ31">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR31">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AS31">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AT31">
-        <v>2.72</v>
+        <v>2.91</v>
       </c>
       <c r="AU31">
         <v>0</v>
@@ -7717,25 +7717,25 @@
         <v>1.75</v>
       </c>
       <c r="AN32">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AP32">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ32">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR32">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AS32">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AT32">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AU32">
         <v>7</v>
@@ -7923,25 +7923,25 @@
         <v>1.41</v>
       </c>
       <c r="AN33">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO33">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AP33">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ33">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR33">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="AS33">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AT33">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AU33">
         <v>3</v>
@@ -8129,25 +8129,25 @@
         <v>2.25</v>
       </c>
       <c r="AN34">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="AO34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR34">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AS34">
-        <v>0.84</v>
+        <v>1.21</v>
       </c>
       <c r="AT34">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AU34">
         <v>9</v>
@@ -8335,25 +8335,25 @@
         <v>1.66</v>
       </c>
       <c r="AN35">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AO35">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP35">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ35">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR35">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AS35">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AT35">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="AU35">
         <v>4</v>
@@ -8541,25 +8541,25 @@
         <v>1.58</v>
       </c>
       <c r="AN36">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO36">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ36">
+        <v>1.2</v>
+      </c>
+      <c r="AR36">
+        <v>1.34</v>
+      </c>
+      <c r="AS36">
         <v>1.08</v>
       </c>
-      <c r="AR36">
-        <v>1.45</v>
-      </c>
-      <c r="AS36">
-        <v>1.35</v>
-      </c>
       <c r="AT36">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="AU36">
         <v>5</v>
@@ -8747,25 +8747,25 @@
         <v>1.45</v>
       </c>
       <c r="AN37">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AO37">
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ37">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR37">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS37">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AT37">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -8953,25 +8953,25 @@
         <v>1.04</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO38">
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ38">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR38">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="AS38">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AT38">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="AU38">
         <v>2</v>
@@ -9159,25 +9159,25 @@
         <v>2.9</v>
       </c>
       <c r="AN39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP39">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ39">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AR39">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="AS39">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AT39">
-        <v>3.33</v>
+        <v>2.79</v>
       </c>
       <c r="AU39">
         <v>5</v>
@@ -9365,25 +9365,25 @@
         <v>1.63</v>
       </c>
       <c r="AN40">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="AO40">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ40">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR40">
-        <v>0.9399999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="AS40">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AT40">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AU40">
         <v>4</v>
@@ -9571,25 +9571,25 @@
         <v>1.77</v>
       </c>
       <c r="AN41">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AO41">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP41">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR41">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AS41">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AT41">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -9777,25 +9777,25 @@
         <v>1.62</v>
       </c>
       <c r="AN42">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO42">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP42">
+        <v>1.08</v>
+      </c>
+      <c r="AQ42">
+        <v>1.12</v>
+      </c>
+      <c r="AR42">
+        <v>1.46</v>
+      </c>
+      <c r="AS42">
         <v>1.15</v>
       </c>
-      <c r="AQ42">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AR42">
-        <v>1.64</v>
-      </c>
-      <c r="AS42">
-        <v>0.99</v>
-      </c>
       <c r="AT42">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="AU42">
         <v>4</v>
@@ -9983,25 +9983,25 @@
         <v>1.02</v>
       </c>
       <c r="AN43">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO43">
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ43">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR43">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AS43">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AT43">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="AU43">
         <v>6</v>
@@ -10192,22 +10192,22 @@
         <v>3</v>
       </c>
       <c r="AO44">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="AP44">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ44">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR44">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AS44">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="AT44">
-        <v>2.27</v>
+        <v>2.52</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10395,25 +10395,25 @@
         <v>5.7</v>
       </c>
       <c r="AN45">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AO45">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AP45">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ45">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR45">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AS45">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AT45">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="AU45">
         <v>7</v>
@@ -10607,19 +10607,19 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR46">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AS46">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AT46">
-        <v>3.39</v>
+        <v>3.33</v>
       </c>
       <c r="AU46">
         <v>8</v>
@@ -10807,25 +10807,25 @@
         <v>1.57</v>
       </c>
       <c r="AN47">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AO47">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ47">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AR47">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AS47">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AT47">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -11013,25 +11013,25 @@
         <v>2</v>
       </c>
       <c r="AN48">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="AO48">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP48">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ48">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AR48">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AS48">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AT48">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="AU48">
         <v>5</v>
@@ -11219,25 +11219,25 @@
         <v>1.83</v>
       </c>
       <c r="AN49">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AO49">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR49">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AS49">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AT49">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="AU49">
         <v>4</v>
@@ -11425,25 +11425,25 @@
         <v>1.5</v>
       </c>
       <c r="AN50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO50">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="AP50">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR50">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AS50">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
       <c r="AT50">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AU50">
         <v>8</v>
@@ -11631,25 +11631,25 @@
         <v>1.12</v>
       </c>
       <c r="AN51">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AO51">
-        <v>1.33</v>
+        <v>2.29</v>
       </c>
       <c r="AP51">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ51">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR51">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AS51">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AT51">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AU51">
         <v>4</v>
@@ -11837,25 +11837,25 @@
         <v>2.15</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AO52">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AP52">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ52">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR52">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AS52">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AT52">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12043,25 +12043,25 @@
         <v>1.36</v>
       </c>
       <c r="AN53">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AO53">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP53">
+        <v>1.04</v>
+      </c>
+      <c r="AQ53">
+        <v>1.12</v>
+      </c>
+      <c r="AR53">
         <v>1.08</v>
       </c>
-      <c r="AQ53">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AR53">
-        <v>1.34</v>
-      </c>
       <c r="AS53">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT53">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12249,25 +12249,25 @@
         <v>2.2</v>
       </c>
       <c r="AN54">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AO54">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AP54">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ54">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR54">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AS54">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AT54">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AU54">
         <v>6</v>
@@ -12455,25 +12455,25 @@
         <v>1.6</v>
       </c>
       <c r="AN55">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="AO55">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP55">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ55">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR55">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AS55">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AT55">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="AU55">
         <v>8</v>
@@ -12661,25 +12661,25 @@
         <v>1.02</v>
       </c>
       <c r="AN56">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO56">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ56">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
       </c>
       <c r="AS56">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AT56">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="AU56">
         <v>3</v>
@@ -12867,25 +12867,25 @@
         <v>4</v>
       </c>
       <c r="AN57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO57">
-        <v>0.25</v>
+        <v>0.89</v>
       </c>
       <c r="AP57">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ57">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AR57">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AS57">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT57">
-        <v>3.15</v>
+        <v>2.73</v>
       </c>
       <c r="AU57">
         <v>8</v>
@@ -13073,25 +13073,25 @@
         <v>1.93</v>
       </c>
       <c r="AN58">
-        <v>1.25</v>
+        <v>0.6</v>
       </c>
       <c r="AO58">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP58">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ58">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AR58">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AS58">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AT58">
-        <v>2.71</v>
+        <v>2.48</v>
       </c>
       <c r="AU58">
         <v>6</v>
@@ -13279,25 +13279,25 @@
         <v>1.33</v>
       </c>
       <c r="AN59">
+        <v>1</v>
+      </c>
+      <c r="AO59">
+        <v>0.67</v>
+      </c>
+      <c r="AP59">
+        <v>1.04</v>
+      </c>
+      <c r="AQ59">
+        <v>1.32</v>
+      </c>
+      <c r="AR59">
+        <v>1.09</v>
+      </c>
+      <c r="AS59">
         <v>1.33</v>
       </c>
-      <c r="AO59">
-        <v>0.25</v>
-      </c>
-      <c r="AP59">
-        <v>1.08</v>
-      </c>
-      <c r="AQ59">
-        <v>1.08</v>
-      </c>
-      <c r="AR59">
-        <v>1.31</v>
-      </c>
-      <c r="AS59">
-        <v>1.36</v>
-      </c>
       <c r="AT59">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="AU59">
         <v>3</v>
@@ -13485,25 +13485,25 @@
         <v>2.05</v>
       </c>
       <c r="AN60">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AO60">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ60">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR60">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AS60">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AT60">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AU60">
         <v>6</v>
@@ -13691,25 +13691,25 @@
         <v>1.67</v>
       </c>
       <c r="AN61">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AO61">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP61">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR61">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AS61">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AT61">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AU61">
         <v>6</v>
@@ -13897,25 +13897,25 @@
         <v>6.25</v>
       </c>
       <c r="AN62">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AO62">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AP62">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR62">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AS62">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AT62">
-        <v>3.48</v>
+        <v>3.53</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14103,25 +14103,25 @@
         <v>1.25</v>
       </c>
       <c r="AN63">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AO63">
-        <v>1</v>
+        <v>2.11</v>
       </c>
       <c r="AP63">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ63">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR63">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AS63">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AT63">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14309,25 +14309,25 @@
         <v>1.22</v>
       </c>
       <c r="AN64">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="AO64">
-        <v>0.17</v>
+        <v>0.55</v>
       </c>
       <c r="AP64">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ64">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR64">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AS64">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AT64">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14515,25 +14515,25 @@
         <v>2.05</v>
       </c>
       <c r="AN65">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AO65">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR65">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AS65">
-        <v>0.77</v>
+        <v>1.1</v>
       </c>
       <c r="AT65">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="AU65">
         <v>4</v>
@@ -14721,25 +14721,25 @@
         <v>1.53</v>
       </c>
       <c r="AN66">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AO66">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AP66">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ66">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AR66">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS66">
         <v>1.21</v>
       </c>
       <c r="AT66">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -14927,25 +14927,25 @@
         <v>2</v>
       </c>
       <c r="AN67">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AO67">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ67">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR67">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AS67">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AT67">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AU67">
         <v>4</v>
@@ -15133,25 +15133,25 @@
         <v>2.05</v>
       </c>
       <c r="AN68">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AO68">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR68">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AS68">
-        <v>0.82</v>
+        <v>1.1</v>
       </c>
       <c r="AT68">
-        <v>2.04</v>
+        <v>2.29</v>
       </c>
       <c r="AU68">
         <v>5</v>
@@ -15339,25 +15339,25 @@
         <v>1.93</v>
       </c>
       <c r="AN69">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AO69">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ69">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AR69">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS69">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AT69">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15545,25 +15545,25 @@
         <v>1.95</v>
       </c>
       <c r="AN70">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AO70">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP70">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ70">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR70">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AS70">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AT70">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15751,25 +15751,25 @@
         <v>2.15</v>
       </c>
       <c r="AN71">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO71">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AP71">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR71">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AS71">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AT71">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15957,25 +15957,25 @@
         <v>1.07</v>
       </c>
       <c r="AN72">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AO72">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AP72">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ72">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR72">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AS72">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AT72">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -16163,25 +16163,25 @@
         <v>2.88</v>
       </c>
       <c r="AN73">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="AO73">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ73">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR73">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AS73">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AT73">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16369,25 +16369,25 @@
         <v>1.36</v>
       </c>
       <c r="AN74">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="AO74">
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ74">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AR74">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AS74">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AT74">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="AU74">
         <v>5</v>
@@ -16575,25 +16575,25 @@
         <v>1.45</v>
       </c>
       <c r="AN75">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AO75">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AP75">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR75">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AS75">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AT75">
-        <v>2.52</v>
+        <v>2.31</v>
       </c>
       <c r="AU75">
         <v>-1</v>
@@ -16781,25 +16781,25 @@
         <v>3.75</v>
       </c>
       <c r="AN76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO76">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AP76">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ76">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR76">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AS76">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AT76">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="AU76">
         <v>12</v>
@@ -16987,25 +16987,25 @@
         <v>1.38</v>
       </c>
       <c r="AN77">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AO77">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="AP77">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR77">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AS77">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AT77">
-        <v>2.28</v>
+        <v>2.51</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17193,25 +17193,25 @@
         <v>1.47</v>
       </c>
       <c r="AN78">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AO78">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="AP78">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ78">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AR78">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AS78">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AT78">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="AU78">
         <v>-1</v>
@@ -17399,25 +17399,25 @@
         <v>1.09</v>
       </c>
       <c r="AN79">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO79">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="AP79">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ79">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR79">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AS79">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AT79">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AU79">
         <v>-1</v>
@@ -17605,25 +17605,25 @@
         <v>1.55</v>
       </c>
       <c r="AN80">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="AO80">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="AP80">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ80">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR80">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AS80">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AT80">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17811,25 +17811,25 @@
         <v>7.5</v>
       </c>
       <c r="AN81">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AO81">
-        <v>0.5</v>
+        <v>1.07</v>
       </c>
       <c r="AP81">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR81">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AS81">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AT81">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="AU81">
         <v>10</v>
@@ -18017,25 +18017,25 @@
         <v>1.68</v>
       </c>
       <c r="AN82">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AO82">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="AP82">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ82">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AR82">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AS82">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AT82">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -18223,25 +18223,25 @@
         <v>1.8</v>
       </c>
       <c r="AN83">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AO83">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AP83">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR83">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AS83">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AT83">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="AU83">
         <v>6</v>
@@ -18429,25 +18429,25 @@
         <v>1.53</v>
       </c>
       <c r="AN84">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AO84">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ84">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AR84">
         <v>1.24</v>
       </c>
       <c r="AS84">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AT84">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AU84">
         <v>4</v>
@@ -18635,25 +18635,25 @@
         <v>1.03</v>
       </c>
       <c r="AN85">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AO85">
-        <v>0.8</v>
+        <v>1.92</v>
       </c>
       <c r="AP85">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ85">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR85">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AS85">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AT85">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="AU85">
         <v>2</v>
@@ -18841,25 +18841,25 @@
         <v>1.6</v>
       </c>
       <c r="AN86">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="AO86">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="AP86">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR86">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AS86">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AT86">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AU86">
         <v>4</v>
@@ -19047,25 +19047,25 @@
         <v>3.75</v>
       </c>
       <c r="AN87">
-        <v>2.71</v>
+        <v>2</v>
       </c>
       <c r="AO87">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="AP87">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ87">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AR87">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="AS87">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AT87">
-        <v>3.22</v>
+        <v>3.07</v>
       </c>
       <c r="AU87">
         <v>12</v>
@@ -19253,25 +19253,25 @@
         <v>1.75</v>
       </c>
       <c r="AN88">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AO88">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AP88">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR88">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AS88">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AT88">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19459,25 +19459,25 @@
         <v>1.11</v>
       </c>
       <c r="AN89">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="AO89">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AP89">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ89">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR89">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AS89">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AT89">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="AU89">
         <v>5</v>
@@ -19665,25 +19665,25 @@
         <v>1.68</v>
       </c>
       <c r="AN90">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AO90">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AP90">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR90">
         <v>1.21</v>
       </c>
       <c r="AS90">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AT90">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AU90">
         <v>7</v>
@@ -19871,25 +19871,25 @@
         <v>2.4</v>
       </c>
       <c r="AN91">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AO91">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AP91">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ91">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR91">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AS91">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AT91">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AU91">
         <v>3</v>
@@ -20077,25 +20077,25 @@
         <v>5.75</v>
       </c>
       <c r="AN92">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="AO92">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="AP92">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ92">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AR92">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AS92">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AT92">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="AU92">
         <v>12</v>
@@ -20283,25 +20283,25 @@
         <v>1.66</v>
       </c>
       <c r="AN93">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AO93">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="AP93">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ93">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AR93">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS93">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AT93">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AU93">
         <v>8</v>
@@ -20489,25 +20489,25 @@
         <v>1.87</v>
       </c>
       <c r="AN94">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="AO94">
-        <v>0.86</v>
+        <v>1.27</v>
       </c>
       <c r="AP94">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR94">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AS94">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AT94">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU94">
         <v>9</v>
@@ -20695,25 +20695,25 @@
         <v>1.03</v>
       </c>
       <c r="AN95">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO95">
-        <v>1.17</v>
+        <v>2.07</v>
       </c>
       <c r="AP95">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ95">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR95">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="AS95">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AT95">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AU95">
         <v>3</v>
@@ -20901,25 +20901,25 @@
         <v>1.45</v>
       </c>
       <c r="AN96">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AO96">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="AP96">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ96">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AR96">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AS96">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT96">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -21107,25 +21107,25 @@
         <v>2.45</v>
       </c>
       <c r="AN97">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AO97">
-        <v>0.43</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP97">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR97">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AS97">
-        <v>0.76</v>
+        <v>1.02</v>
       </c>
       <c r="AT97">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="AU97">
         <v>8</v>
@@ -21313,25 +21313,25 @@
         <v>1.52</v>
       </c>
       <c r="AN98">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AO98">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AP98">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ98">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR98">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AS98">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AT98">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21519,25 +21519,25 @@
         <v>1.35</v>
       </c>
       <c r="AN99">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO99">
-        <v>0.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP99">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ99">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR99">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS99">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AT99">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="AU99">
         <v>6</v>
@@ -21725,25 +21725,25 @@
         <v>1.57</v>
       </c>
       <c r="AN100">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AO100">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP100">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ100">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AR100">
+        <v>1.29</v>
+      </c>
+      <c r="AS100">
         <v>1.24</v>
       </c>
-      <c r="AS100">
-        <v>1.17</v>
-      </c>
       <c r="AT100">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21931,25 +21931,25 @@
         <v>1.36</v>
       </c>
       <c r="AN101">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AO101">
-        <v>0.88</v>
+        <v>1.24</v>
       </c>
       <c r="AP101">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ101">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AR101">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AS101">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT101">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AU101">
         <v>2</v>
@@ -22137,25 +22137,25 @@
         <v>4.5</v>
       </c>
       <c r="AN102">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO102">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AP102">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR102">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AS102">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AT102">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="AU102">
         <v>5</v>
@@ -22343,25 +22343,25 @@
         <v>1.65</v>
       </c>
       <c r="AN103">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="AO103">
-        <v>0.63</v>
+        <v>0.88</v>
       </c>
       <c r="AP103">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ103">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AR103">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AS103">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AT103">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="AU103">
         <v>3</v>
@@ -22549,25 +22549,25 @@
         <v>1.01</v>
       </c>
       <c r="AN104">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO104">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AP104">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ104">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR104">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AS104">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AT104">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22755,25 +22755,25 @@
         <v>2.55</v>
       </c>
       <c r="AN105">
-        <v>1.13</v>
+        <v>0.76</v>
       </c>
       <c r="AO105">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="AP105">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ105">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR105">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AS105">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AT105">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="AU105">
         <v>7</v>
@@ -22961,25 +22961,25 @@
         <v>1.74</v>
       </c>
       <c r="AN106">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AO106">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ106">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AR106">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AS106">
         <v>1.47</v>
       </c>
       <c r="AT106">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="AU106">
         <v>6</v>
@@ -23167,25 +23167,25 @@
         <v>6.1</v>
       </c>
       <c r="AN107">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AO107">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AP107">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ107">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR107">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AS107">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AT107">
-        <v>3.59</v>
+        <v>3.32</v>
       </c>
       <c r="AU107">
         <v>8</v>
@@ -23373,25 +23373,25 @@
         <v>2</v>
       </c>
       <c r="AN108">
-        <v>1.63</v>
+        <v>1.12</v>
       </c>
       <c r="AO108">
-        <v>0.38</v>
+        <v>0.83</v>
       </c>
       <c r="AP108">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR108">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AS108">
-        <v>0.8100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="AT108">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AU108">
         <v>3</v>
@@ -23579,25 +23579,25 @@
         <v>1.48</v>
       </c>
       <c r="AN109">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AO109">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AP109">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR109">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AS109">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT109">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AU109">
         <v>9</v>
@@ -23785,25 +23785,25 @@
         <v>1.4</v>
       </c>
       <c r="AN110">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AO110">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AP110">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ110">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR110">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AS110">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AT110">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AU110">
         <v>5</v>
@@ -23991,25 +23991,25 @@
         <v>1.08</v>
       </c>
       <c r="AN111">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AO111">
-        <v>1.43</v>
+        <v>2.19</v>
       </c>
       <c r="AP111">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ111">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR111">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AS111">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="AT111">
-        <v>2.83</v>
+        <v>3.07</v>
       </c>
       <c r="AU111">
         <v>4</v>
@@ -24197,25 +24197,25 @@
         <v>1.22</v>
       </c>
       <c r="AN112">
+        <v>0.95</v>
+      </c>
+      <c r="AO112">
+        <v>0.84</v>
+      </c>
+      <c r="AP112">
+        <v>1.04</v>
+      </c>
+      <c r="AQ112">
         <v>1.2</v>
       </c>
-      <c r="AO112">
-        <v>0.44</v>
-      </c>
-      <c r="AP112">
-        <v>1.08</v>
-      </c>
-      <c r="AQ112">
-        <v>0.92</v>
-      </c>
       <c r="AR112">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AS112">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AT112">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AU112">
         <v>5</v>
@@ -24403,25 +24403,25 @@
         <v>6.75</v>
       </c>
       <c r="AN113">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="AO113">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="AP113">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ113">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR113">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AS113">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AT113">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AU113">
         <v>12</v>
@@ -24612,22 +24612,22 @@
         <v>1.11</v>
       </c>
       <c r="AO114">
-        <v>0.82</v>
+        <v>1.11</v>
       </c>
       <c r="AP114">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ114">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AR114">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AS114">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AT114">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AU114">
         <v>3</v>
@@ -24815,25 +24815,25 @@
         <v>1.07</v>
       </c>
       <c r="AN115">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AO115">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="AP115">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR115">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AS115">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AT115">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="AU115">
         <v>6</v>
@@ -25021,25 +25021,25 @@
         <v>1.68</v>
       </c>
       <c r="AN116">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AO116">
-        <v>0.67</v>
+        <v>1.06</v>
       </c>
       <c r="AP116">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ116">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR116">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AS116">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AT116">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="AU116">
         <v>6</v>
@@ -25227,22 +25227,22 @@
         <v>1.44</v>
       </c>
       <c r="AN117">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AO117">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AP117">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ117">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR117">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AS117">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AT117">
         <v>2.58</v>
@@ -25433,25 +25433,25 @@
         <v>1.47</v>
       </c>
       <c r="AN118">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="AO118">
         <v>2.78</v>
       </c>
       <c r="AP118">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ118">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR118">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="AS118">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AT118">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="AU118">
         <v>10</v>
@@ -25639,25 +25639,25 @@
         <v>1.27</v>
       </c>
       <c r="AN119">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AO119">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AP119">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ119">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AR119">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AS119">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AT119">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AU119">
         <v>3</v>
@@ -25845,25 +25845,25 @@
         <v>1.98</v>
       </c>
       <c r="AN120">
+        <v>0.85</v>
+      </c>
+      <c r="AO120">
+        <v>1.42</v>
+      </c>
+      <c r="AP120">
         <v>1.2</v>
       </c>
-      <c r="AO120">
-        <v>1.33</v>
-      </c>
-      <c r="AP120">
-        <v>1.5</v>
-      </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR120">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AS120">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AT120">
-        <v>2.87</v>
+        <v>2.57</v>
       </c>
       <c r="AU120">
         <v>7</v>
@@ -26051,25 +26051,25 @@
         <v>1.73</v>
       </c>
       <c r="AN121">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AO121">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AP121">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ121">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AR121">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AS121">
         <v>1.22</v>
       </c>
       <c r="AT121">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26257,25 +26257,25 @@
         <v>2.5</v>
       </c>
       <c r="AN122">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AO122">
-        <v>0.67</v>
+        <v>0.95</v>
       </c>
       <c r="AP122">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR122">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AS122">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="AT122">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AU122">
         <v>5</v>
@@ -26463,25 +26463,25 @@
         <v>1.5</v>
       </c>
       <c r="AN123">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AO123">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AP123">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ123">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR123">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AS123">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AT123">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="AU123">
         <v>5</v>
@@ -26669,25 +26669,25 @@
         <v>1.11</v>
       </c>
       <c r="AN124">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AO124">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AP124">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ124">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR124">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AS124">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AT124">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="AU124">
         <v>7</v>
@@ -26875,25 +26875,25 @@
         <v>1.47</v>
       </c>
       <c r="AN125">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AO125">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AP125">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ125">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR125">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AS125">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AT125">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AU125">
         <v>4</v>
@@ -27081,25 +27081,25 @@
         <v>5.25</v>
       </c>
       <c r="AN126">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="AO126">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AP126">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ126">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AR126">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="AS126">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AT126">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27287,25 +27287,25 @@
         <v>1.58</v>
       </c>
       <c r="AN127">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AO127">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AP127">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ127">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR127">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AS127">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AT127">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AU127">
         <v>2</v>
@@ -27493,22 +27493,22 @@
         <v>2.4</v>
       </c>
       <c r="AN128">
-        <v>1.67</v>
+        <v>1.14</v>
       </c>
       <c r="AO128">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AP128">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR128">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AS128">
-        <v>0.96</v>
+        <v>1.11</v>
       </c>
       <c r="AT128">
         <v>2.38</v>
@@ -27699,25 +27699,25 @@
         <v>1.41</v>
       </c>
       <c r="AN129">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AO129">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AP129">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ129">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR129">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AS129">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AT129">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AU129">
         <v>6</v>
@@ -27905,25 +27905,25 @@
         <v>1.73</v>
       </c>
       <c r="AN130">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AO130">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AP130">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR130">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS130">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AT130">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="AU130">
         <v>4</v>
@@ -28111,25 +28111,25 @@
         <v>4.75</v>
       </c>
       <c r="AN131">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AO131">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AP131">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ131">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR131">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AS131">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AT131">
-        <v>3.52</v>
+        <v>3.33</v>
       </c>
       <c r="AU131">
         <v>7</v>
@@ -28317,25 +28317,25 @@
         <v>1.05</v>
       </c>
       <c r="AN132">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AO132">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AP132">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ132">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR132">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AS132">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AT132">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="AU132">
         <v>3</v>
@@ -28523,25 +28523,25 @@
         <v>1.02</v>
       </c>
       <c r="AN133">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AO133">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AP133">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AQ133">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR133">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AS133">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AT133">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="AU133">
         <v>2</v>
@@ -28729,22 +28729,22 @@
         <v>1.52</v>
       </c>
       <c r="AN134">
+        <v>1.23</v>
+      </c>
+      <c r="AO134">
         <v>1.55</v>
       </c>
-      <c r="AO134">
-        <v>1.45</v>
-      </c>
       <c r="AP134">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ134">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR134">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AS134">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AT134">
         <v>2.43</v>
@@ -28935,25 +28935,25 @@
         <v>1.95</v>
       </c>
       <c r="AN135">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AO135">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AP135">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR135">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AS135">
         <v>1.15</v>
       </c>
       <c r="AT135">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AU135">
         <v>4</v>
@@ -29141,25 +29141,25 @@
         <v>7.25</v>
       </c>
       <c r="AN136">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="AO136">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="AP136">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ136">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR136">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AS136">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AT136">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="AU136">
         <v>7</v>
@@ -29347,25 +29347,25 @@
         <v>1.6</v>
       </c>
       <c r="AN137">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AO137">
-        <v>0.73</v>
+        <v>1.05</v>
       </c>
       <c r="AP137">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ137">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR137">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AS137">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="AT137">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AU137">
         <v>2</v>
@@ -29553,25 +29553,25 @@
         <v>1.04</v>
       </c>
       <c r="AN138">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AO138">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="AP138">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ138">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR138">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AS138">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AT138">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="AU138">
         <v>6</v>
@@ -29759,25 +29759,25 @@
         <v>3.7</v>
       </c>
       <c r="AN139">
-        <v>2.82</v>
+        <v>2</v>
       </c>
       <c r="AO139">
-        <v>1.2</v>
+        <v>1.59</v>
       </c>
       <c r="AP139">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ139">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR139">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AS139">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AT139">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AU139">
         <v>13</v>
@@ -29965,25 +29965,25 @@
         <v>1.78</v>
       </c>
       <c r="AN140">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AO140">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AP140">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AQ140">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AR140">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AS140">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AT140">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AU140">
         <v>8</v>
@@ -30171,25 +30171,25 @@
         <v>1.8</v>
       </c>
       <c r="AN141">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AO141">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AP141">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ141">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AR141">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="AS141">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AT141">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="AU141">
         <v>6</v>
@@ -30377,25 +30377,25 @@
         <v>1.28</v>
       </c>
       <c r="AN142">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AO142">
+        <v>1.26</v>
+      </c>
+      <c r="AP142">
+        <v>1.04</v>
+      </c>
+      <c r="AQ142">
+        <v>1.32</v>
+      </c>
+      <c r="AR142">
         <v>1.09</v>
       </c>
-      <c r="AP142">
-        <v>1.08</v>
-      </c>
-      <c r="AQ142">
-        <v>1.08</v>
-      </c>
-      <c r="AR142">
-        <v>1.21</v>
-      </c>
       <c r="AS142">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AT142">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="AU142">
         <v>3</v>
@@ -30583,25 +30583,25 @@
         <v>1.44</v>
       </c>
       <c r="AN143">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AO143">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AP143">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AQ143">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AR143">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AS143">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AT143">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="AU143">
         <v>7</v>
@@ -30789,25 +30789,25 @@
         <v>1.13</v>
       </c>
       <c r="AN144">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AO144">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AP144">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ144">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AR144">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AS144">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AT144">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="AU144">
         <v>8</v>
@@ -30995,25 +30995,25 @@
         <v>1.98</v>
       </c>
       <c r="AN145">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AO145">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP145">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AQ145">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AR145">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AS145">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AT145">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AU145">
         <v>5</v>
@@ -31201,25 +31201,25 @@
         <v>1.41</v>
       </c>
       <c r="AN146">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AO146">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AP146">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ146">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="AR146">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AS146">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AT146">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="AU146">
         <v>4</v>
@@ -31407,25 +31407,25 @@
         <v>1.85</v>
       </c>
       <c r="AN147">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AO147">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="AP147">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AQ147">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR147">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AS147">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AT147">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="AU147">
         <v>6</v>
@@ -31613,25 +31613,25 @@
         <v>1.55</v>
       </c>
       <c r="AN148">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="AO148">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AP148">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AQ148">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR148">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AS148">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AT148">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AU148">
         <v>5</v>
@@ -31819,25 +31819,25 @@
         <v>5.25</v>
       </c>
       <c r="AN149">
-        <v>2.83</v>
+        <v>2.08</v>
       </c>
       <c r="AO149">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AP149">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="AQ149">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR149">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="AS149">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="AT149">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="AU149">
         <v>10</v>
@@ -32025,25 +32025,25 @@
         <v>1.03</v>
       </c>
       <c r="AN150">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AO150">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AP150">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AQ150">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AR150">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AS150">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AT150">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="AU150">
         <v>2</v>
@@ -32231,25 +32231,25 @@
         <v>7</v>
       </c>
       <c r="AN151">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="AO151">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AP151">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="AQ151">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR151">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="AS151">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AT151">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="AU151">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1749,10 +1749,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1955,10 +1955,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ5">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2367,10 +2367,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ6">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2573,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AQ7">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2773,25 +2773,25 @@
         <v>4.33</v>
       </c>
       <c r="AN8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ8">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU8">
         <v>10</v>
@@ -2979,25 +2979,25 @@
         <v>1.5</v>
       </c>
       <c r="AN9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR9">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU9">
         <v>6</v>
@@ -3185,25 +3185,25 @@
         <v>1.36</v>
       </c>
       <c r="AN10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AQ10">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR10">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>8</v>
@@ -3394,22 +3394,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ11">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR11">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>0</v>
@@ -3597,25 +3597,25 @@
         <v>1.95</v>
       </c>
       <c r="AN12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ12">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AR12">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>4</v>
@@ -3809,19 +3809,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ13">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR13">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>3</v>
@@ -4012,22 +4012,22 @@
         <v>1</v>
       </c>
       <c r="AO14">
+        <v>3</v>
+      </c>
+      <c r="AP14">
         <v>1.5</v>
       </c>
-      <c r="AP14">
-        <v>1.48</v>
-      </c>
       <c r="AQ14">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR14">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="AS14">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AT14">
-        <v>2.98</v>
+        <v>3.54</v>
       </c>
       <c r="AU14">
         <v>3</v>
@@ -4218,22 +4218,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ15">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR15">
-        <v>1</v>
+        <v>0.53</v>
       </c>
       <c r="AS15">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AT15">
-        <v>2.58</v>
+        <v>2.13</v>
       </c>
       <c r="AU15">
         <v>3</v>
@@ -4421,25 +4421,25 @@
         <v>4.5</v>
       </c>
       <c r="AN16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO16">
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ16">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR16">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="AS16">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="AT16">
-        <v>2.99</v>
+        <v>3.13</v>
       </c>
       <c r="AU16">
         <v>10</v>
@@ -4627,25 +4627,25 @@
         <v>1.02</v>
       </c>
       <c r="AN17">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO17">
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR17">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AS17">
-        <v>2.38</v>
+        <v>1.65</v>
       </c>
       <c r="AT17">
-        <v>3.53</v>
+        <v>2.72</v>
       </c>
       <c r="AU17">
         <v>2</v>
@@ -4833,25 +4833,25 @@
         <v>1.4</v>
       </c>
       <c r="AN18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR18">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="AS18">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AT18">
-        <v>2.44</v>
+        <v>2.86</v>
       </c>
       <c r="AU18">
         <v>7</v>
@@ -5045,19 +5045,19 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ19">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR19">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="AS19">
-        <v>1.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AT19">
-        <v>2.48</v>
+        <v>1.79</v>
       </c>
       <c r="AU19">
         <v>4</v>
@@ -5245,25 +5245,25 @@
         <v>1.73</v>
       </c>
       <c r="AN20">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AO20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP20">
+        <v>1.15</v>
+      </c>
+      <c r="AQ20">
         <v>1.08</v>
       </c>
-      <c r="AQ20">
-        <v>1.2</v>
-      </c>
       <c r="AR20">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AS20">
-        <v>0.91</v>
+        <v>1.22</v>
       </c>
       <c r="AT20">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="AU20">
         <v>6</v>
@@ -5451,25 +5451,25 @@
         <v>1.42</v>
       </c>
       <c r="AN21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO21">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AQ21">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR21">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AS21">
-        <v>1.26</v>
+        <v>0.88</v>
       </c>
       <c r="AT21">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="AU21">
         <v>6</v>
@@ -5657,25 +5657,25 @@
         <v>1.3</v>
       </c>
       <c r="AN22">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO22">
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ22">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR22">
-        <v>1.12</v>
+        <v>1.66</v>
       </c>
       <c r="AS22">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AT22">
-        <v>2.46</v>
+        <v>3.43</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5866,22 +5866,22 @@
         <v>3</v>
       </c>
       <c r="AO23">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ23">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR23">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="AS23">
-        <v>1.74</v>
+        <v>1.18</v>
       </c>
       <c r="AT23">
-        <v>3.96</v>
+        <v>4.28</v>
       </c>
       <c r="AU23">
         <v>5</v>
@@ -6069,25 +6069,25 @@
         <v>2</v>
       </c>
       <c r="AN24">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AO24">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AS24">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="AT24">
-        <v>2.47</v>
+        <v>2.19</v>
       </c>
       <c r="AU24">
         <v>3</v>
@@ -6278,22 +6278,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ25">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AR25">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="AS25">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="AT25">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6484,22 +6484,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ26">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR26">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AS26">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AT26">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6690,22 +6690,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ27">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR27">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="AS27">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AT27">
-        <v>3.19</v>
+        <v>3.36</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6896,22 +6896,22 @@
         <v>0.5</v>
       </c>
       <c r="AO28">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ28">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR28">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="AS28">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AT28">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -7102,22 +7102,22 @@
         <v>0.5</v>
       </c>
       <c r="AO29">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ29">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR29">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AS29">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AT29">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7305,25 +7305,25 @@
         <v>1.66</v>
       </c>
       <c r="AN30">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO30">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ30">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR30">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="AS30">
-        <v>1.09</v>
+        <v>0.85</v>
       </c>
       <c r="AT30">
-        <v>2.14</v>
+        <v>1.61</v>
       </c>
       <c r="AU30">
         <v>4</v>
@@ -7514,22 +7514,22 @@
         <v>2</v>
       </c>
       <c r="AO31">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR31">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AS31">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AT31">
-        <v>2.91</v>
+        <v>2.72</v>
       </c>
       <c r="AU31">
         <v>0</v>
@@ -7717,25 +7717,25 @@
         <v>1.75</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO32">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AP32">
+        <v>1.08</v>
+      </c>
+      <c r="AQ32">
+        <v>0.85</v>
+      </c>
+      <c r="AR32">
+        <v>1.31</v>
+      </c>
+      <c r="AS32">
         <v>1.04</v>
       </c>
-      <c r="AQ32">
-        <v>0.84</v>
-      </c>
-      <c r="AR32">
-        <v>1.12</v>
-      </c>
-      <c r="AS32">
-        <v>1.19</v>
-      </c>
       <c r="AT32">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AU32">
         <v>7</v>
@@ -7923,25 +7923,25 @@
         <v>1.41</v>
       </c>
       <c r="AN33">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO33">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ33">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR33">
-        <v>1.06</v>
+        <v>0.87</v>
       </c>
       <c r="AS33">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AT33">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AU33">
         <v>3</v>
@@ -8129,25 +8129,25 @@
         <v>2.25</v>
       </c>
       <c r="AN34">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="AO34">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR34">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AS34">
-        <v>1.21</v>
+        <v>0.84</v>
       </c>
       <c r="AT34">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AU34">
         <v>9</v>
@@ -8335,25 +8335,25 @@
         <v>1.66</v>
       </c>
       <c r="AN35">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AO35">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP35">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ35">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR35">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AS35">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AT35">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AU35">
         <v>4</v>
@@ -8541,25 +8541,25 @@
         <v>1.58</v>
       </c>
       <c r="AN36">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO36">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AR36">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AS36">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AT36">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="AU36">
         <v>5</v>
@@ -8747,25 +8747,25 @@
         <v>1.45</v>
       </c>
       <c r="AN37">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AO37">
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AQ37">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR37">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AS37">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AT37">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -8953,25 +8953,25 @@
         <v>1.04</v>
       </c>
       <c r="AN38">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO38">
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AQ38">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR38">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="AS38">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="AT38">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="AU38">
         <v>2</v>
@@ -9159,25 +9159,25 @@
         <v>2.9</v>
       </c>
       <c r="AN39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ39">
+        <v>1.08</v>
+      </c>
+      <c r="AR39">
+        <v>2.01</v>
+      </c>
+      <c r="AS39">
         <v>1.32</v>
       </c>
-      <c r="AR39">
-        <v>1.59</v>
-      </c>
-      <c r="AS39">
-        <v>1.2</v>
-      </c>
       <c r="AT39">
-        <v>2.79</v>
+        <v>3.33</v>
       </c>
       <c r="AU39">
         <v>5</v>
@@ -9365,25 +9365,25 @@
         <v>1.63</v>
       </c>
       <c r="AN40">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AO40">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AP40">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ40">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR40">
-        <v>1.22</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS40">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AT40">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AU40">
         <v>4</v>
@@ -9571,25 +9571,25 @@
         <v>1.77</v>
       </c>
       <c r="AN41">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AO41">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ41">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR41">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AS41">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AT41">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -9777,25 +9777,25 @@
         <v>1.62</v>
       </c>
       <c r="AN42">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO42">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AQ42">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR42">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AS42">
-        <v>1.15</v>
+        <v>0.99</v>
       </c>
       <c r="AT42">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AU42">
         <v>4</v>
@@ -9983,25 +9983,25 @@
         <v>1.02</v>
       </c>
       <c r="AN43">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO43">
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ43">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR43">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AS43">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AT43">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="AU43">
         <v>6</v>
@@ -10192,22 +10192,22 @@
         <v>3</v>
       </c>
       <c r="AO44">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ44">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR44">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AS44">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AT44">
-        <v>2.52</v>
+        <v>2.27</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10395,25 +10395,25 @@
         <v>5.7</v>
       </c>
       <c r="AN45">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="AO45">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AP45">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ45">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR45">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AS45">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AT45">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="AU45">
         <v>7</v>
@@ -10607,19 +10607,19 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ46">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR46">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AS46">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AT46">
-        <v>3.33</v>
+        <v>3.39</v>
       </c>
       <c r="AU46">
         <v>8</v>
@@ -10807,25 +10807,25 @@
         <v>1.57</v>
       </c>
       <c r="AN47">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AO47">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AR47">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AS47">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AT47">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -11013,25 +11013,25 @@
         <v>2</v>
       </c>
       <c r="AN48">
-        <v>0.25</v>
+        <v>0.67</v>
       </c>
       <c r="AO48">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AR48">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="AS48">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="AT48">
-        <v>2.57</v>
+        <v>3.21</v>
       </c>
       <c r="AU48">
         <v>5</v>
@@ -11219,25 +11219,25 @@
         <v>1.83</v>
       </c>
       <c r="AN49">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AO49">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR49">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AS49">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AT49">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="AU49">
         <v>4</v>
@@ -11425,25 +11425,25 @@
         <v>1.5</v>
       </c>
       <c r="AN50">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO50">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="AP50">
+        <v>0.83</v>
+      </c>
+      <c r="AQ50">
+        <v>1</v>
+      </c>
+      <c r="AR50">
+        <v>1.16</v>
+      </c>
+      <c r="AS50">
         <v>0.84</v>
       </c>
-      <c r="AQ50">
-        <v>1.04</v>
-      </c>
-      <c r="AR50">
-        <v>1.07</v>
-      </c>
-      <c r="AS50">
-        <v>1.15</v>
-      </c>
       <c r="AT50">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AU50">
         <v>8</v>
@@ -11631,25 +11631,25 @@
         <v>1.12</v>
       </c>
       <c r="AN51">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="AO51">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ51">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR51">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AS51">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AT51">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AU51">
         <v>4</v>
@@ -11837,25 +11837,25 @@
         <v>2.15</v>
       </c>
       <c r="AN52">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP52">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AQ52">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR52">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AS52">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AT52">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12043,25 +12043,25 @@
         <v>1.36</v>
       </c>
       <c r="AN53">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AO53">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ53">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR53">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AS53">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AT53">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12249,25 +12249,25 @@
         <v>2.2</v>
       </c>
       <c r="AN54">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AO54">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ54">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR54">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AS54">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AT54">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AU54">
         <v>6</v>
@@ -12455,25 +12455,25 @@
         <v>1.6</v>
       </c>
       <c r="AN55">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="AO55">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ55">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR55">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AS55">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AT55">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="AU55">
         <v>8</v>
@@ -12661,25 +12661,25 @@
         <v>1.02</v>
       </c>
       <c r="AN56">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO56">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
       </c>
       <c r="AS56">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AT56">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="AU56">
         <v>3</v>
@@ -12867,25 +12867,25 @@
         <v>4</v>
       </c>
       <c r="AN57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO57">
-        <v>0.89</v>
+        <v>0.25</v>
       </c>
       <c r="AP57">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ57">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AR57">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AS57">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AT57">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="AU57">
         <v>8</v>
@@ -13073,25 +13073,25 @@
         <v>1.93</v>
       </c>
       <c r="AN58">
-        <v>0.6</v>
+        <v>1.25</v>
       </c>
       <c r="AO58">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR58">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AS58">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AT58">
-        <v>2.48</v>
+        <v>2.71</v>
       </c>
       <c r="AU58">
         <v>6</v>
@@ -13279,25 +13279,25 @@
         <v>1.33</v>
       </c>
       <c r="AN59">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO59">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="AP59">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ59">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AR59">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AS59">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AT59">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="AU59">
         <v>3</v>
@@ -13485,25 +13485,25 @@
         <v>2.05</v>
       </c>
       <c r="AN60">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AP60">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ60">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR60">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AS60">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AT60">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AU60">
         <v>6</v>
@@ -13691,25 +13691,25 @@
         <v>1.67</v>
       </c>
       <c r="AN61">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AO61">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61">
+        <v>1</v>
+      </c>
+      <c r="AR61">
+        <v>1.15</v>
+      </c>
+      <c r="AS61">
         <v>1.24</v>
       </c>
-      <c r="AR61">
-        <v>1.17</v>
-      </c>
-      <c r="AS61">
-        <v>1.21</v>
-      </c>
       <c r="AT61">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AU61">
         <v>6</v>
@@ -13897,25 +13897,25 @@
         <v>6.25</v>
       </c>
       <c r="AN62">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AO62">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AP62">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ62">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR62">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AS62">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AT62">
-        <v>3.53</v>
+        <v>3.48</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14103,25 +14103,25 @@
         <v>1.25</v>
       </c>
       <c r="AN63">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AO63">
-        <v>2.11</v>
+        <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ63">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR63">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AS63">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AT63">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14309,25 +14309,25 @@
         <v>1.22</v>
       </c>
       <c r="AN64">
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
       <c r="AO64">
-        <v>0.55</v>
+        <v>0.17</v>
       </c>
       <c r="AP64">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AQ64">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR64">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AS64">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AT64">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14515,25 +14515,25 @@
         <v>2.05</v>
       </c>
       <c r="AN65">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AO65">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ65">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR65">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AS65">
-        <v>1.1</v>
+        <v>0.77</v>
       </c>
       <c r="AT65">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="AU65">
         <v>4</v>
@@ -14721,25 +14721,25 @@
         <v>1.53</v>
       </c>
       <c r="AN66">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AO66">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AP66">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AQ66">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR66">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AS66">
         <v>1.21</v>
       </c>
       <c r="AT66">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -14927,25 +14927,25 @@
         <v>2</v>
       </c>
       <c r="AN67">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AO67">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ67">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR67">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AS67">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AT67">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AU67">
         <v>4</v>
@@ -15133,25 +15133,25 @@
         <v>2.05</v>
       </c>
       <c r="AN68">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AO68">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AP68">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AQ68">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR68">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AS68">
-        <v>1.1</v>
+        <v>0.82</v>
       </c>
       <c r="AT68">
-        <v>2.29</v>
+        <v>2.04</v>
       </c>
       <c r="AU68">
         <v>5</v>
@@ -15339,25 +15339,25 @@
         <v>1.93</v>
       </c>
       <c r="AN69">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AO69">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AP69">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ69">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AR69">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AS69">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AT69">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15545,25 +15545,25 @@
         <v>1.95</v>
       </c>
       <c r="AN70">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AO70">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AP70">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AQ70">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR70">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AS70">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AT70">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15751,25 +15751,25 @@
         <v>2.15</v>
       </c>
       <c r="AN71">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AO71">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ71">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR71">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AS71">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AT71">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15957,25 +15957,25 @@
         <v>1.07</v>
       </c>
       <c r="AN72">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AO72">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AP72">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ72">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR72">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AS72">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AT72">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -16163,25 +16163,25 @@
         <v>2.88</v>
       </c>
       <c r="AN73">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="AO73">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="AP73">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ73">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR73">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AS73">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AT73">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16369,25 +16369,25 @@
         <v>1.36</v>
       </c>
       <c r="AN74">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="AO74">
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AQ74">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR74">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AS74">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AT74">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="AU74">
         <v>5</v>
@@ -16575,25 +16575,25 @@
         <v>1.45</v>
       </c>
       <c r="AN75">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AO75">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AP75">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ75">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR75">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AS75">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AT75">
-        <v>2.31</v>
+        <v>2.52</v>
       </c>
       <c r="AU75">
         <v>-1</v>
@@ -16781,25 +16781,25 @@
         <v>3.75</v>
       </c>
       <c r="AN76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO76">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ76">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR76">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AS76">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AT76">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="AU76">
         <v>12</v>
@@ -16987,25 +16987,25 @@
         <v>1.38</v>
       </c>
       <c r="AN77">
+        <v>1.57</v>
+      </c>
+      <c r="AO77">
+        <v>2.5</v>
+      </c>
+      <c r="AP77">
+        <v>1.31</v>
+      </c>
+      <c r="AQ77">
+        <v>1</v>
+      </c>
+      <c r="AR77">
+        <v>1.13</v>
+      </c>
+      <c r="AS77">
         <v>1.15</v>
       </c>
-      <c r="AO77">
-        <v>2.82</v>
-      </c>
-      <c r="AP77">
-        <v>1.2</v>
-      </c>
-      <c r="AQ77">
-        <v>1.4</v>
-      </c>
-      <c r="AR77">
-        <v>1.19</v>
-      </c>
-      <c r="AS77">
-        <v>1.32</v>
-      </c>
       <c r="AT77">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17193,25 +17193,25 @@
         <v>1.47</v>
       </c>
       <c r="AN78">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO78">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="AP78">
+        <v>1.15</v>
+      </c>
+      <c r="AQ78">
         <v>1.08</v>
       </c>
-      <c r="AQ78">
-        <v>1.32</v>
-      </c>
       <c r="AR78">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AS78">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AT78">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="AU78">
         <v>-1</v>
@@ -17399,25 +17399,25 @@
         <v>1.09</v>
       </c>
       <c r="AN79">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="AO79">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AP79">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR79">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AS79">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AT79">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AU79">
         <v>-1</v>
@@ -17605,25 +17605,25 @@
         <v>1.55</v>
       </c>
       <c r="AN80">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="AO80">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="AP80">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ80">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR80">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AS80">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AT80">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17811,25 +17811,25 @@
         <v>7.5</v>
       </c>
       <c r="AN81">
+        <v>2.6</v>
+      </c>
+      <c r="AO81">
+        <v>0.5</v>
+      </c>
+      <c r="AP81">
         <v>2.83</v>
       </c>
-      <c r="AO81">
-        <v>1.07</v>
-      </c>
-      <c r="AP81">
-        <v>2.64</v>
-      </c>
       <c r="AQ81">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR81">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AS81">
-        <v>1.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT81">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="AU81">
         <v>10</v>
@@ -18017,25 +18017,25 @@
         <v>1.68</v>
       </c>
       <c r="AN82">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AO82">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AQ82">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AR82">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AS82">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AT82">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -18223,25 +18223,25 @@
         <v>1.8</v>
       </c>
       <c r="AN83">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AO83">
-        <v>1.15</v>
+        <v>0.83</v>
       </c>
       <c r="AP83">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ83">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR83">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AS83">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AT83">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="AU83">
         <v>6</v>
@@ -18429,25 +18429,25 @@
         <v>1.53</v>
       </c>
       <c r="AN84">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AO84">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AR84">
         <v>1.24</v>
       </c>
       <c r="AS84">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AT84">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AU84">
         <v>4</v>
@@ -18635,25 +18635,25 @@
         <v>1.03</v>
       </c>
       <c r="AN85">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AO85">
-        <v>1.92</v>
+        <v>0.8</v>
       </c>
       <c r="AP85">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AQ85">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR85">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AS85">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="AT85">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="AU85">
         <v>2</v>
@@ -18841,25 +18841,25 @@
         <v>1.6</v>
       </c>
       <c r="AN86">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AO86">
-        <v>2.46</v>
+        <v>1.83</v>
       </c>
       <c r="AP86">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ86">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR86">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AS86">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AT86">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="AU86">
         <v>4</v>
@@ -19047,25 +19047,25 @@
         <v>3.75</v>
       </c>
       <c r="AN87">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="AO87">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AP87">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ87">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR87">
-        <v>1.77</v>
+        <v>1.99</v>
       </c>
       <c r="AS87">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AT87">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="AU87">
         <v>12</v>
@@ -19253,25 +19253,25 @@
         <v>1.75</v>
       </c>
       <c r="AN88">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AO88">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AQ88">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR88">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AS88">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AT88">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19459,25 +19459,25 @@
         <v>1.11</v>
       </c>
       <c r="AN89">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="AO89">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AP89">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ89">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR89">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AS89">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AT89">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="AU89">
         <v>5</v>
@@ -19665,25 +19665,25 @@
         <v>1.68</v>
       </c>
       <c r="AN90">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AO90">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AP90">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ90">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.21</v>
       </c>
       <c r="AS90">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AT90">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AU90">
         <v>7</v>
@@ -19871,25 +19871,25 @@
         <v>2.4</v>
       </c>
       <c r="AN91">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AO91">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AP91">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ91">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR91">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AS91">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AT91">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AU91">
         <v>3</v>
@@ -20077,25 +20077,25 @@
         <v>5.75</v>
       </c>
       <c r="AN92">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AO92">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ92">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AR92">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AS92">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AT92">
-        <v>3.47</v>
+        <v>3.65</v>
       </c>
       <c r="AU92">
         <v>12</v>
@@ -20283,25 +20283,25 @@
         <v>1.66</v>
       </c>
       <c r="AN93">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AO93">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="AP93">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AQ93">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR93">
+        <v>1.35</v>
+      </c>
+      <c r="AS93">
         <v>1.12</v>
       </c>
-      <c r="AR93">
-        <v>1.22</v>
-      </c>
-      <c r="AS93">
-        <v>1.23</v>
-      </c>
       <c r="AT93">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AU93">
         <v>8</v>
@@ -20489,25 +20489,25 @@
         <v>1.87</v>
       </c>
       <c r="AN94">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AO94">
-        <v>1.27</v>
+        <v>0.86</v>
       </c>
       <c r="AP94">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ94">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR94">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AS94">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AT94">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="AU94">
         <v>9</v>
@@ -20695,25 +20695,25 @@
         <v>1.03</v>
       </c>
       <c r="AN95">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO95">
-        <v>2.07</v>
+        <v>1.17</v>
       </c>
       <c r="AP95">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ95">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR95">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AS95">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AT95">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AU95">
         <v>3</v>
@@ -20901,25 +20901,25 @@
         <v>1.45</v>
       </c>
       <c r="AN96">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="AO96">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AQ96">
+        <v>1.08</v>
+      </c>
+      <c r="AR96">
+        <v>1.26</v>
+      </c>
+      <c r="AS96">
         <v>1.2</v>
       </c>
-      <c r="AR96">
-        <v>1.16</v>
-      </c>
-      <c r="AS96">
-        <v>1.22</v>
-      </c>
       <c r="AT96">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -21107,25 +21107,25 @@
         <v>2.45</v>
       </c>
       <c r="AN97">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AO97">
-        <v>0.9399999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="AP97">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ97">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR97">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AS97">
-        <v>1.02</v>
+        <v>0.76</v>
       </c>
       <c r="AT97">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="AU97">
         <v>8</v>
@@ -21313,25 +21313,25 @@
         <v>1.52</v>
       </c>
       <c r="AN98">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AO98">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AP98">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AQ98">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR98">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AS98">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AT98">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21519,25 +21519,25 @@
         <v>1.35</v>
       </c>
       <c r="AN99">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO99">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ99">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR99">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS99">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="AT99">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AU99">
         <v>6</v>
@@ -21725,25 +21725,25 @@
         <v>1.57</v>
       </c>
       <c r="AN100">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AO100">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP100">
+        <v>1.5</v>
+      </c>
+      <c r="AQ100">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR100">
         <v>1.24</v>
       </c>
-      <c r="AQ100">
-        <v>1.12</v>
-      </c>
-      <c r="AR100">
-        <v>1.29</v>
-      </c>
       <c r="AS100">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AT100">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21931,25 +21931,25 @@
         <v>1.36</v>
       </c>
       <c r="AN101">
+        <v>1.33</v>
+      </c>
+      <c r="AO101">
         <v>0.88</v>
       </c>
-      <c r="AO101">
+      <c r="AP101">
+        <v>1.08</v>
+      </c>
+      <c r="AQ101">
+        <v>1.08</v>
+      </c>
+      <c r="AR101">
         <v>1.24</v>
       </c>
-      <c r="AP101">
-        <v>1.04</v>
-      </c>
-      <c r="AQ101">
+      <c r="AS101">
         <v>1.2</v>
       </c>
-      <c r="AR101">
-        <v>1.03</v>
-      </c>
-      <c r="AS101">
-        <v>1.22</v>
-      </c>
       <c r="AT101">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AU101">
         <v>2</v>
@@ -22137,25 +22137,25 @@
         <v>4.5</v>
       </c>
       <c r="AN102">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="AO102">
-        <v>1.19</v>
+        <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ102">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR102">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AS102">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AT102">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="AU102">
         <v>5</v>
@@ -22343,25 +22343,25 @@
         <v>1.65</v>
       </c>
       <c r="AN103">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="AO103">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="AP103">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ103">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AR103">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AS103">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AT103">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="AU103">
         <v>3</v>
@@ -22549,25 +22549,25 @@
         <v>1.01</v>
       </c>
       <c r="AN104">
+        <v>1.75</v>
+      </c>
+      <c r="AO104">
+        <v>3</v>
+      </c>
+      <c r="AP104">
         <v>1.5</v>
       </c>
-      <c r="AO104">
-        <v>2.87</v>
-      </c>
-      <c r="AP104">
-        <v>1.48</v>
-      </c>
       <c r="AQ104">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR104">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AS104">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AT104">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22755,25 +22755,25 @@
         <v>2.55</v>
       </c>
       <c r="AN105">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="AO105">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="AP105">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ105">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR105">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="AS105">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AT105">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="AU105">
         <v>7</v>
@@ -22961,25 +22961,25 @@
         <v>1.74</v>
       </c>
       <c r="AN106">
+        <v>1.33</v>
+      </c>
+      <c r="AO106">
         <v>0.89</v>
       </c>
-      <c r="AO106">
-        <v>1</v>
-      </c>
       <c r="AP106">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ106">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AR106">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AS106">
         <v>1.47</v>
       </c>
       <c r="AT106">
-        <v>2.84</v>
+        <v>3.14</v>
       </c>
       <c r="AU106">
         <v>6</v>
@@ -23167,25 +23167,25 @@
         <v>6.1</v>
       </c>
       <c r="AN107">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AO107">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AP107">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ107">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR107">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AS107">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AT107">
-        <v>3.32</v>
+        <v>3.59</v>
       </c>
       <c r="AU107">
         <v>8</v>
@@ -23373,25 +23373,25 @@
         <v>2</v>
       </c>
       <c r="AN108">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="AO108">
-        <v>0.83</v>
+        <v>0.38</v>
       </c>
       <c r="AP108">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AQ108">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR108">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AS108">
-        <v>1.04</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT108">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AU108">
         <v>3</v>
@@ -23579,25 +23579,25 @@
         <v>1.48</v>
       </c>
       <c r="AN109">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AO109">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AP109">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ109">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR109">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AS109">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT109">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AU109">
         <v>9</v>
@@ -23785,25 +23785,25 @@
         <v>1.4</v>
       </c>
       <c r="AN110">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AO110">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AP110">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AQ110">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR110">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AS110">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AT110">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AU110">
         <v>5</v>
@@ -23991,25 +23991,25 @@
         <v>1.08</v>
       </c>
       <c r="AN111">
+        <v>1.56</v>
+      </c>
+      <c r="AO111">
+        <v>1.43</v>
+      </c>
+      <c r="AP111">
+        <v>1.31</v>
+      </c>
+      <c r="AQ111">
         <v>1.33</v>
       </c>
-      <c r="AO111">
-        <v>2.19</v>
-      </c>
-      <c r="AP111">
-        <v>1.2</v>
-      </c>
-      <c r="AQ111">
-        <v>2.12</v>
-      </c>
       <c r="AR111">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AS111">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="AT111">
-        <v>3.07</v>
+        <v>2.83</v>
       </c>
       <c r="AU111">
         <v>4</v>
@@ -24197,25 +24197,25 @@
         <v>1.22</v>
       </c>
       <c r="AN112">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
       <c r="AO112">
-        <v>0.84</v>
+        <v>0.44</v>
       </c>
       <c r="AP112">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ112">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR112">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AS112">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="AT112">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AU112">
         <v>5</v>
@@ -24403,25 +24403,25 @@
         <v>6.75</v>
       </c>
       <c r="AN113">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="AO113">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ113">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR113">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="AS113">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AT113">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AU113">
         <v>12</v>
@@ -24612,22 +24612,22 @@
         <v>1.11</v>
       </c>
       <c r="AO114">
-        <v>1.11</v>
+        <v>0.82</v>
       </c>
       <c r="AP114">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ114">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR114">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AS114">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AT114">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AU114">
         <v>3</v>
@@ -24815,25 +24815,25 @@
         <v>1.07</v>
       </c>
       <c r="AN115">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AO115">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="AP115">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AQ115">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AS115">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AT115">
-        <v>3.05</v>
+        <v>2.81</v>
       </c>
       <c r="AU115">
         <v>6</v>
@@ -25021,25 +25021,25 @@
         <v>1.68</v>
       </c>
       <c r="AN116">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AO116">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="AP116">
+        <v>1.31</v>
+      </c>
+      <c r="AQ116">
+        <v>1</v>
+      </c>
+      <c r="AR116">
         <v>1.2</v>
       </c>
-      <c r="AQ116">
-        <v>1.08</v>
-      </c>
-      <c r="AR116">
-        <v>1.21</v>
-      </c>
       <c r="AS116">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT116">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="AU116">
         <v>6</v>
@@ -25227,22 +25227,22 @@
         <v>1.44</v>
       </c>
       <c r="AN117">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AO117">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AQ117">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR117">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AS117">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AT117">
         <v>2.58</v>
@@ -25433,25 +25433,25 @@
         <v>1.47</v>
       </c>
       <c r="AN118">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="AO118">
         <v>2.78</v>
       </c>
       <c r="AP118">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ118">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR118">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="AS118">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AT118">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="AU118">
         <v>10</v>
@@ -25639,25 +25639,25 @@
         <v>1.27</v>
       </c>
       <c r="AN119">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="AO119">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AP119">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AQ119">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AR119">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AS119">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AT119">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AU119">
         <v>3</v>
@@ -25845,25 +25845,25 @@
         <v>1.98</v>
       </c>
       <c r="AN120">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="AO120">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ120">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR120">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AS120">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AT120">
-        <v>2.57</v>
+        <v>2.87</v>
       </c>
       <c r="AU120">
         <v>7</v>
@@ -26051,25 +26051,25 @@
         <v>1.73</v>
       </c>
       <c r="AN121">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AO121">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AP121">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ121">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AR121">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AS121">
         <v>1.22</v>
       </c>
       <c r="AT121">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26257,25 +26257,25 @@
         <v>2.5</v>
       </c>
       <c r="AN122">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AO122">
+        <v>0.67</v>
+      </c>
+      <c r="AP122">
+        <v>1.77</v>
+      </c>
+      <c r="AQ122">
+        <v>1</v>
+      </c>
+      <c r="AR122">
+        <v>1.36</v>
+      </c>
+      <c r="AS122">
         <v>0.95</v>
       </c>
-      <c r="AP122">
-        <v>1.4</v>
-      </c>
-      <c r="AQ122">
-        <v>1.04</v>
-      </c>
-      <c r="AR122">
-        <v>1.29</v>
-      </c>
-      <c r="AS122">
-        <v>1.11</v>
-      </c>
       <c r="AT122">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AU122">
         <v>5</v>
@@ -26463,25 +26463,25 @@
         <v>1.5</v>
       </c>
       <c r="AN123">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="AO123">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AP123">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AQ123">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR123">
+        <v>1.36</v>
+      </c>
+      <c r="AS123">
         <v>1.22</v>
       </c>
-      <c r="AS123">
-        <v>1.29</v>
-      </c>
       <c r="AT123">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="AU123">
         <v>5</v>
@@ -26669,25 +26669,25 @@
         <v>1.11</v>
       </c>
       <c r="AN124">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AO124">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="AP124">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ124">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR124">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AS124">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AT124">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="AU124">
         <v>7</v>
@@ -26875,25 +26875,25 @@
         <v>1.47</v>
       </c>
       <c r="AN125">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AO125">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AP125">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AQ125">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR125">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AS125">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AT125">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AU125">
         <v>4</v>
@@ -27081,25 +27081,25 @@
         <v>5.25</v>
       </c>
       <c r="AN126">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="AO126">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AP126">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ126">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AR126">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="AS126">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AT126">
-        <v>3.26</v>
+        <v>3.52</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27287,25 +27287,25 @@
         <v>1.58</v>
       </c>
       <c r="AN127">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AO127">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AP127">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AQ127">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR127">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AS127">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AT127">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AU127">
         <v>2</v>
@@ -27493,22 +27493,22 @@
         <v>2.4</v>
       </c>
       <c r="AN128">
-        <v>1.14</v>
+        <v>1.67</v>
       </c>
       <c r="AO128">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ128">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR128">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AS128">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="AT128">
         <v>2.38</v>
@@ -27699,25 +27699,25 @@
         <v>1.41</v>
       </c>
       <c r="AN129">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="AO129">
+        <v>0.9</v>
+      </c>
+      <c r="AP129">
+        <v>0.83</v>
+      </c>
+      <c r="AQ129">
+        <v>1</v>
+      </c>
+      <c r="AR129">
+        <v>1.19</v>
+      </c>
+      <c r="AS129">
         <v>1.1</v>
       </c>
-      <c r="AP129">
-        <v>0.84</v>
-      </c>
-      <c r="AQ129">
-        <v>1.08</v>
-      </c>
-      <c r="AR129">
-        <v>1.11</v>
-      </c>
-      <c r="AS129">
-        <v>1.23</v>
-      </c>
       <c r="AT129">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AU129">
         <v>6</v>
@@ -27905,25 +27905,25 @@
         <v>1.73</v>
       </c>
       <c r="AN130">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AO130">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AP130">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ130">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR130">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AS130">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AT130">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="AU130">
         <v>4</v>
@@ -28111,25 +28111,25 @@
         <v>4.75</v>
       </c>
       <c r="AN131">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AO131">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AP131">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ131">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR131">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AS131">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AT131">
-        <v>3.33</v>
+        <v>3.52</v>
       </c>
       <c r="AU131">
         <v>7</v>
@@ -28317,25 +28317,25 @@
         <v>1.05</v>
       </c>
       <c r="AN132">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AO132">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AP132">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AQ132">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR132">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AS132">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AT132">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AU132">
         <v>3</v>
@@ -28523,25 +28523,25 @@
         <v>1.02</v>
       </c>
       <c r="AN133">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AO133">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AP133">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ133">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR133">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AS133">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AT133">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="AU133">
         <v>2</v>
@@ -28729,22 +28729,22 @@
         <v>1.52</v>
       </c>
       <c r="AN134">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AO134">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AP134">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ134">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR134">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AS134">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AT134">
         <v>2.43</v>
@@ -28935,25 +28935,25 @@
         <v>1.95</v>
       </c>
       <c r="AN135">
+        <v>1.27</v>
+      </c>
+      <c r="AO135">
         <v>1.18</v>
       </c>
-      <c r="AO135">
-        <v>1.41</v>
-      </c>
       <c r="AP135">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ135">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR135">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AS135">
         <v>1.15</v>
       </c>
       <c r="AT135">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AU135">
         <v>4</v>
@@ -29141,25 +29141,25 @@
         <v>7.25</v>
       </c>
       <c r="AN136">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="AO136">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="AP136">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ136">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR136">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AS136">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AT136">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="AU136">
         <v>7</v>
@@ -29347,25 +29347,25 @@
         <v>1.6</v>
       </c>
       <c r="AN137">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AO137">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="AP137">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ137">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR137">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AS137">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="AT137">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AU137">
         <v>2</v>
@@ -29553,25 +29553,25 @@
         <v>1.04</v>
       </c>
       <c r="AN138">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AO138">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="AP138">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AQ138">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR138">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AS138">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AT138">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="AU138">
         <v>6</v>
@@ -29759,25 +29759,25 @@
         <v>3.7</v>
       </c>
       <c r="AN139">
-        <v>2</v>
+        <v>2.82</v>
       </c>
       <c r="AO139">
-        <v>1.59</v>
+        <v>1.2</v>
       </c>
       <c r="AP139">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ139">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR139">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AS139">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AT139">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AU139">
         <v>13</v>
@@ -29965,25 +29965,25 @@
         <v>1.78</v>
       </c>
       <c r="AN140">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AO140">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AP140">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AQ140">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AR140">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AS140">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AT140">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AU140">
         <v>8</v>
@@ -30171,25 +30171,25 @@
         <v>1.8</v>
       </c>
       <c r="AN141">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AO141">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AP141">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ141">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR141">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="AS141">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AT141">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="AU141">
         <v>6</v>
@@ -30377,25 +30377,25 @@
         <v>1.28</v>
       </c>
       <c r="AN142">
+        <v>1.08</v>
+      </c>
+      <c r="AO142">
         <v>1.09</v>
       </c>
-      <c r="AO142">
-        <v>1.26</v>
-      </c>
       <c r="AP142">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AQ142">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AR142">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AS142">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AT142">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="AU142">
         <v>3</v>
@@ -30583,25 +30583,25 @@
         <v>1.44</v>
       </c>
       <c r="AN143">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AO143">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AP143">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AQ143">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AR143">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AS143">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AT143">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="AU143">
         <v>7</v>
@@ -30789,25 +30789,25 @@
         <v>1.13</v>
       </c>
       <c r="AN144">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AO144">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AP144">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AQ144">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR144">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AS144">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AT144">
-        <v>3.21</v>
+        <v>3.04</v>
       </c>
       <c r="AU144">
         <v>8</v>
@@ -30995,25 +30995,25 @@
         <v>1.98</v>
       </c>
       <c r="AN145">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AO145">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP145">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ145">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AR145">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AS145">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AT145">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AU145">
         <v>5</v>
@@ -31201,25 +31201,25 @@
         <v>1.41</v>
       </c>
       <c r="AN146">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AO146">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AP146">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AQ146">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="AR146">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AS146">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="AT146">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AU146">
         <v>4</v>
@@ -31407,25 +31407,25 @@
         <v>1.85</v>
       </c>
       <c r="AN147">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AO147">
-        <v>1.46</v>
+        <v>1.09</v>
       </c>
       <c r="AP147">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AQ147">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR147">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AS147">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AT147">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="AU147">
         <v>6</v>
@@ -31613,25 +31613,25 @@
         <v>1.55</v>
       </c>
       <c r="AN148">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="AO148">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AP148">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AQ148">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR148">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AS148">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AT148">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AU148">
         <v>5</v>
@@ -31819,25 +31819,25 @@
         <v>5.25</v>
       </c>
       <c r="AN149">
-        <v>2.08</v>
+        <v>2.83</v>
       </c>
       <c r="AO149">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AP149">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AQ149">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR149">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="AS149">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="AT149">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="AU149">
         <v>10</v>
@@ -32025,25 +32025,25 @@
         <v>1.03</v>
       </c>
       <c r="AN150">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AO150">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AP150">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AQ150">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AR150">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AS150">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AT150">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="AU150">
         <v>2</v>
@@ -32231,25 +32231,25 @@
         <v>7</v>
       </c>
       <c r="AN151">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="AO151">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AP151">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ151">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR151">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="AS151">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AT151">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="AU151">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="283">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -610,6 +610,15 @@
     <t>['18', '45+1', '55', '59', '71', '81']</t>
   </si>
   <si>
+    <t>['23', '35', '84']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['9', '56', '60']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -823,9 +832,6 @@
     <t>['40', '81', '90+6', '90+8']</t>
   </si>
   <si>
-    <t>['54']</t>
-  </si>
-  <si>
     <t>['5', '53', '90+3']</t>
   </si>
   <si>
@@ -848,6 +854,15 @@
   </si>
   <si>
     <t>['1', '29', '90+4']</t>
+  </si>
+  <si>
+    <t>['29', '52']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['32', '59', '89']</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1749,10 +1764,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1877,7 +1892,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2367,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ6">
         <v>0.6899999999999999</v>
@@ -2495,7 +2510,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2576,7 +2591,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2907,7 +2922,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -2988,7 +3003,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3191,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ10">
         <v>0.92</v>
@@ -3319,7 +3334,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3525,7 +3540,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3731,7 +3746,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -3809,10 +3824,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ13">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4018,7 +4033,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR14">
         <v>2.04</v>
@@ -4143,7 +4158,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4430,7 +4445,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR16">
         <v>2.02</v>
@@ -4555,7 +4570,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4839,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ18">
         <v>0.92</v>
@@ -5173,7 +5188,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5251,7 +5266,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ20">
         <v>1.08</v>
@@ -5379,7 +5394,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5585,7 +5600,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5666,7 +5681,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR22">
         <v>1.66</v>
@@ -5869,7 +5884,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ23">
         <v>1.33</v>
@@ -5997,7 +6012,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6078,7 +6093,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR24">
         <v>1.14</v>
@@ -6203,7 +6218,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6281,7 +6296,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ25">
         <v>1.08</v>
@@ -6693,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ27">
         <v>0.92</v>
@@ -6902,7 +6917,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ28">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR28">
         <v>0.85</v>
@@ -7233,7 +7248,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7645,7 +7660,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7726,7 +7741,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ32">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR32">
         <v>1.31</v>
@@ -8057,7 +8072,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8138,7 +8153,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR34">
         <v>1.25</v>
@@ -8263,7 +8278,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8341,10 +8356,10 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ35">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR35">
         <v>1.32</v>
@@ -8469,7 +8484,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8547,7 +8562,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ36">
         <v>1.08</v>
@@ -8675,7 +8690,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8753,10 +8768,10 @@
         <v>3</v>
       </c>
       <c r="AP37">
+        <v>1.07</v>
+      </c>
+      <c r="AQ37">
         <v>1.15</v>
-      </c>
-      <c r="AQ37">
-        <v>1</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -8881,7 +8896,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9293,7 +9308,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9374,7 +9389,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ40">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR40">
         <v>0.9399999999999999</v>
@@ -9499,7 +9514,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9705,7 +9720,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9783,7 +9798,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ42">
         <v>0.6899999999999999</v>
@@ -9911,7 +9926,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10117,7 +10132,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10404,7 +10419,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ45">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR45">
         <v>1.85</v>
@@ -10529,7 +10544,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10607,10 +10622,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR46">
         <v>2.16</v>
@@ -10735,7 +10750,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11147,7 +11162,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11225,7 +11240,7 @@
         <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ49">
         <v>1</v>
@@ -11434,7 +11449,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11637,7 +11652,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ51">
         <v>1.33</v>
@@ -11765,7 +11780,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11843,10 +11858,10 @@
         <v>0.8</v>
       </c>
       <c r="AP52">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ52">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -11971,7 +11986,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12258,7 +12273,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ54">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR54">
         <v>1.17</v>
@@ -12589,7 +12604,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12667,7 +12682,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ56">
         <v>2.46</v>
@@ -12795,7 +12810,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -13001,7 +13016,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13413,7 +13428,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13494,7 +13509,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ60">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR60">
         <v>1.06</v>
@@ -13619,7 +13634,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13903,7 +13918,7 @@
         <v>1.25</v>
       </c>
       <c r="AP62">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14031,7 +14046,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14237,7 +14252,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14524,7 +14539,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR65">
         <v>1.13</v>
@@ -14649,7 +14664,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14727,7 +14742,7 @@
         <v>1.17</v>
       </c>
       <c r="AP66">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ66">
         <v>0.6899999999999999</v>
@@ -14855,7 +14870,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -14936,7 +14951,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ67">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR67">
         <v>1.3</v>
@@ -15142,7 +15157,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR68">
         <v>1.22</v>
@@ -15267,7 +15282,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15473,7 +15488,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15551,10 +15566,10 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ70">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR70">
         <v>1.19</v>
@@ -15679,7 +15694,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15885,7 +15900,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -15963,7 +15978,7 @@
         <v>3</v>
       </c>
       <c r="AP72">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ72">
         <v>2.46</v>
@@ -16503,7 +16518,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16790,7 +16805,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ76">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR76">
         <v>1.75</v>
@@ -16915,7 +16930,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16996,7 +17011,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR77">
         <v>1.13</v>
@@ -17121,7 +17136,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17199,7 +17214,7 @@
         <v>0.4</v>
       </c>
       <c r="AP78">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ78">
         <v>1.08</v>
@@ -17327,7 +17342,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17533,7 +17548,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17614,7 +17629,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ80">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR80">
         <v>1.33</v>
@@ -17817,10 +17832,10 @@
         <v>0.5</v>
       </c>
       <c r="AP81">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR81">
         <v>2.21</v>
@@ -18151,7 +18166,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18229,7 +18244,7 @@
         <v>0.83</v>
       </c>
       <c r="AP83">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18357,7 +18372,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18435,7 +18450,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ84">
         <v>1.08</v>
@@ -18563,7 +18578,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18769,7 +18784,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18850,7 +18865,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR86">
         <v>1.56</v>
@@ -19259,7 +19274,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ88">
         <v>1</v>
@@ -19387,7 +19402,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19880,7 +19895,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ91">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR91">
         <v>1.37</v>
@@ -20083,7 +20098,7 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ92">
         <v>1.08</v>
@@ -20623,7 +20638,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20829,7 +20844,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21035,7 +21050,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21116,7 +21131,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR97">
         <v>1.38</v>
@@ -21241,7 +21256,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21319,10 +21334,10 @@
         <v>1.43</v>
       </c>
       <c r="AP98">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ98">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR98">
         <v>1.21</v>
@@ -21525,7 +21540,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ99">
         <v>0.92</v>
@@ -21653,7 +21668,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21731,7 +21746,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ100">
         <v>0.6899999999999999</v>
@@ -21859,7 +21874,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22271,7 +22286,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22764,7 +22779,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ105">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR105">
         <v>1.69</v>
@@ -22889,7 +22904,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23173,7 +23188,7 @@
         <v>1.5</v>
       </c>
       <c r="AP107">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23301,7 +23316,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23379,10 +23394,10 @@
         <v>0.38</v>
       </c>
       <c r="AP108">
+        <v>1.07</v>
+      </c>
+      <c r="AQ108">
         <v>1.15</v>
-      </c>
-      <c r="AQ108">
-        <v>1</v>
       </c>
       <c r="AR108">
         <v>1.38</v>
@@ -23585,10 +23600,10 @@
         <v>1.71</v>
       </c>
       <c r="AP109">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR109">
         <v>1.35</v>
@@ -23713,7 +23728,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23794,7 +23809,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ110">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR110">
         <v>1.25</v>
@@ -24125,7 +24140,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24409,10 +24424,10 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ113">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR113">
         <v>2.24</v>
@@ -24743,7 +24758,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24821,7 +24836,7 @@
         <v>1.25</v>
       </c>
       <c r="AP115">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ115">
         <v>1.33</v>
@@ -24949,7 +24964,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25236,7 +25251,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ117">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR117">
         <v>1.33</v>
@@ -26057,7 +26072,7 @@
         <v>1.11</v>
       </c>
       <c r="AP121">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ121">
         <v>1.08</v>
@@ -26185,7 +26200,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26266,7 +26281,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR122">
         <v>1.36</v>
@@ -26391,7 +26406,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26469,10 +26484,10 @@
         <v>1.44</v>
       </c>
       <c r="AP123">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ123">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR123">
         <v>1.36</v>
@@ -26597,7 +26612,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26881,10 +26896,10 @@
         <v>1.33</v>
       </c>
       <c r="AP125">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ125">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR125">
         <v>1.17</v>
@@ -27087,7 +27102,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ126">
         <v>1.08</v>
@@ -27215,7 +27230,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27421,7 +27436,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27499,10 +27514,10 @@
         <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR128">
         <v>1.42</v>
@@ -27627,7 +27642,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -27911,7 +27926,7 @@
         <v>1.2</v>
       </c>
       <c r="AP130">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -28117,10 +28132,10 @@
         <v>1.6</v>
       </c>
       <c r="AP131">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ131">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR131">
         <v>2.28</v>
@@ -28323,7 +28338,7 @@
         <v>1.2</v>
       </c>
       <c r="AP132">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ132">
         <v>1.33</v>
@@ -28451,7 +28466,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28738,7 +28753,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ134">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR134">
         <v>1.22</v>
@@ -28863,7 +28878,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29069,7 +29084,7 @@
         <v>187</v>
       </c>
       <c r="P136" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="Q136">
         <v>1.37</v>
@@ -29150,7 +29165,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ136">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR136">
         <v>2.05</v>
@@ -29481,7 +29496,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29559,7 +29574,7 @@
         <v>2.55</v>
       </c>
       <c r="AP138">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ138">
         <v>2.46</v>
@@ -29768,7 +29783,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ139">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR139">
         <v>2</v>
@@ -29893,7 +29908,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30099,7 +30114,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30305,7 +30320,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30511,7 +30526,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30717,7 +30732,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30923,7 +30938,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31004,7 +31019,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ145">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR145">
         <v>1.26</v>
@@ -31129,7 +31144,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31207,7 +31222,7 @@
         <v>0.75</v>
       </c>
       <c r="AP146">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ146">
         <v>0.92</v>
@@ -31416,7 +31431,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ147">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR147">
         <v>1.38</v>
@@ -31619,10 +31634,10 @@
         <v>1.58</v>
       </c>
       <c r="AP148">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ148">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR148">
         <v>1.42</v>
@@ -31828,7 +31843,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ149">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR149">
         <v>2.11</v>
@@ -31953,7 +31968,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32031,7 +32046,7 @@
         <v>2.42</v>
       </c>
       <c r="AP150">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ150">
         <v>2.46</v>
@@ -32237,7 +32252,7 @@
         <v>1.09</v>
       </c>
       <c r="AP151">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ151">
         <v>1</v>
@@ -32316,6 +32331,830 @@
       </c>
       <c r="BP151">
         <v>1.98</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7480288</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F152">
+        <v>26</v>
+      </c>
+      <c r="G152" t="s">
+        <v>74</v>
+      </c>
+      <c r="H152" t="s">
+        <v>72</v>
+      </c>
+      <c r="I152">
+        <v>2</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>2</v>
+      </c>
+      <c r="L152">
+        <v>3</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>3</v>
+      </c>
+      <c r="O152" t="s">
+        <v>198</v>
+      </c>
+      <c r="P152" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q152">
+        <v>1.53</v>
+      </c>
+      <c r="R152">
+        <v>3.1</v>
+      </c>
+      <c r="S152">
+        <v>10</v>
+      </c>
+      <c r="T152">
+        <v>1.2</v>
+      </c>
+      <c r="U152">
+        <v>4.33</v>
+      </c>
+      <c r="V152">
+        <v>2</v>
+      </c>
+      <c r="W152">
+        <v>1.73</v>
+      </c>
+      <c r="X152">
+        <v>4</v>
+      </c>
+      <c r="Y152">
+        <v>1.22</v>
+      </c>
+      <c r="Z152">
+        <v>1.17</v>
+      </c>
+      <c r="AA152">
+        <v>7.4</v>
+      </c>
+      <c r="AB152">
+        <v>12</v>
+      </c>
+      <c r="AC152">
+        <v>0</v>
+      </c>
+      <c r="AD152">
+        <v>0</v>
+      </c>
+      <c r="AE152">
+        <v>1.09</v>
+      </c>
+      <c r="AF152">
+        <v>7</v>
+      </c>
+      <c r="AG152">
+        <v>1.37</v>
+      </c>
+      <c r="AH152">
+        <v>2.94</v>
+      </c>
+      <c r="AI152">
+        <v>1.95</v>
+      </c>
+      <c r="AJ152">
+        <v>1.8</v>
+      </c>
+      <c r="AK152">
+        <v>1.03</v>
+      </c>
+      <c r="AL152">
+        <v>1.11</v>
+      </c>
+      <c r="AM152">
+        <v>4.8</v>
+      </c>
+      <c r="AN152">
+        <v>2.83</v>
+      </c>
+      <c r="AO152">
+        <v>1.46</v>
+      </c>
+      <c r="AP152">
+        <v>2.85</v>
+      </c>
+      <c r="AQ152">
+        <v>1.36</v>
+      </c>
+      <c r="AR152">
+        <v>2.26</v>
+      </c>
+      <c r="AS152">
+        <v>1.28</v>
+      </c>
+      <c r="AT152">
+        <v>3.54</v>
+      </c>
+      <c r="AU152">
+        <v>8</v>
+      </c>
+      <c r="AV152">
+        <v>4</v>
+      </c>
+      <c r="AW152">
+        <v>14</v>
+      </c>
+      <c r="AX152">
+        <v>4</v>
+      </c>
+      <c r="AY152">
+        <v>22</v>
+      </c>
+      <c r="AZ152">
+        <v>8</v>
+      </c>
+      <c r="BA152">
+        <v>15</v>
+      </c>
+      <c r="BB152">
+        <v>0</v>
+      </c>
+      <c r="BC152">
+        <v>15</v>
+      </c>
+      <c r="BD152">
+        <v>1.08</v>
+      </c>
+      <c r="BE152">
+        <v>13</v>
+      </c>
+      <c r="BF152">
+        <v>7.5</v>
+      </c>
+      <c r="BG152">
+        <v>1.15</v>
+      </c>
+      <c r="BH152">
+        <v>4.6</v>
+      </c>
+      <c r="BI152">
+        <v>1.26</v>
+      </c>
+      <c r="BJ152">
+        <v>3.4</v>
+      </c>
+      <c r="BK152">
+        <v>1.44</v>
+      </c>
+      <c r="BL152">
+        <v>2.55</v>
+      </c>
+      <c r="BM152">
+        <v>1.67</v>
+      </c>
+      <c r="BN152">
+        <v>2.04</v>
+      </c>
+      <c r="BO152">
+        <v>2</v>
+      </c>
+      <c r="BP152">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7480289</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F153">
+        <v>26</v>
+      </c>
+      <c r="G153" t="s">
+        <v>78</v>
+      </c>
+      <c r="H153" t="s">
+        <v>80</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>1</v>
+      </c>
+      <c r="K153">
+        <v>1</v>
+      </c>
+      <c r="L153">
+        <v>1</v>
+      </c>
+      <c r="M153">
+        <v>2</v>
+      </c>
+      <c r="N153">
+        <v>3</v>
+      </c>
+      <c r="O153" t="s">
+        <v>199</v>
+      </c>
+      <c r="P153" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q153">
+        <v>3.2</v>
+      </c>
+      <c r="R153">
+        <v>2.25</v>
+      </c>
+      <c r="S153">
+        <v>3.1</v>
+      </c>
+      <c r="T153">
+        <v>1.36</v>
+      </c>
+      <c r="U153">
+        <v>3</v>
+      </c>
+      <c r="V153">
+        <v>2.63</v>
+      </c>
+      <c r="W153">
+        <v>1.44</v>
+      </c>
+      <c r="X153">
+        <v>7</v>
+      </c>
+      <c r="Y153">
+        <v>1.1</v>
+      </c>
+      <c r="Z153">
+        <v>2.79</v>
+      </c>
+      <c r="AA153">
+        <v>3.29</v>
+      </c>
+      <c r="AB153">
+        <v>2.46</v>
+      </c>
+      <c r="AC153">
+        <v>1.05</v>
+      </c>
+      <c r="AD153">
+        <v>11</v>
+      </c>
+      <c r="AE153">
+        <v>1.25</v>
+      </c>
+      <c r="AF153">
+        <v>3.75</v>
+      </c>
+      <c r="AG153">
+        <v>1.79</v>
+      </c>
+      <c r="AH153">
+        <v>1.95</v>
+      </c>
+      <c r="AI153">
+        <v>1.62</v>
+      </c>
+      <c r="AJ153">
+        <v>2.2</v>
+      </c>
+      <c r="AK153">
+        <v>1.5</v>
+      </c>
+      <c r="AL153">
+        <v>1.29</v>
+      </c>
+      <c r="AM153">
+        <v>1.46</v>
+      </c>
+      <c r="AN153">
+        <v>1.15</v>
+      </c>
+      <c r="AO153">
+        <v>1</v>
+      </c>
+      <c r="AP153">
+        <v>1.07</v>
+      </c>
+      <c r="AQ153">
+        <v>1.15</v>
+      </c>
+      <c r="AR153">
+        <v>1.3</v>
+      </c>
+      <c r="AS153">
+        <v>1.18</v>
+      </c>
+      <c r="AT153">
+        <v>2.48</v>
+      </c>
+      <c r="AU153">
+        <v>6</v>
+      </c>
+      <c r="AV153">
+        <v>7</v>
+      </c>
+      <c r="AW153">
+        <v>19</v>
+      </c>
+      <c r="AX153">
+        <v>7</v>
+      </c>
+      <c r="AY153">
+        <v>25</v>
+      </c>
+      <c r="AZ153">
+        <v>14</v>
+      </c>
+      <c r="BA153">
+        <v>8</v>
+      </c>
+      <c r="BB153">
+        <v>7</v>
+      </c>
+      <c r="BC153">
+        <v>15</v>
+      </c>
+      <c r="BD153">
+        <v>1.9</v>
+      </c>
+      <c r="BE153">
+        <v>6.75</v>
+      </c>
+      <c r="BF153">
+        <v>2.07</v>
+      </c>
+      <c r="BG153">
+        <v>1.18</v>
+      </c>
+      <c r="BH153">
+        <v>4.1</v>
+      </c>
+      <c r="BI153">
+        <v>1.3</v>
+      </c>
+      <c r="BJ153">
+        <v>3.05</v>
+      </c>
+      <c r="BK153">
+        <v>1.53</v>
+      </c>
+      <c r="BL153">
+        <v>2.32</v>
+      </c>
+      <c r="BM153">
+        <v>1.84</v>
+      </c>
+      <c r="BN153">
+        <v>1.84</v>
+      </c>
+      <c r="BO153">
+        <v>2.3</v>
+      </c>
+      <c r="BP153">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7480291</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F154">
+        <v>26</v>
+      </c>
+      <c r="G154" t="s">
+        <v>81</v>
+      </c>
+      <c r="H154" t="s">
+        <v>75</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>1</v>
+      </c>
+      <c r="L154">
+        <v>3</v>
+      </c>
+      <c r="M154">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>4</v>
+      </c>
+      <c r="O154" t="s">
+        <v>200</v>
+      </c>
+      <c r="P154" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q154">
+        <v>2.5</v>
+      </c>
+      <c r="R154">
+        <v>2.2</v>
+      </c>
+      <c r="S154">
+        <v>4.5</v>
+      </c>
+      <c r="T154">
+        <v>1.4</v>
+      </c>
+      <c r="U154">
+        <v>2.75</v>
+      </c>
+      <c r="V154">
+        <v>2.75</v>
+      </c>
+      <c r="W154">
+        <v>1.4</v>
+      </c>
+      <c r="X154">
+        <v>8</v>
+      </c>
+      <c r="Y154">
+        <v>1.08</v>
+      </c>
+      <c r="Z154">
+        <v>1.93</v>
+      </c>
+      <c r="AA154">
+        <v>3.18</v>
+      </c>
+      <c r="AB154">
+        <v>4.2</v>
+      </c>
+      <c r="AC154">
+        <v>1.06</v>
+      </c>
+      <c r="AD154">
+        <v>9.5</v>
+      </c>
+      <c r="AE154">
+        <v>1.3</v>
+      </c>
+      <c r="AF154">
+        <v>3.4</v>
+      </c>
+      <c r="AG154">
+        <v>1.87</v>
+      </c>
+      <c r="AH154">
+        <v>1.87</v>
+      </c>
+      <c r="AI154">
+        <v>1.8</v>
+      </c>
+      <c r="AJ154">
+        <v>1.95</v>
+      </c>
+      <c r="AK154">
+        <v>1.23</v>
+      </c>
+      <c r="AL154">
+        <v>1.29</v>
+      </c>
+      <c r="AM154">
+        <v>1.87</v>
+      </c>
+      <c r="AN154">
+        <v>1.58</v>
+      </c>
+      <c r="AO154">
+        <v>0.85</v>
+      </c>
+      <c r="AP154">
+        <v>1.69</v>
+      </c>
+      <c r="AQ154">
+        <v>0.79</v>
+      </c>
+      <c r="AR154">
+        <v>1.41</v>
+      </c>
+      <c r="AS154">
+        <v>0.99</v>
+      </c>
+      <c r="AT154">
+        <v>2.4</v>
+      </c>
+      <c r="AU154">
+        <v>5</v>
+      </c>
+      <c r="AV154">
+        <v>5</v>
+      </c>
+      <c r="AW154">
+        <v>8</v>
+      </c>
+      <c r="AX154">
+        <v>7</v>
+      </c>
+      <c r="AY154">
+        <v>13</v>
+      </c>
+      <c r="AZ154">
+        <v>12</v>
+      </c>
+      <c r="BA154">
+        <v>7</v>
+      </c>
+      <c r="BB154">
+        <v>5</v>
+      </c>
+      <c r="BC154">
+        <v>12</v>
+      </c>
+      <c r="BD154">
+        <v>1.45</v>
+      </c>
+      <c r="BE154">
+        <v>7</v>
+      </c>
+      <c r="BF154">
+        <v>3.05</v>
+      </c>
+      <c r="BG154">
+        <v>1.22</v>
+      </c>
+      <c r="BH154">
+        <v>3.65</v>
+      </c>
+      <c r="BI154">
+        <v>1.41</v>
+      </c>
+      <c r="BJ154">
+        <v>2.65</v>
+      </c>
+      <c r="BK154">
+        <v>1.66</v>
+      </c>
+      <c r="BL154">
+        <v>2.07</v>
+      </c>
+      <c r="BM154">
+        <v>2.02</v>
+      </c>
+      <c r="BN154">
+        <v>1.7</v>
+      </c>
+      <c r="BO154">
+        <v>2.55</v>
+      </c>
+      <c r="BP154">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7480292</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F155">
+        <v>26</v>
+      </c>
+      <c r="G155" t="s">
+        <v>71</v>
+      </c>
+      <c r="H155" t="s">
+        <v>77</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>1</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>3</v>
+      </c>
+      <c r="N155">
+        <v>3</v>
+      </c>
+      <c r="O155" t="s">
+        <v>82</v>
+      </c>
+      <c r="P155" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q155">
+        <v>2.75</v>
+      </c>
+      <c r="R155">
+        <v>2.1</v>
+      </c>
+      <c r="S155">
+        <v>4</v>
+      </c>
+      <c r="T155">
+        <v>1.44</v>
+      </c>
+      <c r="U155">
+        <v>2.63</v>
+      </c>
+      <c r="V155">
+        <v>3.25</v>
+      </c>
+      <c r="W155">
+        <v>1.33</v>
+      </c>
+      <c r="X155">
+        <v>9</v>
+      </c>
+      <c r="Y155">
+        <v>1.07</v>
+      </c>
+      <c r="Z155">
+        <v>2.01</v>
+      </c>
+      <c r="AA155">
+        <v>3.4</v>
+      </c>
+      <c r="AB155">
+        <v>3.6</v>
+      </c>
+      <c r="AC155">
+        <v>1.06</v>
+      </c>
+      <c r="AD155">
+        <v>9.5</v>
+      </c>
+      <c r="AE155">
+        <v>1.33</v>
+      </c>
+      <c r="AF155">
+        <v>3.25</v>
+      </c>
+      <c r="AG155">
+        <v>1.8</v>
+      </c>
+      <c r="AH155">
+        <v>1.94</v>
+      </c>
+      <c r="AI155">
+        <v>1.8</v>
+      </c>
+      <c r="AJ155">
+        <v>1.95</v>
+      </c>
+      <c r="AK155">
+        <v>1.3</v>
+      </c>
+      <c r="AL155">
+        <v>1.28</v>
+      </c>
+      <c r="AM155">
+        <v>1.72</v>
+      </c>
+      <c r="AN155">
+        <v>1.5</v>
+      </c>
+      <c r="AO155">
+        <v>1</v>
+      </c>
+      <c r="AP155">
+        <v>1.38</v>
+      </c>
+      <c r="AQ155">
+        <v>1.15</v>
+      </c>
+      <c r="AR155">
+        <v>1.1</v>
+      </c>
+      <c r="AS155">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT155">
+        <v>2.04</v>
+      </c>
+      <c r="AU155">
+        <v>3</v>
+      </c>
+      <c r="AV155">
+        <v>9</v>
+      </c>
+      <c r="AW155">
+        <v>17</v>
+      </c>
+      <c r="AX155">
+        <v>5</v>
+      </c>
+      <c r="AY155">
+        <v>20</v>
+      </c>
+      <c r="AZ155">
+        <v>14</v>
+      </c>
+      <c r="BA155">
+        <v>6</v>
+      </c>
+      <c r="BB155">
+        <v>3</v>
+      </c>
+      <c r="BC155">
+        <v>9</v>
+      </c>
+      <c r="BD155">
+        <v>1.5</v>
+      </c>
+      <c r="BE155">
+        <v>7</v>
+      </c>
+      <c r="BF155">
+        <v>2.8</v>
+      </c>
+      <c r="BG155">
+        <v>1.17</v>
+      </c>
+      <c r="BH155">
+        <v>4.35</v>
+      </c>
+      <c r="BI155">
+        <v>1.3</v>
+      </c>
+      <c r="BJ155">
+        <v>3.15</v>
+      </c>
+      <c r="BK155">
+        <v>1.5</v>
+      </c>
+      <c r="BL155">
+        <v>2.4</v>
+      </c>
+      <c r="BM155">
+        <v>1.77</v>
+      </c>
+      <c r="BN155">
+        <v>1.92</v>
+      </c>
+      <c r="BO155">
+        <v>2.17</v>
+      </c>
+      <c r="BP155">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="285">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -619,6 +619,9 @@
     <t>['9', '56', '60']</t>
   </si>
   <si>
+    <t>['49']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -863,6 +866,9 @@
   </si>
   <si>
     <t>['32', '59', '89']</t>
+  </si>
+  <si>
+    <t>['20', '61', '73']</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1558,10 +1564,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1892,7 +1898,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2176,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5">
         <v>1.08</v>
@@ -2510,7 +2516,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2922,7 +2928,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3334,7 +3340,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3540,7 +3546,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3746,7 +3752,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -4158,7 +4164,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4570,7 +4576,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4648,7 +4654,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ17">
         <v>2.46</v>
@@ -5188,7 +5194,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5394,7 +5400,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5600,7 +5606,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5887,7 +5893,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR23">
         <v>3.1</v>
@@ -6012,7 +6018,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6090,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ24">
         <v>1.36</v>
@@ -6218,7 +6224,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -7248,7 +7254,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7326,7 +7332,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ30">
         <v>0.6899999999999999</v>
@@ -7535,7 +7541,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR31">
         <v>1.46</v>
@@ -7660,7 +7666,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7944,7 +7950,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ33">
         <v>0.92</v>
@@ -8072,7 +8078,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8150,7 +8156,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ34">
         <v>1.15</v>
@@ -8278,7 +8284,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8484,7 +8490,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8690,7 +8696,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8896,7 +8902,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9308,7 +9314,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9386,7 +9392,7 @@
         <v>1.67</v>
       </c>
       <c r="AP40">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ40">
         <v>1.36</v>
@@ -9514,7 +9520,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9720,7 +9726,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9926,7 +9932,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10132,7 +10138,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10544,7 +10550,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10750,7 +10756,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11034,7 +11040,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ48">
         <v>1.08</v>
@@ -11162,7 +11168,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11655,7 +11661,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ51">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR51">
         <v>1.31</v>
@@ -11780,7 +11786,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11986,7 +11992,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12604,7 +12610,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12810,7 +12816,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -13016,7 +13022,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13094,7 +13100,7 @@
         <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ58">
         <v>0.6899999999999999</v>
@@ -13428,7 +13434,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13506,7 +13512,7 @@
         <v>1.17</v>
       </c>
       <c r="AP60">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ60">
         <v>0.79</v>
@@ -13634,7 +13640,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14046,7 +14052,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14127,7 +14133,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ63">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR63">
         <v>1.25</v>
@@ -14252,7 +14258,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14536,7 +14542,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ65">
         <v>1.15</v>
@@ -14664,7 +14670,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14870,7 +14876,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15282,7 +15288,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15488,7 +15494,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15694,7 +15700,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15900,7 +15906,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16518,7 +16524,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16930,7 +16936,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17008,7 +17014,7 @@
         <v>2.5</v>
       </c>
       <c r="AP77">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ77">
         <v>1.15</v>
@@ -17136,7 +17142,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17342,7 +17348,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17420,7 +17426,7 @@
         <v>3</v>
       </c>
       <c r="AP79">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ79">
         <v>2.46</v>
@@ -17548,7 +17554,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18166,7 +18172,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18372,7 +18378,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18578,7 +18584,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18659,7 +18665,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ85">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18784,7 +18790,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18862,7 +18868,7 @@
         <v>1.83</v>
       </c>
       <c r="AP86">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ86">
         <v>1.15</v>
@@ -19402,7 +19408,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19686,7 +19692,7 @@
         <v>1.29</v>
       </c>
       <c r="AP90">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -20510,7 +20516,7 @@
         <v>0.86</v>
       </c>
       <c r="AP94">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20638,7 +20644,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20719,7 +20725,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ95">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR95">
         <v>1.29</v>
@@ -20844,7 +20850,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21050,7 +21056,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21256,7 +21262,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21668,7 +21674,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21874,7 +21880,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22286,7 +22292,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22776,7 +22782,7 @@
         <v>0.89</v>
       </c>
       <c r="AP105">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ105">
         <v>0.79</v>
@@ -22904,7 +22910,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -22982,7 +22988,7 @@
         <v>0.89</v>
       </c>
       <c r="AP106">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ106">
         <v>1.08</v>
@@ -23316,7 +23322,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23728,7 +23734,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24012,10 +24018,10 @@
         <v>1.43</v>
       </c>
       <c r="AP111">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ111">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR111">
         <v>1.24</v>
@@ -24140,7 +24146,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24758,7 +24764,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24839,7 +24845,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR115">
         <v>1.18</v>
@@ -24964,7 +24970,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25042,7 +25048,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ116">
         <v>1</v>
@@ -25866,7 +25872,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -26200,7 +26206,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26406,7 +26412,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26612,7 +26618,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26693,7 +26699,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ124">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR124">
         <v>1.42</v>
@@ -27230,7 +27236,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27436,7 +27442,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27642,7 +27648,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -28341,7 +28347,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ132">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28466,7 +28472,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28750,7 +28756,7 @@
         <v>1.45</v>
       </c>
       <c r="AP134">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ134">
         <v>1.36</v>
@@ -28878,7 +28884,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29496,7 +29502,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29908,7 +29914,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30114,7 +30120,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30192,7 +30198,7 @@
         <v>0.75</v>
       </c>
       <c r="AP141">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ141">
         <v>0.6899999999999999</v>
@@ -30320,7 +30326,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30526,7 +30532,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30732,7 +30738,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30813,7 +30819,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ144">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR144">
         <v>1.31</v>
@@ -30938,7 +30944,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31016,7 +31022,7 @@
         <v>0.67</v>
       </c>
       <c r="AP145">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ145">
         <v>0.79</v>
@@ -31144,7 +31150,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31968,7 +31974,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32586,7 +32592,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q153">
         <v>3.2</v>
@@ -32792,7 +32798,7 @@
         <v>200</v>
       </c>
       <c r="P154" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q154">
         <v>2.5</v>
@@ -32998,7 +33004,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q155">
         <v>2.75</v>
@@ -33155,6 +33161,418 @@
       </c>
       <c r="BP155">
         <v>1.6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7480290</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45704.375</v>
+      </c>
+      <c r="F156">
+        <v>26</v>
+      </c>
+      <c r="G156" t="s">
+        <v>70</v>
+      </c>
+      <c r="H156" t="s">
+        <v>76</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>1</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156">
+        <v>1</v>
+      </c>
+      <c r="M156">
+        <v>3</v>
+      </c>
+      <c r="N156">
+        <v>4</v>
+      </c>
+      <c r="O156" t="s">
+        <v>201</v>
+      </c>
+      <c r="P156" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q156">
+        <v>5</v>
+      </c>
+      <c r="R156">
+        <v>2.3</v>
+      </c>
+      <c r="S156">
+        <v>2.2</v>
+      </c>
+      <c r="T156">
+        <v>1.33</v>
+      </c>
+      <c r="U156">
+        <v>3.25</v>
+      </c>
+      <c r="V156">
+        <v>2.63</v>
+      </c>
+      <c r="W156">
+        <v>1.44</v>
+      </c>
+      <c r="X156">
+        <v>6.5</v>
+      </c>
+      <c r="Y156">
+        <v>1.11</v>
+      </c>
+      <c r="Z156">
+        <v>4.9</v>
+      </c>
+      <c r="AA156">
+        <v>3.98</v>
+      </c>
+      <c r="AB156">
+        <v>1.63</v>
+      </c>
+      <c r="AC156">
+        <v>1.03</v>
+      </c>
+      <c r="AD156">
+        <v>15</v>
+      </c>
+      <c r="AE156">
+        <v>1.22</v>
+      </c>
+      <c r="AF156">
+        <v>4.2</v>
+      </c>
+      <c r="AG156">
+        <v>1.8</v>
+      </c>
+      <c r="AH156">
+        <v>1.91</v>
+      </c>
+      <c r="AI156">
+        <v>1.75</v>
+      </c>
+      <c r="AJ156">
+        <v>2</v>
+      </c>
+      <c r="AK156">
+        <v>2.15</v>
+      </c>
+      <c r="AL156">
+        <v>1.24</v>
+      </c>
+      <c r="AM156">
+        <v>1.17</v>
+      </c>
+      <c r="AN156">
+        <v>1.5</v>
+      </c>
+      <c r="AO156">
+        <v>1.33</v>
+      </c>
+      <c r="AP156">
+        <v>1.38</v>
+      </c>
+      <c r="AQ156">
+        <v>1.46</v>
+      </c>
+      <c r="AR156">
+        <v>1.65</v>
+      </c>
+      <c r="AS156">
+        <v>1.83</v>
+      </c>
+      <c r="AT156">
+        <v>3.48</v>
+      </c>
+      <c r="AU156">
+        <v>11</v>
+      </c>
+      <c r="AV156">
+        <v>14</v>
+      </c>
+      <c r="AW156">
+        <v>10</v>
+      </c>
+      <c r="AX156">
+        <v>5</v>
+      </c>
+      <c r="AY156">
+        <v>25</v>
+      </c>
+      <c r="AZ156">
+        <v>22</v>
+      </c>
+      <c r="BA156">
+        <v>10</v>
+      </c>
+      <c r="BB156">
+        <v>7</v>
+      </c>
+      <c r="BC156">
+        <v>17</v>
+      </c>
+      <c r="BD156">
+        <v>3.2</v>
+      </c>
+      <c r="BE156">
+        <v>7.5</v>
+      </c>
+      <c r="BF156">
+        <v>1.41</v>
+      </c>
+      <c r="BG156">
+        <v>1.15</v>
+      </c>
+      <c r="BH156">
+        <v>4.6</v>
+      </c>
+      <c r="BI156">
+        <v>1.28</v>
+      </c>
+      <c r="BJ156">
+        <v>3.3</v>
+      </c>
+      <c r="BK156">
+        <v>1.47</v>
+      </c>
+      <c r="BL156">
+        <v>2.48</v>
+      </c>
+      <c r="BM156">
+        <v>1.74</v>
+      </c>
+      <c r="BN156">
+        <v>1.96</v>
+      </c>
+      <c r="BO156">
+        <v>2.08</v>
+      </c>
+      <c r="BP156">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7480293</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F157">
+        <v>26</v>
+      </c>
+      <c r="G157" t="s">
+        <v>73</v>
+      </c>
+      <c r="H157" t="s">
+        <v>79</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>0</v>
+      </c>
+      <c r="O157" t="s">
+        <v>82</v>
+      </c>
+      <c r="P157" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q157">
+        <v>3.75</v>
+      </c>
+      <c r="R157">
+        <v>2.1</v>
+      </c>
+      <c r="S157">
+        <v>3</v>
+      </c>
+      <c r="T157">
+        <v>1.4</v>
+      </c>
+      <c r="U157">
+        <v>2.75</v>
+      </c>
+      <c r="V157">
+        <v>3</v>
+      </c>
+      <c r="W157">
+        <v>1.36</v>
+      </c>
+      <c r="X157">
+        <v>9</v>
+      </c>
+      <c r="Y157">
+        <v>1.07</v>
+      </c>
+      <c r="Z157">
+        <v>3.07</v>
+      </c>
+      <c r="AA157">
+        <v>3.25</v>
+      </c>
+      <c r="AB157">
+        <v>2.3</v>
+      </c>
+      <c r="AC157">
+        <v>1.06</v>
+      </c>
+      <c r="AD157">
+        <v>9.5</v>
+      </c>
+      <c r="AE157">
+        <v>1.33</v>
+      </c>
+      <c r="AF157">
+        <v>3.25</v>
+      </c>
+      <c r="AG157">
+        <v>1.91</v>
+      </c>
+      <c r="AH157">
+        <v>1.83</v>
+      </c>
+      <c r="AI157">
+        <v>1.75</v>
+      </c>
+      <c r="AJ157">
+        <v>2</v>
+      </c>
+      <c r="AK157">
+        <v>1.6</v>
+      </c>
+      <c r="AL157">
+        <v>1.31</v>
+      </c>
+      <c r="AM157">
+        <v>1.37</v>
+      </c>
+      <c r="AN157">
+        <v>1.31</v>
+      </c>
+      <c r="AO157">
+        <v>1.08</v>
+      </c>
+      <c r="AP157">
+        <v>1.29</v>
+      </c>
+      <c r="AQ157">
+        <v>1.08</v>
+      </c>
+      <c r="AR157">
+        <v>1.3</v>
+      </c>
+      <c r="AS157">
+        <v>1.51</v>
+      </c>
+      <c r="AT157">
+        <v>2.81</v>
+      </c>
+      <c r="AU157">
+        <v>6</v>
+      </c>
+      <c r="AV157">
+        <v>2</v>
+      </c>
+      <c r="AW157">
+        <v>6</v>
+      </c>
+      <c r="AX157">
+        <v>5</v>
+      </c>
+      <c r="AY157">
+        <v>12</v>
+      </c>
+      <c r="AZ157">
+        <v>7</v>
+      </c>
+      <c r="BA157">
+        <v>4</v>
+      </c>
+      <c r="BB157">
+        <v>3</v>
+      </c>
+      <c r="BC157">
+        <v>7</v>
+      </c>
+      <c r="BD157">
+        <v>2.17</v>
+      </c>
+      <c r="BE157">
+        <v>6.75</v>
+      </c>
+      <c r="BF157">
+        <v>1.81</v>
+      </c>
+      <c r="BG157">
+        <v>1.19</v>
+      </c>
+      <c r="BH157">
+        <v>4.1</v>
+      </c>
+      <c r="BI157">
+        <v>1.33</v>
+      </c>
+      <c r="BJ157">
+        <v>2.95</v>
+      </c>
+      <c r="BK157">
+        <v>1.55</v>
+      </c>
+      <c r="BL157">
+        <v>2.28</v>
+      </c>
+      <c r="BM157">
+        <v>1.88</v>
+      </c>
+      <c r="BN157">
+        <v>1.81</v>
+      </c>
+      <c r="BO157">
+        <v>2.33</v>
+      </c>
+      <c r="BP157">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="289">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -622,6 +622,18 @@
     <t>['49']</t>
   </si>
   <si>
+    <t>['2', '45+4']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['31']</t>
+  </si>
+  <si>
+    <t>['18', '47', '49']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -862,13 +874,13 @@
     <t>['29', '52']</t>
   </si>
   <si>
-    <t>['90+1']</t>
-  </si>
-  <si>
     <t>['32', '59', '89']</t>
   </si>
   <si>
     <t>['20', '61', '73']</t>
+  </si>
+  <si>
+    <t>['51', '70']</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP157"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1898,7 +1910,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1976,10 +1988,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2391,7 +2403,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ6">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2516,7 +2528,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2800,10 +2812,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2928,7 +2940,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3006,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ9">
         <v>1.36</v>
@@ -3340,7 +3352,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3418,10 +3430,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ11">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3546,7 +3558,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3624,10 +3636,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ12">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3752,7 +3764,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -4036,7 +4048,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ14">
         <v>0.79</v>
@@ -4164,7 +4176,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4242,10 +4254,10 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR15">
         <v>0.53</v>
@@ -4448,7 +4460,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ16">
         <v>1.15</v>
@@ -4576,7 +4588,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4657,7 +4669,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ17">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR17">
         <v>1.07</v>
@@ -5066,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ19">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR19">
         <v>1.1</v>
@@ -5194,7 +5206,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5275,7 +5287,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ20">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR20">
         <v>1.56</v>
@@ -5400,7 +5412,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5481,7 +5493,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR21">
         <v>1.39</v>
@@ -5606,7 +5618,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5684,7 +5696,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ22">
         <v>1.15</v>
@@ -6018,7 +6030,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6224,7 +6236,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6508,10 +6520,10 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR26">
         <v>1.12</v>
@@ -6920,7 +6932,7 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ28">
         <v>0.79</v>
@@ -7126,10 +7138,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR29">
         <v>1.33</v>
@@ -7254,7 +7266,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7335,7 +7347,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ30">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR30">
         <v>0.76</v>
@@ -7538,7 +7550,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ31">
         <v>1.46</v>
@@ -7666,7 +7678,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7744,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ32">
         <v>0.79</v>
@@ -8078,7 +8090,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8284,7 +8296,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8490,7 +8502,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8571,7 +8583,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ36">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR36">
         <v>1.45</v>
@@ -8696,7 +8708,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8902,7 +8914,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -8983,7 +8995,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ38">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR38">
         <v>1.42</v>
@@ -9186,7 +9198,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ39">
         <v>1.08</v>
@@ -9314,7 +9326,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9520,7 +9532,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9598,10 +9610,10 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR41">
         <v>1.12</v>
@@ -9726,7 +9738,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9807,7 +9819,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ42">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR42">
         <v>1.64</v>
@@ -9932,7 +9944,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10010,10 +10022,10 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ43">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR43">
         <v>1.4</v>
@@ -10138,7 +10150,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10216,7 +10228,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ44">
         <v>0.92</v>
@@ -10422,7 +10434,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ45">
         <v>0.79</v>
@@ -10550,7 +10562,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10756,7 +10768,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10834,7 +10846,7 @@
         <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ47">
         <v>1.08</v>
@@ -11043,7 +11055,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ48">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR48">
         <v>1.61</v>
@@ -11168,7 +11180,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11249,7 +11261,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR49">
         <v>1.3</v>
@@ -11786,7 +11798,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11992,7 +12004,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12070,10 +12082,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ53">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR53">
         <v>1.34</v>
@@ -12276,7 +12288,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ54">
         <v>1.36</v>
@@ -12482,7 +12494,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ55">
         <v>0.92</v>
@@ -12610,7 +12622,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12691,7 +12703,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ56">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
@@ -12816,7 +12828,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -12894,10 +12906,10 @@
         <v>0.25</v>
       </c>
       <c r="AP57">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ57">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR57">
         <v>1.86</v>
@@ -13022,7 +13034,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13103,7 +13115,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ58">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR58">
         <v>1.54</v>
@@ -13306,7 +13318,7 @@
         <v>0.25</v>
       </c>
       <c r="AP59">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ59">
         <v>1.08</v>
@@ -13434,7 +13446,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13640,7 +13652,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13718,10 +13730,10 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR61">
         <v>1.15</v>
@@ -13927,7 +13939,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR62">
         <v>2.17</v>
@@ -14052,7 +14064,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14130,7 +14142,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ63">
         <v>1.46</v>
@@ -14258,7 +14270,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14670,7 +14682,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14751,7 +14763,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ66">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR66">
         <v>1.42</v>
@@ -14876,7 +14888,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -14954,7 +14966,7 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ67">
         <v>1.36</v>
@@ -15160,7 +15172,7 @@
         <v>0.6</v>
       </c>
       <c r="AP68">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ68">
         <v>1.15</v>
@@ -15288,7 +15300,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15366,10 +15378,10 @@
         <v>0.2</v>
       </c>
       <c r="AP69">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ69">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR69">
         <v>1.35</v>
@@ -15494,7 +15506,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15700,7 +15712,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15778,10 +15790,10 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR71">
         <v>1.32</v>
@@ -15906,7 +15918,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -15987,7 +15999,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ72">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR72">
         <v>1.22</v>
@@ -16190,7 +16202,7 @@
         <v>0.57</v>
       </c>
       <c r="AP73">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ73">
         <v>0.92</v>
@@ -16399,7 +16411,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ74">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR74">
         <v>1.37</v>
@@ -16524,7 +16536,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16602,10 +16614,10 @@
         <v>1.8</v>
       </c>
       <c r="AP75">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR75">
         <v>1.29</v>
@@ -16808,7 +16820,7 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ76">
         <v>1.36</v>
@@ -16936,7 +16948,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17142,7 +17154,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17348,7 +17360,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17429,7 +17441,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ79">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR79">
         <v>1.56</v>
@@ -17554,7 +17566,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17632,7 +17644,7 @@
         <v>2</v>
       </c>
       <c r="AP80">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ80">
         <v>1.15</v>
@@ -18044,10 +18056,10 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ82">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR82">
         <v>1.31</v>
@@ -18172,7 +18184,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18253,7 +18265,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR83">
         <v>1.34</v>
@@ -18378,7 +18390,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18584,7 +18596,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18790,7 +18802,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19074,10 +19086,10 @@
         <v>0.88</v>
       </c>
       <c r="AP87">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ87">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR87">
         <v>1.99</v>
@@ -19283,7 +19295,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR88">
         <v>1.42</v>
@@ -19408,7 +19420,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19486,10 +19498,10 @@
         <v>3</v>
       </c>
       <c r="AP89">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ89">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19695,7 +19707,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR90">
         <v>1.21</v>
@@ -19898,7 +19910,7 @@
         <v>0.88</v>
       </c>
       <c r="AP91">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ91">
         <v>0.79</v>
@@ -20310,10 +20322,10 @@
         <v>0.78</v>
       </c>
       <c r="AP93">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ93">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR93">
         <v>1.35</v>
@@ -20519,7 +20531,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR94">
         <v>1.63</v>
@@ -20644,7 +20656,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20722,7 +20734,7 @@
         <v>1.17</v>
       </c>
       <c r="AP95">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ95">
         <v>1.46</v>
@@ -20850,7 +20862,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -20931,7 +20943,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ96">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR96">
         <v>1.26</v>
@@ -21056,7 +21068,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21134,7 +21146,7 @@
         <v>0.43</v>
       </c>
       <c r="AP97">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ97">
         <v>1.15</v>
@@ -21262,7 +21274,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21674,7 +21686,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21755,7 +21767,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ100">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR100">
         <v>1.24</v>
@@ -21880,7 +21892,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21958,10 +21970,10 @@
         <v>0.88</v>
       </c>
       <c r="AP101">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ101">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR101">
         <v>1.24</v>
@@ -22164,10 +22176,10 @@
         <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR102">
         <v>2.07</v>
@@ -22292,7 +22304,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22370,7 +22382,7 @@
         <v>0.63</v>
       </c>
       <c r="AP103">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ103">
         <v>1.08</v>
@@ -22576,10 +22588,10 @@
         <v>3</v>
       </c>
       <c r="AP104">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ104">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR104">
         <v>1.42</v>
@@ -22910,7 +22922,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23197,7 +23209,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ107">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR107">
         <v>2.23</v>
@@ -23322,7 +23334,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23734,7 +23746,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24146,7 +24158,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24224,7 +24236,7 @@
         <v>0.44</v>
       </c>
       <c r="AP112">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ112">
         <v>0.92</v>
@@ -24636,10 +24648,10 @@
         <v>0.82</v>
       </c>
       <c r="AP114">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ114">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR114">
         <v>1.47</v>
@@ -24764,7 +24776,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24970,7 +24982,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25051,7 +25063,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ116">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR116">
         <v>1.2</v>
@@ -25254,7 +25266,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ117">
         <v>1.15</v>
@@ -25460,10 +25472,10 @@
         <v>2.78</v>
       </c>
       <c r="AP118">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ118">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR118">
         <v>2.04</v>
@@ -25875,7 +25887,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR120">
         <v>1.65</v>
@@ -26081,7 +26093,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ121">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR121">
         <v>1.44</v>
@@ -26206,7 +26218,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26284,7 +26296,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ122">
         <v>1.15</v>
@@ -26412,7 +26424,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26618,7 +26630,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26696,7 +26708,7 @@
         <v>1.22</v>
       </c>
       <c r="AP124">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ124">
         <v>1.46</v>
@@ -27111,7 +27123,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ126">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR126">
         <v>2.36</v>
@@ -27236,7 +27248,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27314,7 +27326,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ127">
         <v>0.92</v>
@@ -27442,7 +27454,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27648,7 +27660,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -27729,7 +27741,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ129">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR129">
         <v>1.19</v>
@@ -27935,7 +27947,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR130">
         <v>1.4</v>
@@ -28472,7 +28484,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28550,10 +28562,10 @@
         <v>2.5</v>
       </c>
       <c r="AP133">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ133">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR133">
         <v>1.25</v>
@@ -28884,7 +28896,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -28962,10 +28974,10 @@
         <v>1.18</v>
       </c>
       <c r="AP135">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR135">
         <v>1.42</v>
@@ -29168,7 +29180,7 @@
         <v>0.73</v>
       </c>
       <c r="AP136">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ136">
         <v>0.79</v>
@@ -29374,7 +29386,7 @@
         <v>0.73</v>
       </c>
       <c r="AP137">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ137">
         <v>0.92</v>
@@ -29502,7 +29514,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29583,7 +29595,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ138">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR138">
         <v>1.32</v>
@@ -29786,7 +29798,7 @@
         <v>1.2</v>
       </c>
       <c r="AP139">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ139">
         <v>1.15</v>
@@ -29914,7 +29926,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -29992,10 +30004,10 @@
         <v>0.91</v>
       </c>
       <c r="AP140">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ140">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR140">
         <v>1.33</v>
@@ -30120,7 +30132,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30201,7 +30213,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ141">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR141">
         <v>1.67</v>
@@ -30326,7 +30338,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30404,7 +30416,7 @@
         <v>1.09</v>
       </c>
       <c r="AP142">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ142">
         <v>1.08</v>
@@ -30532,7 +30544,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30613,7 +30625,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ143">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR143">
         <v>1.28</v>
@@ -30738,7 +30750,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30816,7 +30828,7 @@
         <v>1.18</v>
       </c>
       <c r="AP144">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ144">
         <v>1.46</v>
@@ -30944,7 +30956,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31150,7 +31162,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31434,7 +31446,7 @@
         <v>1.09</v>
       </c>
       <c r="AP147">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ147">
         <v>1.15</v>
@@ -31846,7 +31858,7 @@
         <v>1.09</v>
       </c>
       <c r="AP149">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AQ149">
         <v>1.15</v>
@@ -31974,7 +31986,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32055,7 +32067,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ150">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AR150">
         <v>1.15</v>
@@ -32261,7 +32273,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ151">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR151">
         <v>2.26</v>
@@ -32592,7 +32604,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q153">
         <v>3.2</v>
@@ -32798,7 +32810,7 @@
         <v>200</v>
       </c>
       <c r="P154" t="s">
-        <v>282</v>
+        <v>203</v>
       </c>
       <c r="Q154">
         <v>2.5</v>
@@ -33004,7 +33016,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q155">
         <v>2.75</v>
@@ -33210,7 +33222,7 @@
         <v>201</v>
       </c>
       <c r="P156" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33573,6 +33585,1036 @@
       </c>
       <c r="BP157">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7480296</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45710.39583333334</v>
+      </c>
+      <c r="F158">
+        <v>27</v>
+      </c>
+      <c r="G158" t="s">
+        <v>79</v>
+      </c>
+      <c r="H158" t="s">
+        <v>74</v>
+      </c>
+      <c r="I158">
+        <v>2</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>2</v>
+      </c>
+      <c r="L158">
+        <v>2</v>
+      </c>
+      <c r="M158">
+        <v>1</v>
+      </c>
+      <c r="N158">
+        <v>3</v>
+      </c>
+      <c r="O158" t="s">
+        <v>202</v>
+      </c>
+      <c r="P158" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q158">
+        <v>6</v>
+      </c>
+      <c r="R158">
+        <v>2.4</v>
+      </c>
+      <c r="S158">
+        <v>2</v>
+      </c>
+      <c r="T158">
+        <v>1.3</v>
+      </c>
+      <c r="U158">
+        <v>3.4</v>
+      </c>
+      <c r="V158">
+        <v>2.5</v>
+      </c>
+      <c r="W158">
+        <v>1.5</v>
+      </c>
+      <c r="X158">
+        <v>6</v>
+      </c>
+      <c r="Y158">
+        <v>1.13</v>
+      </c>
+      <c r="Z158">
+        <v>6.5</v>
+      </c>
+      <c r="AA158">
+        <v>4.2</v>
+      </c>
+      <c r="AB158">
+        <v>1.48</v>
+      </c>
+      <c r="AC158">
+        <v>1.02</v>
+      </c>
+      <c r="AD158">
+        <v>17</v>
+      </c>
+      <c r="AE158">
+        <v>1.2</v>
+      </c>
+      <c r="AF158">
+        <v>4.33</v>
+      </c>
+      <c r="AG158">
+        <v>1.62</v>
+      </c>
+      <c r="AH158">
+        <v>2.21</v>
+      </c>
+      <c r="AI158">
+        <v>1.75</v>
+      </c>
+      <c r="AJ158">
+        <v>2</v>
+      </c>
+      <c r="AK158">
+        <v>2.55</v>
+      </c>
+      <c r="AL158">
+        <v>1.19</v>
+      </c>
+      <c r="AM158">
+        <v>1.12</v>
+      </c>
+      <c r="AN158">
+        <v>1.54</v>
+      </c>
+      <c r="AO158">
+        <v>2.46</v>
+      </c>
+      <c r="AP158">
+        <v>1.64</v>
+      </c>
+      <c r="AQ158">
+        <v>2.29</v>
+      </c>
+      <c r="AR158">
+        <v>1.37</v>
+      </c>
+      <c r="AS158">
+        <v>1.9</v>
+      </c>
+      <c r="AT158">
+        <v>3.27</v>
+      </c>
+      <c r="AU158">
+        <v>7</v>
+      </c>
+      <c r="AV158">
+        <v>6</v>
+      </c>
+      <c r="AW158">
+        <v>5</v>
+      </c>
+      <c r="AX158">
+        <v>10</v>
+      </c>
+      <c r="AY158">
+        <v>12</v>
+      </c>
+      <c r="AZ158">
+        <v>16</v>
+      </c>
+      <c r="BA158">
+        <v>5</v>
+      </c>
+      <c r="BB158">
+        <v>10</v>
+      </c>
+      <c r="BC158">
+        <v>15</v>
+      </c>
+      <c r="BD158">
+        <v>4.1</v>
+      </c>
+      <c r="BE158">
+        <v>8</v>
+      </c>
+      <c r="BF158">
+        <v>1.25</v>
+      </c>
+      <c r="BG158">
+        <v>1.17</v>
+      </c>
+      <c r="BH158">
+        <v>4.35</v>
+      </c>
+      <c r="BI158">
+        <v>1.29</v>
+      </c>
+      <c r="BJ158">
+        <v>3.2</v>
+      </c>
+      <c r="BK158">
+        <v>1.48</v>
+      </c>
+      <c r="BL158">
+        <v>2.43</v>
+      </c>
+      <c r="BM158">
+        <v>1.73</v>
+      </c>
+      <c r="BN158">
+        <v>1.96</v>
+      </c>
+      <c r="BO158">
+        <v>2.1</v>
+      </c>
+      <c r="BP158">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7480294</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F159">
+        <v>27</v>
+      </c>
+      <c r="G159" t="s">
+        <v>80</v>
+      </c>
+      <c r="H159" t="s">
+        <v>81</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>1</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>1</v>
+      </c>
+      <c r="O159" t="s">
+        <v>203</v>
+      </c>
+      <c r="P159" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q159">
+        <v>2.75</v>
+      </c>
+      <c r="R159">
+        <v>2.2</v>
+      </c>
+      <c r="S159">
+        <v>4</v>
+      </c>
+      <c r="T159">
+        <v>1.4</v>
+      </c>
+      <c r="U159">
+        <v>2.75</v>
+      </c>
+      <c r="V159">
+        <v>3</v>
+      </c>
+      <c r="W159">
+        <v>1.36</v>
+      </c>
+      <c r="X159">
+        <v>8</v>
+      </c>
+      <c r="Y159">
+        <v>1.08</v>
+      </c>
+      <c r="Z159">
+        <v>2.16</v>
+      </c>
+      <c r="AA159">
+        <v>3.1</v>
+      </c>
+      <c r="AB159">
+        <v>3.51</v>
+      </c>
+      <c r="AC159">
+        <v>1.07</v>
+      </c>
+      <c r="AD159">
+        <v>9.5</v>
+      </c>
+      <c r="AE159">
+        <v>1.33</v>
+      </c>
+      <c r="AF159">
+        <v>3.3</v>
+      </c>
+      <c r="AG159">
+        <v>1.94</v>
+      </c>
+      <c r="AH159">
+        <v>1.8</v>
+      </c>
+      <c r="AI159">
+        <v>1.75</v>
+      </c>
+      <c r="AJ159">
+        <v>2</v>
+      </c>
+      <c r="AK159">
+        <v>1.32</v>
+      </c>
+      <c r="AL159">
+        <v>1.31</v>
+      </c>
+      <c r="AM159">
+        <v>1.66</v>
+      </c>
+      <c r="AN159">
+        <v>1.77</v>
+      </c>
+      <c r="AO159">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP159">
+        <v>1.86</v>
+      </c>
+      <c r="AQ159">
+        <v>0.64</v>
+      </c>
+      <c r="AR159">
+        <v>1.39</v>
+      </c>
+      <c r="AS159">
+        <v>1.2</v>
+      </c>
+      <c r="AT159">
+        <v>2.59</v>
+      </c>
+      <c r="AU159">
+        <v>5</v>
+      </c>
+      <c r="AV159">
+        <v>6</v>
+      </c>
+      <c r="AW159">
+        <v>4</v>
+      </c>
+      <c r="AX159">
+        <v>4</v>
+      </c>
+      <c r="AY159">
+        <v>9</v>
+      </c>
+      <c r="AZ159">
+        <v>10</v>
+      </c>
+      <c r="BA159">
+        <v>8</v>
+      </c>
+      <c r="BB159">
+        <v>5</v>
+      </c>
+      <c r="BC159">
+        <v>13</v>
+      </c>
+      <c r="BD159">
+        <v>1.68</v>
+      </c>
+      <c r="BE159">
+        <v>6.75</v>
+      </c>
+      <c r="BF159">
+        <v>2.4</v>
+      </c>
+      <c r="BG159">
+        <v>1.21</v>
+      </c>
+      <c r="BH159">
+        <v>3.8</v>
+      </c>
+      <c r="BI159">
+        <v>1.38</v>
+      </c>
+      <c r="BJ159">
+        <v>2.75</v>
+      </c>
+      <c r="BK159">
+        <v>1.62</v>
+      </c>
+      <c r="BL159">
+        <v>2.14</v>
+      </c>
+      <c r="BM159">
+        <v>2</v>
+      </c>
+      <c r="BN159">
+        <v>1.8</v>
+      </c>
+      <c r="BO159">
+        <v>2.5</v>
+      </c>
+      <c r="BP159">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7480295</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F160">
+        <v>27</v>
+      </c>
+      <c r="G160" t="s">
+        <v>72</v>
+      </c>
+      <c r="H160" t="s">
+        <v>71</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>1</v>
+      </c>
+      <c r="L160">
+        <v>1</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>1</v>
+      </c>
+      <c r="O160" t="s">
+        <v>204</v>
+      </c>
+      <c r="P160" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q160">
+        <v>2.3</v>
+      </c>
+      <c r="R160">
+        <v>2.25</v>
+      </c>
+      <c r="S160">
+        <v>5</v>
+      </c>
+      <c r="T160">
+        <v>1.36</v>
+      </c>
+      <c r="U160">
+        <v>3</v>
+      </c>
+      <c r="V160">
+        <v>2.75</v>
+      </c>
+      <c r="W160">
+        <v>1.4</v>
+      </c>
+      <c r="X160">
+        <v>7</v>
+      </c>
+      <c r="Y160">
+        <v>1.1</v>
+      </c>
+      <c r="Z160">
+        <v>1.76</v>
+      </c>
+      <c r="AA160">
+        <v>3.61</v>
+      </c>
+      <c r="AB160">
+        <v>4.5</v>
+      </c>
+      <c r="AC160">
+        <v>1.04</v>
+      </c>
+      <c r="AD160">
+        <v>12</v>
+      </c>
+      <c r="AE160">
+        <v>1.25</v>
+      </c>
+      <c r="AF160">
+        <v>3.75</v>
+      </c>
+      <c r="AG160">
+        <v>1.82</v>
+      </c>
+      <c r="AH160">
+        <v>1.92</v>
+      </c>
+      <c r="AI160">
+        <v>1.8</v>
+      </c>
+      <c r="AJ160">
+        <v>1.95</v>
+      </c>
+      <c r="AK160">
+        <v>1.2</v>
+      </c>
+      <c r="AL160">
+        <v>1.27</v>
+      </c>
+      <c r="AM160">
+        <v>2</v>
+      </c>
+      <c r="AN160">
+        <v>1.5</v>
+      </c>
+      <c r="AO160">
+        <v>1</v>
+      </c>
+      <c r="AP160">
+        <v>1.62</v>
+      </c>
+      <c r="AQ160">
+        <v>0.93</v>
+      </c>
+      <c r="AR160">
+        <v>1.35</v>
+      </c>
+      <c r="AS160">
+        <v>1.12</v>
+      </c>
+      <c r="AT160">
+        <v>2.47</v>
+      </c>
+      <c r="AU160">
+        <v>4</v>
+      </c>
+      <c r="AV160">
+        <v>3</v>
+      </c>
+      <c r="AW160">
+        <v>8</v>
+      </c>
+      <c r="AX160">
+        <v>8</v>
+      </c>
+      <c r="AY160">
+        <v>12</v>
+      </c>
+      <c r="AZ160">
+        <v>11</v>
+      </c>
+      <c r="BA160">
+        <v>2</v>
+      </c>
+      <c r="BB160">
+        <v>8</v>
+      </c>
+      <c r="BC160">
+        <v>10</v>
+      </c>
+      <c r="BD160">
+        <v>1.64</v>
+      </c>
+      <c r="BE160">
+        <v>7</v>
+      </c>
+      <c r="BF160">
+        <v>2.48</v>
+      </c>
+      <c r="BG160">
+        <v>1.19</v>
+      </c>
+      <c r="BH160">
+        <v>4.1</v>
+      </c>
+      <c r="BI160">
+        <v>1.33</v>
+      </c>
+      <c r="BJ160">
+        <v>2.95</v>
+      </c>
+      <c r="BK160">
+        <v>1.55</v>
+      </c>
+      <c r="BL160">
+        <v>2.28</v>
+      </c>
+      <c r="BM160">
+        <v>2</v>
+      </c>
+      <c r="BN160">
+        <v>1.8</v>
+      </c>
+      <c r="BO160">
+        <v>2.33</v>
+      </c>
+      <c r="BP160">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7480297</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F161">
+        <v>27</v>
+      </c>
+      <c r="G161" t="s">
+        <v>76</v>
+      </c>
+      <c r="H161" t="s">
+        <v>73</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <v>2</v>
+      </c>
+      <c r="N161">
+        <v>2</v>
+      </c>
+      <c r="O161" t="s">
+        <v>82</v>
+      </c>
+      <c r="P161" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q161">
+        <v>1.57</v>
+      </c>
+      <c r="R161">
+        <v>3</v>
+      </c>
+      <c r="S161">
+        <v>9.5</v>
+      </c>
+      <c r="T161">
+        <v>1.2</v>
+      </c>
+      <c r="U161">
+        <v>4.33</v>
+      </c>
+      <c r="V161">
+        <v>2</v>
+      </c>
+      <c r="W161">
+        <v>1.73</v>
+      </c>
+      <c r="X161">
+        <v>4</v>
+      </c>
+      <c r="Y161">
+        <v>1.22</v>
+      </c>
+      <c r="Z161">
+        <v>1.22</v>
+      </c>
+      <c r="AA161">
+        <v>6</v>
+      </c>
+      <c r="AB161">
+        <v>12</v>
+      </c>
+      <c r="AC161">
+        <v>1.01</v>
+      </c>
+      <c r="AD161">
+        <v>17</v>
+      </c>
+      <c r="AE161">
+        <v>1.1</v>
+      </c>
+      <c r="AF161">
+        <v>6.5</v>
+      </c>
+      <c r="AG161">
+        <v>1.36</v>
+      </c>
+      <c r="AH161">
+        <v>2.99</v>
+      </c>
+      <c r="AI161">
+        <v>1.91</v>
+      </c>
+      <c r="AJ161">
+        <v>1.91</v>
+      </c>
+      <c r="AK161">
+        <v>1.03</v>
+      </c>
+      <c r="AL161">
+        <v>1.09</v>
+      </c>
+      <c r="AM161">
+        <v>4.6</v>
+      </c>
+      <c r="AN161">
+        <v>2.85</v>
+      </c>
+      <c r="AO161">
+        <v>1.08</v>
+      </c>
+      <c r="AP161">
+        <v>2.64</v>
+      </c>
+      <c r="AQ161">
+        <v>1.23</v>
+      </c>
+      <c r="AR161">
+        <v>2.16</v>
+      </c>
+      <c r="AS161">
+        <v>1.11</v>
+      </c>
+      <c r="AT161">
+        <v>3.27</v>
+      </c>
+      <c r="AU161">
+        <v>4</v>
+      </c>
+      <c r="AV161">
+        <v>8</v>
+      </c>
+      <c r="AW161">
+        <v>14</v>
+      </c>
+      <c r="AX161">
+        <v>4</v>
+      </c>
+      <c r="AY161">
+        <v>18</v>
+      </c>
+      <c r="AZ161">
+        <v>12</v>
+      </c>
+      <c r="BA161">
+        <v>11</v>
+      </c>
+      <c r="BB161">
+        <v>3</v>
+      </c>
+      <c r="BC161">
+        <v>14</v>
+      </c>
+      <c r="BD161">
+        <v>1.14</v>
+      </c>
+      <c r="BE161">
+        <v>10</v>
+      </c>
+      <c r="BF161">
+        <v>5.8</v>
+      </c>
+      <c r="BG161">
+        <v>1.25</v>
+      </c>
+      <c r="BH161">
+        <v>3.45</v>
+      </c>
+      <c r="BI161">
+        <v>1.44</v>
+      </c>
+      <c r="BJ161">
+        <v>2.55</v>
+      </c>
+      <c r="BK161">
+        <v>1.68</v>
+      </c>
+      <c r="BL161">
+        <v>2.02</v>
+      </c>
+      <c r="BM161">
+        <v>2.05</v>
+      </c>
+      <c r="BN161">
+        <v>1.66</v>
+      </c>
+      <c r="BO161">
+        <v>2.55</v>
+      </c>
+      <c r="BP161">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7480298</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F162">
+        <v>27</v>
+      </c>
+      <c r="G162" t="s">
+        <v>77</v>
+      </c>
+      <c r="H162" t="s">
+        <v>78</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>2</v>
+      </c>
+      <c r="L162">
+        <v>3</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>4</v>
+      </c>
+      <c r="O162" t="s">
+        <v>205</v>
+      </c>
+      <c r="P162" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q162">
+        <v>3.1</v>
+      </c>
+      <c r="R162">
+        <v>2.1</v>
+      </c>
+      <c r="S162">
+        <v>3.6</v>
+      </c>
+      <c r="T162">
+        <v>1.4</v>
+      </c>
+      <c r="U162">
+        <v>2.75</v>
+      </c>
+      <c r="V162">
+        <v>3</v>
+      </c>
+      <c r="W162">
+        <v>1.36</v>
+      </c>
+      <c r="X162">
+        <v>9</v>
+      </c>
+      <c r="Y162">
+        <v>1.07</v>
+      </c>
+      <c r="Z162">
+        <v>2.41</v>
+      </c>
+      <c r="AA162">
+        <v>3.23</v>
+      </c>
+      <c r="AB162">
+        <v>2.9</v>
+      </c>
+      <c r="AC162">
+        <v>1.05</v>
+      </c>
+      <c r="AD162">
+        <v>11</v>
+      </c>
+      <c r="AE162">
+        <v>1.3</v>
+      </c>
+      <c r="AF162">
+        <v>3.5</v>
+      </c>
+      <c r="AG162">
+        <v>1.85</v>
+      </c>
+      <c r="AH162">
+        <v>1.89</v>
+      </c>
+      <c r="AI162">
+        <v>1.75</v>
+      </c>
+      <c r="AJ162">
+        <v>2</v>
+      </c>
+      <c r="AK162">
+        <v>1.41</v>
+      </c>
+      <c r="AL162">
+        <v>1.29</v>
+      </c>
+      <c r="AM162">
+        <v>1.55</v>
+      </c>
+      <c r="AN162">
+        <v>1.08</v>
+      </c>
+      <c r="AO162">
+        <v>1</v>
+      </c>
+      <c r="AP162">
+        <v>1.21</v>
+      </c>
+      <c r="AQ162">
+        <v>0.92</v>
+      </c>
+      <c r="AR162">
+        <v>1.18</v>
+      </c>
+      <c r="AS162">
+        <v>1.07</v>
+      </c>
+      <c r="AT162">
+        <v>2.25</v>
+      </c>
+      <c r="AU162">
+        <v>11</v>
+      </c>
+      <c r="AV162">
+        <v>3</v>
+      </c>
+      <c r="AW162">
+        <v>10</v>
+      </c>
+      <c r="AX162">
+        <v>10</v>
+      </c>
+      <c r="AY162">
+        <v>21</v>
+      </c>
+      <c r="AZ162">
+        <v>13</v>
+      </c>
+      <c r="BA162">
+        <v>9</v>
+      </c>
+      <c r="BB162">
+        <v>6</v>
+      </c>
+      <c r="BC162">
+        <v>15</v>
+      </c>
+      <c r="BD162">
+        <v>1.98</v>
+      </c>
+      <c r="BE162">
+        <v>6.75</v>
+      </c>
+      <c r="BF162">
+        <v>1.98</v>
+      </c>
+      <c r="BG162">
+        <v>1.21</v>
+      </c>
+      <c r="BH162">
+        <v>3.8</v>
+      </c>
+      <c r="BI162">
+        <v>1.37</v>
+      </c>
+      <c r="BJ162">
+        <v>2.8</v>
+      </c>
+      <c r="BK162">
+        <v>1.62</v>
+      </c>
+      <c r="BL162">
+        <v>2.12</v>
+      </c>
+      <c r="BM162">
+        <v>1.98</v>
+      </c>
+      <c r="BN162">
+        <v>1.72</v>
+      </c>
+      <c r="BO162">
+        <v>2.48</v>
+      </c>
+      <c r="BP162">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="290">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -882,6 +882,9 @@
   <si>
     <t>['51', '70']</t>
   </si>
+  <si>
+    <t>['36', '57']</t>
+  </si>
 </sst>
 </file>
 
@@ -1242,7 +1245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2606,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ7">
         <v>1.15</v>
@@ -3227,7 +3230,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ10">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -4875,7 +4878,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ18">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR18">
         <v>1.47</v>
@@ -5490,7 +5493,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ21">
         <v>0.93</v>
@@ -6729,7 +6732,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ27">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR27">
         <v>2.21</v>
@@ -7965,7 +7968,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ33">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR33">
         <v>0.87</v>
@@ -8992,7 +8995,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ38">
         <v>2.29</v>
@@ -10231,7 +10234,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ44">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR44">
         <v>1.19</v>
@@ -11464,7 +11467,7 @@
         <v>0.67</v>
       </c>
       <c r="AP50">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ50">
         <v>1.15</v>
@@ -12497,7 +12500,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ55">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR55">
         <v>1.27</v>
@@ -14348,10 +14351,10 @@
         <v>0.17</v>
       </c>
       <c r="AP64">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ64">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR64">
         <v>1.33</v>
@@ -16205,7 +16208,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ73">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR73">
         <v>1.87</v>
@@ -16408,7 +16411,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ74">
         <v>0.64</v>
@@ -18674,7 +18677,7 @@
         <v>0.8</v>
       </c>
       <c r="AP85">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ85">
         <v>1.46</v>
@@ -20940,7 +20943,7 @@
         <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ96">
         <v>1.23</v>
@@ -21561,7 +21564,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ99">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR99">
         <v>1.4</v>
@@ -23824,7 +23827,7 @@
         <v>1.25</v>
       </c>
       <c r="AP110">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ110">
         <v>1.36</v>
@@ -24239,7 +24242,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ112">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR112">
         <v>1.24</v>
@@ -25678,7 +25681,7 @@
         <v>1.1</v>
       </c>
       <c r="AP119">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ119">
         <v>1.08</v>
@@ -27329,7 +27332,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ127">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR127">
         <v>1.36</v>
@@ -27738,7 +27741,7 @@
         <v>0.9</v>
       </c>
       <c r="AP129">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ129">
         <v>0.92</v>
@@ -29389,7 +29392,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ137">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR137">
         <v>1.38</v>
@@ -30622,7 +30625,7 @@
         <v>1.08</v>
       </c>
       <c r="AP143">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ143">
         <v>0.93</v>
@@ -31243,7 +31246,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ146">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR146">
         <v>1.31</v>
@@ -34160,10 +34163,10 @@
         <v>2</v>
       </c>
       <c r="BB160">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC160">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD160">
         <v>1.64</v>
@@ -34615,6 +34618,212 @@
       </c>
       <c r="BP162">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7480299</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45711.375</v>
+      </c>
+      <c r="F163">
+        <v>27</v>
+      </c>
+      <c r="G163" t="s">
+        <v>75</v>
+      </c>
+      <c r="H163" t="s">
+        <v>70</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="M163">
+        <v>2</v>
+      </c>
+      <c r="N163">
+        <v>3</v>
+      </c>
+      <c r="O163" t="s">
+        <v>140</v>
+      </c>
+      <c r="P163" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q163">
+        <v>4.33</v>
+      </c>
+      <c r="R163">
+        <v>2.1</v>
+      </c>
+      <c r="S163">
+        <v>2.75</v>
+      </c>
+      <c r="T163">
+        <v>1.44</v>
+      </c>
+      <c r="U163">
+        <v>2.63</v>
+      </c>
+      <c r="V163">
+        <v>3</v>
+      </c>
+      <c r="W163">
+        <v>1.36</v>
+      </c>
+      <c r="X163">
+        <v>9</v>
+      </c>
+      <c r="Y163">
+        <v>1.07</v>
+      </c>
+      <c r="Z163">
+        <v>4.1</v>
+      </c>
+      <c r="AA163">
+        <v>3.57</v>
+      </c>
+      <c r="AB163">
+        <v>1.84</v>
+      </c>
+      <c r="AC163">
+        <v>1.05</v>
+      </c>
+      <c r="AD163">
+        <v>10</v>
+      </c>
+      <c r="AE163">
+        <v>1.33</v>
+      </c>
+      <c r="AF163">
+        <v>3.25</v>
+      </c>
+      <c r="AG163">
+        <v>1.94</v>
+      </c>
+      <c r="AH163">
+        <v>1.8</v>
+      </c>
+      <c r="AI163">
+        <v>1.8</v>
+      </c>
+      <c r="AJ163">
+        <v>1.95</v>
+      </c>
+      <c r="AK163">
+        <v>1.75</v>
+      </c>
+      <c r="AL163">
+        <v>1.29</v>
+      </c>
+      <c r="AM163">
+        <v>1.29</v>
+      </c>
+      <c r="AN163">
+        <v>0.83</v>
+      </c>
+      <c r="AO163">
+        <v>0.92</v>
+      </c>
+      <c r="AP163">
+        <v>0.77</v>
+      </c>
+      <c r="AQ163">
+        <v>1.07</v>
+      </c>
+      <c r="AR163">
+        <v>1.34</v>
+      </c>
+      <c r="AS163">
+        <v>1.24</v>
+      </c>
+      <c r="AT163">
+        <v>2.58</v>
+      </c>
+      <c r="AU163">
+        <v>3</v>
+      </c>
+      <c r="AV163">
+        <v>4</v>
+      </c>
+      <c r="AW163">
+        <v>6</v>
+      </c>
+      <c r="AX163">
+        <v>5</v>
+      </c>
+      <c r="AY163">
+        <v>9</v>
+      </c>
+      <c r="AZ163">
+        <v>9</v>
+      </c>
+      <c r="BA163">
+        <v>3</v>
+      </c>
+      <c r="BB163">
+        <v>6</v>
+      </c>
+      <c r="BC163">
+        <v>9</v>
+      </c>
+      <c r="BD163">
+        <v>2.55</v>
+      </c>
+      <c r="BE163">
+        <v>7</v>
+      </c>
+      <c r="BF163">
+        <v>1.58</v>
+      </c>
+      <c r="BG163">
+        <v>1.19</v>
+      </c>
+      <c r="BH163">
+        <v>4.1</v>
+      </c>
+      <c r="BI163">
+        <v>1.33</v>
+      </c>
+      <c r="BJ163">
+        <v>2.95</v>
+      </c>
+      <c r="BK163">
+        <v>1.53</v>
+      </c>
+      <c r="BL163">
+        <v>2.32</v>
+      </c>
+      <c r="BM163">
+        <v>1.85</v>
+      </c>
+      <c r="BN163">
+        <v>1.83</v>
+      </c>
+      <c r="BO163">
+        <v>2.3</v>
+      </c>
+      <c r="BP163">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="291">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -634,6 +634,9 @@
     <t>['18', '47', '49']</t>
   </si>
   <si>
+    <t>['24', '30', '45', '72', '90+2']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -1245,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1913,7 +1916,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2403,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ6">
         <v>0.64</v>
@@ -2531,7 +2534,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2612,7 +2615,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ7">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2943,7 +2946,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3355,7 +3358,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3561,7 +3564,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3767,7 +3770,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -4179,7 +4182,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4591,7 +4594,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -5209,7 +5212,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5415,7 +5418,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5621,7 +5624,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5702,7 +5705,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ22">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR22">
         <v>1.66</v>
@@ -5905,7 +5908,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ23">
         <v>1.46</v>
@@ -6033,7 +6036,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6239,7 +6242,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6729,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ27">
         <v>1.07</v>
@@ -7269,7 +7272,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7681,7 +7684,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8093,7 +8096,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8299,7 +8302,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8505,7 +8508,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8711,7 +8714,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8792,7 +8795,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ37">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -8917,7 +8920,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9329,7 +9332,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9535,7 +9538,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9741,7 +9744,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9947,7 +9950,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10153,7 +10156,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10565,7 +10568,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10643,10 +10646,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ46">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR46">
         <v>2.16</v>
@@ -10771,7 +10774,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11183,7 +11186,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11801,7 +11804,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12007,7 +12010,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12625,7 +12628,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12831,7 +12834,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -13037,7 +13040,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13449,7 +13452,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13655,7 +13658,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13939,7 +13942,7 @@
         <v>1.25</v>
       </c>
       <c r="AP62">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ62">
         <v>0.92</v>
@@ -14067,7 +14070,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14273,7 +14276,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14685,7 +14688,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14891,7 +14894,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15303,7 +15306,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15509,7 +15512,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15715,7 +15718,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15921,7 +15924,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16539,7 +16542,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16951,7 +16954,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17032,7 +17035,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ77">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR77">
         <v>1.13</v>
@@ -17157,7 +17160,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17363,7 +17366,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17569,7 +17572,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17650,7 +17653,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ80">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR80">
         <v>1.33</v>
@@ -17853,7 +17856,7 @@
         <v>0.5</v>
       </c>
       <c r="AP81">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ81">
         <v>1.15</v>
@@ -18187,7 +18190,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18393,7 +18396,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18599,7 +18602,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18805,7 +18808,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18886,7 +18889,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ86">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR86">
         <v>1.56</v>
@@ -19423,7 +19426,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -20119,7 +20122,7 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ92">
         <v>1.08</v>
@@ -20659,7 +20662,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20865,7 +20868,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21071,7 +21074,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21277,7 +21280,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21689,7 +21692,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21895,7 +21898,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22307,7 +22310,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22925,7 +22928,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23209,7 +23212,7 @@
         <v>1.5</v>
       </c>
       <c r="AP107">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ107">
         <v>0.93</v>
@@ -23337,7 +23340,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23624,7 +23627,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ109">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR109">
         <v>1.35</v>
@@ -23749,7 +23752,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24161,7 +24164,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24445,7 +24448,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ113">
         <v>0.79</v>
@@ -24779,7 +24782,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24985,7 +24988,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25272,7 +25275,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ117">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR117">
         <v>1.33</v>
@@ -26221,7 +26224,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26427,7 +26430,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26633,7 +26636,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26920,7 +26923,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ125">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR125">
         <v>1.17</v>
@@ -27123,7 +27126,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ126">
         <v>1.23</v>
@@ -27251,7 +27254,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27457,7 +27460,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27663,7 +27666,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -28153,7 +28156,7 @@
         <v>1.6</v>
       </c>
       <c r="AP131">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ131">
         <v>1.36</v>
@@ -28487,7 +28490,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28899,7 +28902,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29517,7 +29520,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29804,7 +29807,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ139">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR139">
         <v>2</v>
@@ -29929,7 +29932,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30135,7 +30138,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30341,7 +30344,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30547,7 +30550,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30753,7 +30756,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30959,7 +30962,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31165,7 +31168,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31452,7 +31455,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ147">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR147">
         <v>1.38</v>
@@ -31989,7 +31992,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32273,7 +32276,7 @@
         <v>1.09</v>
       </c>
       <c r="AP151">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ151">
         <v>0.92</v>
@@ -32479,7 +32482,7 @@
         <v>1.46</v>
       </c>
       <c r="AP152">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ152">
         <v>1.36</v>
@@ -32607,7 +32610,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q153">
         <v>3.2</v>
@@ -32688,7 +32691,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ153">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR153">
         <v>1.3</v>
@@ -33019,7 +33022,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q155">
         <v>2.75</v>
@@ -33225,7 +33228,7 @@
         <v>201</v>
       </c>
       <c r="P156" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -34255,7 +34258,7 @@
         <v>82</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q161">
         <v>1.57</v>
@@ -34461,7 +34464,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q162">
         <v>3.1</v>
@@ -34667,7 +34670,7 @@
         <v>140</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q163">
         <v>4.33</v>
@@ -34824,6 +34827,212 @@
       </c>
       <c r="BP163">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7480300</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45713.70833333334</v>
+      </c>
+      <c r="F164">
+        <v>28</v>
+      </c>
+      <c r="G164" t="s">
+        <v>74</v>
+      </c>
+      <c r="H164" t="s">
+        <v>80</v>
+      </c>
+      <c r="I164">
+        <v>3</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>3</v>
+      </c>
+      <c r="L164">
+        <v>5</v>
+      </c>
+      <c r="M164">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>6</v>
+      </c>
+      <c r="O164" t="s">
+        <v>206</v>
+      </c>
+      <c r="P164" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q164">
+        <v>1.57</v>
+      </c>
+      <c r="R164">
+        <v>3</v>
+      </c>
+      <c r="S164">
+        <v>10</v>
+      </c>
+      <c r="T164">
+        <v>1.22</v>
+      </c>
+      <c r="U164">
+        <v>4</v>
+      </c>
+      <c r="V164">
+        <v>2</v>
+      </c>
+      <c r="W164">
+        <v>1.73</v>
+      </c>
+      <c r="X164">
+        <v>4.33</v>
+      </c>
+      <c r="Y164">
+        <v>1.2</v>
+      </c>
+      <c r="Z164">
+        <v>1.18</v>
+      </c>
+      <c r="AA164">
+        <v>7.4</v>
+      </c>
+      <c r="AB164">
+        <v>12</v>
+      </c>
+      <c r="AC164">
+        <v>1.01</v>
+      </c>
+      <c r="AD164">
+        <v>22</v>
+      </c>
+      <c r="AE164">
+        <v>1.11</v>
+      </c>
+      <c r="AF164">
+        <v>6.25</v>
+      </c>
+      <c r="AG164">
+        <v>1.29</v>
+      </c>
+      <c r="AH164">
+        <v>3.27</v>
+      </c>
+      <c r="AI164">
+        <v>2</v>
+      </c>
+      <c r="AJ164">
+        <v>1.75</v>
+      </c>
+      <c r="AK164">
+        <v>1.04</v>
+      </c>
+      <c r="AL164">
+        <v>1.1</v>
+      </c>
+      <c r="AM164">
+        <v>4.33</v>
+      </c>
+      <c r="AN164">
+        <v>2.85</v>
+      </c>
+      <c r="AO164">
+        <v>1.15</v>
+      </c>
+      <c r="AP164">
+        <v>2.86</v>
+      </c>
+      <c r="AQ164">
+        <v>1.07</v>
+      </c>
+      <c r="AR164">
+        <v>2.28</v>
+      </c>
+      <c r="AS164">
+        <v>1.22</v>
+      </c>
+      <c r="AT164">
+        <v>3.5</v>
+      </c>
+      <c r="AU164">
+        <v>8</v>
+      </c>
+      <c r="AV164">
+        <v>2</v>
+      </c>
+      <c r="AW164">
+        <v>8</v>
+      </c>
+      <c r="AX164">
+        <v>7</v>
+      </c>
+      <c r="AY164">
+        <v>16</v>
+      </c>
+      <c r="AZ164">
+        <v>9</v>
+      </c>
+      <c r="BA164">
+        <v>4</v>
+      </c>
+      <c r="BB164">
+        <v>3</v>
+      </c>
+      <c r="BC164">
+        <v>7</v>
+      </c>
+      <c r="BD164">
+        <v>1.09</v>
+      </c>
+      <c r="BE164">
+        <v>13</v>
+      </c>
+      <c r="BF164">
+        <v>6.75</v>
+      </c>
+      <c r="BG164">
+        <v>1.14</v>
+      </c>
+      <c r="BH164">
+        <v>4.8</v>
+      </c>
+      <c r="BI164">
+        <v>1.25</v>
+      </c>
+      <c r="BJ164">
+        <v>3.45</v>
+      </c>
+      <c r="BK164">
+        <v>1.42</v>
+      </c>
+      <c r="BL164">
+        <v>2.63</v>
+      </c>
+      <c r="BM164">
+        <v>1.65</v>
+      </c>
+      <c r="BN164">
+        <v>2.08</v>
+      </c>
+      <c r="BO164">
+        <v>1.97</v>
+      </c>
+      <c r="BP164">
+        <v>1.73</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="296">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -637,6 +637,15 @@
     <t>['24', '30', '45', '72', '90+2']</t>
   </si>
   <si>
+    <t>['12', '84']</t>
+  </si>
+  <si>
+    <t>['56', '63', '90+5']</t>
+  </si>
+  <si>
+    <t>['11', '14']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -887,6 +896,12 @@
   </si>
   <si>
     <t>['36', '57']</t>
+  </si>
+  <si>
+    <t>['18', '90', '90+10']</t>
+  </si>
+  <si>
+    <t>['35', '53', '62', '85']</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP164"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1582,10 +1597,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1788,10 +1803,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1916,7 +1931,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1994,10 +2009,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2203,7 +2218,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ5">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2534,7 +2549,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2612,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ7">
         <v>1.07</v>
@@ -2946,7 +2961,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3358,7 +3373,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3564,7 +3579,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3645,7 +3660,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ12">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3770,7 +3785,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -3848,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ13">
         <v>0.79</v>
@@ -4054,7 +4069,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ14">
         <v>0.79</v>
@@ -4182,7 +4197,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4263,7 +4278,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ15">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR15">
         <v>0.53</v>
@@ -4469,7 +4484,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ16">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR16">
         <v>2.02</v>
@@ -4594,7 +4609,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4878,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18">
         <v>1.07</v>
@@ -5212,7 +5227,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5293,7 +5308,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ20">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR20">
         <v>1.56</v>
@@ -5418,7 +5433,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5496,7 +5511,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ21">
         <v>0.93</v>
@@ -5624,7 +5639,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5911,7 +5926,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ23">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR23">
         <v>3.1</v>
@@ -6036,7 +6051,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6114,7 +6129,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24">
         <v>1.36</v>
@@ -6242,7 +6257,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6320,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ25">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR25">
         <v>1.41</v>
@@ -7147,7 +7162,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ29">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR29">
         <v>1.33</v>
@@ -7272,7 +7287,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7556,10 +7571,10 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR31">
         <v>1.46</v>
@@ -7684,7 +7699,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8096,7 +8111,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8174,10 +8189,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR34">
         <v>1.25</v>
@@ -8302,7 +8317,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8380,7 +8395,7 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ35">
         <v>1.36</v>
@@ -8508,7 +8523,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8586,10 +8601,10 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR36">
         <v>1.45</v>
@@ -8714,7 +8729,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8920,7 +8935,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -8998,7 +9013,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ38">
         <v>2.29</v>
@@ -9207,7 +9222,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ39">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR39">
         <v>2.01</v>
@@ -9332,7 +9347,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9538,7 +9553,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9744,7 +9759,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9950,7 +9965,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10156,7 +10171,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10568,7 +10583,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10774,7 +10789,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10852,10 +10867,10 @@
         <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR47">
         <v>1.19</v>
@@ -11058,10 +11073,10 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR48">
         <v>1.61</v>
@@ -11186,7 +11201,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11264,10 +11279,10 @@
         <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR49">
         <v>1.3</v>
@@ -11470,10 +11485,10 @@
         <v>0.67</v>
       </c>
       <c r="AP50">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ50">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11676,10 +11691,10 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ51">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR51">
         <v>1.31</v>
@@ -11804,7 +11819,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12010,7 +12025,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12628,7 +12643,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12706,7 +12721,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
         <v>2.29</v>
@@ -12834,7 +12849,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -12915,7 +12930,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ57">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR57">
         <v>1.86</v>
@@ -13040,7 +13055,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13118,7 +13133,7 @@
         <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58">
         <v>0.64</v>
@@ -13327,7 +13342,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ59">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR59">
         <v>1.31</v>
@@ -13452,7 +13467,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13658,7 +13673,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13736,7 +13751,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61">
         <v>0.93</v>
@@ -13945,7 +13960,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ62">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR62">
         <v>2.17</v>
@@ -14070,7 +14085,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14151,7 +14166,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ63">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR63">
         <v>1.25</v>
@@ -14276,7 +14291,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14354,7 +14369,7 @@
         <v>0.17</v>
       </c>
       <c r="AP64">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ64">
         <v>1.07</v>
@@ -14563,7 +14578,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ65">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR65">
         <v>1.13</v>
@@ -14688,7 +14703,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14894,7 +14909,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15178,10 +15193,10 @@
         <v>0.6</v>
       </c>
       <c r="AP68">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ68">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR68">
         <v>1.22</v>
@@ -15306,7 +15321,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15387,7 +15402,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ69">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR69">
         <v>1.35</v>
@@ -15512,7 +15527,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15590,7 +15605,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ70">
         <v>0.79</v>
@@ -15718,7 +15733,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15799,7 +15814,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ71">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR71">
         <v>1.32</v>
@@ -15924,7 +15939,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16002,7 +16017,7 @@
         <v>3</v>
       </c>
       <c r="AP72">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ72">
         <v>2.29</v>
@@ -16414,7 +16429,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ74">
         <v>0.64</v>
@@ -16542,7 +16557,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16954,7 +16969,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17160,7 +17175,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17241,7 +17256,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ78">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR78">
         <v>1.42</v>
@@ -17366,7 +17381,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17444,7 +17459,7 @@
         <v>3</v>
       </c>
       <c r="AP79">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ79">
         <v>2.29</v>
@@ -17572,7 +17587,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17859,7 +17874,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ81">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR81">
         <v>2.21</v>
@@ -18062,10 +18077,10 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ82">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR82">
         <v>1.31</v>
@@ -18190,7 +18205,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18268,10 +18283,10 @@
         <v>0.83</v>
       </c>
       <c r="AP83">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ83">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR83">
         <v>1.34</v>
@@ -18396,7 +18411,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18474,10 +18489,10 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR84">
         <v>1.24</v>
@@ -18602,7 +18617,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18680,10 +18695,10 @@
         <v>0.8</v>
       </c>
       <c r="AP85">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ85">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18808,7 +18823,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18886,7 +18901,7 @@
         <v>1.83</v>
       </c>
       <c r="AP86">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ86">
         <v>1.07</v>
@@ -19426,7 +19441,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -20125,7 +20140,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ92">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR92">
         <v>2.19</v>
@@ -20328,7 +20343,7 @@
         <v>0.78</v>
       </c>
       <c r="AP93">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ93">
         <v>0.64</v>
@@ -20534,10 +20549,10 @@
         <v>0.86</v>
       </c>
       <c r="AP94">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ94">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR94">
         <v>1.63</v>
@@ -20662,7 +20677,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20743,7 +20758,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ95">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR95">
         <v>1.29</v>
@@ -20868,7 +20883,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -20946,10 +20961,10 @@
         <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ96">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR96">
         <v>1.26</v>
@@ -21074,7 +21089,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21155,7 +21170,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ97">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR97">
         <v>1.38</v>
@@ -21280,7 +21295,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21358,7 +21373,7 @@
         <v>1.43</v>
       </c>
       <c r="AP98">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ98">
         <v>1.36</v>
@@ -21564,7 +21579,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ99">
         <v>1.07</v>
@@ -21692,7 +21707,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21770,7 +21785,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ100">
         <v>0.64</v>
@@ -21898,7 +21913,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21979,7 +21994,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ101">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR101">
         <v>1.24</v>
@@ -22185,7 +22200,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ102">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR102">
         <v>2.07</v>
@@ -22310,7 +22325,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22391,7 +22406,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ103">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR103">
         <v>1.34</v>
@@ -22594,7 +22609,7 @@
         <v>3</v>
       </c>
       <c r="AP104">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ104">
         <v>2.29</v>
@@ -22800,7 +22815,7 @@
         <v>0.89</v>
       </c>
       <c r="AP105">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ105">
         <v>0.79</v>
@@ -22928,7 +22943,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23006,10 +23021,10 @@
         <v>0.89</v>
       </c>
       <c r="AP106">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ106">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR106">
         <v>1.67</v>
@@ -23340,7 +23355,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23421,7 +23436,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ108">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR108">
         <v>1.38</v>
@@ -23624,7 +23639,7 @@
         <v>1.71</v>
       </c>
       <c r="AP109">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ109">
         <v>1.07</v>
@@ -23752,7 +23767,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23830,7 +23845,7 @@
         <v>1.25</v>
       </c>
       <c r="AP110">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ110">
         <v>1.36</v>
@@ -24039,7 +24054,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ111">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR111">
         <v>1.24</v>
@@ -24164,7 +24179,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24782,7 +24797,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24860,10 +24875,10 @@
         <v>1.25</v>
       </c>
       <c r="AP115">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ115">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR115">
         <v>1.18</v>
@@ -24988,7 +25003,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25069,7 +25084,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ116">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR116">
         <v>1.2</v>
@@ -25272,7 +25287,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ117">
         <v>1.07</v>
@@ -25684,10 +25699,10 @@
         <v>1.1</v>
       </c>
       <c r="AP119">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ119">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR119">
         <v>1.24</v>
@@ -25890,7 +25905,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ120">
         <v>0.93</v>
@@ -26096,10 +26111,10 @@
         <v>1.11</v>
       </c>
       <c r="AP121">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ121">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR121">
         <v>1.44</v>
@@ -26224,7 +26239,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26305,7 +26320,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ122">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR122">
         <v>1.36</v>
@@ -26430,7 +26445,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26636,7 +26651,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26717,7 +26732,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ124">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR124">
         <v>1.42</v>
@@ -26920,7 +26935,7 @@
         <v>1.33</v>
       </c>
       <c r="AP125">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ125">
         <v>1.07</v>
@@ -27129,7 +27144,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ126">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR126">
         <v>2.36</v>
@@ -27254,7 +27269,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27332,7 +27347,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ127">
         <v>1.07</v>
@@ -27460,7 +27475,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27538,10 +27553,10 @@
         <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ128">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR128">
         <v>1.42</v>
@@ -27666,7 +27681,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -27744,10 +27759,10 @@
         <v>0.9</v>
       </c>
       <c r="AP129">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ129">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR129">
         <v>1.19</v>
@@ -27950,7 +27965,7 @@
         <v>1.2</v>
       </c>
       <c r="AP130">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ130">
         <v>0.93</v>
@@ -28365,7 +28380,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ132">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28490,7 +28505,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28902,7 +28917,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29520,7 +29535,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29932,7 +29947,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30013,7 +30028,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ140">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR140">
         <v>1.33</v>
@@ -30138,7 +30153,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30216,7 +30231,7 @@
         <v>0.75</v>
       </c>
       <c r="AP141">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ141">
         <v>0.64</v>
@@ -30344,7 +30359,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30425,7 +30440,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ142">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR142">
         <v>1.21</v>
@@ -30550,7 +30565,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30628,7 +30643,7 @@
         <v>1.08</v>
       </c>
       <c r="AP143">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ143">
         <v>0.93</v>
@@ -30756,7 +30771,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30834,10 +30849,10 @@
         <v>1.18</v>
       </c>
       <c r="AP144">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ144">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR144">
         <v>1.31</v>
@@ -30962,7 +30977,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31168,7 +31183,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31658,7 +31673,7 @@
         <v>1.58</v>
       </c>
       <c r="AP148">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ148">
         <v>1.36</v>
@@ -31867,7 +31882,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ149">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR149">
         <v>2.11</v>
@@ -31992,7 +32007,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32070,7 +32085,7 @@
         <v>2.42</v>
       </c>
       <c r="AP150">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ150">
         <v>2.29</v>
@@ -32279,7 +32294,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ151">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR151">
         <v>2.26</v>
@@ -32610,7 +32625,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q153">
         <v>3.2</v>
@@ -32894,7 +32909,7 @@
         <v>0.85</v>
       </c>
       <c r="AP154">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ154">
         <v>0.79</v>
@@ -33022,7 +33037,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q155">
         <v>2.75</v>
@@ -33100,10 +33115,10 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ155">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR155">
         <v>1.1</v>
@@ -33228,7 +33243,7 @@
         <v>201</v>
       </c>
       <c r="P156" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33306,10 +33321,10 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ156">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR156">
         <v>1.65</v>
@@ -33515,7 +33530,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ157">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR157">
         <v>1.3</v>
@@ -34130,7 +34145,7 @@
         <v>1</v>
       </c>
       <c r="AP160">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ160">
         <v>0.93</v>
@@ -34258,7 +34273,7 @@
         <v>82</v>
       </c>
       <c r="P161" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q161">
         <v>1.57</v>
@@ -34339,7 +34354,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ161">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR161">
         <v>2.16</v>
@@ -34464,7 +34479,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q162">
         <v>3.1</v>
@@ -34545,7 +34560,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ162">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR162">
         <v>1.18</v>
@@ -34670,7 +34685,7 @@
         <v>140</v>
       </c>
       <c r="P163" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q163">
         <v>4.33</v>
@@ -34748,7 +34763,7 @@
         <v>0.92</v>
       </c>
       <c r="AP163">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ163">
         <v>1.07</v>
@@ -34876,7 +34891,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q164">
         <v>1.57</v>
@@ -35033,6 +35048,1036 @@
       </c>
       <c r="BP164">
         <v>1.73</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7480304</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45714.69791666666</v>
+      </c>
+      <c r="F165">
+        <v>28</v>
+      </c>
+      <c r="G165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H165" t="s">
+        <v>77</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165">
+        <v>1</v>
+      </c>
+      <c r="O165" t="s">
+        <v>142</v>
+      </c>
+      <c r="P165" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q165">
+        <v>3.1</v>
+      </c>
+      <c r="R165">
+        <v>2.2</v>
+      </c>
+      <c r="S165">
+        <v>3.25</v>
+      </c>
+      <c r="T165">
+        <v>1.36</v>
+      </c>
+      <c r="U165">
+        <v>3</v>
+      </c>
+      <c r="V165">
+        <v>2.63</v>
+      </c>
+      <c r="W165">
+        <v>1.44</v>
+      </c>
+      <c r="X165">
+        <v>7</v>
+      </c>
+      <c r="Y165">
+        <v>1.1</v>
+      </c>
+      <c r="Z165">
+        <v>2.49</v>
+      </c>
+      <c r="AA165">
+        <v>3.29</v>
+      </c>
+      <c r="AB165">
+        <v>2.74</v>
+      </c>
+      <c r="AC165">
+        <v>1.04</v>
+      </c>
+      <c r="AD165">
+        <v>12</v>
+      </c>
+      <c r="AE165">
+        <v>1.28</v>
+      </c>
+      <c r="AF165">
+        <v>3.75</v>
+      </c>
+      <c r="AG165">
+        <v>1.77</v>
+      </c>
+      <c r="AH165">
+        <v>1.98</v>
+      </c>
+      <c r="AI165">
+        <v>1.62</v>
+      </c>
+      <c r="AJ165">
+        <v>2.2</v>
+      </c>
+      <c r="AK165">
+        <v>1.44</v>
+      </c>
+      <c r="AL165">
+        <v>1.3</v>
+      </c>
+      <c r="AM165">
+        <v>1.51</v>
+      </c>
+      <c r="AN165">
+        <v>0.77</v>
+      </c>
+      <c r="AO165">
+        <v>1.15</v>
+      </c>
+      <c r="AP165">
+        <v>0.93</v>
+      </c>
+      <c r="AQ165">
+        <v>1.07</v>
+      </c>
+      <c r="AR165">
+        <v>1.32</v>
+      </c>
+      <c r="AS165">
+        <v>1</v>
+      </c>
+      <c r="AT165">
+        <v>2.32</v>
+      </c>
+      <c r="AU165">
+        <v>5</v>
+      </c>
+      <c r="AV165">
+        <v>3</v>
+      </c>
+      <c r="AW165">
+        <v>8</v>
+      </c>
+      <c r="AX165">
+        <v>3</v>
+      </c>
+      <c r="AY165">
+        <v>13</v>
+      </c>
+      <c r="AZ165">
+        <v>6</v>
+      </c>
+      <c r="BA165">
+        <v>12</v>
+      </c>
+      <c r="BB165">
+        <v>3</v>
+      </c>
+      <c r="BC165">
+        <v>15</v>
+      </c>
+      <c r="BD165">
+        <v>1.9</v>
+      </c>
+      <c r="BE165">
+        <v>6.5</v>
+      </c>
+      <c r="BF165">
+        <v>2.08</v>
+      </c>
+      <c r="BG165">
+        <v>1.2</v>
+      </c>
+      <c r="BH165">
+        <v>3.95</v>
+      </c>
+      <c r="BI165">
+        <v>1.35</v>
+      </c>
+      <c r="BJ165">
+        <v>2.9</v>
+      </c>
+      <c r="BK165">
+        <v>1.57</v>
+      </c>
+      <c r="BL165">
+        <v>2.23</v>
+      </c>
+      <c r="BM165">
+        <v>1.9</v>
+      </c>
+      <c r="BN165">
+        <v>1.79</v>
+      </c>
+      <c r="BO165">
+        <v>2.38</v>
+      </c>
+      <c r="BP165">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7481843</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45714.69791666666</v>
+      </c>
+      <c r="F166">
+        <v>28</v>
+      </c>
+      <c r="G166" t="s">
+        <v>71</v>
+      </c>
+      <c r="H166" t="s">
+        <v>78</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="L166">
+        <v>2</v>
+      </c>
+      <c r="M166">
+        <v>1</v>
+      </c>
+      <c r="N166">
+        <v>3</v>
+      </c>
+      <c r="O166" t="s">
+        <v>207</v>
+      </c>
+      <c r="P166" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q166">
+        <v>3</v>
+      </c>
+      <c r="R166">
+        <v>2.2</v>
+      </c>
+      <c r="S166">
+        <v>3.5</v>
+      </c>
+      <c r="T166">
+        <v>1.36</v>
+      </c>
+      <c r="U166">
+        <v>3</v>
+      </c>
+      <c r="V166">
+        <v>2.63</v>
+      </c>
+      <c r="W166">
+        <v>1.44</v>
+      </c>
+      <c r="X166">
+        <v>7</v>
+      </c>
+      <c r="Y166">
+        <v>1.1</v>
+      </c>
+      <c r="Z166">
+        <v>2.19</v>
+      </c>
+      <c r="AA166">
+        <v>3.47</v>
+      </c>
+      <c r="AB166">
+        <v>3.08</v>
+      </c>
+      <c r="AC166">
+        <v>1.05</v>
+      </c>
+      <c r="AD166">
+        <v>11</v>
+      </c>
+      <c r="AE166">
+        <v>1.28</v>
+      </c>
+      <c r="AF166">
+        <v>3.6</v>
+      </c>
+      <c r="AG166">
+        <v>1.77</v>
+      </c>
+      <c r="AH166">
+        <v>1.98</v>
+      </c>
+      <c r="AI166">
+        <v>1.67</v>
+      </c>
+      <c r="AJ166">
+        <v>2.1</v>
+      </c>
+      <c r="AK166">
+        <v>1.39</v>
+      </c>
+      <c r="AL166">
+        <v>1.3</v>
+      </c>
+      <c r="AM166">
+        <v>1.58</v>
+      </c>
+      <c r="AN166">
+        <v>1.38</v>
+      </c>
+      <c r="AO166">
+        <v>0.92</v>
+      </c>
+      <c r="AP166">
+        <v>1.5</v>
+      </c>
+      <c r="AQ166">
+        <v>0.86</v>
+      </c>
+      <c r="AR166">
+        <v>1.16</v>
+      </c>
+      <c r="AS166">
+        <v>1.09</v>
+      </c>
+      <c r="AT166">
+        <v>2.25</v>
+      </c>
+      <c r="AU166">
+        <v>7</v>
+      </c>
+      <c r="AV166">
+        <v>3</v>
+      </c>
+      <c r="AW166">
+        <v>8</v>
+      </c>
+      <c r="AX166">
+        <v>9</v>
+      </c>
+      <c r="AY166">
+        <v>15</v>
+      </c>
+      <c r="AZ166">
+        <v>12</v>
+      </c>
+      <c r="BA166">
+        <v>5</v>
+      </c>
+      <c r="BB166">
+        <v>10</v>
+      </c>
+      <c r="BC166">
+        <v>15</v>
+      </c>
+      <c r="BD166">
+        <v>1.8</v>
+      </c>
+      <c r="BE166">
+        <v>6.75</v>
+      </c>
+      <c r="BF166">
+        <v>2.18</v>
+      </c>
+      <c r="BG166">
+        <v>1.21</v>
+      </c>
+      <c r="BH166">
+        <v>3.8</v>
+      </c>
+      <c r="BI166">
+        <v>1.38</v>
+      </c>
+      <c r="BJ166">
+        <v>2.75</v>
+      </c>
+      <c r="BK166">
+        <v>1.63</v>
+      </c>
+      <c r="BL166">
+        <v>2.12</v>
+      </c>
+      <c r="BM166">
+        <v>1.98</v>
+      </c>
+      <c r="BN166">
+        <v>1.72</v>
+      </c>
+      <c r="BO166">
+        <v>2.48</v>
+      </c>
+      <c r="BP166">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7480302</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45714.69791666666</v>
+      </c>
+      <c r="F167">
+        <v>28</v>
+      </c>
+      <c r="G167" t="s">
+        <v>70</v>
+      </c>
+      <c r="H167" t="s">
+        <v>73</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167">
+        <v>3</v>
+      </c>
+      <c r="M167">
+        <v>1</v>
+      </c>
+      <c r="N167">
+        <v>4</v>
+      </c>
+      <c r="O167" t="s">
+        <v>208</v>
+      </c>
+      <c r="P167" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q167">
+        <v>2.4</v>
+      </c>
+      <c r="R167">
+        <v>2.1</v>
+      </c>
+      <c r="S167">
+        <v>5</v>
+      </c>
+      <c r="T167">
+        <v>1.44</v>
+      </c>
+      <c r="U167">
+        <v>2.63</v>
+      </c>
+      <c r="V167">
+        <v>3</v>
+      </c>
+      <c r="W167">
+        <v>1.36</v>
+      </c>
+      <c r="X167">
+        <v>9</v>
+      </c>
+      <c r="Y167">
+        <v>1.07</v>
+      </c>
+      <c r="Z167">
+        <v>1.76</v>
+      </c>
+      <c r="AA167">
+        <v>3.72</v>
+      </c>
+      <c r="AB167">
+        <v>4.3</v>
+      </c>
+      <c r="AC167">
+        <v>1.05</v>
+      </c>
+      <c r="AD167">
+        <v>10</v>
+      </c>
+      <c r="AE167">
+        <v>1.33</v>
+      </c>
+      <c r="AF167">
+        <v>3.25</v>
+      </c>
+      <c r="AG167">
+        <v>1.98</v>
+      </c>
+      <c r="AH167">
+        <v>1.77</v>
+      </c>
+      <c r="AI167">
+        <v>1.95</v>
+      </c>
+      <c r="AJ167">
+        <v>1.8</v>
+      </c>
+      <c r="AK167">
+        <v>1.21</v>
+      </c>
+      <c r="AL167">
+        <v>1.27</v>
+      </c>
+      <c r="AM167">
+        <v>1.98</v>
+      </c>
+      <c r="AN167">
+        <v>1.38</v>
+      </c>
+      <c r="AO167">
+        <v>1.23</v>
+      </c>
+      <c r="AP167">
+        <v>1.5</v>
+      </c>
+      <c r="AQ167">
+        <v>1.14</v>
+      </c>
+      <c r="AR167">
+        <v>1.74</v>
+      </c>
+      <c r="AS167">
+        <v>1.15</v>
+      </c>
+      <c r="AT167">
+        <v>2.89</v>
+      </c>
+      <c r="AU167">
+        <v>8</v>
+      </c>
+      <c r="AV167">
+        <v>4</v>
+      </c>
+      <c r="AW167">
+        <v>5</v>
+      </c>
+      <c r="AX167">
+        <v>6</v>
+      </c>
+      <c r="AY167">
+        <v>13</v>
+      </c>
+      <c r="AZ167">
+        <v>10</v>
+      </c>
+      <c r="BA167">
+        <v>5</v>
+      </c>
+      <c r="BB167">
+        <v>6</v>
+      </c>
+      <c r="BC167">
+        <v>11</v>
+      </c>
+      <c r="BD167">
+        <v>1.44</v>
+      </c>
+      <c r="BE167">
+        <v>7.5</v>
+      </c>
+      <c r="BF167">
+        <v>3.05</v>
+      </c>
+      <c r="BG167">
+        <v>1.17</v>
+      </c>
+      <c r="BH167">
+        <v>4.3</v>
+      </c>
+      <c r="BI167">
+        <v>1.3</v>
+      </c>
+      <c r="BJ167">
+        <v>3.1</v>
+      </c>
+      <c r="BK167">
+        <v>1.5</v>
+      </c>
+      <c r="BL167">
+        <v>2.4</v>
+      </c>
+      <c r="BM167">
+        <v>1.78</v>
+      </c>
+      <c r="BN167">
+        <v>1.91</v>
+      </c>
+      <c r="BO167">
+        <v>2.18</v>
+      </c>
+      <c r="BP167">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7480301</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45714.69791666666</v>
+      </c>
+      <c r="F168">
+        <v>28</v>
+      </c>
+      <c r="G168" t="s">
+        <v>72</v>
+      </c>
+      <c r="H168" t="s">
+        <v>79</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
+      <c r="J168">
+        <v>1</v>
+      </c>
+      <c r="K168">
+        <v>2</v>
+      </c>
+      <c r="L168">
+        <v>1</v>
+      </c>
+      <c r="M168">
+        <v>3</v>
+      </c>
+      <c r="N168">
+        <v>4</v>
+      </c>
+      <c r="O168" t="s">
+        <v>139</v>
+      </c>
+      <c r="P168" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q168">
+        <v>3.4</v>
+      </c>
+      <c r="R168">
+        <v>2.2</v>
+      </c>
+      <c r="S168">
+        <v>3.1</v>
+      </c>
+      <c r="T168">
+        <v>1.4</v>
+      </c>
+      <c r="U168">
+        <v>2.75</v>
+      </c>
+      <c r="V168">
+        <v>2.75</v>
+      </c>
+      <c r="W168">
+        <v>1.4</v>
+      </c>
+      <c r="X168">
+        <v>8</v>
+      </c>
+      <c r="Y168">
+        <v>1.08</v>
+      </c>
+      <c r="Z168">
+        <v>2.56</v>
+      </c>
+      <c r="AA168">
+        <v>3.32</v>
+      </c>
+      <c r="AB168">
+        <v>2.64</v>
+      </c>
+      <c r="AC168">
+        <v>1.05</v>
+      </c>
+      <c r="AD168">
+        <v>11</v>
+      </c>
+      <c r="AE168">
+        <v>1.3</v>
+      </c>
+      <c r="AF168">
+        <v>3.5</v>
+      </c>
+      <c r="AG168">
+        <v>2.05</v>
+      </c>
+      <c r="AH168">
+        <v>1.7</v>
+      </c>
+      <c r="AI168">
+        <v>1.7</v>
+      </c>
+      <c r="AJ168">
+        <v>2.05</v>
+      </c>
+      <c r="AK168">
+        <v>1.47</v>
+      </c>
+      <c r="AL168">
+        <v>1.31</v>
+      </c>
+      <c r="AM168">
+        <v>1.46</v>
+      </c>
+      <c r="AN168">
+        <v>1.62</v>
+      </c>
+      <c r="AO168">
+        <v>1.08</v>
+      </c>
+      <c r="AP168">
+        <v>1.5</v>
+      </c>
+      <c r="AQ168">
+        <v>1.21</v>
+      </c>
+      <c r="AR168">
+        <v>1.35</v>
+      </c>
+      <c r="AS168">
+        <v>1.45</v>
+      </c>
+      <c r="AT168">
+        <v>2.8</v>
+      </c>
+      <c r="AU168">
+        <v>4</v>
+      </c>
+      <c r="AV168">
+        <v>6</v>
+      </c>
+      <c r="AW168">
+        <v>7</v>
+      </c>
+      <c r="AX168">
+        <v>4</v>
+      </c>
+      <c r="AY168">
+        <v>11</v>
+      </c>
+      <c r="AZ168">
+        <v>10</v>
+      </c>
+      <c r="BA168">
+        <v>1</v>
+      </c>
+      <c r="BB168">
+        <v>10</v>
+      </c>
+      <c r="BC168">
+        <v>11</v>
+      </c>
+      <c r="BD168">
+        <v>2.07</v>
+      </c>
+      <c r="BE168">
+        <v>6.75</v>
+      </c>
+      <c r="BF168">
+        <v>1.91</v>
+      </c>
+      <c r="BG168">
+        <v>1.2</v>
+      </c>
+      <c r="BH168">
+        <v>3.9</v>
+      </c>
+      <c r="BI168">
+        <v>1.36</v>
+      </c>
+      <c r="BJ168">
+        <v>2.8</v>
+      </c>
+      <c r="BK168">
+        <v>1.61</v>
+      </c>
+      <c r="BL168">
+        <v>2.15</v>
+      </c>
+      <c r="BM168">
+        <v>1.95</v>
+      </c>
+      <c r="BN168">
+        <v>1.75</v>
+      </c>
+      <c r="BO168">
+        <v>2.43</v>
+      </c>
+      <c r="BP168">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7480303</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45714.70833333334</v>
+      </c>
+      <c r="F169">
+        <v>28</v>
+      </c>
+      <c r="G169" t="s">
+        <v>81</v>
+      </c>
+      <c r="H169" t="s">
+        <v>76</v>
+      </c>
+      <c r="I169">
+        <v>2</v>
+      </c>
+      <c r="J169">
+        <v>1</v>
+      </c>
+      <c r="K169">
+        <v>3</v>
+      </c>
+      <c r="L169">
+        <v>2</v>
+      </c>
+      <c r="M169">
+        <v>4</v>
+      </c>
+      <c r="N169">
+        <v>6</v>
+      </c>
+      <c r="O169" t="s">
+        <v>209</v>
+      </c>
+      <c r="P169" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q169">
+        <v>5.5</v>
+      </c>
+      <c r="R169">
+        <v>2.38</v>
+      </c>
+      <c r="S169">
+        <v>2.1</v>
+      </c>
+      <c r="T169">
+        <v>1.33</v>
+      </c>
+      <c r="U169">
+        <v>3.25</v>
+      </c>
+      <c r="V169">
+        <v>2.63</v>
+      </c>
+      <c r="W169">
+        <v>1.44</v>
+      </c>
+      <c r="X169">
+        <v>6.5</v>
+      </c>
+      <c r="Y169">
+        <v>1.11</v>
+      </c>
+      <c r="Z169">
+        <v>5.9</v>
+      </c>
+      <c r="AA169">
+        <v>4.1</v>
+      </c>
+      <c r="AB169">
+        <v>1.52</v>
+      </c>
+      <c r="AC169">
+        <v>1.02</v>
+      </c>
+      <c r="AD169">
+        <v>15</v>
+      </c>
+      <c r="AE169">
+        <v>1.22</v>
+      </c>
+      <c r="AF169">
+        <v>4.2</v>
+      </c>
+      <c r="AG169">
+        <v>1.79</v>
+      </c>
+      <c r="AH169">
+        <v>1.95</v>
+      </c>
+      <c r="AI169">
+        <v>1.8</v>
+      </c>
+      <c r="AJ169">
+        <v>1.95</v>
+      </c>
+      <c r="AK169">
+        <v>2.4</v>
+      </c>
+      <c r="AL169">
+        <v>1.22</v>
+      </c>
+      <c r="AM169">
+        <v>1.13</v>
+      </c>
+      <c r="AN169">
+        <v>1.69</v>
+      </c>
+      <c r="AO169">
+        <v>1.46</v>
+      </c>
+      <c r="AP169">
+        <v>1.57</v>
+      </c>
+      <c r="AQ169">
+        <v>1.57</v>
+      </c>
+      <c r="AR169">
+        <v>1.42</v>
+      </c>
+      <c r="AS169">
+        <v>1.9</v>
+      </c>
+      <c r="AT169">
+        <v>3.32</v>
+      </c>
+      <c r="AU169">
+        <v>5</v>
+      </c>
+      <c r="AV169">
+        <v>10</v>
+      </c>
+      <c r="AW169">
+        <v>6</v>
+      </c>
+      <c r="AX169">
+        <v>8</v>
+      </c>
+      <c r="AY169">
+        <v>11</v>
+      </c>
+      <c r="AZ169">
+        <v>18</v>
+      </c>
+      <c r="BA169">
+        <v>6</v>
+      </c>
+      <c r="BB169">
+        <v>4</v>
+      </c>
+      <c r="BC169">
+        <v>10</v>
+      </c>
+      <c r="BD169">
+        <v>3.45</v>
+      </c>
+      <c r="BE169">
+        <v>7.5</v>
+      </c>
+      <c r="BF169">
+        <v>1.35</v>
+      </c>
+      <c r="BG169">
+        <v>1.25</v>
+      </c>
+      <c r="BH169">
+        <v>3.4</v>
+      </c>
+      <c r="BI169">
+        <v>1.44</v>
+      </c>
+      <c r="BJ169">
+        <v>2.55</v>
+      </c>
+      <c r="BK169">
+        <v>1.72</v>
+      </c>
+      <c r="BL169">
+        <v>1.97</v>
+      </c>
+      <c r="BM169">
+        <v>2.12</v>
+      </c>
+      <c r="BN169">
+        <v>1.63</v>
+      </c>
+      <c r="BO169">
+        <v>2.65</v>
+      </c>
+      <c r="BP169">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="299">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -646,6 +646,12 @@
     <t>['11', '14']</t>
   </si>
   <si>
+    <t>['35']</t>
+  </si>
+  <si>
+    <t>['33', '48']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -689,9 +695,6 @@
   </si>
   <si>
     <t>['44', '60', '84']</t>
-  </si>
-  <si>
-    <t>['35']</t>
   </si>
   <si>
     <t>['21', '79', '90+9']</t>
@@ -902,6 +905,12 @@
   </si>
   <si>
     <t>['35', '53', '62', '85']</t>
+  </si>
+  <si>
+    <t>['9', '30']</t>
+  </si>
+  <si>
+    <t>['28', '45+1', '68', '88', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1931,7 +1940,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2215,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5">
         <v>1.21</v>
@@ -2424,7 +2433,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ6">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2549,7 +2558,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2833,10 +2842,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ8">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2961,7 +2970,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3039,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9">
         <v>1.36</v>
@@ -3373,7 +3382,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3454,7 +3463,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ11">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3579,7 +3588,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3785,7 +3794,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -3866,7 +3875,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ13">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4072,7 +4081,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR14">
         <v>2.04</v>
@@ -4197,7 +4206,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4481,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ16">
         <v>1.07</v>
@@ -4609,7 +4618,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4687,10 +4696,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ17">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR17">
         <v>1.07</v>
@@ -5102,7 +5111,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ19">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR19">
         <v>1.1</v>
@@ -5227,7 +5236,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5433,7 +5442,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5514,7 +5523,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ21">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR21">
         <v>1.39</v>
@@ -5639,7 +5648,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5717,7 +5726,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22">
         <v>1.07</v>
@@ -6051,7 +6060,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6257,7 +6266,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6544,7 +6553,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ26">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR26">
         <v>1.12</v>
@@ -6956,7 +6965,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ28">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR28">
         <v>0.85</v>
@@ -7159,7 +7168,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ29">
         <v>0.86</v>
@@ -7287,7 +7296,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7365,10 +7374,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ30">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR30">
         <v>0.76</v>
@@ -7699,7 +7708,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7777,10 +7786,10 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR32">
         <v>1.31</v>
@@ -7983,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ33">
         <v>1.07</v>
@@ -8111,7 +8120,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8317,7 +8326,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8523,7 +8532,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8729,7 +8738,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8935,7 +8944,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9016,7 +9025,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ38">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR38">
         <v>1.42</v>
@@ -9219,7 +9228,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ39">
         <v>1.21</v>
@@ -9347,7 +9356,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9425,7 +9434,7 @@
         <v>1.67</v>
       </c>
       <c r="AP40">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ40">
         <v>1.36</v>
@@ -9553,7 +9562,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9634,7 +9643,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ41">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR41">
         <v>1.12</v>
@@ -9759,7 +9768,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9840,7 +9849,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ42">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR42">
         <v>1.64</v>
@@ -9965,7 +9974,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10043,10 +10052,10 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ43">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR43">
         <v>1.4</v>
@@ -10171,7 +10180,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10455,10 +10464,10 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ45">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR45">
         <v>1.85</v>
@@ -10583,7 +10592,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10789,7 +10798,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11201,7 +11210,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11819,7 +11828,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11900,7 +11909,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ52">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -12025,7 +12034,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12103,10 +12112,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ53">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR53">
         <v>1.34</v>
@@ -12643,7 +12652,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12724,7 +12733,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
@@ -12849,7 +12858,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -12927,7 +12936,7 @@
         <v>0.25</v>
       </c>
       <c r="AP57">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ57">
         <v>1.14</v>
@@ -13055,7 +13064,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13136,7 +13145,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ58">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR58">
         <v>1.54</v>
@@ -13339,7 +13348,7 @@
         <v>0.25</v>
       </c>
       <c r="AP59">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ59">
         <v>1.21</v>
@@ -13467,7 +13476,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13545,10 +13554,10 @@
         <v>1.17</v>
       </c>
       <c r="AP60">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ60">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR60">
         <v>1.06</v>
@@ -13673,7 +13682,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13754,7 +13763,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ61">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR61">
         <v>1.15</v>
@@ -14085,7 +14094,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14291,7 +14300,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14575,7 +14584,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ65">
         <v>1.07</v>
@@ -14703,7 +14712,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14784,7 +14793,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ66">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR66">
         <v>1.42</v>
@@ -14909,7 +14918,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15321,7 +15330,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15527,7 +15536,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15608,7 +15617,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ70">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR70">
         <v>1.19</v>
@@ -15733,7 +15742,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15939,7 +15948,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16020,7 +16029,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ72">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR72">
         <v>1.22</v>
@@ -16223,7 +16232,7 @@
         <v>0.57</v>
       </c>
       <c r="AP73">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ73">
         <v>1.07</v>
@@ -16432,7 +16441,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ74">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR74">
         <v>1.37</v>
@@ -16557,7 +16566,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16635,10 +16644,10 @@
         <v>1.8</v>
       </c>
       <c r="AP75">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ75">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR75">
         <v>1.29</v>
@@ -16841,7 +16850,7 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ76">
         <v>1.36</v>
@@ -16969,7 +16978,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17047,7 +17056,7 @@
         <v>2.5</v>
       </c>
       <c r="AP77">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ77">
         <v>1.07</v>
@@ -17175,7 +17184,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17381,7 +17390,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17462,7 +17471,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR79">
         <v>1.56</v>
@@ -17587,7 +17596,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18205,7 +18214,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18411,7 +18420,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18617,7 +18626,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18823,7 +18832,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19107,10 +19116,10 @@
         <v>0.88</v>
       </c>
       <c r="AP87">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ87">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR87">
         <v>1.99</v>
@@ -19316,7 +19325,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ88">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR88">
         <v>1.42</v>
@@ -19441,7 +19450,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19522,7 +19531,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ89">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19725,10 +19734,10 @@
         <v>1.29</v>
       </c>
       <c r="AP90">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ90">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR90">
         <v>1.21</v>
@@ -19934,7 +19943,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ91">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR91">
         <v>1.37</v>
@@ -20346,7 +20355,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ93">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR93">
         <v>1.35</v>
@@ -20677,7 +20686,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20755,7 +20764,7 @@
         <v>1.17</v>
       </c>
       <c r="AP95">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ95">
         <v>1.57</v>
@@ -20883,7 +20892,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21089,7 +21098,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21295,7 +21304,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21707,7 +21716,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21788,7 +21797,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ100">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR100">
         <v>1.24</v>
@@ -21913,7 +21922,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21991,7 +22000,7 @@
         <v>0.88</v>
       </c>
       <c r="AP101">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ101">
         <v>1.14</v>
@@ -22197,7 +22206,7 @@
         <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ102">
         <v>0.86</v>
@@ -22325,7 +22334,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22612,7 +22621,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR104">
         <v>1.42</v>
@@ -22818,7 +22827,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ105">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR105">
         <v>1.69</v>
@@ -22943,7 +22952,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23230,7 +23239,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ107">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR107">
         <v>2.23</v>
@@ -23355,7 +23364,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23767,7 +23776,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24051,7 +24060,7 @@
         <v>1.43</v>
       </c>
       <c r="AP111">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ111">
         <v>1.57</v>
@@ -24179,7 +24188,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24257,7 +24266,7 @@
         <v>0.44</v>
       </c>
       <c r="AP112">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ112">
         <v>1.07</v>
@@ -24466,7 +24475,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ113">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR113">
         <v>2.24</v>
@@ -24672,7 +24681,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ114">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR114">
         <v>1.47</v>
@@ -24797,7 +24806,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -25003,7 +25012,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25081,7 +25090,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ116">
         <v>0.86</v>
@@ -25493,10 +25502,10 @@
         <v>2.78</v>
       </c>
       <c r="AP118">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ118">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR118">
         <v>2.04</v>
@@ -25908,7 +25917,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ120">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR120">
         <v>1.65</v>
@@ -26239,7 +26248,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26445,7 +26454,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26651,7 +26660,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -27269,7 +27278,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27475,7 +27484,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27681,7 +27690,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -27968,7 +27977,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ130">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR130">
         <v>1.4</v>
@@ -28505,7 +28514,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28583,10 +28592,10 @@
         <v>2.5</v>
       </c>
       <c r="AP133">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ133">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR133">
         <v>1.25</v>
@@ -28789,7 +28798,7 @@
         <v>1.45</v>
       </c>
       <c r="AP134">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ134">
         <v>1.36</v>
@@ -28917,7 +28926,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -28998,7 +29007,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ135">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR135">
         <v>1.42</v>
@@ -29201,10 +29210,10 @@
         <v>0.73</v>
       </c>
       <c r="AP136">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ136">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR136">
         <v>2.05</v>
@@ -29535,7 +29544,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29616,7 +29625,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ138">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR138">
         <v>1.32</v>
@@ -29819,7 +29828,7 @@
         <v>1.2</v>
       </c>
       <c r="AP139">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ139">
         <v>1.07</v>
@@ -29947,7 +29956,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30153,7 +30162,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30234,7 +30243,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ141">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR141">
         <v>1.67</v>
@@ -30359,7 +30368,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30437,7 +30446,7 @@
         <v>1.09</v>
       </c>
       <c r="AP142">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ142">
         <v>1.21</v>
@@ -30565,7 +30574,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30646,7 +30655,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ143">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR143">
         <v>1.28</v>
@@ -30771,7 +30780,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30977,7 +30986,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31055,10 +31064,10 @@
         <v>0.67</v>
       </c>
       <c r="AP145">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ145">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR145">
         <v>1.26</v>
@@ -31183,7 +31192,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31879,7 +31888,7 @@
         <v>1.09</v>
       </c>
       <c r="AP149">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ149">
         <v>1.07</v>
@@ -32007,7 +32016,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32088,7 +32097,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ150">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR150">
         <v>1.15</v>
@@ -32625,7 +32634,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q153">
         <v>3.2</v>
@@ -32912,7 +32921,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ154">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -33037,7 +33046,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q155">
         <v>2.75</v>
@@ -33243,7 +33252,7 @@
         <v>201</v>
       </c>
       <c r="P156" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33527,7 +33536,7 @@
         <v>1.08</v>
       </c>
       <c r="AP157">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ157">
         <v>1.21</v>
@@ -33736,7 +33745,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ158">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR158">
         <v>1.37</v>
@@ -33942,7 +33951,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ159">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR159">
         <v>1.39</v>
@@ -34148,7 +34157,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ160">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR160">
         <v>1.35</v>
@@ -34273,7 +34282,7 @@
         <v>82</v>
       </c>
       <c r="P161" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q161">
         <v>1.57</v>
@@ -34351,7 +34360,7 @@
         <v>1.08</v>
       </c>
       <c r="AP161">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ161">
         <v>1.14</v>
@@ -34479,7 +34488,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q162">
         <v>3.1</v>
@@ -34557,7 +34566,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ162">
         <v>0.86</v>
@@ -34685,7 +34694,7 @@
         <v>140</v>
       </c>
       <c r="P163" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q163">
         <v>4.33</v>
@@ -34891,7 +34900,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q164">
         <v>1.57</v>
@@ -35509,7 +35518,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q167">
         <v>2.4</v>
@@ -35715,7 +35724,7 @@
         <v>139</v>
       </c>
       <c r="P168" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q168">
         <v>3.4</v>
@@ -35921,7 +35930,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36078,6 +36087,830 @@
       </c>
       <c r="BP169">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7480306</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45717.5</v>
+      </c>
+      <c r="F170">
+        <v>29</v>
+      </c>
+      <c r="G170" t="s">
+        <v>78</v>
+      </c>
+      <c r="H170" t="s">
+        <v>75</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>2</v>
+      </c>
+      <c r="L170">
+        <v>1</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+      <c r="N170">
+        <v>2</v>
+      </c>
+      <c r="O170" t="s">
+        <v>114</v>
+      </c>
+      <c r="P170" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q170">
+        <v>2.5</v>
+      </c>
+      <c r="R170">
+        <v>2.2</v>
+      </c>
+      <c r="S170">
+        <v>4.33</v>
+      </c>
+      <c r="T170">
+        <v>1.36</v>
+      </c>
+      <c r="U170">
+        <v>3</v>
+      </c>
+      <c r="V170">
+        <v>2.75</v>
+      </c>
+      <c r="W170">
+        <v>1.4</v>
+      </c>
+      <c r="X170">
+        <v>7</v>
+      </c>
+      <c r="Y170">
+        <v>1.1</v>
+      </c>
+      <c r="Z170">
+        <v>1.85</v>
+      </c>
+      <c r="AA170">
+        <v>3.59</v>
+      </c>
+      <c r="AB170">
+        <v>3.99</v>
+      </c>
+      <c r="AC170">
+        <v>1.04</v>
+      </c>
+      <c r="AD170">
+        <v>13</v>
+      </c>
+      <c r="AE170">
+        <v>1.28</v>
+      </c>
+      <c r="AF170">
+        <v>3.6</v>
+      </c>
+      <c r="AG170">
+        <v>1.8</v>
+      </c>
+      <c r="AH170">
+        <v>1.94</v>
+      </c>
+      <c r="AI170">
+        <v>1.75</v>
+      </c>
+      <c r="AJ170">
+        <v>2</v>
+      </c>
+      <c r="AK170">
+        <v>1.25</v>
+      </c>
+      <c r="AL170">
+        <v>1.22</v>
+      </c>
+      <c r="AM170">
+        <v>1.9</v>
+      </c>
+      <c r="AN170">
+        <v>1.07</v>
+      </c>
+      <c r="AO170">
+        <v>0.79</v>
+      </c>
+      <c r="AP170">
+        <v>1.07</v>
+      </c>
+      <c r="AQ170">
+        <v>0.8</v>
+      </c>
+      <c r="AR170">
+        <v>1.39</v>
+      </c>
+      <c r="AS170">
+        <v>1.02</v>
+      </c>
+      <c r="AT170">
+        <v>2.41</v>
+      </c>
+      <c r="AU170">
+        <v>6</v>
+      </c>
+      <c r="AV170">
+        <v>4</v>
+      </c>
+      <c r="AW170">
+        <v>9</v>
+      </c>
+      <c r="AX170">
+        <v>7</v>
+      </c>
+      <c r="AY170">
+        <v>15</v>
+      </c>
+      <c r="AZ170">
+        <v>11</v>
+      </c>
+      <c r="BA170">
+        <v>4</v>
+      </c>
+      <c r="BB170">
+        <v>4</v>
+      </c>
+      <c r="BC170">
+        <v>8</v>
+      </c>
+      <c r="BD170">
+        <v>1.45</v>
+      </c>
+      <c r="BE170">
+        <v>7</v>
+      </c>
+      <c r="BF170">
+        <v>3.05</v>
+      </c>
+      <c r="BG170">
+        <v>1.26</v>
+      </c>
+      <c r="BH170">
+        <v>3.4</v>
+      </c>
+      <c r="BI170">
+        <v>1.46</v>
+      </c>
+      <c r="BJ170">
+        <v>2.5</v>
+      </c>
+      <c r="BK170">
+        <v>1.73</v>
+      </c>
+      <c r="BL170">
+        <v>1.96</v>
+      </c>
+      <c r="BM170">
+        <v>2.14</v>
+      </c>
+      <c r="BN170">
+        <v>1.62</v>
+      </c>
+      <c r="BO170">
+        <v>2.7</v>
+      </c>
+      <c r="BP170">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7480308</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45717.5</v>
+      </c>
+      <c r="F171">
+        <v>29</v>
+      </c>
+      <c r="G171" t="s">
+        <v>76</v>
+      </c>
+      <c r="H171" t="s">
+        <v>71</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>2</v>
+      </c>
+      <c r="K171">
+        <v>2</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="M171">
+        <v>2</v>
+      </c>
+      <c r="N171">
+        <v>3</v>
+      </c>
+      <c r="O171" t="s">
+        <v>199</v>
+      </c>
+      <c r="P171" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q171">
+        <v>1.53</v>
+      </c>
+      <c r="R171">
+        <v>3</v>
+      </c>
+      <c r="S171">
+        <v>11</v>
+      </c>
+      <c r="T171">
+        <v>1.22</v>
+      </c>
+      <c r="U171">
+        <v>4</v>
+      </c>
+      <c r="V171">
+        <v>2.1</v>
+      </c>
+      <c r="W171">
+        <v>1.67</v>
+      </c>
+      <c r="X171">
+        <v>4.5</v>
+      </c>
+      <c r="Y171">
+        <v>1.18</v>
+      </c>
+      <c r="Z171">
+        <v>1.18</v>
+      </c>
+      <c r="AA171">
+        <v>6.5</v>
+      </c>
+      <c r="AB171">
+        <v>15</v>
+      </c>
+      <c r="AC171">
+        <v>0</v>
+      </c>
+      <c r="AD171">
+        <v>0</v>
+      </c>
+      <c r="AE171">
+        <v>1.12</v>
+      </c>
+      <c r="AF171">
+        <v>6</v>
+      </c>
+      <c r="AG171">
+        <v>1.28</v>
+      </c>
+      <c r="AH171">
+        <v>3.47</v>
+      </c>
+      <c r="AI171">
+        <v>2.05</v>
+      </c>
+      <c r="AJ171">
+        <v>1.7</v>
+      </c>
+      <c r="AK171">
+        <v>1.02</v>
+      </c>
+      <c r="AL171">
+        <v>1.1</v>
+      </c>
+      <c r="AM171">
+        <v>4.75</v>
+      </c>
+      <c r="AN171">
+        <v>2.64</v>
+      </c>
+      <c r="AO171">
+        <v>0.93</v>
+      </c>
+      <c r="AP171">
+        <v>2.47</v>
+      </c>
+      <c r="AQ171">
+        <v>1.07</v>
+      </c>
+      <c r="AR171">
+        <v>2.14</v>
+      </c>
+      <c r="AS171">
+        <v>1.13</v>
+      </c>
+      <c r="AT171">
+        <v>3.27</v>
+      </c>
+      <c r="AU171">
+        <v>9</v>
+      </c>
+      <c r="AV171">
+        <v>3</v>
+      </c>
+      <c r="AW171">
+        <v>16</v>
+      </c>
+      <c r="AX171">
+        <v>3</v>
+      </c>
+      <c r="AY171">
+        <v>25</v>
+      </c>
+      <c r="AZ171">
+        <v>6</v>
+      </c>
+      <c r="BA171">
+        <v>12</v>
+      </c>
+      <c r="BB171">
+        <v>3</v>
+      </c>
+      <c r="BC171">
+        <v>15</v>
+      </c>
+      <c r="BD171">
+        <v>1.13</v>
+      </c>
+      <c r="BE171">
+        <v>11</v>
+      </c>
+      <c r="BF171">
+        <v>5.8</v>
+      </c>
+      <c r="BG171">
+        <v>1.19</v>
+      </c>
+      <c r="BH171">
+        <v>4.1</v>
+      </c>
+      <c r="BI171">
+        <v>1.32</v>
+      </c>
+      <c r="BJ171">
+        <v>3</v>
+      </c>
+      <c r="BK171">
+        <v>1.53</v>
+      </c>
+      <c r="BL171">
+        <v>2.3</v>
+      </c>
+      <c r="BM171">
+        <v>1.83</v>
+      </c>
+      <c r="BN171">
+        <v>1.85</v>
+      </c>
+      <c r="BO171">
+        <v>2.28</v>
+      </c>
+      <c r="BP171">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7480309</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45717.5</v>
+      </c>
+      <c r="F172">
+        <v>29</v>
+      </c>
+      <c r="G172" t="s">
+        <v>77</v>
+      </c>
+      <c r="H172" t="s">
+        <v>81</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>1</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>1</v>
+      </c>
+      <c r="O172" t="s">
+        <v>210</v>
+      </c>
+      <c r="P172" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q172">
+        <v>4</v>
+      </c>
+      <c r="R172">
+        <v>2.1</v>
+      </c>
+      <c r="S172">
+        <v>2.75</v>
+      </c>
+      <c r="T172">
+        <v>1.4</v>
+      </c>
+      <c r="U172">
+        <v>2.75</v>
+      </c>
+      <c r="V172">
+        <v>3</v>
+      </c>
+      <c r="W172">
+        <v>1.36</v>
+      </c>
+      <c r="X172">
+        <v>8</v>
+      </c>
+      <c r="Y172">
+        <v>1.08</v>
+      </c>
+      <c r="Z172">
+        <v>3.37</v>
+      </c>
+      <c r="AA172">
+        <v>3.27</v>
+      </c>
+      <c r="AB172">
+        <v>2.14</v>
+      </c>
+      <c r="AC172">
+        <v>1.05</v>
+      </c>
+      <c r="AD172">
+        <v>10</v>
+      </c>
+      <c r="AE172">
+        <v>1.33</v>
+      </c>
+      <c r="AF172">
+        <v>3.3</v>
+      </c>
+      <c r="AG172">
+        <v>1.91</v>
+      </c>
+      <c r="AH172">
+        <v>1.83</v>
+      </c>
+      <c r="AI172">
+        <v>1.75</v>
+      </c>
+      <c r="AJ172">
+        <v>2</v>
+      </c>
+      <c r="AK172">
+        <v>1.68</v>
+      </c>
+      <c r="AL172">
+        <v>1.31</v>
+      </c>
+      <c r="AM172">
+        <v>1.31</v>
+      </c>
+      <c r="AN172">
+        <v>1.21</v>
+      </c>
+      <c r="AO172">
+        <v>0.64</v>
+      </c>
+      <c r="AP172">
+        <v>1.33</v>
+      </c>
+      <c r="AQ172">
+        <v>0.6</v>
+      </c>
+      <c r="AR172">
+        <v>1.27</v>
+      </c>
+      <c r="AS172">
+        <v>1.22</v>
+      </c>
+      <c r="AT172">
+        <v>2.49</v>
+      </c>
+      <c r="AU172">
+        <v>3</v>
+      </c>
+      <c r="AV172">
+        <v>6</v>
+      </c>
+      <c r="AW172">
+        <v>5</v>
+      </c>
+      <c r="AX172">
+        <v>15</v>
+      </c>
+      <c r="AY172">
+        <v>8</v>
+      </c>
+      <c r="AZ172">
+        <v>21</v>
+      </c>
+      <c r="BA172">
+        <v>5</v>
+      </c>
+      <c r="BB172">
+        <v>6</v>
+      </c>
+      <c r="BC172">
+        <v>11</v>
+      </c>
+      <c r="BD172">
+        <v>2.48</v>
+      </c>
+      <c r="BE172">
+        <v>7</v>
+      </c>
+      <c r="BF172">
+        <v>1.64</v>
+      </c>
+      <c r="BG172">
+        <v>1.19</v>
+      </c>
+      <c r="BH172">
+        <v>4.1</v>
+      </c>
+      <c r="BI172">
+        <v>1.32</v>
+      </c>
+      <c r="BJ172">
+        <v>3.05</v>
+      </c>
+      <c r="BK172">
+        <v>1.53</v>
+      </c>
+      <c r="BL172">
+        <v>2.3</v>
+      </c>
+      <c r="BM172">
+        <v>1.84</v>
+      </c>
+      <c r="BN172">
+        <v>1.84</v>
+      </c>
+      <c r="BO172">
+        <v>2.28</v>
+      </c>
+      <c r="BP172">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7480310</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45717.60416666666</v>
+      </c>
+      <c r="F173">
+        <v>29</v>
+      </c>
+      <c r="G173" t="s">
+        <v>73</v>
+      </c>
+      <c r="H173" t="s">
+        <v>74</v>
+      </c>
+      <c r="I173">
+        <v>1</v>
+      </c>
+      <c r="J173">
+        <v>2</v>
+      </c>
+      <c r="K173">
+        <v>3</v>
+      </c>
+      <c r="L173">
+        <v>2</v>
+      </c>
+      <c r="M173">
+        <v>5</v>
+      </c>
+      <c r="N173">
+        <v>7</v>
+      </c>
+      <c r="O173" t="s">
+        <v>211</v>
+      </c>
+      <c r="P173" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q173">
+        <v>10</v>
+      </c>
+      <c r="R173">
+        <v>2.88</v>
+      </c>
+      <c r="S173">
+        <v>1.57</v>
+      </c>
+      <c r="T173">
+        <v>1.25</v>
+      </c>
+      <c r="U173">
+        <v>3.75</v>
+      </c>
+      <c r="V173">
+        <v>2.2</v>
+      </c>
+      <c r="W173">
+        <v>1.62</v>
+      </c>
+      <c r="X173">
+        <v>5</v>
+      </c>
+      <c r="Y173">
+        <v>1.17</v>
+      </c>
+      <c r="Z173">
+        <v>13</v>
+      </c>
+      <c r="AA173">
+        <v>6.4</v>
+      </c>
+      <c r="AB173">
+        <v>1.2</v>
+      </c>
+      <c r="AC173">
+        <v>1.01</v>
+      </c>
+      <c r="AD173">
+        <v>17</v>
+      </c>
+      <c r="AE173">
+        <v>1.14</v>
+      </c>
+      <c r="AF173">
+        <v>5.5</v>
+      </c>
+      <c r="AG173">
+        <v>1.58</v>
+      </c>
+      <c r="AH173">
+        <v>2.3</v>
+      </c>
+      <c r="AI173">
+        <v>2.1</v>
+      </c>
+      <c r="AJ173">
+        <v>1.67</v>
+      </c>
+      <c r="AK173">
+        <v>4.2</v>
+      </c>
+      <c r="AL173">
+        <v>1.11</v>
+      </c>
+      <c r="AM173">
+        <v>1.04</v>
+      </c>
+      <c r="AN173">
+        <v>1.29</v>
+      </c>
+      <c r="AO173">
+        <v>2.29</v>
+      </c>
+      <c r="AP173">
+        <v>1.2</v>
+      </c>
+      <c r="AQ173">
+        <v>2.33</v>
+      </c>
+      <c r="AR173">
+        <v>1.32</v>
+      </c>
+      <c r="AS173">
+        <v>1.9</v>
+      </c>
+      <c r="AT173">
+        <v>3.22</v>
+      </c>
+      <c r="AU173">
+        <v>8</v>
+      </c>
+      <c r="AV173">
+        <v>10</v>
+      </c>
+      <c r="AW173">
+        <v>7</v>
+      </c>
+      <c r="AX173">
+        <v>8</v>
+      </c>
+      <c r="AY173">
+        <v>15</v>
+      </c>
+      <c r="AZ173">
+        <v>18</v>
+      </c>
+      <c r="BA173">
+        <v>3</v>
+      </c>
+      <c r="BB173">
+        <v>3</v>
+      </c>
+      <c r="BC173">
+        <v>6</v>
+      </c>
+      <c r="BD173">
+        <v>5.4</v>
+      </c>
+      <c r="BE173">
+        <v>10</v>
+      </c>
+      <c r="BF173">
+        <v>1.16</v>
+      </c>
+      <c r="BG173">
+        <v>1.18</v>
+      </c>
+      <c r="BH173">
+        <v>4.1</v>
+      </c>
+      <c r="BI173">
+        <v>1.32</v>
+      </c>
+      <c r="BJ173">
+        <v>3.05</v>
+      </c>
+      <c r="BK173">
+        <v>1.54</v>
+      </c>
+      <c r="BL173">
+        <v>2.3</v>
+      </c>
+      <c r="BM173">
+        <v>1.84</v>
+      </c>
+      <c r="BN173">
+        <v>1.84</v>
+      </c>
+      <c r="BO173">
+        <v>2.28</v>
+      </c>
+      <c r="BP173">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -652,6 +652,9 @@
     <t>['33', '48']</t>
   </si>
   <si>
+    <t>['6', '74']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -1272,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1940,7 +1943,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2558,7 +2561,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2970,7 +2973,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3257,7 +3260,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ10">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3382,7 +3385,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3460,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ11">
         <v>2.33</v>
@@ -3588,7 +3591,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3794,7 +3797,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -4206,7 +4209,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4284,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ15">
         <v>0.86</v>
@@ -4618,7 +4621,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4905,7 +4908,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ18">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>1.47</v>
@@ -5236,7 +5239,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5442,7 +5445,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5648,7 +5651,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6060,7 +6063,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6266,7 +6269,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6759,7 +6762,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ27">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>2.21</v>
@@ -6962,7 +6965,7 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ28">
         <v>0.8</v>
@@ -7296,7 +7299,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7708,7 +7711,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7995,7 +7998,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ33">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>0.87</v>
@@ -8326,7 +8329,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8532,7 +8535,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8738,7 +8741,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8944,7 +8947,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9356,7 +9359,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9562,7 +9565,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9640,7 +9643,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ41">
         <v>1.07</v>
@@ -9768,7 +9771,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9974,7 +9977,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10180,7 +10183,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10261,7 +10264,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ44">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.19</v>
@@ -10592,7 +10595,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10798,7 +10801,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11210,7 +11213,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11828,7 +11831,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12034,7 +12037,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12524,10 +12527,10 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ55">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>1.27</v>
@@ -12652,7 +12655,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12858,7 +12861,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -13064,7 +13067,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13476,7 +13479,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13682,7 +13685,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14094,7 +14097,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14300,7 +14303,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14381,7 +14384,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ64">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR64">
         <v>1.33</v>
@@ -14712,7 +14715,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14918,7 +14921,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -14996,7 +14999,7 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ67">
         <v>1.36</v>
@@ -15330,7 +15333,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15408,7 +15411,7 @@
         <v>0.2</v>
       </c>
       <c r="AP69">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ69">
         <v>1.14</v>
@@ -15536,7 +15539,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15742,7 +15745,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15948,7 +15951,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16235,7 +16238,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ73">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR73">
         <v>1.87</v>
@@ -16566,7 +16569,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16978,7 +16981,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17184,7 +17187,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17390,7 +17393,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17596,7 +17599,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17674,7 +17677,7 @@
         <v>2</v>
       </c>
       <c r="AP80">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ80">
         <v>1.07</v>
@@ -18214,7 +18217,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18420,7 +18423,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18626,7 +18629,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18832,7 +18835,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19450,7 +19453,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -20686,7 +20689,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20892,7 +20895,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21098,7 +21101,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21176,7 +21179,7 @@
         <v>0.43</v>
       </c>
       <c r="AP97">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ97">
         <v>1.07</v>
@@ -21304,7 +21307,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21591,7 +21594,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ99">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR99">
         <v>1.4</v>
@@ -21716,7 +21719,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21922,7 +21925,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22334,7 +22337,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22952,7 +22955,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23364,7 +23367,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23776,7 +23779,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24188,7 +24191,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24269,7 +24272,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ112">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>1.24</v>
@@ -24678,7 +24681,7 @@
         <v>0.82</v>
       </c>
       <c r="AP114">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ114">
         <v>0.6</v>
@@ -24806,7 +24809,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -25012,7 +25015,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -26248,7 +26251,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26454,7 +26457,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26660,7 +26663,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26738,7 +26741,7 @@
         <v>1.22</v>
       </c>
       <c r="AP124">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ124">
         <v>1.57</v>
@@ -27278,7 +27281,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27359,7 +27362,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ127">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR127">
         <v>1.36</v>
@@ -27484,7 +27487,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27690,7 +27693,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -28514,7 +28517,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28926,7 +28929,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29004,7 +29007,7 @@
         <v>1.18</v>
       </c>
       <c r="AP135">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ135">
         <v>1.07</v>
@@ -29419,7 +29422,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ137">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR137">
         <v>1.38</v>
@@ -29544,7 +29547,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29956,7 +29959,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30162,7 +30165,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30368,7 +30371,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30574,7 +30577,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30780,7 +30783,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30986,7 +30989,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31192,7 +31195,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31273,7 +31276,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ146">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR146">
         <v>1.31</v>
@@ -31476,7 +31479,7 @@
         <v>1.09</v>
       </c>
       <c r="AP147">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ147">
         <v>1.07</v>
@@ -32016,7 +32019,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32634,7 +32637,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q153">
         <v>3.2</v>
@@ -33046,7 +33049,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q155">
         <v>2.75</v>
@@ -33252,7 +33255,7 @@
         <v>201</v>
       </c>
       <c r="P156" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33742,7 +33745,7 @@
         <v>2.46</v>
       </c>
       <c r="AP158">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ158">
         <v>2.33</v>
@@ -34282,7 +34285,7 @@
         <v>82</v>
       </c>
       <c r="P161" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q161">
         <v>1.57</v>
@@ -34488,7 +34491,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q162">
         <v>3.1</v>
@@ -34694,7 +34697,7 @@
         <v>140</v>
       </c>
       <c r="P163" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q163">
         <v>4.33</v>
@@ -34775,7 +34778,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ163">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR163">
         <v>1.34</v>
@@ -34900,7 +34903,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q164">
         <v>1.57</v>
@@ -35518,7 +35521,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q167">
         <v>2.4</v>
@@ -35724,7 +35727,7 @@
         <v>139</v>
       </c>
       <c r="P168" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q168">
         <v>3.4</v>
@@ -35930,7 +35933,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36342,7 +36345,7 @@
         <v>199</v>
       </c>
       <c r="P171" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q171">
         <v>1.53</v>
@@ -36754,7 +36757,7 @@
         <v>211</v>
       </c>
       <c r="P173" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q173">
         <v>10</v>
@@ -36911,6 +36914,212 @@
       </c>
       <c r="BP173">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7480307</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45718.39583333334</v>
+      </c>
+      <c r="F174">
+        <v>29</v>
+      </c>
+      <c r="G174" t="s">
+        <v>79</v>
+      </c>
+      <c r="H174" t="s">
+        <v>70</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174">
+        <v>2</v>
+      </c>
+      <c r="L174">
+        <v>2</v>
+      </c>
+      <c r="M174">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>3</v>
+      </c>
+      <c r="O174" t="s">
+        <v>212</v>
+      </c>
+      <c r="P174" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q174">
+        <v>3</v>
+      </c>
+      <c r="R174">
+        <v>2.1</v>
+      </c>
+      <c r="S174">
+        <v>3.6</v>
+      </c>
+      <c r="T174">
+        <v>1.4</v>
+      </c>
+      <c r="U174">
+        <v>2.75</v>
+      </c>
+      <c r="V174">
+        <v>3</v>
+      </c>
+      <c r="W174">
+        <v>1.36</v>
+      </c>
+      <c r="X174">
+        <v>8</v>
+      </c>
+      <c r="Y174">
+        <v>1.08</v>
+      </c>
+      <c r="Z174">
+        <v>2.29</v>
+      </c>
+      <c r="AA174">
+        <v>3.37</v>
+      </c>
+      <c r="AB174">
+        <v>2.98</v>
+      </c>
+      <c r="AC174">
+        <v>1.05</v>
+      </c>
+      <c r="AD174">
+        <v>11</v>
+      </c>
+      <c r="AE174">
+        <v>1.3</v>
+      </c>
+      <c r="AF174">
+        <v>3.4</v>
+      </c>
+      <c r="AG174">
+        <v>1.87</v>
+      </c>
+      <c r="AH174">
+        <v>1.87</v>
+      </c>
+      <c r="AI174">
+        <v>1.75</v>
+      </c>
+      <c r="AJ174">
+        <v>2</v>
+      </c>
+      <c r="AK174">
+        <v>1.37</v>
+      </c>
+      <c r="AL174">
+        <v>1.3</v>
+      </c>
+      <c r="AM174">
+        <v>1.58</v>
+      </c>
+      <c r="AN174">
+        <v>1.64</v>
+      </c>
+      <c r="AO174">
+        <v>1.07</v>
+      </c>
+      <c r="AP174">
+        <v>1.73</v>
+      </c>
+      <c r="AQ174">
+        <v>1</v>
+      </c>
+      <c r="AR174">
+        <v>1.38</v>
+      </c>
+      <c r="AS174">
+        <v>1.24</v>
+      </c>
+      <c r="AT174">
+        <v>2.62</v>
+      </c>
+      <c r="AU174">
+        <v>5</v>
+      </c>
+      <c r="AV174">
+        <v>4</v>
+      </c>
+      <c r="AW174">
+        <v>7</v>
+      </c>
+      <c r="AX174">
+        <v>8</v>
+      </c>
+      <c r="AY174">
+        <v>12</v>
+      </c>
+      <c r="AZ174">
+        <v>12</v>
+      </c>
+      <c r="BA174">
+        <v>4</v>
+      </c>
+      <c r="BB174">
+        <v>6</v>
+      </c>
+      <c r="BC174">
+        <v>10</v>
+      </c>
+      <c r="BD174">
+        <v>1.84</v>
+      </c>
+      <c r="BE174">
+        <v>6.75</v>
+      </c>
+      <c r="BF174">
+        <v>2.1</v>
+      </c>
+      <c r="BG174">
+        <v>1.15</v>
+      </c>
+      <c r="BH174">
+        <v>4.6</v>
+      </c>
+      <c r="BI174">
+        <v>1.27</v>
+      </c>
+      <c r="BJ174">
+        <v>3.3</v>
+      </c>
+      <c r="BK174">
+        <v>1.46</v>
+      </c>
+      <c r="BL174">
+        <v>2.5</v>
+      </c>
+      <c r="BM174">
+        <v>1.72</v>
+      </c>
+      <c r="BN174">
+        <v>1.98</v>
+      </c>
+      <c r="BO174">
+        <v>2.07</v>
+      </c>
+      <c r="BP174">
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="302">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -655,6 +655,9 @@
     <t>['6', '74']</t>
   </si>
   <si>
+    <t>['75', '90+1']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -914,6 +917,9 @@
   </si>
   <si>
     <t>['28', '45+1', '68', '88', '90+3']</t>
+  </si>
+  <si>
+    <t>['20', '45+9']</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP174"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1943,7 +1949,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2561,7 +2567,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2973,7 +2979,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3054,7 +3060,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ9">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3385,7 +3391,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3591,7 +3597,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3669,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ12">
         <v>1.14</v>
@@ -3797,7 +3803,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -4209,7 +4215,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4621,7 +4627,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -5111,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ19">
         <v>0.6</v>
@@ -5239,7 +5245,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5445,7 +5451,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5651,7 +5657,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6063,7 +6069,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6144,7 +6150,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR24">
         <v>1.14</v>
@@ -6269,7 +6275,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6553,7 +6559,7 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ26">
         <v>1.07</v>
@@ -7299,7 +7305,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7711,7 +7717,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8329,7 +8335,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8410,7 +8416,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ35">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR35">
         <v>1.32</v>
@@ -8535,7 +8541,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8741,7 +8747,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8947,7 +8953,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9359,7 +9365,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9440,7 +9446,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ40">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR40">
         <v>0.9399999999999999</v>
@@ -9565,7 +9571,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9771,7 +9777,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9977,7 +9983,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10183,7 +10189,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10261,7 +10267,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10595,7 +10601,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10801,7 +10807,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11213,7 +11219,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11831,7 +11837,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12037,7 +12043,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12321,10 +12327,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ54">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR54">
         <v>1.17</v>
@@ -12655,7 +12661,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12861,7 +12867,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -13067,7 +13073,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13479,7 +13485,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13685,7 +13691,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14097,7 +14103,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14175,7 +14181,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ63">
         <v>1.57</v>
@@ -14303,7 +14309,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14715,7 +14721,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14921,7 +14927,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15002,7 +15008,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ67">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR67">
         <v>1.3</v>
@@ -15333,7 +15339,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15539,7 +15545,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15745,7 +15751,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15823,7 +15829,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ71">
         <v>0.86</v>
@@ -15951,7 +15957,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16569,7 +16575,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16856,7 +16862,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ76">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR76">
         <v>1.75</v>
@@ -16981,7 +16987,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17187,7 +17193,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17393,7 +17399,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17599,7 +17605,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18217,7 +18223,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18423,7 +18429,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18629,7 +18635,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18835,7 +18841,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19453,7 +19459,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19531,7 +19537,7 @@
         <v>3</v>
       </c>
       <c r="AP89">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ89">
         <v>2.33</v>
@@ -19943,7 +19949,7 @@
         <v>0.88</v>
       </c>
       <c r="AP91">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ91">
         <v>0.8</v>
@@ -20689,7 +20695,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20895,7 +20901,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21101,7 +21107,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21307,7 +21313,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21388,7 +21394,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ98">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR98">
         <v>1.21</v>
@@ -21719,7 +21725,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21925,7 +21931,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22337,7 +22343,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22415,7 +22421,7 @@
         <v>0.63</v>
       </c>
       <c r="AP103">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ103">
         <v>1.21</v>
@@ -22955,7 +22961,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23367,7 +23373,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23779,7 +23785,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23860,7 +23866,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ110">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR110">
         <v>1.25</v>
@@ -24191,7 +24197,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24809,7 +24815,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -25015,7 +25021,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -26251,7 +26257,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26329,7 +26335,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ122">
         <v>1.07</v>
@@ -26457,7 +26463,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26538,7 +26544,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ123">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR123">
         <v>1.36</v>
@@ -26663,7 +26669,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -27281,7 +27287,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27487,7 +27493,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27693,7 +27699,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -28186,7 +28192,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ131">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR131">
         <v>2.28</v>
@@ -28517,7 +28523,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28804,7 +28810,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ134">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR134">
         <v>1.22</v>
@@ -28929,7 +28935,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29419,7 +29425,7 @@
         <v>0.73</v>
       </c>
       <c r="AP137">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ137">
         <v>1</v>
@@ -29547,7 +29553,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29959,7 +29965,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30037,7 +30043,7 @@
         <v>0.91</v>
       </c>
       <c r="AP140">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ140">
         <v>1.14</v>
@@ -30165,7 +30171,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30371,7 +30377,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30577,7 +30583,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30783,7 +30789,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30989,7 +30995,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31195,7 +31201,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31688,7 +31694,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ148">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR148">
         <v>1.42</v>
@@ -32019,7 +32025,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32512,7 +32518,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ152">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR152">
         <v>2.26</v>
@@ -32637,7 +32643,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q153">
         <v>3.2</v>
@@ -33049,7 +33055,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q155">
         <v>2.75</v>
@@ -33255,7 +33261,7 @@
         <v>201</v>
       </c>
       <c r="P156" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33951,7 +33957,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP159">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ159">
         <v>0.6</v>
@@ -34285,7 +34291,7 @@
         <v>82</v>
       </c>
       <c r="P161" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q161">
         <v>1.57</v>
@@ -34491,7 +34497,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q162">
         <v>3.1</v>
@@ -34697,7 +34703,7 @@
         <v>140</v>
       </c>
       <c r="P163" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q163">
         <v>4.33</v>
@@ -34903,7 +34909,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q164">
         <v>1.57</v>
@@ -35521,7 +35527,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q167">
         <v>2.4</v>
@@ -35727,7 +35733,7 @@
         <v>139</v>
       </c>
       <c r="P168" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q168">
         <v>3.4</v>
@@ -35933,7 +35939,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36345,7 +36351,7 @@
         <v>199</v>
       </c>
       <c r="P171" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q171">
         <v>1.53</v>
@@ -36757,7 +36763,7 @@
         <v>211</v>
       </c>
       <c r="P173" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q173">
         <v>10</v>
@@ -36963,7 +36969,7 @@
         <v>212</v>
       </c>
       <c r="P174" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q174">
         <v>3</v>
@@ -37120,6 +37126,212 @@
       </c>
       <c r="BP174">
         <v>1.65</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7480305</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45718.5</v>
+      </c>
+      <c r="F175">
+        <v>29</v>
+      </c>
+      <c r="G175" t="s">
+        <v>80</v>
+      </c>
+      <c r="H175" t="s">
+        <v>72</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>2</v>
+      </c>
+      <c r="K175">
+        <v>2</v>
+      </c>
+      <c r="L175">
+        <v>2</v>
+      </c>
+      <c r="M175">
+        <v>2</v>
+      </c>
+      <c r="N175">
+        <v>4</v>
+      </c>
+      <c r="O175" t="s">
+        <v>213</v>
+      </c>
+      <c r="P175" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q175">
+        <v>2.88</v>
+      </c>
+      <c r="R175">
+        <v>2.1</v>
+      </c>
+      <c r="S175">
+        <v>3.75</v>
+      </c>
+      <c r="T175">
+        <v>1.4</v>
+      </c>
+      <c r="U175">
+        <v>2.75</v>
+      </c>
+      <c r="V175">
+        <v>3</v>
+      </c>
+      <c r="W175">
+        <v>1.36</v>
+      </c>
+      <c r="X175">
+        <v>8</v>
+      </c>
+      <c r="Y175">
+        <v>1.08</v>
+      </c>
+      <c r="Z175">
+        <v>2.15</v>
+      </c>
+      <c r="AA175">
+        <v>3.23</v>
+      </c>
+      <c r="AB175">
+        <v>3.39</v>
+      </c>
+      <c r="AC175">
+        <v>1.06</v>
+      </c>
+      <c r="AD175">
+        <v>9.5</v>
+      </c>
+      <c r="AE175">
+        <v>1.33</v>
+      </c>
+      <c r="AF175">
+        <v>3.25</v>
+      </c>
+      <c r="AG175">
+        <v>1.98</v>
+      </c>
+      <c r="AH175">
+        <v>1.77</v>
+      </c>
+      <c r="AI175">
+        <v>1.75</v>
+      </c>
+      <c r="AJ175">
+        <v>2</v>
+      </c>
+      <c r="AK175">
+        <v>1.32</v>
+      </c>
+      <c r="AL175">
+        <v>1.31</v>
+      </c>
+      <c r="AM175">
+        <v>1.66</v>
+      </c>
+      <c r="AN175">
+        <v>1.86</v>
+      </c>
+      <c r="AO175">
+        <v>1.36</v>
+      </c>
+      <c r="AP175">
+        <v>1.8</v>
+      </c>
+      <c r="AQ175">
+        <v>1.33</v>
+      </c>
+      <c r="AR175">
+        <v>1.38</v>
+      </c>
+      <c r="AS175">
+        <v>1.25</v>
+      </c>
+      <c r="AT175">
+        <v>2.63</v>
+      </c>
+      <c r="AU175">
+        <v>3</v>
+      </c>
+      <c r="AV175">
+        <v>4</v>
+      </c>
+      <c r="AW175">
+        <v>17</v>
+      </c>
+      <c r="AX175">
+        <v>8</v>
+      </c>
+      <c r="AY175">
+        <v>20</v>
+      </c>
+      <c r="AZ175">
+        <v>12</v>
+      </c>
+      <c r="BA175">
+        <v>14</v>
+      </c>
+      <c r="BB175">
+        <v>5</v>
+      </c>
+      <c r="BC175">
+        <v>19</v>
+      </c>
+      <c r="BD175">
+        <v>1.63</v>
+      </c>
+      <c r="BE175">
+        <v>6.75</v>
+      </c>
+      <c r="BF175">
+        <v>2.5</v>
+      </c>
+      <c r="BG175">
+        <v>1.22</v>
+      </c>
+      <c r="BH175">
+        <v>3.7</v>
+      </c>
+      <c r="BI175">
+        <v>1.38</v>
+      </c>
+      <c r="BJ175">
+        <v>2.7</v>
+      </c>
+      <c r="BK175">
+        <v>1.63</v>
+      </c>
+      <c r="BL175">
+        <v>2.1</v>
+      </c>
+      <c r="BM175">
+        <v>1.98</v>
+      </c>
+      <c r="BN175">
+        <v>1.72</v>
+      </c>
+      <c r="BO175">
+        <v>2.5</v>
+      </c>
+      <c r="BP175">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="305">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -658,6 +658,12 @@
     <t>['75', '90+1']</t>
   </si>
   <si>
+    <t>['26', '89']</t>
+  </si>
+  <si>
+    <t>['35', '71']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -920,6 +926,9 @@
   </si>
   <si>
     <t>['20', '45+9']</t>
+  </si>
+  <si>
+    <t>['23', '33']</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP175"/>
+  <dimension ref="A1:BP179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1615,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ2">
         <v>1.57</v>
@@ -1821,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ3">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1949,7 +1958,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2236,7 +2245,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2567,7 +2576,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2979,7 +2988,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3391,7 +3400,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3597,7 +3606,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3678,7 +3687,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ12">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3803,7 +3812,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -3881,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ13">
         <v>0.8</v>
@@ -4215,7 +4224,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4502,7 +4511,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ16">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>2.02</v>
@@ -4627,7 +4636,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4911,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5245,7 +5254,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5326,7 +5335,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ20">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR20">
         <v>1.56</v>
@@ -5451,7 +5460,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5657,7 +5666,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6069,7 +6078,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6147,7 +6156,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ24">
         <v>1.33</v>
@@ -6275,7 +6284,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6353,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ25">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR25">
         <v>1.41</v>
@@ -7305,7 +7314,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7717,7 +7726,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8207,10 +8216,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.25</v>
@@ -8335,7 +8344,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8413,7 +8422,7 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ35">
         <v>1.33</v>
@@ -8541,7 +8550,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8619,10 +8628,10 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ36">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR36">
         <v>1.45</v>
@@ -8747,7 +8756,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8953,7 +8962,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9240,7 +9249,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ39">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR39">
         <v>2.01</v>
@@ -9365,7 +9374,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9571,7 +9580,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9777,7 +9786,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9983,7 +9992,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10189,7 +10198,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10601,7 +10610,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10807,7 +10816,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10888,7 +10897,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR47">
         <v>1.19</v>
@@ -11091,10 +11100,10 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ48">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR48">
         <v>1.61</v>
@@ -11219,7 +11228,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11297,7 +11306,7 @@
         <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ49">
         <v>0.86</v>
@@ -11506,7 +11515,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ50">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11709,7 +11718,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ51">
         <v>1.57</v>
@@ -11837,7 +11846,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12043,7 +12052,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12661,7 +12670,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12739,7 +12748,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ56">
         <v>2.33</v>
@@ -12867,7 +12876,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -12948,7 +12957,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ57">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR57">
         <v>1.86</v>
@@ -13073,7 +13082,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13151,7 +13160,7 @@
         <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ58">
         <v>0.6</v>
@@ -13360,7 +13369,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ59">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR59">
         <v>1.31</v>
@@ -13485,7 +13494,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13691,7 +13700,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14103,7 +14112,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14309,7 +14318,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14596,7 +14605,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ65">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR65">
         <v>1.13</v>
@@ -14721,7 +14730,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14927,7 +14936,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15214,7 +15223,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ68">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.22</v>
@@ -15339,7 +15348,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15420,7 +15429,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ69">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR69">
         <v>1.35</v>
@@ -15545,7 +15554,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15623,7 +15632,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ70">
         <v>0.8</v>
@@ -15751,7 +15760,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15957,7 +15966,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16035,7 +16044,7 @@
         <v>3</v>
       </c>
       <c r="AP72">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ72">
         <v>2.33</v>
@@ -16575,7 +16584,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16987,7 +16996,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17193,7 +17202,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17274,7 +17283,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ78">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR78">
         <v>1.42</v>
@@ -17399,7 +17408,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17477,7 +17486,7 @@
         <v>3</v>
       </c>
       <c r="AP79">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ79">
         <v>2.33</v>
@@ -17605,7 +17614,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17892,7 +17901,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ81">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>2.21</v>
@@ -18098,7 +18107,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ82">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR82">
         <v>1.31</v>
@@ -18223,7 +18232,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18301,7 +18310,7 @@
         <v>0.83</v>
       </c>
       <c r="AP83">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ83">
         <v>0.86</v>
@@ -18429,7 +18438,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18507,10 +18516,10 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ84">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR84">
         <v>1.24</v>
@@ -18635,7 +18644,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18841,7 +18850,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18919,7 +18928,7 @@
         <v>1.83</v>
       </c>
       <c r="AP86">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ86">
         <v>1.07</v>
@@ -19459,7 +19468,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -20158,7 +20167,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ92">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR92">
         <v>2.19</v>
@@ -20567,7 +20576,7 @@
         <v>0.86</v>
       </c>
       <c r="AP94">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ94">
         <v>0.86</v>
@@ -20695,7 +20704,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20901,7 +20910,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -20982,7 +20991,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ96">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR96">
         <v>1.26</v>
@@ -21107,7 +21116,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21188,7 +21197,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ97">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.38</v>
@@ -21313,7 +21322,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21391,7 +21400,7 @@
         <v>1.43</v>
       </c>
       <c r="AP98">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ98">
         <v>1.33</v>
@@ -21597,7 +21606,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ99">
         <v>1</v>
@@ -21725,7 +21734,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21803,7 +21812,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ100">
         <v>0.6</v>
@@ -21931,7 +21940,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22012,7 +22021,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ101">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR101">
         <v>1.24</v>
@@ -22343,7 +22352,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22424,7 +22433,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ103">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR103">
         <v>1.34</v>
@@ -22833,7 +22842,7 @@
         <v>0.89</v>
       </c>
       <c r="AP105">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ105">
         <v>0.8</v>
@@ -22961,7 +22970,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23039,10 +23048,10 @@
         <v>0.89</v>
       </c>
       <c r="AP106">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ106">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR106">
         <v>1.67</v>
@@ -23373,7 +23382,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23454,7 +23463,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ108">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR108">
         <v>1.38</v>
@@ -23657,7 +23666,7 @@
         <v>1.71</v>
       </c>
       <c r="AP109">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ109">
         <v>1.07</v>
@@ -23785,7 +23794,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24197,7 +24206,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24815,7 +24824,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24893,7 +24902,7 @@
         <v>1.25</v>
       </c>
       <c r="AP115">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ115">
         <v>1.57</v>
@@ -25021,7 +25030,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25720,7 +25729,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ119">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR119">
         <v>1.24</v>
@@ -25923,7 +25932,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ120">
         <v>1.07</v>
@@ -26129,10 +26138,10 @@
         <v>1.11</v>
       </c>
       <c r="AP121">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ121">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR121">
         <v>1.44</v>
@@ -26257,7 +26266,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26338,7 +26347,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ122">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR122">
         <v>1.36</v>
@@ -26463,7 +26472,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26669,7 +26678,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26953,7 +26962,7 @@
         <v>1.33</v>
       </c>
       <c r="AP125">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ125">
         <v>1.07</v>
@@ -27162,7 +27171,7 @@
         <v>2.86</v>
       </c>
       <c r="AQ126">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR126">
         <v>2.36</v>
@@ -27287,7 +27296,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27493,7 +27502,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27571,10 +27580,10 @@
         <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ128">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR128">
         <v>1.42</v>
@@ -27699,7 +27708,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -27983,7 +27992,7 @@
         <v>1.2</v>
       </c>
       <c r="AP130">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ130">
         <v>1.07</v>
@@ -28523,7 +28532,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28935,7 +28944,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29553,7 +29562,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29965,7 +29974,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30046,7 +30055,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ140">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR140">
         <v>1.33</v>
@@ -30171,7 +30180,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30249,7 +30258,7 @@
         <v>0.75</v>
       </c>
       <c r="AP141">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ141">
         <v>0.6</v>
@@ -30377,7 +30386,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30458,7 +30467,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ142">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR142">
         <v>1.21</v>
@@ -30583,7 +30592,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30789,7 +30798,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30995,7 +31004,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31201,7 +31210,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31691,7 +31700,7 @@
         <v>1.58</v>
       </c>
       <c r="AP148">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ148">
         <v>1.33</v>
@@ -31900,7 +31909,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ149">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR149">
         <v>2.11</v>
@@ -32025,7 +32034,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32103,7 +32112,7 @@
         <v>2.42</v>
       </c>
       <c r="AP150">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ150">
         <v>2.33</v>
@@ -32643,7 +32652,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q153">
         <v>3.2</v>
@@ -32927,7 +32936,7 @@
         <v>0.85</v>
       </c>
       <c r="AP154">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ154">
         <v>0.8</v>
@@ -33055,7 +33064,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q155">
         <v>2.75</v>
@@ -33133,10 +33142,10 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ155">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR155">
         <v>1.1</v>
@@ -33261,7 +33270,7 @@
         <v>201</v>
       </c>
       <c r="P156" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33339,7 +33348,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ156">
         <v>1.57</v>
@@ -33548,7 +33557,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ157">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR157">
         <v>1.3</v>
@@ -34291,7 +34300,7 @@
         <v>82</v>
       </c>
       <c r="P161" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q161">
         <v>1.57</v>
@@ -34372,7 +34381,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ161">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR161">
         <v>2.16</v>
@@ -34497,7 +34506,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q162">
         <v>3.1</v>
@@ -34703,7 +34712,7 @@
         <v>140</v>
       </c>
       <c r="P163" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q163">
         <v>4.33</v>
@@ -34909,7 +34918,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q164">
         <v>1.57</v>
@@ -35196,7 +35205,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ165">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR165">
         <v>1.32</v>
@@ -35399,7 +35408,7 @@
         <v>0.92</v>
       </c>
       <c r="AP166">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ166">
         <v>0.86</v>
@@ -35527,7 +35536,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q167">
         <v>2.4</v>
@@ -35605,10 +35614,10 @@
         <v>1.23</v>
       </c>
       <c r="AP167">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ167">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR167">
         <v>1.74</v>
@@ -35733,7 +35742,7 @@
         <v>139</v>
       </c>
       <c r="P168" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q168">
         <v>3.4</v>
@@ -35814,7 +35823,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ168">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR168">
         <v>1.35</v>
@@ -35939,7 +35948,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36017,7 +36026,7 @@
         <v>1.46</v>
       </c>
       <c r="AP169">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ169">
         <v>1.57</v>
@@ -36351,7 +36360,7 @@
         <v>199</v>
       </c>
       <c r="P171" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q171">
         <v>1.53</v>
@@ -36763,7 +36772,7 @@
         <v>211</v>
       </c>
       <c r="P173" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q173">
         <v>10</v>
@@ -36969,7 +36978,7 @@
         <v>212</v>
       </c>
       <c r="P174" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q174">
         <v>3</v>
@@ -37175,7 +37184,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q175">
         <v>2.88</v>
@@ -37332,6 +37341,830 @@
       </c>
       <c r="BP175">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7480313</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45731.5</v>
+      </c>
+      <c r="F176">
+        <v>30</v>
+      </c>
+      <c r="G176" t="s">
+        <v>70</v>
+      </c>
+      <c r="H176" t="s">
+        <v>77</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <v>2</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>2</v>
+      </c>
+      <c r="O176" t="s">
+        <v>214</v>
+      </c>
+      <c r="P176" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q176">
+        <v>2.05</v>
+      </c>
+      <c r="R176">
+        <v>2.38</v>
+      </c>
+      <c r="S176">
+        <v>6</v>
+      </c>
+      <c r="T176">
+        <v>1.36</v>
+      </c>
+      <c r="U176">
+        <v>3</v>
+      </c>
+      <c r="V176">
+        <v>2.63</v>
+      </c>
+      <c r="W176">
+        <v>1.44</v>
+      </c>
+      <c r="X176">
+        <v>7</v>
+      </c>
+      <c r="Y176">
+        <v>1.1</v>
+      </c>
+      <c r="Z176">
+        <v>1.48</v>
+      </c>
+      <c r="AA176">
+        <v>4.3</v>
+      </c>
+      <c r="AB176">
+        <v>6.2</v>
+      </c>
+      <c r="AC176">
+        <v>1.04</v>
+      </c>
+      <c r="AD176">
+        <v>10</v>
+      </c>
+      <c r="AE176">
+        <v>1.25</v>
+      </c>
+      <c r="AF176">
+        <v>3.85</v>
+      </c>
+      <c r="AG176">
+        <v>1.82</v>
+      </c>
+      <c r="AH176">
+        <v>1.92</v>
+      </c>
+      <c r="AI176">
+        <v>1.95</v>
+      </c>
+      <c r="AJ176">
+        <v>1.8</v>
+      </c>
+      <c r="AK176">
+        <v>1.12</v>
+      </c>
+      <c r="AL176">
+        <v>1.21</v>
+      </c>
+      <c r="AM176">
+        <v>2.55</v>
+      </c>
+      <c r="AN176">
+        <v>1.5</v>
+      </c>
+      <c r="AO176">
+        <v>1.07</v>
+      </c>
+      <c r="AP176">
+        <v>1.6</v>
+      </c>
+      <c r="AQ176">
+        <v>1</v>
+      </c>
+      <c r="AR176">
+        <v>1.74</v>
+      </c>
+      <c r="AS176">
+        <v>0.99</v>
+      </c>
+      <c r="AT176">
+        <v>2.73</v>
+      </c>
+      <c r="AU176">
+        <v>6</v>
+      </c>
+      <c r="AV176">
+        <v>2</v>
+      </c>
+      <c r="AW176">
+        <v>6</v>
+      </c>
+      <c r="AX176">
+        <v>4</v>
+      </c>
+      <c r="AY176">
+        <v>12</v>
+      </c>
+      <c r="AZ176">
+        <v>6</v>
+      </c>
+      <c r="BA176">
+        <v>6</v>
+      </c>
+      <c r="BB176">
+        <v>6</v>
+      </c>
+      <c r="BC176">
+        <v>12</v>
+      </c>
+      <c r="BD176">
+        <v>1.28</v>
+      </c>
+      <c r="BE176">
+        <v>8</v>
+      </c>
+      <c r="BF176">
+        <v>3.95</v>
+      </c>
+      <c r="BG176">
+        <v>1.15</v>
+      </c>
+      <c r="BH176">
+        <v>4.6</v>
+      </c>
+      <c r="BI176">
+        <v>1.28</v>
+      </c>
+      <c r="BJ176">
+        <v>3.3</v>
+      </c>
+      <c r="BK176">
+        <v>1.47</v>
+      </c>
+      <c r="BL176">
+        <v>2.48</v>
+      </c>
+      <c r="BM176">
+        <v>1.72</v>
+      </c>
+      <c r="BN176">
+        <v>1.97</v>
+      </c>
+      <c r="BO176">
+        <v>2.1</v>
+      </c>
+      <c r="BP176">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7480314</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45731.5</v>
+      </c>
+      <c r="F177">
+        <v>30</v>
+      </c>
+      <c r="G177" t="s">
+        <v>81</v>
+      </c>
+      <c r="H177" t="s">
+        <v>79</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177">
+        <v>1</v>
+      </c>
+      <c r="M177">
+        <v>1</v>
+      </c>
+      <c r="N177">
+        <v>2</v>
+      </c>
+      <c r="O177" t="s">
+        <v>99</v>
+      </c>
+      <c r="P177" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q177">
+        <v>3.4</v>
+      </c>
+      <c r="R177">
+        <v>2.05</v>
+      </c>
+      <c r="S177">
+        <v>3.4</v>
+      </c>
+      <c r="T177">
+        <v>1.44</v>
+      </c>
+      <c r="U177">
+        <v>2.63</v>
+      </c>
+      <c r="V177">
+        <v>3.25</v>
+      </c>
+      <c r="W177">
+        <v>1.33</v>
+      </c>
+      <c r="X177">
+        <v>9</v>
+      </c>
+      <c r="Y177">
+        <v>1.07</v>
+      </c>
+      <c r="Z177">
+        <v>2.68</v>
+      </c>
+      <c r="AA177">
+        <v>3.14</v>
+      </c>
+      <c r="AB177">
+        <v>2.65</v>
+      </c>
+      <c r="AC177">
+        <v>1.07</v>
+      </c>
+      <c r="AD177">
+        <v>8</v>
+      </c>
+      <c r="AE177">
+        <v>1.36</v>
+      </c>
+      <c r="AF177">
+        <v>3.1</v>
+      </c>
+      <c r="AG177">
+        <v>2</v>
+      </c>
+      <c r="AH177">
+        <v>1.75</v>
+      </c>
+      <c r="AI177">
+        <v>1.8</v>
+      </c>
+      <c r="AJ177">
+        <v>1.95</v>
+      </c>
+      <c r="AK177">
+        <v>1.44</v>
+      </c>
+      <c r="AL177">
+        <v>1.34</v>
+      </c>
+      <c r="AM177">
+        <v>1.47</v>
+      </c>
+      <c r="AN177">
+        <v>1.57</v>
+      </c>
+      <c r="AO177">
+        <v>1.21</v>
+      </c>
+      <c r="AP177">
+        <v>1.53</v>
+      </c>
+      <c r="AQ177">
+        <v>1.2</v>
+      </c>
+      <c r="AR177">
+        <v>1.42</v>
+      </c>
+      <c r="AS177">
+        <v>1.45</v>
+      </c>
+      <c r="AT177">
+        <v>2.87</v>
+      </c>
+      <c r="AU177">
+        <v>6</v>
+      </c>
+      <c r="AV177">
+        <v>3</v>
+      </c>
+      <c r="AW177">
+        <v>2</v>
+      </c>
+      <c r="AX177">
+        <v>6</v>
+      </c>
+      <c r="AY177">
+        <v>8</v>
+      </c>
+      <c r="AZ177">
+        <v>9</v>
+      </c>
+      <c r="BA177">
+        <v>4</v>
+      </c>
+      <c r="BB177">
+        <v>5</v>
+      </c>
+      <c r="BC177">
+        <v>9</v>
+      </c>
+      <c r="BD177">
+        <v>1.86</v>
+      </c>
+      <c r="BE177">
+        <v>6.75</v>
+      </c>
+      <c r="BF177">
+        <v>2.1</v>
+      </c>
+      <c r="BG177">
+        <v>1.21</v>
+      </c>
+      <c r="BH177">
+        <v>3.8</v>
+      </c>
+      <c r="BI177">
+        <v>1.37</v>
+      </c>
+      <c r="BJ177">
+        <v>2.8</v>
+      </c>
+      <c r="BK177">
+        <v>1.61</v>
+      </c>
+      <c r="BL177">
+        <v>2.15</v>
+      </c>
+      <c r="BM177">
+        <v>1.96</v>
+      </c>
+      <c r="BN177">
+        <v>1.74</v>
+      </c>
+      <c r="BO177">
+        <v>2.43</v>
+      </c>
+      <c r="BP177">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7480315</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45731.5</v>
+      </c>
+      <c r="F178">
+        <v>30</v>
+      </c>
+      <c r="G178" t="s">
+        <v>71</v>
+      </c>
+      <c r="H178" t="s">
+        <v>73</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178">
+        <v>2</v>
+      </c>
+      <c r="K178">
+        <v>3</v>
+      </c>
+      <c r="L178">
+        <v>2</v>
+      </c>
+      <c r="M178">
+        <v>2</v>
+      </c>
+      <c r="N178">
+        <v>4</v>
+      </c>
+      <c r="O178" t="s">
+        <v>215</v>
+      </c>
+      <c r="P178" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q178">
+        <v>3.4</v>
+      </c>
+      <c r="R178">
+        <v>2</v>
+      </c>
+      <c r="S178">
+        <v>3.4</v>
+      </c>
+      <c r="T178">
+        <v>1.5</v>
+      </c>
+      <c r="U178">
+        <v>2.5</v>
+      </c>
+      <c r="V178">
+        <v>3.4</v>
+      </c>
+      <c r="W178">
+        <v>1.3</v>
+      </c>
+      <c r="X178">
+        <v>10</v>
+      </c>
+      <c r="Y178">
+        <v>1.06</v>
+      </c>
+      <c r="Z178">
+        <v>2.77</v>
+      </c>
+      <c r="AA178">
+        <v>2.9</v>
+      </c>
+      <c r="AB178">
+        <v>2.75</v>
+      </c>
+      <c r="AC178">
+        <v>1.08</v>
+      </c>
+      <c r="AD178">
+        <v>7.5</v>
+      </c>
+      <c r="AE178">
+        <v>1.4</v>
+      </c>
+      <c r="AF178">
+        <v>2.88</v>
+      </c>
+      <c r="AG178">
+        <v>1.95</v>
+      </c>
+      <c r="AH178">
+        <v>1.75</v>
+      </c>
+      <c r="AI178">
+        <v>1.95</v>
+      </c>
+      <c r="AJ178">
+        <v>1.8</v>
+      </c>
+      <c r="AK178">
+        <v>1.44</v>
+      </c>
+      <c r="AL178">
+        <v>1.35</v>
+      </c>
+      <c r="AM178">
+        <v>1.44</v>
+      </c>
+      <c r="AN178">
+        <v>1.5</v>
+      </c>
+      <c r="AO178">
+        <v>1.14</v>
+      </c>
+      <c r="AP178">
+        <v>1.47</v>
+      </c>
+      <c r="AQ178">
+        <v>1.13</v>
+      </c>
+      <c r="AR178">
+        <v>1.21</v>
+      </c>
+      <c r="AS178">
+        <v>1.16</v>
+      </c>
+      <c r="AT178">
+        <v>2.37</v>
+      </c>
+      <c r="AU178">
+        <v>3</v>
+      </c>
+      <c r="AV178">
+        <v>5</v>
+      </c>
+      <c r="AW178">
+        <v>3</v>
+      </c>
+      <c r="AX178">
+        <v>7</v>
+      </c>
+      <c r="AY178">
+        <v>6</v>
+      </c>
+      <c r="AZ178">
+        <v>12</v>
+      </c>
+      <c r="BA178">
+        <v>0</v>
+      </c>
+      <c r="BB178">
+        <v>7</v>
+      </c>
+      <c r="BC178">
+        <v>7</v>
+      </c>
+      <c r="BD178">
+        <v>1.9</v>
+      </c>
+      <c r="BE178">
+        <v>6.5</v>
+      </c>
+      <c r="BF178">
+        <v>2.08</v>
+      </c>
+      <c r="BG178">
+        <v>1.27</v>
+      </c>
+      <c r="BH178">
+        <v>3.3</v>
+      </c>
+      <c r="BI178">
+        <v>1.48</v>
+      </c>
+      <c r="BJ178">
+        <v>2.45</v>
+      </c>
+      <c r="BK178">
+        <v>1.76</v>
+      </c>
+      <c r="BL178">
+        <v>1.94</v>
+      </c>
+      <c r="BM178">
+        <v>2.18</v>
+      </c>
+      <c r="BN178">
+        <v>1.58</v>
+      </c>
+      <c r="BO178">
+        <v>2.8</v>
+      </c>
+      <c r="BP178">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7480316</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45731.5</v>
+      </c>
+      <c r="F179">
+        <v>30</v>
+      </c>
+      <c r="G179" t="s">
+        <v>75</v>
+      </c>
+      <c r="H179" t="s">
+        <v>80</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179" t="s">
+        <v>82</v>
+      </c>
+      <c r="P179" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q179">
+        <v>3.6</v>
+      </c>
+      <c r="R179">
+        <v>2.1</v>
+      </c>
+      <c r="S179">
+        <v>3</v>
+      </c>
+      <c r="T179">
+        <v>1.4</v>
+      </c>
+      <c r="U179">
+        <v>2.75</v>
+      </c>
+      <c r="V179">
+        <v>3</v>
+      </c>
+      <c r="W179">
+        <v>1.36</v>
+      </c>
+      <c r="X179">
+        <v>8</v>
+      </c>
+      <c r="Y179">
+        <v>1.08</v>
+      </c>
+      <c r="Z179">
+        <v>3.57</v>
+      </c>
+      <c r="AA179">
+        <v>3.36</v>
+      </c>
+      <c r="AB179">
+        <v>2.03</v>
+      </c>
+      <c r="AC179">
+        <v>1.06</v>
+      </c>
+      <c r="AD179">
+        <v>8.5</v>
+      </c>
+      <c r="AE179">
+        <v>1.3</v>
+      </c>
+      <c r="AF179">
+        <v>3.35</v>
+      </c>
+      <c r="AG179">
+        <v>1.92</v>
+      </c>
+      <c r="AH179">
+        <v>1.82</v>
+      </c>
+      <c r="AI179">
+        <v>1.75</v>
+      </c>
+      <c r="AJ179">
+        <v>2</v>
+      </c>
+      <c r="AK179">
+        <v>1.6</v>
+      </c>
+      <c r="AL179">
+        <v>1.31</v>
+      </c>
+      <c r="AM179">
+        <v>1.36</v>
+      </c>
+      <c r="AN179">
+        <v>0.93</v>
+      </c>
+      <c r="AO179">
+        <v>1.07</v>
+      </c>
+      <c r="AP179">
+        <v>0.93</v>
+      </c>
+      <c r="AQ179">
+        <v>1.07</v>
+      </c>
+      <c r="AR179">
+        <v>1.35</v>
+      </c>
+      <c r="AS179">
+        <v>1.2</v>
+      </c>
+      <c r="AT179">
+        <v>2.55</v>
+      </c>
+      <c r="AU179">
+        <v>5</v>
+      </c>
+      <c r="AV179">
+        <v>3</v>
+      </c>
+      <c r="AW179">
+        <v>3</v>
+      </c>
+      <c r="AX179">
+        <v>6</v>
+      </c>
+      <c r="AY179">
+        <v>8</v>
+      </c>
+      <c r="AZ179">
+        <v>9</v>
+      </c>
+      <c r="BA179">
+        <v>1</v>
+      </c>
+      <c r="BB179">
+        <v>6</v>
+      </c>
+      <c r="BC179">
+        <v>7</v>
+      </c>
+      <c r="BD179">
+        <v>2.2</v>
+      </c>
+      <c r="BE179">
+        <v>6.75</v>
+      </c>
+      <c r="BF179">
+        <v>1.79</v>
+      </c>
+      <c r="BG179">
+        <v>1.2</v>
+      </c>
+      <c r="BH179">
+        <v>3.9</v>
+      </c>
+      <c r="BI179">
+        <v>1.35</v>
+      </c>
+      <c r="BJ179">
+        <v>2.9</v>
+      </c>
+      <c r="BK179">
+        <v>1.58</v>
+      </c>
+      <c r="BL179">
+        <v>2.18</v>
+      </c>
+      <c r="BM179">
+        <v>1.94</v>
+      </c>
+      <c r="BN179">
+        <v>1.76</v>
+      </c>
+      <c r="BO179">
+        <v>2.4</v>
+      </c>
+      <c r="BP179">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="309">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -664,6 +664,12 @@
     <t>['35', '71']</t>
   </si>
   <si>
+    <t>['49', '74']</t>
+  </si>
+  <si>
+    <t>['31', '49']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -929,6 +935,12 @@
   </si>
   <si>
     <t>['23', '33']</t>
+  </si>
+  <si>
+    <t>['4', '37', '88']</t>
+  </si>
+  <si>
+    <t>['17', '23', '39', '90+7']</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP179"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1627,7 +1639,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ2">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1958,7 +1970,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2036,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ4">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2448,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ6">
         <v>0.6</v>
@@ -2576,7 +2588,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2988,7 +3000,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3400,7 +3412,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3606,7 +3618,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3812,7 +3824,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -4096,7 +4108,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ14">
         <v>0.8</v>
@@ -4224,7 +4236,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4305,7 +4317,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ15">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0.53</v>
@@ -4636,7 +4648,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -5254,7 +5266,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5460,7 +5472,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5666,7 +5678,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5950,10 +5962,10 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ23">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR23">
         <v>3.1</v>
@@ -6078,7 +6090,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6284,7 +6296,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6774,7 +6786,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7189,7 +7201,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ29">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>1.33</v>
@@ -7314,7 +7326,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7598,10 +7610,10 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ31">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR31">
         <v>1.46</v>
@@ -7726,7 +7738,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8344,7 +8356,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8550,7 +8562,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8756,7 +8768,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8962,7 +8974,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9374,7 +9386,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9580,7 +9592,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9786,7 +9798,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9992,7 +10004,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10198,7 +10210,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10610,7 +10622,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10688,7 +10700,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ46">
         <v>1.07</v>
@@ -10816,7 +10828,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10894,7 +10906,7 @@
         <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ47">
         <v>1.2</v>
@@ -11228,7 +11240,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11309,7 +11321,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ49">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>1.3</v>
@@ -11721,7 +11733,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ51">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR51">
         <v>1.31</v>
@@ -11846,7 +11858,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12052,7 +12064,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12670,7 +12682,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12876,7 +12888,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -13082,7 +13094,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13494,7 +13506,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13700,7 +13712,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13778,7 +13790,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ61">
         <v>1.07</v>
@@ -13984,10 +13996,10 @@
         <v>1.25</v>
       </c>
       <c r="AP62">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ62">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>2.17</v>
@@ -14112,7 +14124,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14193,7 +14205,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ63">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR63">
         <v>1.25</v>
@@ -14318,7 +14330,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14730,7 +14742,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14936,7 +14948,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15220,7 +15232,7 @@
         <v>0.6</v>
       </c>
       <c r="AP68">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15348,7 +15360,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15554,7 +15566,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15760,7 +15772,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15841,7 +15853,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ71">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>1.32</v>
@@ -15966,7 +15978,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16584,7 +16596,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16996,7 +17008,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17202,7 +17214,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17408,7 +17420,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17614,7 +17626,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17898,7 +17910,7 @@
         <v>0.5</v>
       </c>
       <c r="AP81">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -18104,7 +18116,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ82">
         <v>1.13</v>
@@ -18232,7 +18244,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18313,7 +18325,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ83">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR83">
         <v>1.34</v>
@@ -18438,7 +18450,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18644,7 +18656,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18725,7 +18737,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ85">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18850,7 +18862,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19468,7 +19480,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -20164,7 +20176,7 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ92">
         <v>1.2</v>
@@ -20370,7 +20382,7 @@
         <v>0.78</v>
       </c>
       <c r="AP93">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ93">
         <v>0.6</v>
@@ -20579,7 +20591,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ94">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.63</v>
@@ -20704,7 +20716,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20785,7 +20797,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ95">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR95">
         <v>1.29</v>
@@ -20910,7 +20922,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21116,7 +21128,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21322,7 +21334,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21734,7 +21746,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21940,7 +21952,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22227,7 +22239,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ102">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR102">
         <v>2.07</v>
@@ -22352,7 +22364,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22636,7 +22648,7 @@
         <v>3</v>
       </c>
       <c r="AP104">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ104">
         <v>2.33</v>
@@ -22970,7 +22982,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23254,7 +23266,7 @@
         <v>1.5</v>
       </c>
       <c r="AP107">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ107">
         <v>1.07</v>
@@ -23382,7 +23394,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23794,7 +23806,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24081,7 +24093,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ111">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR111">
         <v>1.24</v>
@@ -24206,7 +24218,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24490,7 +24502,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ113">
         <v>0.8</v>
@@ -24824,7 +24836,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24905,7 +24917,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ115">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR115">
         <v>1.18</v>
@@ -25030,7 +25042,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25111,7 +25123,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ116">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR116">
         <v>1.2</v>
@@ -25314,7 +25326,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ117">
         <v>1.07</v>
@@ -26266,7 +26278,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26472,7 +26484,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26678,7 +26690,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26759,7 +26771,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ124">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR124">
         <v>1.42</v>
@@ -27168,7 +27180,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ126">
         <v>1.13</v>
@@ -27296,7 +27308,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27374,7 +27386,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ127">
         <v>1</v>
@@ -27502,7 +27514,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27708,7 +27720,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -27789,7 +27801,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ129">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR129">
         <v>1.19</v>
@@ -28198,7 +28210,7 @@
         <v>1.6</v>
       </c>
       <c r="AP131">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ131">
         <v>1.33</v>
@@ -28407,7 +28419,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ132">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28532,7 +28544,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28944,7 +28956,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29562,7 +29574,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29974,7 +29986,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30180,7 +30192,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30386,7 +30398,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30592,7 +30604,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30798,7 +30810,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30876,10 +30888,10 @@
         <v>1.18</v>
       </c>
       <c r="AP144">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ144">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR144">
         <v>1.31</v>
@@ -31004,7 +31016,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31210,7 +31222,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -32034,7 +32046,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32318,10 +32330,10 @@
         <v>1.09</v>
       </c>
       <c r="AP151">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ151">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR151">
         <v>2.26</v>
@@ -32524,7 +32536,7 @@
         <v>1.46</v>
       </c>
       <c r="AP152">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ152">
         <v>1.33</v>
@@ -32652,7 +32664,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q153">
         <v>3.2</v>
@@ -33064,7 +33076,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q155">
         <v>2.75</v>
@@ -33270,7 +33282,7 @@
         <v>201</v>
       </c>
       <c r="P156" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33351,7 +33363,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ156">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR156">
         <v>1.65</v>
@@ -34172,7 +34184,7 @@
         <v>1</v>
       </c>
       <c r="AP160">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ160">
         <v>1.07</v>
@@ -34300,7 +34312,7 @@
         <v>82</v>
       </c>
       <c r="P161" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q161">
         <v>1.57</v>
@@ -34506,7 +34518,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q162">
         <v>3.1</v>
@@ -34587,7 +34599,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ162">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR162">
         <v>1.18</v>
@@ -34712,7 +34724,7 @@
         <v>140</v>
       </c>
       <c r="P163" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q163">
         <v>4.33</v>
@@ -34918,7 +34930,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q164">
         <v>1.57</v>
@@ -34996,7 +35008,7 @@
         <v>1.15</v>
       </c>
       <c r="AP164">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AQ164">
         <v>1.07</v>
@@ -35411,7 +35423,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ166">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR166">
         <v>1.16</v>
@@ -35536,7 +35548,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q167">
         <v>2.4</v>
@@ -35742,7 +35754,7 @@
         <v>139</v>
       </c>
       <c r="P168" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q168">
         <v>3.4</v>
@@ -35820,7 +35832,7 @@
         <v>1.08</v>
       </c>
       <c r="AP168">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ168">
         <v>1.2</v>
@@ -35948,7 +35960,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36029,7 +36041,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ169">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR169">
         <v>1.42</v>
@@ -36360,7 +36372,7 @@
         <v>199</v>
       </c>
       <c r="P171" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q171">
         <v>1.53</v>
@@ -36772,7 +36784,7 @@
         <v>211</v>
       </c>
       <c r="P173" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q173">
         <v>10</v>
@@ -36978,7 +36990,7 @@
         <v>212</v>
       </c>
       <c r="P174" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q174">
         <v>3</v>
@@ -37184,7 +37196,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q175">
         <v>2.88</v>
@@ -37802,7 +37814,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q178">
         <v>3.4</v>
@@ -38165,6 +38177,418 @@
       </c>
       <c r="BP179">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7480311</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45732.39583333334</v>
+      </c>
+      <c r="F180">
+        <v>30</v>
+      </c>
+      <c r="G180" t="s">
+        <v>74</v>
+      </c>
+      <c r="H180" t="s">
+        <v>76</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>2</v>
+      </c>
+      <c r="K180">
+        <v>2</v>
+      </c>
+      <c r="L180">
+        <v>2</v>
+      </c>
+      <c r="M180">
+        <v>3</v>
+      </c>
+      <c r="N180">
+        <v>5</v>
+      </c>
+      <c r="O180" t="s">
+        <v>216</v>
+      </c>
+      <c r="P180" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q180">
+        <v>2.25</v>
+      </c>
+      <c r="R180">
+        <v>2.4</v>
+      </c>
+      <c r="S180">
+        <v>4.33</v>
+      </c>
+      <c r="T180">
+        <v>1.29</v>
+      </c>
+      <c r="U180">
+        <v>3.5</v>
+      </c>
+      <c r="V180">
+        <v>2.25</v>
+      </c>
+      <c r="W180">
+        <v>1.57</v>
+      </c>
+      <c r="X180">
+        <v>5.5</v>
+      </c>
+      <c r="Y180">
+        <v>1.14</v>
+      </c>
+      <c r="Z180">
+        <v>1.72</v>
+      </c>
+      <c r="AA180">
+        <v>3.84</v>
+      </c>
+      <c r="AB180">
+        <v>4.4</v>
+      </c>
+      <c r="AC180">
+        <v>1.02</v>
+      </c>
+      <c r="AD180">
+        <v>14.4</v>
+      </c>
+      <c r="AE180">
+        <v>1.12</v>
+      </c>
+      <c r="AF180">
+        <v>4.7</v>
+      </c>
+      <c r="AG180">
+        <v>1.53</v>
+      </c>
+      <c r="AH180">
+        <v>2.29</v>
+      </c>
+      <c r="AI180">
+        <v>1.57</v>
+      </c>
+      <c r="AJ180">
+        <v>2.25</v>
+      </c>
+      <c r="AK180">
+        <v>1.22</v>
+      </c>
+      <c r="AL180">
+        <v>1.2</v>
+      </c>
+      <c r="AM180">
+        <v>2</v>
+      </c>
+      <c r="AN180">
+        <v>2.86</v>
+      </c>
+      <c r="AO180">
+        <v>1.57</v>
+      </c>
+      <c r="AP180">
+        <v>2.67</v>
+      </c>
+      <c r="AQ180">
+        <v>1.67</v>
+      </c>
+      <c r="AR180">
+        <v>2.25</v>
+      </c>
+      <c r="AS180">
+        <v>1.91</v>
+      </c>
+      <c r="AT180">
+        <v>4.16</v>
+      </c>
+      <c r="AU180">
+        <v>7</v>
+      </c>
+      <c r="AV180">
+        <v>6</v>
+      </c>
+      <c r="AW180">
+        <v>8</v>
+      </c>
+      <c r="AX180">
+        <v>5</v>
+      </c>
+      <c r="AY180">
+        <v>16</v>
+      </c>
+      <c r="AZ180">
+        <v>12</v>
+      </c>
+      <c r="BA180">
+        <v>7</v>
+      </c>
+      <c r="BB180">
+        <v>6</v>
+      </c>
+      <c r="BC180">
+        <v>13</v>
+      </c>
+      <c r="BD180">
+        <v>1.39</v>
+      </c>
+      <c r="BE180">
+        <v>10.5</v>
+      </c>
+      <c r="BF180">
+        <v>3.6</v>
+      </c>
+      <c r="BG180">
+        <v>1.07</v>
+      </c>
+      <c r="BH180">
+        <v>5.75</v>
+      </c>
+      <c r="BI180">
+        <v>1.18</v>
+      </c>
+      <c r="BJ180">
+        <v>3.84</v>
+      </c>
+      <c r="BK180">
+        <v>1.37</v>
+      </c>
+      <c r="BL180">
+        <v>2.75</v>
+      </c>
+      <c r="BM180">
+        <v>1.65</v>
+      </c>
+      <c r="BN180">
+        <v>2.11</v>
+      </c>
+      <c r="BO180">
+        <v>1.95</v>
+      </c>
+      <c r="BP180">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7480312</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45732.5</v>
+      </c>
+      <c r="F181">
+        <v>30</v>
+      </c>
+      <c r="G181" t="s">
+        <v>72</v>
+      </c>
+      <c r="H181" t="s">
+        <v>78</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181">
+        <v>3</v>
+      </c>
+      <c r="K181">
+        <v>4</v>
+      </c>
+      <c r="L181">
+        <v>2</v>
+      </c>
+      <c r="M181">
+        <v>4</v>
+      </c>
+      <c r="N181">
+        <v>6</v>
+      </c>
+      <c r="O181" t="s">
+        <v>217</v>
+      </c>
+      <c r="P181" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q181">
+        <v>2.4</v>
+      </c>
+      <c r="R181">
+        <v>2.2</v>
+      </c>
+      <c r="S181">
+        <v>4.75</v>
+      </c>
+      <c r="T181">
+        <v>1.4</v>
+      </c>
+      <c r="U181">
+        <v>2.75</v>
+      </c>
+      <c r="V181">
+        <v>2.75</v>
+      </c>
+      <c r="W181">
+        <v>1.4</v>
+      </c>
+      <c r="X181">
+        <v>8</v>
+      </c>
+      <c r="Y181">
+        <v>1.08</v>
+      </c>
+      <c r="Z181">
+        <v>1.79</v>
+      </c>
+      <c r="AA181">
+        <v>3.58</v>
+      </c>
+      <c r="AB181">
+        <v>4.3</v>
+      </c>
+      <c r="AC181">
+        <v>1.05</v>
+      </c>
+      <c r="AD181">
+        <v>9.5</v>
+      </c>
+      <c r="AE181">
+        <v>1.28</v>
+      </c>
+      <c r="AF181">
+        <v>3.5</v>
+      </c>
+      <c r="AG181">
+        <v>1.87</v>
+      </c>
+      <c r="AH181">
+        <v>1.87</v>
+      </c>
+      <c r="AI181">
+        <v>1.8</v>
+      </c>
+      <c r="AJ181">
+        <v>1.95</v>
+      </c>
+      <c r="AK181">
+        <v>1.22</v>
+      </c>
+      <c r="AL181">
+        <v>1.27</v>
+      </c>
+      <c r="AM181">
+        <v>1.93</v>
+      </c>
+      <c r="AN181">
+        <v>1.5</v>
+      </c>
+      <c r="AO181">
+        <v>0.86</v>
+      </c>
+      <c r="AP181">
+        <v>1.4</v>
+      </c>
+      <c r="AQ181">
+        <v>1</v>
+      </c>
+      <c r="AR181">
+        <v>1.35</v>
+      </c>
+      <c r="AS181">
+        <v>1.11</v>
+      </c>
+      <c r="AT181">
+        <v>2.46</v>
+      </c>
+      <c r="AU181">
+        <v>8</v>
+      </c>
+      <c r="AV181">
+        <v>13</v>
+      </c>
+      <c r="AW181">
+        <v>5</v>
+      </c>
+      <c r="AX181">
+        <v>4</v>
+      </c>
+      <c r="AY181">
+        <v>13</v>
+      </c>
+      <c r="AZ181">
+        <v>17</v>
+      </c>
+      <c r="BA181">
+        <v>2</v>
+      </c>
+      <c r="BB181">
+        <v>4</v>
+      </c>
+      <c r="BC181">
+        <v>6</v>
+      </c>
+      <c r="BD181">
+        <v>1.58</v>
+      </c>
+      <c r="BE181">
+        <v>6.75</v>
+      </c>
+      <c r="BF181">
+        <v>2.55</v>
+      </c>
+      <c r="BG181">
+        <v>1.23</v>
+      </c>
+      <c r="BH181">
+        <v>3.65</v>
+      </c>
+      <c r="BI181">
+        <v>1.4</v>
+      </c>
+      <c r="BJ181">
+        <v>2.65</v>
+      </c>
+      <c r="BK181">
+        <v>1.65</v>
+      </c>
+      <c r="BL181">
+        <v>2.08</v>
+      </c>
+      <c r="BM181">
+        <v>2.02</v>
+      </c>
+      <c r="BN181">
+        <v>1.68</v>
+      </c>
+      <c r="BO181">
+        <v>2.55</v>
+      </c>
+      <c r="BP181">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="316">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -670,6 +670,21 @@
     <t>['31', '49']</t>
   </si>
   <si>
+    <t>['17', '24', '41']</t>
+  </si>
+  <si>
+    <t>['13', '37', '77', '90+2']</t>
+  </si>
+  <si>
+    <t>['6', '9', '58', '65', '69']</t>
+  </si>
+  <si>
+    <t>['18', '29', '90+5']</t>
+  </si>
+  <si>
+    <t>['2', '19', '62']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -941,6 +956,12 @@
   </si>
   <si>
     <t>['17', '23', '39', '90+7']</t>
+  </si>
+  <si>
+    <t>['5']</t>
+  </si>
+  <si>
+    <t>['43', '75', '81', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1639,7 +1660,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ2">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1970,7 +1991,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2254,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ5">
         <v>1.2</v>
@@ -2460,10 +2481,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ6">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2588,7 +2609,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2875,7 +2896,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ8">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3000,7 +3021,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3078,10 +3099,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3284,10 +3305,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3412,7 +3433,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3490,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ11">
         <v>2.33</v>
@@ -3618,7 +3639,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3696,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ12">
         <v>1.13</v>
@@ -3824,7 +3845,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -3905,7 +3926,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ13">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4111,7 +4132,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ14">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR14">
         <v>2.04</v>
@@ -4236,7 +4257,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4314,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4648,7 +4669,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4726,7 +4747,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ17">
         <v>2.33</v>
@@ -4935,7 +4956,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR18">
         <v>1.47</v>
@@ -5138,10 +5159,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ19">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR19">
         <v>1.1</v>
@@ -5266,7 +5287,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5344,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ20">
         <v>1.13</v>
@@ -5472,7 +5493,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5553,7 +5574,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ21">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR21">
         <v>1.39</v>
@@ -5678,7 +5699,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5756,7 +5777,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ22">
         <v>1.07</v>
@@ -5962,10 +5983,10 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ23">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR23">
         <v>3.1</v>
@@ -6090,7 +6111,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6171,7 +6192,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR24">
         <v>1.14</v>
@@ -6296,7 +6317,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6580,10 +6601,10 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ26">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR26">
         <v>1.12</v>
@@ -6786,10 +6807,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR27">
         <v>2.21</v>
@@ -6992,10 +7013,10 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ28">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR28">
         <v>0.85</v>
@@ -7198,7 +7219,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7326,7 +7347,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7404,10 +7425,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ30">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR30">
         <v>0.76</v>
@@ -7613,7 +7634,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ31">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR31">
         <v>1.46</v>
@@ -7738,7 +7759,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7816,10 +7837,10 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ32">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR32">
         <v>1.31</v>
@@ -8022,10 +8043,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR33">
         <v>0.87</v>
@@ -8356,7 +8377,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8437,7 +8458,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR35">
         <v>1.32</v>
@@ -8562,7 +8583,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8768,7 +8789,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8846,7 +8867,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
         <v>1.07</v>
@@ -8974,7 +8995,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9386,7 +9407,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9464,10 +9485,10 @@
         <v>1.67</v>
       </c>
       <c r="AP40">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ40">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR40">
         <v>0.9399999999999999</v>
@@ -9592,7 +9613,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9670,10 +9691,10 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ41">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR41">
         <v>1.12</v>
@@ -9798,7 +9819,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9876,10 +9897,10 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR42">
         <v>1.64</v>
@@ -10004,7 +10025,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10082,7 +10103,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ43">
         <v>2.33</v>
@@ -10210,7 +10231,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10288,10 +10309,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR44">
         <v>1.19</v>
@@ -10497,7 +10518,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ45">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR45">
         <v>1.85</v>
@@ -10622,7 +10643,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10700,7 +10721,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ46">
         <v>1.07</v>
@@ -10828,7 +10849,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11240,7 +11261,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11733,7 +11754,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ51">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR51">
         <v>1.31</v>
@@ -11858,7 +11879,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11936,10 +11957,10 @@
         <v>0.8</v>
       </c>
       <c r="AP52">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ52">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -12064,7 +12085,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12142,10 +12163,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ53">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR53">
         <v>1.34</v>
@@ -12348,10 +12369,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR54">
         <v>1.17</v>
@@ -12554,10 +12575,10 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ55">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR55">
         <v>1.27</v>
@@ -12682,7 +12703,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12888,7 +12909,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -13094,7 +13115,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13175,7 +13196,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ58">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR58">
         <v>1.54</v>
@@ -13378,7 +13399,7 @@
         <v>0.25</v>
       </c>
       <c r="AP59">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ59">
         <v>1.2</v>
@@ -13506,7 +13527,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13584,10 +13605,10 @@
         <v>1.17</v>
       </c>
       <c r="AP60">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ60">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR60">
         <v>1.06</v>
@@ -13712,7 +13733,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13793,7 +13814,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ61">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR61">
         <v>1.15</v>
@@ -13996,7 +14017,7 @@
         <v>1.25</v>
       </c>
       <c r="AP62">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14124,7 +14145,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14202,10 +14223,10 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ63">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR63">
         <v>1.25</v>
@@ -14330,7 +14351,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14411,7 +14432,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR64">
         <v>1.33</v>
@@ -14614,7 +14635,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -14742,7 +14763,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14820,10 +14841,10 @@
         <v>1.17</v>
       </c>
       <c r="AP66">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR66">
         <v>1.42</v>
@@ -14948,7 +14969,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15026,10 +15047,10 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ67">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR67">
         <v>1.3</v>
@@ -15360,7 +15381,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15438,7 +15459,7 @@
         <v>0.2</v>
       </c>
       <c r="AP69">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ69">
         <v>1.13</v>
@@ -15566,7 +15587,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15647,7 +15668,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ70">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR70">
         <v>1.19</v>
@@ -15772,7 +15793,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15850,7 +15871,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -15978,7 +15999,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16265,7 +16286,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR73">
         <v>1.87</v>
@@ -16471,7 +16492,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ74">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR74">
         <v>1.37</v>
@@ -16596,7 +16617,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16674,10 +16695,10 @@
         <v>1.8</v>
       </c>
       <c r="AP75">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ75">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>1.29</v>
@@ -16883,7 +16904,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR76">
         <v>1.75</v>
@@ -17008,7 +17029,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17086,7 +17107,7 @@
         <v>2.5</v>
       </c>
       <c r="AP77">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ77">
         <v>1.07</v>
@@ -17214,7 +17235,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17292,7 +17313,7 @@
         <v>0.4</v>
       </c>
       <c r="AP78">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ78">
         <v>1.2</v>
@@ -17420,7 +17441,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17626,7 +17647,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17704,7 +17725,7 @@
         <v>2</v>
       </c>
       <c r="AP80">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ80">
         <v>1.07</v>
@@ -17910,7 +17931,7 @@
         <v>0.5</v>
       </c>
       <c r="AP81">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -18244,7 +18265,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18450,7 +18471,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18656,7 +18677,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18737,7 +18758,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ85">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18862,7 +18883,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19149,7 +19170,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ87">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR87">
         <v>1.99</v>
@@ -19352,10 +19373,10 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ88">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.42</v>
@@ -19480,7 +19501,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19558,7 +19579,7 @@
         <v>3</v>
       </c>
       <c r="AP89">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ89">
         <v>2.33</v>
@@ -19764,10 +19785,10 @@
         <v>1.29</v>
       </c>
       <c r="AP90">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ90">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.21</v>
@@ -19970,10 +19991,10 @@
         <v>0.88</v>
       </c>
       <c r="AP91">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ91">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR91">
         <v>1.37</v>
@@ -20176,7 +20197,7 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ92">
         <v>1.2</v>
@@ -20385,7 +20406,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ93">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR93">
         <v>1.35</v>
@@ -20716,7 +20737,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20794,10 +20815,10 @@
         <v>1.17</v>
       </c>
       <c r="AP95">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ95">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR95">
         <v>1.29</v>
@@ -20922,7 +20943,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21128,7 +21149,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21206,7 +21227,7 @@
         <v>0.43</v>
       </c>
       <c r="AP97">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21334,7 +21355,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21415,7 +21436,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ98">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR98">
         <v>1.21</v>
@@ -21621,7 +21642,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR99">
         <v>1.4</v>
@@ -21746,7 +21767,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21827,7 +21848,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ100">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR100">
         <v>1.24</v>
@@ -21952,7 +21973,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22030,7 +22051,7 @@
         <v>0.88</v>
       </c>
       <c r="AP101">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ101">
         <v>1.13</v>
@@ -22364,7 +22385,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22442,7 +22463,7 @@
         <v>0.63</v>
       </c>
       <c r="AP103">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ103">
         <v>1.2</v>
@@ -22857,7 +22878,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ105">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR105">
         <v>1.69</v>
@@ -22982,7 +23003,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23266,10 +23287,10 @@
         <v>1.5</v>
       </c>
       <c r="AP107">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ107">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR107">
         <v>2.23</v>
@@ -23394,7 +23415,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23472,7 +23493,7 @@
         <v>0.38</v>
       </c>
       <c r="AP108">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23806,7 +23827,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23887,7 +23908,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ110">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR110">
         <v>1.25</v>
@@ -24090,10 +24111,10 @@
         <v>1.43</v>
       </c>
       <c r="AP111">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ111">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR111">
         <v>1.24</v>
@@ -24218,7 +24239,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24296,10 +24317,10 @@
         <v>0.44</v>
       </c>
       <c r="AP112">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR112">
         <v>1.24</v>
@@ -24502,10 +24523,10 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ113">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR113">
         <v>2.24</v>
@@ -24708,10 +24729,10 @@
         <v>0.82</v>
       </c>
       <c r="AP114">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ114">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR114">
         <v>1.47</v>
@@ -24836,7 +24857,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24917,7 +24938,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ115">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR115">
         <v>1.18</v>
@@ -25042,7 +25063,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25120,7 +25141,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ116">
         <v>1</v>
@@ -25947,7 +25968,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ120">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR120">
         <v>1.65</v>
@@ -26278,7 +26299,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26356,7 +26377,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -26484,7 +26505,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26562,10 +26583,10 @@
         <v>1.44</v>
       </c>
       <c r="AP123">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ123">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR123">
         <v>1.36</v>
@@ -26690,7 +26711,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26768,10 +26789,10 @@
         <v>1.22</v>
       </c>
       <c r="AP124">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ124">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR124">
         <v>1.42</v>
@@ -27180,7 +27201,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ126">
         <v>1.13</v>
@@ -27308,7 +27329,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27389,7 +27410,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ127">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR127">
         <v>1.36</v>
@@ -27514,7 +27535,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27720,7 +27741,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -28007,7 +28028,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ130">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR130">
         <v>1.4</v>
@@ -28210,10 +28231,10 @@
         <v>1.6</v>
       </c>
       <c r="AP131">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ131">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR131">
         <v>2.28</v>
@@ -28416,10 +28437,10 @@
         <v>1.2</v>
       </c>
       <c r="AP132">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28544,7 +28565,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28622,7 +28643,7 @@
         <v>2.5</v>
       </c>
       <c r="AP133">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ133">
         <v>2.33</v>
@@ -28828,10 +28849,10 @@
         <v>1.45</v>
       </c>
       <c r="AP134">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ134">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR134">
         <v>1.22</v>
@@ -28956,7 +28977,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29034,10 +29055,10 @@
         <v>1.18</v>
       </c>
       <c r="AP135">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ135">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR135">
         <v>1.42</v>
@@ -29243,7 +29264,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ136">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR136">
         <v>2.05</v>
@@ -29446,10 +29467,10 @@
         <v>0.73</v>
       </c>
       <c r="AP137">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ137">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR137">
         <v>1.38</v>
@@ -29574,7 +29595,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29652,7 +29673,7 @@
         <v>2.55</v>
       </c>
       <c r="AP138">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ138">
         <v>2.33</v>
@@ -29986,7 +30007,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30064,7 +30085,7 @@
         <v>0.91</v>
       </c>
       <c r="AP140">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ140">
         <v>1.13</v>
@@ -30192,7 +30213,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30273,7 +30294,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ141">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR141">
         <v>1.67</v>
@@ -30398,7 +30419,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30476,7 +30497,7 @@
         <v>1.09</v>
       </c>
       <c r="AP142">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ142">
         <v>1.2</v>
@@ -30604,7 +30625,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30685,7 +30706,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ143">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR143">
         <v>1.28</v>
@@ -30810,7 +30831,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -30891,7 +30912,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ144">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR144">
         <v>1.31</v>
@@ -31016,7 +31037,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31094,10 +31115,10 @@
         <v>0.67</v>
       </c>
       <c r="AP145">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ145">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR145">
         <v>1.26</v>
@@ -31222,7 +31243,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31300,10 +31321,10 @@
         <v>0.75</v>
       </c>
       <c r="AP146">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ146">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR146">
         <v>1.31</v>
@@ -31506,7 +31527,7 @@
         <v>1.09</v>
       </c>
       <c r="AP147">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ147">
         <v>1.07</v>
@@ -31715,7 +31736,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ148">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR148">
         <v>1.42</v>
@@ -32046,7 +32067,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32330,7 +32351,7 @@
         <v>1.09</v>
       </c>
       <c r="AP151">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ151">
         <v>1</v>
@@ -32536,10 +32557,10 @@
         <v>1.46</v>
       </c>
       <c r="AP152">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ152">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR152">
         <v>2.26</v>
@@ -32664,7 +32685,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q153">
         <v>3.2</v>
@@ -32742,7 +32763,7 @@
         <v>1</v>
       </c>
       <c r="AP153">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ153">
         <v>1.07</v>
@@ -32951,7 +32972,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ154">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -33076,7 +33097,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q155">
         <v>2.75</v>
@@ -33282,7 +33303,7 @@
         <v>201</v>
       </c>
       <c r="P156" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33363,7 +33384,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ156">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR156">
         <v>1.65</v>
@@ -33566,7 +33587,7 @@
         <v>1.08</v>
       </c>
       <c r="AP157">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ157">
         <v>1.2</v>
@@ -33772,7 +33793,7 @@
         <v>2.46</v>
       </c>
       <c r="AP158">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ158">
         <v>2.33</v>
@@ -33978,10 +33999,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP159">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ159">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR159">
         <v>1.39</v>
@@ -34187,7 +34208,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ160">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR160">
         <v>1.35</v>
@@ -34312,7 +34333,7 @@
         <v>82</v>
       </c>
       <c r="P161" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q161">
         <v>1.57</v>
@@ -34518,7 +34539,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q162">
         <v>3.1</v>
@@ -34596,7 +34617,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ162">
         <v>1</v>
@@ -34724,7 +34745,7 @@
         <v>140</v>
       </c>
       <c r="P163" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q163">
         <v>4.33</v>
@@ -34805,7 +34826,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ163">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR163">
         <v>1.34</v>
@@ -34930,7 +34951,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q164">
         <v>1.57</v>
@@ -35008,7 +35029,7 @@
         <v>1.15</v>
       </c>
       <c r="AP164">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ164">
         <v>1.07</v>
@@ -35548,7 +35569,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q167">
         <v>2.4</v>
@@ -35754,7 +35775,7 @@
         <v>139</v>
       </c>
       <c r="P168" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q168">
         <v>3.4</v>
@@ -35960,7 +35981,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36041,7 +36062,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ169">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR169">
         <v>1.42</v>
@@ -36244,10 +36265,10 @@
         <v>0.79</v>
       </c>
       <c r="AP170">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ170">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR170">
         <v>1.39</v>
@@ -36372,7 +36393,7 @@
         <v>199</v>
       </c>
       <c r="P171" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q171">
         <v>1.53</v>
@@ -36453,7 +36474,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ171">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR171">
         <v>2.14</v>
@@ -36656,10 +36677,10 @@
         <v>0.64</v>
       </c>
       <c r="AP172">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ172">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR172">
         <v>1.27</v>
@@ -36784,7 +36805,7 @@
         <v>211</v>
       </c>
       <c r="P173" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q173">
         <v>10</v>
@@ -36862,7 +36883,7 @@
         <v>2.29</v>
       </c>
       <c r="AP173">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ173">
         <v>2.33</v>
@@ -36990,7 +37011,7 @@
         <v>212</v>
       </c>
       <c r="P174" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q174">
         <v>3</v>
@@ -37068,10 +37089,10 @@
         <v>1.07</v>
       </c>
       <c r="AP174">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ174">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR174">
         <v>1.38</v>
@@ -37196,7 +37217,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q175">
         <v>2.88</v>
@@ -37274,10 +37295,10 @@
         <v>1.36</v>
       </c>
       <c r="AP175">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ175">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR175">
         <v>1.38</v>
@@ -37814,7 +37835,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q178">
         <v>3.4</v>
@@ -38226,7 +38247,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q180">
         <v>2.25</v>
@@ -38304,10 +38325,10 @@
         <v>1.57</v>
       </c>
       <c r="AP180">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ180">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR180">
         <v>2.25</v>
@@ -38432,7 +38453,7 @@
         <v>217</v>
       </c>
       <c r="P181" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q181">
         <v>2.4</v>
@@ -38589,6 +38610,1242 @@
       </c>
       <c r="BP181">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7480318</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45745.5</v>
+      </c>
+      <c r="F182">
+        <v>31</v>
+      </c>
+      <c r="G182" t="s">
+        <v>74</v>
+      </c>
+      <c r="H182" t="s">
+        <v>70</v>
+      </c>
+      <c r="I182">
+        <v>3</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>3</v>
+      </c>
+      <c r="L182">
+        <v>3</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+      <c r="N182">
+        <v>3</v>
+      </c>
+      <c r="O182" t="s">
+        <v>218</v>
+      </c>
+      <c r="P182" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q182">
+        <v>1.67</v>
+      </c>
+      <c r="R182">
+        <v>2.88</v>
+      </c>
+      <c r="S182">
+        <v>8</v>
+      </c>
+      <c r="T182">
+        <v>1.22</v>
+      </c>
+      <c r="U182">
+        <v>4</v>
+      </c>
+      <c r="V182">
+        <v>2</v>
+      </c>
+      <c r="W182">
+        <v>1.73</v>
+      </c>
+      <c r="X182">
+        <v>4.33</v>
+      </c>
+      <c r="Y182">
+        <v>1.2</v>
+      </c>
+      <c r="Z182">
+        <v>1.23</v>
+      </c>
+      <c r="AA182">
+        <v>6.4</v>
+      </c>
+      <c r="AB182">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC182">
+        <v>0</v>
+      </c>
+      <c r="AD182">
+        <v>0</v>
+      </c>
+      <c r="AE182">
+        <v>0</v>
+      </c>
+      <c r="AF182">
+        <v>0</v>
+      </c>
+      <c r="AG182">
+        <v>1.38</v>
+      </c>
+      <c r="AH182">
+        <v>2.9</v>
+      </c>
+      <c r="AI182">
+        <v>1.8</v>
+      </c>
+      <c r="AJ182">
+        <v>1.95</v>
+      </c>
+      <c r="AK182">
+        <v>0</v>
+      </c>
+      <c r="AL182">
+        <v>0</v>
+      </c>
+      <c r="AM182">
+        <v>0</v>
+      </c>
+      <c r="AN182">
+        <v>2.67</v>
+      </c>
+      <c r="AO182">
+        <v>1</v>
+      </c>
+      <c r="AP182">
+        <v>2.69</v>
+      </c>
+      <c r="AQ182">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR182">
+        <v>2.24</v>
+      </c>
+      <c r="AS182">
+        <v>1.24</v>
+      </c>
+      <c r="AT182">
+        <v>3.48</v>
+      </c>
+      <c r="AU182">
+        <v>7</v>
+      </c>
+      <c r="AV182">
+        <v>3</v>
+      </c>
+      <c r="AW182">
+        <v>4</v>
+      </c>
+      <c r="AX182">
+        <v>5</v>
+      </c>
+      <c r="AY182">
+        <v>11</v>
+      </c>
+      <c r="AZ182">
+        <v>8</v>
+      </c>
+      <c r="BA182">
+        <v>6</v>
+      </c>
+      <c r="BB182">
+        <v>1</v>
+      </c>
+      <c r="BC182">
+        <v>7</v>
+      </c>
+      <c r="BD182">
+        <v>0</v>
+      </c>
+      <c r="BE182">
+        <v>0</v>
+      </c>
+      <c r="BF182">
+        <v>0</v>
+      </c>
+      <c r="BG182">
+        <v>0</v>
+      </c>
+      <c r="BH182">
+        <v>0</v>
+      </c>
+      <c r="BI182">
+        <v>0</v>
+      </c>
+      <c r="BJ182">
+        <v>0</v>
+      </c>
+      <c r="BK182">
+        <v>0</v>
+      </c>
+      <c r="BL182">
+        <v>0</v>
+      </c>
+      <c r="BM182">
+        <v>0</v>
+      </c>
+      <c r="BN182">
+        <v>0</v>
+      </c>
+      <c r="BO182">
+        <v>0</v>
+      </c>
+      <c r="BP182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7480317</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45745.5</v>
+      </c>
+      <c r="F183">
+        <v>31</v>
+      </c>
+      <c r="G183" t="s">
+        <v>80</v>
+      </c>
+      <c r="H183" t="s">
+        <v>71</v>
+      </c>
+      <c r="I183">
+        <v>2</v>
+      </c>
+      <c r="J183">
+        <v>1</v>
+      </c>
+      <c r="K183">
+        <v>3</v>
+      </c>
+      <c r="L183">
+        <v>4</v>
+      </c>
+      <c r="M183">
+        <v>1</v>
+      </c>
+      <c r="N183">
+        <v>5</v>
+      </c>
+      <c r="O183" t="s">
+        <v>219</v>
+      </c>
+      <c r="P183" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q183">
+        <v>2.3</v>
+      </c>
+      <c r="R183">
+        <v>2.2</v>
+      </c>
+      <c r="S183">
+        <v>5</v>
+      </c>
+      <c r="T183">
+        <v>1.4</v>
+      </c>
+      <c r="U183">
+        <v>2.75</v>
+      </c>
+      <c r="V183">
+        <v>2.75</v>
+      </c>
+      <c r="W183">
+        <v>1.4</v>
+      </c>
+      <c r="X183">
+        <v>8</v>
+      </c>
+      <c r="Y183">
+        <v>1.08</v>
+      </c>
+      <c r="Z183">
+        <v>1.74</v>
+      </c>
+      <c r="AA183">
+        <v>3.75</v>
+      </c>
+      <c r="AB183">
+        <v>4.33</v>
+      </c>
+      <c r="AC183">
+        <v>0</v>
+      </c>
+      <c r="AD183">
+        <v>0</v>
+      </c>
+      <c r="AE183">
+        <v>0</v>
+      </c>
+      <c r="AF183">
+        <v>0</v>
+      </c>
+      <c r="AG183">
+        <v>1.87</v>
+      </c>
+      <c r="AH183">
+        <v>1.87</v>
+      </c>
+      <c r="AI183">
+        <v>1.8</v>
+      </c>
+      <c r="AJ183">
+        <v>1.95</v>
+      </c>
+      <c r="AK183">
+        <v>0</v>
+      </c>
+      <c r="AL183">
+        <v>0</v>
+      </c>
+      <c r="AM183">
+        <v>0</v>
+      </c>
+      <c r="AN183">
+        <v>1.8</v>
+      </c>
+      <c r="AO183">
+        <v>1.07</v>
+      </c>
+      <c r="AP183">
+        <v>1.88</v>
+      </c>
+      <c r="AQ183">
+        <v>1</v>
+      </c>
+      <c r="AR183">
+        <v>1.44</v>
+      </c>
+      <c r="AS183">
+        <v>1.11</v>
+      </c>
+      <c r="AT183">
+        <v>2.55</v>
+      </c>
+      <c r="AU183">
+        <v>5</v>
+      </c>
+      <c r="AV183">
+        <v>3</v>
+      </c>
+      <c r="AW183">
+        <v>13</v>
+      </c>
+      <c r="AX183">
+        <v>7</v>
+      </c>
+      <c r="AY183">
+        <v>18</v>
+      </c>
+      <c r="AZ183">
+        <v>10</v>
+      </c>
+      <c r="BA183">
+        <v>9</v>
+      </c>
+      <c r="BB183">
+        <v>4</v>
+      </c>
+      <c r="BC183">
+        <v>13</v>
+      </c>
+      <c r="BD183">
+        <v>0</v>
+      </c>
+      <c r="BE183">
+        <v>0</v>
+      </c>
+      <c r="BF183">
+        <v>0</v>
+      </c>
+      <c r="BG183">
+        <v>0</v>
+      </c>
+      <c r="BH183">
+        <v>0</v>
+      </c>
+      <c r="BI183">
+        <v>0</v>
+      </c>
+      <c r="BJ183">
+        <v>0</v>
+      </c>
+      <c r="BK183">
+        <v>0</v>
+      </c>
+      <c r="BL183">
+        <v>0</v>
+      </c>
+      <c r="BM183">
+        <v>0</v>
+      </c>
+      <c r="BN183">
+        <v>0</v>
+      </c>
+      <c r="BO183">
+        <v>0</v>
+      </c>
+      <c r="BP183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7480322</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45745.5</v>
+      </c>
+      <c r="F184">
+        <v>31</v>
+      </c>
+      <c r="G184" t="s">
+        <v>73</v>
+      </c>
+      <c r="H184" t="s">
+        <v>81</v>
+      </c>
+      <c r="I184">
+        <v>2</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>2</v>
+      </c>
+      <c r="L184">
+        <v>5</v>
+      </c>
+      <c r="M184">
+        <v>1</v>
+      </c>
+      <c r="N184">
+        <v>6</v>
+      </c>
+      <c r="O184" t="s">
+        <v>220</v>
+      </c>
+      <c r="P184" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q184">
+        <v>3</v>
+      </c>
+      <c r="R184">
+        <v>2.05</v>
+      </c>
+      <c r="S184">
+        <v>3.75</v>
+      </c>
+      <c r="T184">
+        <v>1.44</v>
+      </c>
+      <c r="U184">
+        <v>2.63</v>
+      </c>
+      <c r="V184">
+        <v>3.25</v>
+      </c>
+      <c r="W184">
+        <v>1.33</v>
+      </c>
+      <c r="X184">
+        <v>10</v>
+      </c>
+      <c r="Y184">
+        <v>1.06</v>
+      </c>
+      <c r="Z184">
+        <v>2.3</v>
+      </c>
+      <c r="AA184">
+        <v>3.15</v>
+      </c>
+      <c r="AB184">
+        <v>3.15</v>
+      </c>
+      <c r="AC184">
+        <v>0</v>
+      </c>
+      <c r="AD184">
+        <v>0</v>
+      </c>
+      <c r="AE184">
+        <v>0</v>
+      </c>
+      <c r="AF184">
+        <v>0</v>
+      </c>
+      <c r="AG184">
+        <v>2.05</v>
+      </c>
+      <c r="AH184">
+        <v>1.7</v>
+      </c>
+      <c r="AI184">
+        <v>1.91</v>
+      </c>
+      <c r="AJ184">
+        <v>1.91</v>
+      </c>
+      <c r="AK184">
+        <v>0</v>
+      </c>
+      <c r="AL184">
+        <v>0</v>
+      </c>
+      <c r="AM184">
+        <v>0</v>
+      </c>
+      <c r="AN184">
+        <v>1.2</v>
+      </c>
+      <c r="AO184">
+        <v>0.6</v>
+      </c>
+      <c r="AP184">
+        <v>1.31</v>
+      </c>
+      <c r="AQ184">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR184">
+        <v>1.35</v>
+      </c>
+      <c r="AS184">
+        <v>1.28</v>
+      </c>
+      <c r="AT184">
+        <v>2.63</v>
+      </c>
+      <c r="AU184">
+        <v>8</v>
+      </c>
+      <c r="AV184">
+        <v>2</v>
+      </c>
+      <c r="AW184">
+        <v>4</v>
+      </c>
+      <c r="AX184">
+        <v>5</v>
+      </c>
+      <c r="AY184">
+        <v>15</v>
+      </c>
+      <c r="AZ184">
+        <v>9</v>
+      </c>
+      <c r="BA184">
+        <v>4</v>
+      </c>
+      <c r="BB184">
+        <v>7</v>
+      </c>
+      <c r="BC184">
+        <v>11</v>
+      </c>
+      <c r="BD184">
+        <v>0</v>
+      </c>
+      <c r="BE184">
+        <v>0</v>
+      </c>
+      <c r="BF184">
+        <v>0</v>
+      </c>
+      <c r="BG184">
+        <v>0</v>
+      </c>
+      <c r="BH184">
+        <v>0</v>
+      </c>
+      <c r="BI184">
+        <v>0</v>
+      </c>
+      <c r="BJ184">
+        <v>0</v>
+      </c>
+      <c r="BK184">
+        <v>0</v>
+      </c>
+      <c r="BL184">
+        <v>0</v>
+      </c>
+      <c r="BM184">
+        <v>0</v>
+      </c>
+      <c r="BN184">
+        <v>0</v>
+      </c>
+      <c r="BO184">
+        <v>0</v>
+      </c>
+      <c r="BP184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7480320</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45745.5</v>
+      </c>
+      <c r="F185">
+        <v>31</v>
+      </c>
+      <c r="G185" t="s">
+        <v>79</v>
+      </c>
+      <c r="H185" t="s">
+        <v>75</v>
+      </c>
+      <c r="I185">
+        <v>2</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>2</v>
+      </c>
+      <c r="L185">
+        <v>3</v>
+      </c>
+      <c r="M185">
+        <v>0</v>
+      </c>
+      <c r="N185">
+        <v>3</v>
+      </c>
+      <c r="O185" t="s">
+        <v>221</v>
+      </c>
+      <c r="P185" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q185">
+        <v>2.3</v>
+      </c>
+      <c r="R185">
+        <v>2.2</v>
+      </c>
+      <c r="S185">
+        <v>5.5</v>
+      </c>
+      <c r="T185">
+        <v>1.44</v>
+      </c>
+      <c r="U185">
+        <v>2.63</v>
+      </c>
+      <c r="V185">
+        <v>3</v>
+      </c>
+      <c r="W185">
+        <v>1.36</v>
+      </c>
+      <c r="X185">
+        <v>9</v>
+      </c>
+      <c r="Y185">
+        <v>1.07</v>
+      </c>
+      <c r="Z185">
+        <v>1.66</v>
+      </c>
+      <c r="AA185">
+        <v>3.7</v>
+      </c>
+      <c r="AB185">
+        <v>5.1</v>
+      </c>
+      <c r="AC185">
+        <v>0</v>
+      </c>
+      <c r="AD185">
+        <v>0</v>
+      </c>
+      <c r="AE185">
+        <v>0</v>
+      </c>
+      <c r="AF185">
+        <v>0</v>
+      </c>
+      <c r="AG185">
+        <v>1.98</v>
+      </c>
+      <c r="AH185">
+        <v>1.77</v>
+      </c>
+      <c r="AI185">
+        <v>2</v>
+      </c>
+      <c r="AJ185">
+        <v>1.75</v>
+      </c>
+      <c r="AK185">
+        <v>0</v>
+      </c>
+      <c r="AL185">
+        <v>0</v>
+      </c>
+      <c r="AM185">
+        <v>0</v>
+      </c>
+      <c r="AN185">
+        <v>1.73</v>
+      </c>
+      <c r="AO185">
+        <v>0.8</v>
+      </c>
+      <c r="AP185">
+        <v>1.81</v>
+      </c>
+      <c r="AQ185">
+        <v>0.75</v>
+      </c>
+      <c r="AR185">
+        <v>1.38</v>
+      </c>
+      <c r="AS185">
+        <v>1.03</v>
+      </c>
+      <c r="AT185">
+        <v>2.41</v>
+      </c>
+      <c r="AU185">
+        <v>6</v>
+      </c>
+      <c r="AV185">
+        <v>0</v>
+      </c>
+      <c r="AW185">
+        <v>10</v>
+      </c>
+      <c r="AX185">
+        <v>2</v>
+      </c>
+      <c r="AY185">
+        <v>19</v>
+      </c>
+      <c r="AZ185">
+        <v>3</v>
+      </c>
+      <c r="BA185">
+        <v>5</v>
+      </c>
+      <c r="BB185">
+        <v>2</v>
+      </c>
+      <c r="BC185">
+        <v>7</v>
+      </c>
+      <c r="BD185">
+        <v>0</v>
+      </c>
+      <c r="BE185">
+        <v>0</v>
+      </c>
+      <c r="BF185">
+        <v>0</v>
+      </c>
+      <c r="BG185">
+        <v>0</v>
+      </c>
+      <c r="BH185">
+        <v>0</v>
+      </c>
+      <c r="BI185">
+        <v>0</v>
+      </c>
+      <c r="BJ185">
+        <v>0</v>
+      </c>
+      <c r="BK185">
+        <v>0</v>
+      </c>
+      <c r="BL185">
+        <v>0</v>
+      </c>
+      <c r="BM185">
+        <v>0</v>
+      </c>
+      <c r="BN185">
+        <v>0</v>
+      </c>
+      <c r="BO185">
+        <v>0</v>
+      </c>
+      <c r="BP185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7480319</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45745.60416666666</v>
+      </c>
+      <c r="F186">
+        <v>31</v>
+      </c>
+      <c r="G186" t="s">
+        <v>78</v>
+      </c>
+      <c r="H186" t="s">
+        <v>76</v>
+      </c>
+      <c r="I186">
+        <v>2</v>
+      </c>
+      <c r="J186">
+        <v>1</v>
+      </c>
+      <c r="K186">
+        <v>3</v>
+      </c>
+      <c r="L186">
+        <v>3</v>
+      </c>
+      <c r="M186">
+        <v>4</v>
+      </c>
+      <c r="N186">
+        <v>7</v>
+      </c>
+      <c r="O186" t="s">
+        <v>222</v>
+      </c>
+      <c r="P186" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q186">
+        <v>6.5</v>
+      </c>
+      <c r="R186">
+        <v>2.75</v>
+      </c>
+      <c r="S186">
+        <v>1.8</v>
+      </c>
+      <c r="T186">
+        <v>1.22</v>
+      </c>
+      <c r="U186">
+        <v>4</v>
+      </c>
+      <c r="V186">
+        <v>2.1</v>
+      </c>
+      <c r="W186">
+        <v>1.67</v>
+      </c>
+      <c r="X186">
+        <v>4.5</v>
+      </c>
+      <c r="Y186">
+        <v>1.18</v>
+      </c>
+      <c r="Z186">
+        <v>7.3</v>
+      </c>
+      <c r="AA186">
+        <v>5.6</v>
+      </c>
+      <c r="AB186">
+        <v>1.32</v>
+      </c>
+      <c r="AC186">
+        <v>0</v>
+      </c>
+      <c r="AD186">
+        <v>0</v>
+      </c>
+      <c r="AE186">
+        <v>0</v>
+      </c>
+      <c r="AF186">
+        <v>0</v>
+      </c>
+      <c r="AG186">
+        <v>1.53</v>
+      </c>
+      <c r="AH186">
+        <v>2.29</v>
+      </c>
+      <c r="AI186">
+        <v>1.7</v>
+      </c>
+      <c r="AJ186">
+        <v>2.05</v>
+      </c>
+      <c r="AK186">
+        <v>0</v>
+      </c>
+      <c r="AL186">
+        <v>0</v>
+      </c>
+      <c r="AM186">
+        <v>0</v>
+      </c>
+      <c r="AN186">
+        <v>1.07</v>
+      </c>
+      <c r="AO186">
+        <v>1.67</v>
+      </c>
+      <c r="AP186">
+        <v>1</v>
+      </c>
+      <c r="AQ186">
+        <v>1.75</v>
+      </c>
+      <c r="AR186">
+        <v>1.42</v>
+      </c>
+      <c r="AS186">
+        <v>1.89</v>
+      </c>
+      <c r="AT186">
+        <v>3.31</v>
+      </c>
+      <c r="AU186">
+        <v>7</v>
+      </c>
+      <c r="AV186">
+        <v>15</v>
+      </c>
+      <c r="AW186">
+        <v>7</v>
+      </c>
+      <c r="AX186">
+        <v>10</v>
+      </c>
+      <c r="AY186">
+        <v>15</v>
+      </c>
+      <c r="AZ186">
+        <v>26</v>
+      </c>
+      <c r="BA186">
+        <v>7</v>
+      </c>
+      <c r="BB186">
+        <v>3</v>
+      </c>
+      <c r="BC186">
+        <v>10</v>
+      </c>
+      <c r="BD186">
+        <v>0</v>
+      </c>
+      <c r="BE186">
+        <v>0</v>
+      </c>
+      <c r="BF186">
+        <v>0</v>
+      </c>
+      <c r="BG186">
+        <v>0</v>
+      </c>
+      <c r="BH186">
+        <v>0</v>
+      </c>
+      <c r="BI186">
+        <v>0</v>
+      </c>
+      <c r="BJ186">
+        <v>0</v>
+      </c>
+      <c r="BK186">
+        <v>0</v>
+      </c>
+      <c r="BL186">
+        <v>0</v>
+      </c>
+      <c r="BM186">
+        <v>0</v>
+      </c>
+      <c r="BN186">
+        <v>0</v>
+      </c>
+      <c r="BO186">
+        <v>0</v>
+      </c>
+      <c r="BP186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7480321</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45746.4375</v>
+      </c>
+      <c r="F187">
+        <v>31</v>
+      </c>
+      <c r="G187" t="s">
+        <v>77</v>
+      </c>
+      <c r="H187" t="s">
+        <v>72</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>1</v>
+      </c>
+      <c r="N187">
+        <v>1</v>
+      </c>
+      <c r="O187" t="s">
+        <v>82</v>
+      </c>
+      <c r="P187" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q187">
+        <v>3.6</v>
+      </c>
+      <c r="R187">
+        <v>2</v>
+      </c>
+      <c r="S187">
+        <v>3.4</v>
+      </c>
+      <c r="T187">
+        <v>1.5</v>
+      </c>
+      <c r="U187">
+        <v>2.5</v>
+      </c>
+      <c r="V187">
+        <v>3.5</v>
+      </c>
+      <c r="W187">
+        <v>1.29</v>
+      </c>
+      <c r="X187">
+        <v>11</v>
+      </c>
+      <c r="Y187">
+        <v>1.05</v>
+      </c>
+      <c r="Z187">
+        <v>2.74</v>
+      </c>
+      <c r="AA187">
+        <v>3.17</v>
+      </c>
+      <c r="AB187">
+        <v>2.57</v>
+      </c>
+      <c r="AC187">
+        <v>0</v>
+      </c>
+      <c r="AD187">
+        <v>0</v>
+      </c>
+      <c r="AE187">
+        <v>0</v>
+      </c>
+      <c r="AF187">
+        <v>0</v>
+      </c>
+      <c r="AG187">
+        <v>2.15</v>
+      </c>
+      <c r="AH187">
+        <v>1.61</v>
+      </c>
+      <c r="AI187">
+        <v>1.95</v>
+      </c>
+      <c r="AJ187">
+        <v>1.8</v>
+      </c>
+      <c r="AK187">
+        <v>0</v>
+      </c>
+      <c r="AL187">
+        <v>0</v>
+      </c>
+      <c r="AM187">
+        <v>0</v>
+      </c>
+      <c r="AN187">
+        <v>1.33</v>
+      </c>
+      <c r="AO187">
+        <v>1.33</v>
+      </c>
+      <c r="AP187">
+        <v>1.25</v>
+      </c>
+      <c r="AQ187">
+        <v>1.44</v>
+      </c>
+      <c r="AR187">
+        <v>1.25</v>
+      </c>
+      <c r="AS187">
+        <v>1.25</v>
+      </c>
+      <c r="AT187">
+        <v>2.5</v>
+      </c>
+      <c r="AU187">
+        <v>-1</v>
+      </c>
+      <c r="AV187">
+        <v>-1</v>
+      </c>
+      <c r="AW187">
+        <v>-1</v>
+      </c>
+      <c r="AX187">
+        <v>-1</v>
+      </c>
+      <c r="AY187">
+        <v>-1</v>
+      </c>
+      <c r="AZ187">
+        <v>-1</v>
+      </c>
+      <c r="BA187">
+        <v>-1</v>
+      </c>
+      <c r="BB187">
+        <v>-1</v>
+      </c>
+      <c r="BC187">
+        <v>-1</v>
+      </c>
+      <c r="BD187">
+        <v>0</v>
+      </c>
+      <c r="BE187">
+        <v>0</v>
+      </c>
+      <c r="BF187">
+        <v>0</v>
+      </c>
+      <c r="BG187">
+        <v>0</v>
+      </c>
+      <c r="BH187">
+        <v>0</v>
+      </c>
+      <c r="BI187">
+        <v>0</v>
+      </c>
+      <c r="BJ187">
+        <v>0</v>
+      </c>
+      <c r="BK187">
+        <v>0</v>
+      </c>
+      <c r="BL187">
+        <v>0</v>
+      </c>
+      <c r="BM187">
+        <v>0</v>
+      </c>
+      <c r="BN187">
+        <v>0</v>
+      </c>
+      <c r="BO187">
+        <v>0</v>
+      </c>
+      <c r="BP187">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -39782,31 +39782,31 @@
         <v>2.5</v>
       </c>
       <c r="AU187">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV187">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW187">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX187">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AY187">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AZ187">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="BA187">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB187">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BC187">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BD187">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="320">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,6 +685,12 @@
     <t>['2', '19', '62']</t>
   </si>
   <si>
+    <t>['2', '63']</t>
+  </si>
+  <si>
+    <t>['22', '53']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -962,6 +968,12 @@
   </si>
   <si>
     <t>['43', '75', '81', '90+3']</t>
+  </si>
+  <si>
+    <t>['8', '69']</t>
+  </si>
+  <si>
+    <t>['33']</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP187"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1991,7 +2003,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2278,7 +2290,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ5">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2609,7 +2621,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2690,7 +2702,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ7">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2893,10 +2905,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3021,7 +3033,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3099,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ9">
         <v>1.44</v>
@@ -3305,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ10">
         <v>0.9399999999999999</v>
@@ -3433,7 +3445,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3639,7 +3651,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3720,7 +3732,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ12">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3845,7 +3857,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -3923,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ13">
         <v>0.75</v>
@@ -4257,7 +4269,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4541,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -4669,7 +4681,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -5287,7 +5299,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5365,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ20">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR20">
         <v>1.56</v>
@@ -5493,7 +5505,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5574,7 +5586,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR21">
         <v>1.39</v>
@@ -5699,7 +5711,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5777,10 +5789,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ22">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR22">
         <v>1.66</v>
@@ -6111,7 +6123,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6317,7 +6329,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6395,10 +6407,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ25">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR25">
         <v>1.41</v>
@@ -6604,7 +6616,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR26">
         <v>1.12</v>
@@ -7219,7 +7231,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7347,7 +7359,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7759,7 +7771,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7837,7 +7849,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ32">
         <v>0.75</v>
@@ -8377,7 +8389,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8455,7 +8467,7 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ35">
         <v>1.44</v>
@@ -8583,7 +8595,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8664,7 +8676,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ36">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR36">
         <v>1.45</v>
@@ -8789,7 +8801,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8867,10 +8879,10 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ37">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -8995,7 +9007,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9279,10 +9291,10 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ39">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR39">
         <v>2.01</v>
@@ -9407,7 +9419,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9613,7 +9625,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9694,7 +9706,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR41">
         <v>1.12</v>
@@ -9819,7 +9831,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9897,7 +9909,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ42">
         <v>0.5600000000000001</v>
@@ -10025,7 +10037,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10103,7 +10115,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ43">
         <v>2.33</v>
@@ -10231,7 +10243,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10515,7 +10527,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ45">
         <v>0.75</v>
@@ -10643,7 +10655,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10724,7 +10736,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ46">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR46">
         <v>2.16</v>
@@ -10849,7 +10861,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10930,7 +10942,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ47">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR47">
         <v>1.19</v>
@@ -11136,7 +11148,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ48">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR48">
         <v>1.61</v>
@@ -11261,7 +11273,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11751,7 +11763,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ51">
         <v>1.75</v>
@@ -11879,7 +11891,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11957,7 +11969,7 @@
         <v>0.8</v>
       </c>
       <c r="AP52">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ52">
         <v>0.75</v>
@@ -12085,7 +12097,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12163,7 +12175,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ53">
         <v>0.5600000000000001</v>
@@ -12703,7 +12715,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12909,7 +12921,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -12987,10 +12999,10 @@
         <v>0.25</v>
       </c>
       <c r="AP57">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ57">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR57">
         <v>1.86</v>
@@ -13115,7 +13127,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13399,10 +13411,10 @@
         <v>0.25</v>
       </c>
       <c r="AP59">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ59">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR59">
         <v>1.31</v>
@@ -13527,7 +13539,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13733,7 +13745,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13814,7 +13826,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR61">
         <v>1.15</v>
@@ -14145,7 +14157,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14351,7 +14363,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14763,7 +14775,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14841,7 +14853,7 @@
         <v>1.17</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ66">
         <v>0.5600000000000001</v>
@@ -14969,7 +14981,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15381,7 +15393,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15462,7 +15474,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ69">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR69">
         <v>1.35</v>
@@ -15587,7 +15599,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15793,7 +15805,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15999,7 +16011,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16077,7 +16089,7 @@
         <v>3</v>
       </c>
       <c r="AP72">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ72">
         <v>2.33</v>
@@ -16283,7 +16295,7 @@
         <v>0.57</v>
       </c>
       <c r="AP73">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ73">
         <v>0.9399999999999999</v>
@@ -16617,7 +16629,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16695,10 +16707,10 @@
         <v>1.8</v>
       </c>
       <c r="AP75">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR75">
         <v>1.29</v>
@@ -16901,7 +16913,7 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ76">
         <v>1.44</v>
@@ -17029,7 +17041,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17110,7 +17122,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ77">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR77">
         <v>1.13</v>
@@ -17235,7 +17247,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17313,10 +17325,10 @@
         <v>0.4</v>
       </c>
       <c r="AP78">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ78">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR78">
         <v>1.42</v>
@@ -17441,7 +17453,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17647,7 +17659,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17728,7 +17740,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ80">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR80">
         <v>1.33</v>
@@ -18140,7 +18152,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ82">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR82">
         <v>1.31</v>
@@ -18265,7 +18277,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18343,7 +18355,7 @@
         <v>0.83</v>
       </c>
       <c r="AP83">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18471,7 +18483,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18552,7 +18564,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ84">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR84">
         <v>1.24</v>
@@ -18677,7 +18689,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18883,7 +18895,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18964,7 +18976,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ86">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR86">
         <v>1.56</v>
@@ -19167,7 +19179,7 @@
         <v>0.88</v>
       </c>
       <c r="AP87">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ87">
         <v>0.5600000000000001</v>
@@ -19373,10 +19385,10 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR88">
         <v>1.42</v>
@@ -19501,7 +19513,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19788,7 +19800,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR90">
         <v>1.21</v>
@@ -20200,7 +20212,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ92">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR92">
         <v>2.19</v>
@@ -20737,7 +20749,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20815,7 +20827,7 @@
         <v>1.17</v>
       </c>
       <c r="AP95">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ95">
         <v>1.75</v>
@@ -20943,7 +20955,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21024,7 +21036,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ96">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR96">
         <v>1.26</v>
@@ -21149,7 +21161,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21355,7 +21367,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21639,7 +21651,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ99">
         <v>0.9399999999999999</v>
@@ -21767,7 +21779,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21973,7 +21985,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22051,10 +22063,10 @@
         <v>0.88</v>
       </c>
       <c r="AP101">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ101">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR101">
         <v>1.24</v>
@@ -22257,7 +22269,7 @@
         <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22385,7 +22397,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22466,7 +22478,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ103">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR103">
         <v>1.34</v>
@@ -23003,7 +23015,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23084,7 +23096,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ106">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR106">
         <v>1.67</v>
@@ -23290,7 +23302,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ107">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR107">
         <v>2.23</v>
@@ -23415,7 +23427,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23493,7 +23505,7 @@
         <v>0.38</v>
       </c>
       <c r="AP108">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23699,10 +23711,10 @@
         <v>1.71</v>
       </c>
       <c r="AP109">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ109">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR109">
         <v>1.35</v>
@@ -23827,7 +23839,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24239,7 +24251,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24317,7 +24329,7 @@
         <v>0.44</v>
       </c>
       <c r="AP112">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ112">
         <v>0.9399999999999999</v>
@@ -24857,7 +24869,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -25063,7 +25075,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25350,7 +25362,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ117">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR117">
         <v>1.33</v>
@@ -25553,7 +25565,7 @@
         <v>2.78</v>
       </c>
       <c r="AP118">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ118">
         <v>2.33</v>
@@ -25762,7 +25774,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ119">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR119">
         <v>1.24</v>
@@ -25968,7 +25980,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR120">
         <v>1.65</v>
@@ -26171,10 +26183,10 @@
         <v>1.11</v>
       </c>
       <c r="AP121">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ121">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR121">
         <v>1.44</v>
@@ -26299,7 +26311,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26505,7 +26517,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26583,7 +26595,7 @@
         <v>1.44</v>
       </c>
       <c r="AP123">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ123">
         <v>1.44</v>
@@ -26711,7 +26723,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26998,7 +27010,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ125">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR125">
         <v>1.17</v>
@@ -27204,7 +27216,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ126">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR126">
         <v>2.36</v>
@@ -27329,7 +27341,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27535,7 +27547,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27613,7 +27625,7 @@
         <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -27741,7 +27753,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -28025,10 +28037,10 @@
         <v>1.2</v>
       </c>
       <c r="AP130">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR130">
         <v>1.4</v>
@@ -28437,7 +28449,7 @@
         <v>1.2</v>
       </c>
       <c r="AP132">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ132">
         <v>1.75</v>
@@ -28565,7 +28577,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28643,7 +28655,7 @@
         <v>2.5</v>
       </c>
       <c r="AP133">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ133">
         <v>2.33</v>
@@ -28977,7 +28989,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29058,7 +29070,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR135">
         <v>1.42</v>
@@ -29261,7 +29273,7 @@
         <v>0.73</v>
       </c>
       <c r="AP136">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ136">
         <v>0.75</v>
@@ -29595,7 +29607,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29673,7 +29685,7 @@
         <v>2.55</v>
       </c>
       <c r="AP138">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ138">
         <v>2.33</v>
@@ -29879,10 +29891,10 @@
         <v>1.2</v>
       </c>
       <c r="AP139">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ139">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR139">
         <v>2</v>
@@ -30007,7 +30019,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30088,7 +30100,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ140">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR140">
         <v>1.33</v>
@@ -30213,7 +30225,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30419,7 +30431,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30497,10 +30509,10 @@
         <v>1.09</v>
       </c>
       <c r="AP142">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ142">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR142">
         <v>1.21</v>
@@ -30625,7 +30637,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30706,7 +30718,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ143">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR143">
         <v>1.28</v>
@@ -30831,7 +30843,7 @@
         <v>192</v>
       </c>
       <c r="P144" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q144">
         <v>5.5</v>
@@ -31037,7 +31049,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31243,7 +31255,7 @@
         <v>82</v>
       </c>
       <c r="P146" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q146">
         <v>3.5</v>
@@ -31321,7 +31333,7 @@
         <v>0.75</v>
       </c>
       <c r="AP146">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ146">
         <v>0.9399999999999999</v>
@@ -31530,7 +31542,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ147">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR147">
         <v>1.38</v>
@@ -31733,7 +31745,7 @@
         <v>1.58</v>
       </c>
       <c r="AP148">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ148">
         <v>1.44</v>
@@ -31939,7 +31951,7 @@
         <v>1.09</v>
       </c>
       <c r="AP149">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ149">
         <v>1</v>
@@ -32067,7 +32079,7 @@
         <v>196</v>
       </c>
       <c r="P150" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q150">
         <v>10</v>
@@ -32685,7 +32697,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q153">
         <v>3.2</v>
@@ -32763,10 +32775,10 @@
         <v>1</v>
       </c>
       <c r="AP153">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ153">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR153">
         <v>1.3</v>
@@ -32969,7 +32981,7 @@
         <v>0.85</v>
       </c>
       <c r="AP154">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ154">
         <v>0.75</v>
@@ -33097,7 +33109,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q155">
         <v>2.75</v>
@@ -33303,7 +33315,7 @@
         <v>201</v>
       </c>
       <c r="P156" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33590,7 +33602,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ157">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR157">
         <v>1.3</v>
@@ -34208,7 +34220,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ160">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR160">
         <v>1.35</v>
@@ -34333,7 +34345,7 @@
         <v>82</v>
       </c>
       <c r="P161" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q161">
         <v>1.57</v>
@@ -34411,10 +34423,10 @@
         <v>1.08</v>
       </c>
       <c r="AP161">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ161">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR161">
         <v>2.16</v>
@@ -34539,7 +34551,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q162">
         <v>3.1</v>
@@ -34617,7 +34629,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ162">
         <v>1</v>
@@ -34745,7 +34757,7 @@
         <v>140</v>
       </c>
       <c r="P163" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q163">
         <v>4.33</v>
@@ -34951,7 +34963,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q164">
         <v>1.57</v>
@@ -35032,7 +35044,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ164">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR164">
         <v>2.28</v>
@@ -35569,7 +35581,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q167">
         <v>2.4</v>
@@ -35650,7 +35662,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ167">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR167">
         <v>1.74</v>
@@ -35775,7 +35787,7 @@
         <v>139</v>
       </c>
       <c r="P168" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q168">
         <v>3.4</v>
@@ -35856,7 +35868,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ168">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR168">
         <v>1.35</v>
@@ -35981,7 +35993,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36059,7 +36071,7 @@
         <v>1.46</v>
       </c>
       <c r="AP169">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ169">
         <v>1.75</v>
@@ -36265,7 +36277,7 @@
         <v>0.79</v>
       </c>
       <c r="AP170">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ170">
         <v>0.75</v>
@@ -36393,7 +36405,7 @@
         <v>199</v>
       </c>
       <c r="P171" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q171">
         <v>1.53</v>
@@ -36471,10 +36483,10 @@
         <v>0.93</v>
       </c>
       <c r="AP171">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AQ171">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR171">
         <v>2.14</v>
@@ -36677,7 +36689,7 @@
         <v>0.64</v>
       </c>
       <c r="AP172">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ172">
         <v>0.5600000000000001</v>
@@ -36805,7 +36817,7 @@
         <v>211</v>
       </c>
       <c r="P173" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q173">
         <v>10</v>
@@ -37011,7 +37023,7 @@
         <v>212</v>
       </c>
       <c r="P174" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q174">
         <v>3</v>
@@ -37217,7 +37229,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q175">
         <v>2.88</v>
@@ -37707,10 +37719,10 @@
         <v>1.21</v>
       </c>
       <c r="AP177">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ177">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR177">
         <v>1.42</v>
@@ -37835,7 +37847,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q178">
         <v>3.4</v>
@@ -37916,7 +37928,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ178">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR178">
         <v>1.21</v>
@@ -38122,7 +38134,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ179">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR179">
         <v>1.35</v>
@@ -38247,7 +38259,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q180">
         <v>2.25</v>
@@ -38453,7 +38465,7 @@
         <v>217</v>
       </c>
       <c r="P181" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q181">
         <v>2.4</v>
@@ -38865,7 +38877,7 @@
         <v>219</v>
       </c>
       <c r="P183" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q183">
         <v>2.3</v>
@@ -38946,7 +38958,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ183">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR183">
         <v>1.44</v>
@@ -39483,7 +39495,7 @@
         <v>222</v>
       </c>
       <c r="P186" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q186">
         <v>6.5</v>
@@ -39561,7 +39573,7 @@
         <v>1.67</v>
       </c>
       <c r="AP186">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ186">
         <v>1.75</v>
@@ -39689,7 +39701,7 @@
         <v>82</v>
       </c>
       <c r="P187" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q187">
         <v>3.6</v>
@@ -39767,7 +39779,7 @@
         <v>1.33</v>
       </c>
       <c r="AP187">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ187">
         <v>1.44</v>
@@ -39846,6 +39858,830 @@
       </c>
       <c r="BP187">
         <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7480323</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F188">
+        <v>32</v>
+      </c>
+      <c r="G188" t="s">
+        <v>78</v>
+      </c>
+      <c r="H188" t="s">
+        <v>73</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>1</v>
+      </c>
+      <c r="L188">
+        <v>2</v>
+      </c>
+      <c r="M188">
+        <v>0</v>
+      </c>
+      <c r="N188">
+        <v>2</v>
+      </c>
+      <c r="O188" t="s">
+        <v>223</v>
+      </c>
+      <c r="P188" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q188">
+        <v>3.4</v>
+      </c>
+      <c r="R188">
+        <v>2.2</v>
+      </c>
+      <c r="S188">
+        <v>3.1</v>
+      </c>
+      <c r="T188">
+        <v>1.4</v>
+      </c>
+      <c r="U188">
+        <v>2.75</v>
+      </c>
+      <c r="V188">
+        <v>2.75</v>
+      </c>
+      <c r="W188">
+        <v>1.4</v>
+      </c>
+      <c r="X188">
+        <v>8</v>
+      </c>
+      <c r="Y188">
+        <v>1.08</v>
+      </c>
+      <c r="Z188">
+        <v>2.88</v>
+      </c>
+      <c r="AA188">
+        <v>3.26</v>
+      </c>
+      <c r="AB188">
+        <v>2.4</v>
+      </c>
+      <c r="AC188">
+        <v>1</v>
+      </c>
+      <c r="AD188">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE188">
+        <v>1.29</v>
+      </c>
+      <c r="AF188">
+        <v>3.75</v>
+      </c>
+      <c r="AG188">
+        <v>1.82</v>
+      </c>
+      <c r="AH188">
+        <v>1.92</v>
+      </c>
+      <c r="AI188">
+        <v>1.7</v>
+      </c>
+      <c r="AJ188">
+        <v>2.05</v>
+      </c>
+      <c r="AK188">
+        <v>1.53</v>
+      </c>
+      <c r="AL188">
+        <v>1.38</v>
+      </c>
+      <c r="AM188">
+        <v>1.45</v>
+      </c>
+      <c r="AN188">
+        <v>1</v>
+      </c>
+      <c r="AO188">
+        <v>1.13</v>
+      </c>
+      <c r="AP188">
+        <v>1.12</v>
+      </c>
+      <c r="AQ188">
+        <v>1.06</v>
+      </c>
+      <c r="AR188">
+        <v>1.44</v>
+      </c>
+      <c r="AS188">
+        <v>1.18</v>
+      </c>
+      <c r="AT188">
+        <v>2.62</v>
+      </c>
+      <c r="AU188">
+        <v>4</v>
+      </c>
+      <c r="AV188">
+        <v>8</v>
+      </c>
+      <c r="AW188">
+        <v>5</v>
+      </c>
+      <c r="AX188">
+        <v>14</v>
+      </c>
+      <c r="AY188">
+        <v>10</v>
+      </c>
+      <c r="AZ188">
+        <v>28</v>
+      </c>
+      <c r="BA188">
+        <v>4</v>
+      </c>
+      <c r="BB188">
+        <v>10</v>
+      </c>
+      <c r="BC188">
+        <v>14</v>
+      </c>
+      <c r="BD188">
+        <v>2.09</v>
+      </c>
+      <c r="BE188">
+        <v>6.65</v>
+      </c>
+      <c r="BF188">
+        <v>2.15</v>
+      </c>
+      <c r="BG188">
+        <v>1.15</v>
+      </c>
+      <c r="BH188">
+        <v>4.25</v>
+      </c>
+      <c r="BI188">
+        <v>1.31</v>
+      </c>
+      <c r="BJ188">
+        <v>2.92</v>
+      </c>
+      <c r="BK188">
+        <v>1.62</v>
+      </c>
+      <c r="BL188">
+        <v>2.23</v>
+      </c>
+      <c r="BM188">
+        <v>2.03</v>
+      </c>
+      <c r="BN188">
+        <v>1.75</v>
+      </c>
+      <c r="BO188">
+        <v>2.57</v>
+      </c>
+      <c r="BP188">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7480325</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F189">
+        <v>32</v>
+      </c>
+      <c r="G189" t="s">
+        <v>81</v>
+      </c>
+      <c r="H189" t="s">
+        <v>71</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>2</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
+        <v>2</v>
+      </c>
+      <c r="O189" t="s">
+        <v>224</v>
+      </c>
+      <c r="P189" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q189">
+        <v>2.4</v>
+      </c>
+      <c r="R189">
+        <v>2.1</v>
+      </c>
+      <c r="S189">
+        <v>5</v>
+      </c>
+      <c r="T189">
+        <v>1.44</v>
+      </c>
+      <c r="U189">
+        <v>2.63</v>
+      </c>
+      <c r="V189">
+        <v>3.25</v>
+      </c>
+      <c r="W189">
+        <v>1.33</v>
+      </c>
+      <c r="X189">
+        <v>9</v>
+      </c>
+      <c r="Y189">
+        <v>1.07</v>
+      </c>
+      <c r="Z189">
+        <v>1.82</v>
+      </c>
+      <c r="AA189">
+        <v>3.51</v>
+      </c>
+      <c r="AB189">
+        <v>4.3</v>
+      </c>
+      <c r="AC189">
+        <v>1.01</v>
+      </c>
+      <c r="AD189">
+        <v>8.5</v>
+      </c>
+      <c r="AE189">
+        <v>1.31</v>
+      </c>
+      <c r="AF189">
+        <v>3.62</v>
+      </c>
+      <c r="AG189">
+        <v>1.92</v>
+      </c>
+      <c r="AH189">
+        <v>1.82</v>
+      </c>
+      <c r="AI189">
+        <v>1.95</v>
+      </c>
+      <c r="AJ189">
+        <v>1.8</v>
+      </c>
+      <c r="AK189">
+        <v>1.2</v>
+      </c>
+      <c r="AL189">
+        <v>1.3</v>
+      </c>
+      <c r="AM189">
+        <v>2.18</v>
+      </c>
+      <c r="AN189">
+        <v>1.53</v>
+      </c>
+      <c r="AO189">
+        <v>1</v>
+      </c>
+      <c r="AP189">
+        <v>1.63</v>
+      </c>
+      <c r="AQ189">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR189">
+        <v>1.41</v>
+      </c>
+      <c r="AS189">
+        <v>1.1</v>
+      </c>
+      <c r="AT189">
+        <v>2.51</v>
+      </c>
+      <c r="AU189">
+        <v>9</v>
+      </c>
+      <c r="AV189">
+        <v>0</v>
+      </c>
+      <c r="AW189">
+        <v>9</v>
+      </c>
+      <c r="AX189">
+        <v>4</v>
+      </c>
+      <c r="AY189">
+        <v>22</v>
+      </c>
+      <c r="AZ189">
+        <v>6</v>
+      </c>
+      <c r="BA189">
+        <v>6</v>
+      </c>
+      <c r="BB189">
+        <v>2</v>
+      </c>
+      <c r="BC189">
+        <v>8</v>
+      </c>
+      <c r="BD189">
+        <v>1.36</v>
+      </c>
+      <c r="BE189">
+        <v>10.5</v>
+      </c>
+      <c r="BF189">
+        <v>3.78</v>
+      </c>
+      <c r="BG189">
+        <v>1.1</v>
+      </c>
+      <c r="BH189">
+        <v>5.05</v>
+      </c>
+      <c r="BI189">
+        <v>1.24</v>
+      </c>
+      <c r="BJ189">
+        <v>3.34</v>
+      </c>
+      <c r="BK189">
+        <v>1.49</v>
+      </c>
+      <c r="BL189">
+        <v>2.52</v>
+      </c>
+      <c r="BM189">
+        <v>1.83</v>
+      </c>
+      <c r="BN189">
+        <v>1.98</v>
+      </c>
+      <c r="BO189">
+        <v>2.28</v>
+      </c>
+      <c r="BP189">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7480326</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F190">
+        <v>32</v>
+      </c>
+      <c r="G190" t="s">
+        <v>76</v>
+      </c>
+      <c r="H190" t="s">
+        <v>79</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="K190">
+        <v>1</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="M190">
+        <v>2</v>
+      </c>
+      <c r="N190">
+        <v>2</v>
+      </c>
+      <c r="O190" t="s">
+        <v>82</v>
+      </c>
+      <c r="P190" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q190">
+        <v>1.95</v>
+      </c>
+      <c r="R190">
+        <v>2.5</v>
+      </c>
+      <c r="S190">
+        <v>6</v>
+      </c>
+      <c r="T190">
+        <v>1.29</v>
+      </c>
+      <c r="U190">
+        <v>3.5</v>
+      </c>
+      <c r="V190">
+        <v>2.38</v>
+      </c>
+      <c r="W190">
+        <v>1.53</v>
+      </c>
+      <c r="X190">
+        <v>5.5</v>
+      </c>
+      <c r="Y190">
+        <v>1.14</v>
+      </c>
+      <c r="Z190">
+        <v>1.39</v>
+      </c>
+      <c r="AA190">
+        <v>4.6</v>
+      </c>
+      <c r="AB190">
+        <v>7.7</v>
+      </c>
+      <c r="AC190">
+        <v>0</v>
+      </c>
+      <c r="AD190">
+        <v>0</v>
+      </c>
+      <c r="AE190">
+        <v>1.21</v>
+      </c>
+      <c r="AF190">
+        <v>4.7</v>
+      </c>
+      <c r="AG190">
+        <v>1.6</v>
+      </c>
+      <c r="AH190">
+        <v>2.34</v>
+      </c>
+      <c r="AI190">
+        <v>1.8</v>
+      </c>
+      <c r="AJ190">
+        <v>1.95</v>
+      </c>
+      <c r="AK190">
+        <v>1.14</v>
+      </c>
+      <c r="AL190">
+        <v>1.25</v>
+      </c>
+      <c r="AM190">
+        <v>2.6</v>
+      </c>
+      <c r="AN190">
+        <v>2.47</v>
+      </c>
+      <c r="AO190">
+        <v>1.2</v>
+      </c>
+      <c r="AP190">
+        <v>2.31</v>
+      </c>
+      <c r="AQ190">
+        <v>1.31</v>
+      </c>
+      <c r="AR190">
+        <v>2.18</v>
+      </c>
+      <c r="AS190">
+        <v>1.43</v>
+      </c>
+      <c r="AT190">
+        <v>3.61</v>
+      </c>
+      <c r="AU190">
+        <v>5</v>
+      </c>
+      <c r="AV190">
+        <v>4</v>
+      </c>
+      <c r="AW190">
+        <v>12</v>
+      </c>
+      <c r="AX190">
+        <v>4</v>
+      </c>
+      <c r="AY190">
+        <v>23</v>
+      </c>
+      <c r="AZ190">
+        <v>9</v>
+      </c>
+      <c r="BA190">
+        <v>5</v>
+      </c>
+      <c r="BB190">
+        <v>1</v>
+      </c>
+      <c r="BC190">
+        <v>6</v>
+      </c>
+      <c r="BD190">
+        <v>1.38</v>
+      </c>
+      <c r="BE190">
+        <v>10.25</v>
+      </c>
+      <c r="BF190">
+        <v>3.68</v>
+      </c>
+      <c r="BG190">
+        <v>0</v>
+      </c>
+      <c r="BH190">
+        <v>0</v>
+      </c>
+      <c r="BI190">
+        <v>1.18</v>
+      </c>
+      <c r="BJ190">
+        <v>3.88</v>
+      </c>
+      <c r="BK190">
+        <v>1.35</v>
+      </c>
+      <c r="BL190">
+        <v>2.74</v>
+      </c>
+      <c r="BM190">
+        <v>1.65</v>
+      </c>
+      <c r="BN190">
+        <v>2.17</v>
+      </c>
+      <c r="BO190">
+        <v>2.03</v>
+      </c>
+      <c r="BP190">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7480327</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F191">
+        <v>32</v>
+      </c>
+      <c r="G191" t="s">
+        <v>77</v>
+      </c>
+      <c r="H191" t="s">
+        <v>80</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>1</v>
+      </c>
+      <c r="K191">
+        <v>1</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="M191">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>1</v>
+      </c>
+      <c r="O191" t="s">
+        <v>82</v>
+      </c>
+      <c r="P191" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q191">
+        <v>3.75</v>
+      </c>
+      <c r="R191">
+        <v>2.05</v>
+      </c>
+      <c r="S191">
+        <v>3</v>
+      </c>
+      <c r="T191">
+        <v>1.44</v>
+      </c>
+      <c r="U191">
+        <v>2.63</v>
+      </c>
+      <c r="V191">
+        <v>3.25</v>
+      </c>
+      <c r="W191">
+        <v>1.33</v>
+      </c>
+      <c r="X191">
+        <v>10</v>
+      </c>
+      <c r="Y191">
+        <v>1.06</v>
+      </c>
+      <c r="Z191">
+        <v>3.18</v>
+      </c>
+      <c r="AA191">
+        <v>3.23</v>
+      </c>
+      <c r="AB191">
+        <v>2.24</v>
+      </c>
+      <c r="AC191">
+        <v>1.03</v>
+      </c>
+      <c r="AD191">
+        <v>7.4</v>
+      </c>
+      <c r="AE191">
+        <v>1.37</v>
+      </c>
+      <c r="AF191">
+        <v>3.22</v>
+      </c>
+      <c r="AG191">
+        <v>1.98</v>
+      </c>
+      <c r="AH191">
+        <v>1.77</v>
+      </c>
+      <c r="AI191">
+        <v>1.91</v>
+      </c>
+      <c r="AJ191">
+        <v>1.91</v>
+      </c>
+      <c r="AK191">
+        <v>1.86</v>
+      </c>
+      <c r="AL191">
+        <v>1.34</v>
+      </c>
+      <c r="AM191">
+        <v>1.27</v>
+      </c>
+      <c r="AN191">
+        <v>1.25</v>
+      </c>
+      <c r="AO191">
+        <v>1.07</v>
+      </c>
+      <c r="AP191">
+        <v>1.18</v>
+      </c>
+      <c r="AQ191">
+        <v>1.19</v>
+      </c>
+      <c r="AR191">
+        <v>1.23</v>
+      </c>
+      <c r="AS191">
+        <v>1.21</v>
+      </c>
+      <c r="AT191">
+        <v>2.44</v>
+      </c>
+      <c r="AU191">
+        <v>6</v>
+      </c>
+      <c r="AV191">
+        <v>5</v>
+      </c>
+      <c r="AW191">
+        <v>6</v>
+      </c>
+      <c r="AX191">
+        <v>7</v>
+      </c>
+      <c r="AY191">
+        <v>12</v>
+      </c>
+      <c r="AZ191">
+        <v>16</v>
+      </c>
+      <c r="BA191">
+        <v>8</v>
+      </c>
+      <c r="BB191">
+        <v>1</v>
+      </c>
+      <c r="BC191">
+        <v>9</v>
+      </c>
+      <c r="BD191">
+        <v>3.08</v>
+      </c>
+      <c r="BE191">
+        <v>7.2</v>
+      </c>
+      <c r="BF191">
+        <v>1.59</v>
+      </c>
+      <c r="BG191">
+        <v>1.11</v>
+      </c>
+      <c r="BH191">
+        <v>4.95</v>
+      </c>
+      <c r="BI191">
+        <v>1.25</v>
+      </c>
+      <c r="BJ191">
+        <v>3.28</v>
+      </c>
+      <c r="BK191">
+        <v>1.51</v>
+      </c>
+      <c r="BL191">
+        <v>2.44</v>
+      </c>
+      <c r="BM191">
+        <v>1.87</v>
+      </c>
+      <c r="BN191">
+        <v>1.94</v>
+      </c>
+      <c r="BO191">
+        <v>2.27</v>
+      </c>
+      <c r="BP191">
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="320">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -691,6 +691,9 @@
     <t>['22', '53']</t>
   </si>
   <si>
+    <t>['4']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -911,9 +914,6 @@
   </si>
   <si>
     <t>['42']</t>
-  </si>
-  <si>
-    <t>['4']</t>
   </si>
   <si>
     <t>['37', '49', '86']</t>
@@ -1335,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
         <v>1.75</v>
@@ -2003,7 +2003,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2621,7 +2621,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ7">
         <v>1.19</v>
@@ -3033,7 +3033,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3114,7 +3114,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ9">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3526,7 +3526,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ11">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3857,7 +3857,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -4269,7 +4269,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4681,7 +4681,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4762,7 +4762,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR17">
         <v>1.07</v>
@@ -5299,7 +5299,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5505,7 +5505,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5583,7 +5583,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ21">
         <v>0.9399999999999999</v>
@@ -5711,7 +5711,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6123,7 +6123,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6201,10 +6201,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR24">
         <v>1.14</v>
@@ -6329,7 +6329,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -7359,7 +7359,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7771,7 +7771,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8261,7 +8261,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8389,7 +8389,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8470,7 +8470,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ35">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR35">
         <v>1.32</v>
@@ -8595,7 +8595,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8801,7 +8801,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9007,7 +9007,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9085,10 +9085,10 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ38">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR38">
         <v>1.42</v>
@@ -9419,7 +9419,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9500,7 +9500,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ40">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR40">
         <v>0.9399999999999999</v>
@@ -9625,7 +9625,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9831,7 +9831,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10037,7 +10037,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10118,7 +10118,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ43">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR43">
         <v>1.4</v>
@@ -10243,7 +10243,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10655,7 +10655,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10861,7 +10861,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11145,7 +11145,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48">
         <v>1.06</v>
@@ -11273,7 +11273,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11557,7 +11557,7 @@
         <v>0.67</v>
       </c>
       <c r="AP50">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11891,7 +11891,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12097,7 +12097,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12384,7 +12384,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ54">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR54">
         <v>1.17</v>
@@ -12715,7 +12715,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12796,7 +12796,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ56">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
@@ -12921,7 +12921,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -13127,7 +13127,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13205,7 +13205,7 @@
         <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58">
         <v>0.5600000000000001</v>
@@ -13539,7 +13539,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13745,7 +13745,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14157,7 +14157,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14363,7 +14363,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14441,7 +14441,7 @@
         <v>0.17</v>
       </c>
       <c r="AP64">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ64">
         <v>0.9399999999999999</v>
@@ -14775,7 +14775,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14981,7 +14981,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15062,7 +15062,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ67">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR67">
         <v>1.3</v>
@@ -15393,7 +15393,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15599,7 +15599,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15805,7 +15805,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -16011,7 +16011,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16092,7 +16092,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ72">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR72">
         <v>1.22</v>
@@ -16501,7 +16501,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ74">
         <v>0.5600000000000001</v>
@@ -16629,7 +16629,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16916,7 +16916,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ76">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR76">
         <v>1.75</v>
@@ -17041,7 +17041,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17247,7 +17247,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17453,7 +17453,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17531,10 +17531,10 @@
         <v>3</v>
       </c>
       <c r="AP79">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR79">
         <v>1.56</v>
@@ -17659,7 +17659,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18277,7 +18277,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18483,7 +18483,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18689,7 +18689,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18767,7 +18767,7 @@
         <v>0.8</v>
       </c>
       <c r="AP85">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ85">
         <v>1.75</v>
@@ -18895,7 +18895,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18973,7 +18973,7 @@
         <v>1.83</v>
       </c>
       <c r="AP86">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ86">
         <v>1.19</v>
@@ -19513,7 +19513,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19594,7 +19594,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ89">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -20621,7 +20621,7 @@
         <v>0.86</v>
       </c>
       <c r="AP94">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20749,7 +20749,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20955,7 +20955,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21033,7 +21033,7 @@
         <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ96">
         <v>1.06</v>
@@ -21161,7 +21161,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21367,7 +21367,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21448,7 +21448,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ98">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR98">
         <v>1.21</v>
@@ -21779,7 +21779,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21985,7 +21985,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22397,7 +22397,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22684,7 +22684,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ104">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR104">
         <v>1.42</v>
@@ -22887,7 +22887,7 @@
         <v>0.89</v>
       </c>
       <c r="AP105">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ105">
         <v>0.75</v>
@@ -23015,7 +23015,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23093,7 +23093,7 @@
         <v>0.89</v>
       </c>
       <c r="AP106">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ106">
         <v>1.31</v>
@@ -23427,7 +23427,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23839,7 +23839,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23917,10 +23917,10 @@
         <v>1.25</v>
       </c>
       <c r="AP110">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ110">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR110">
         <v>1.25</v>
@@ -24251,7 +24251,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24869,7 +24869,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -25075,7 +25075,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25568,7 +25568,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ118">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR118">
         <v>2.04</v>
@@ -25771,7 +25771,7 @@
         <v>1.1</v>
       </c>
       <c r="AP119">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ119">
         <v>1.31</v>
@@ -25977,7 +25977,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ120">
         <v>0.9399999999999999</v>
@@ -26311,7 +26311,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26517,7 +26517,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26598,7 +26598,7 @@
         <v>1.12</v>
       </c>
       <c r="AQ123">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR123">
         <v>1.36</v>
@@ -26723,7 +26723,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -27341,7 +27341,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27547,7 +27547,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27753,7 +27753,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -27831,7 +27831,7 @@
         <v>0.9</v>
       </c>
       <c r="AP129">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ129">
         <v>1</v>
@@ -28246,7 +28246,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ131">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR131">
         <v>2.28</v>
@@ -28577,7 +28577,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28658,7 +28658,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ133">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR133">
         <v>1.25</v>
@@ -28864,7 +28864,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ134">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR134">
         <v>1.22</v>
@@ -28989,7 +28989,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29607,7 +29607,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29688,7 +29688,7 @@
         <v>1.12</v>
       </c>
       <c r="AQ138">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR138">
         <v>1.32</v>
@@ -30019,7 +30019,7 @@
         <v>82</v>
       </c>
       <c r="P140" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q140">
         <v>2.63</v>
@@ -30225,7 +30225,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q141">
         <v>2.5</v>
@@ -30303,7 +30303,7 @@
         <v>0.75</v>
       </c>
       <c r="AP141">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ141">
         <v>0.5600000000000001</v>
@@ -30431,7 +30431,7 @@
         <v>121</v>
       </c>
       <c r="P142" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30637,7 +30637,7 @@
         <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>299</v>
+        <v>225</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30715,7 +30715,7 @@
         <v>1.08</v>
       </c>
       <c r="AP143">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ143">
         <v>0.9399999999999999</v>
@@ -31049,7 +31049,7 @@
         <v>82</v>
       </c>
       <c r="P145" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q145">
         <v>2.5</v>
@@ -31748,7 +31748,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ148">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR148">
         <v>1.42</v>
@@ -32160,7 +32160,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ150">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR150">
         <v>1.15</v>
@@ -32572,7 +32572,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ152">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR152">
         <v>2.26</v>
@@ -33393,7 +33393,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ156">
         <v>1.75</v>
@@ -33808,7 +33808,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ158">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR158">
         <v>1.37</v>
@@ -34551,7 +34551,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>299</v>
+        <v>225</v>
       </c>
       <c r="Q162">
         <v>3.1</v>
@@ -34835,7 +34835,7 @@
         <v>0.92</v>
       </c>
       <c r="AP163">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ163">
         <v>0.9399999999999999</v>
@@ -34963,7 +34963,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q164">
         <v>1.57</v>
@@ -35247,7 +35247,7 @@
         <v>1.15</v>
       </c>
       <c r="AP165">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ165">
         <v>1</v>
@@ -35581,7 +35581,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q167">
         <v>2.4</v>
@@ -35659,7 +35659,7 @@
         <v>1.23</v>
       </c>
       <c r="AP167">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ167">
         <v>1.06</v>
@@ -36898,7 +36898,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ173">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR173">
         <v>1.32</v>
@@ -37023,7 +37023,7 @@
         <v>212</v>
       </c>
       <c r="P174" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q174">
         <v>3</v>
@@ -37310,7 +37310,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ175">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR175">
         <v>1.38</v>
@@ -37513,7 +37513,7 @@
         <v>1.07</v>
       </c>
       <c r="AP176">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176">
         <v>1</v>
@@ -38131,7 +38131,7 @@
         <v>1.07</v>
       </c>
       <c r="AP179">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ179">
         <v>1.19</v>
@@ -39701,7 +39701,7 @@
         <v>82</v>
       </c>
       <c r="P187" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q187">
         <v>3.6</v>
@@ -39782,7 +39782,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ187">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR187">
         <v>1.25</v>
@@ -40224,13 +40224,13 @@
         <v>6</v>
       </c>
       <c r="BA189">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB189">
         <v>2</v>
       </c>
       <c r="BC189">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD189">
         <v>1.36</v>
@@ -40682,6 +40682,418 @@
       </c>
       <c r="BP191">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7480328</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45753.33333333334</v>
+      </c>
+      <c r="F192">
+        <v>32</v>
+      </c>
+      <c r="G192" t="s">
+        <v>75</v>
+      </c>
+      <c r="H192" t="s">
+        <v>74</v>
+      </c>
+      <c r="I192">
+        <v>1</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192" t="s">
+        <v>225</v>
+      </c>
+      <c r="P192" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q192">
+        <v>12</v>
+      </c>
+      <c r="R192">
+        <v>3</v>
+      </c>
+      <c r="S192">
+        <v>1.53</v>
+      </c>
+      <c r="T192">
+        <v>1.25</v>
+      </c>
+      <c r="U192">
+        <v>3.75</v>
+      </c>
+      <c r="V192">
+        <v>2.1</v>
+      </c>
+      <c r="W192">
+        <v>1.67</v>
+      </c>
+      <c r="X192">
+        <v>4.5</v>
+      </c>
+      <c r="Y192">
+        <v>1.18</v>
+      </c>
+      <c r="Z192">
+        <v>17</v>
+      </c>
+      <c r="AA192">
+        <v>7.5</v>
+      </c>
+      <c r="AB192">
+        <v>1.14</v>
+      </c>
+      <c r="AC192">
+        <v>1.02</v>
+      </c>
+      <c r="AD192">
+        <v>21</v>
+      </c>
+      <c r="AE192">
+        <v>1.12</v>
+      </c>
+      <c r="AF192">
+        <v>5.75</v>
+      </c>
+      <c r="AG192">
+        <v>1.42</v>
+      </c>
+      <c r="AH192">
+        <v>2.65</v>
+      </c>
+      <c r="AI192">
+        <v>2.2</v>
+      </c>
+      <c r="AJ192">
+        <v>1.62</v>
+      </c>
+      <c r="AK192">
+        <v>5</v>
+      </c>
+      <c r="AL192">
+        <v>1.09</v>
+      </c>
+      <c r="AM192">
+        <v>1.02</v>
+      </c>
+      <c r="AN192">
+        <v>0.93</v>
+      </c>
+      <c r="AO192">
+        <v>2.33</v>
+      </c>
+      <c r="AP192">
+        <v>1.06</v>
+      </c>
+      <c r="AQ192">
+        <v>2.19</v>
+      </c>
+      <c r="AR192">
+        <v>1.34</v>
+      </c>
+      <c r="AS192">
+        <v>1.92</v>
+      </c>
+      <c r="AT192">
+        <v>3.26</v>
+      </c>
+      <c r="AU192">
+        <v>5</v>
+      </c>
+      <c r="AV192">
+        <v>10</v>
+      </c>
+      <c r="AW192">
+        <v>5</v>
+      </c>
+      <c r="AX192">
+        <v>17</v>
+      </c>
+      <c r="AY192">
+        <v>12</v>
+      </c>
+      <c r="AZ192">
+        <v>33</v>
+      </c>
+      <c r="BA192">
+        <v>4</v>
+      </c>
+      <c r="BB192">
+        <v>11</v>
+      </c>
+      <c r="BC192">
+        <v>15</v>
+      </c>
+      <c r="BD192">
+        <v>6.5</v>
+      </c>
+      <c r="BE192">
+        <v>11</v>
+      </c>
+      <c r="BF192">
+        <v>1.11</v>
+      </c>
+      <c r="BG192">
+        <v>1.14</v>
+      </c>
+      <c r="BH192">
+        <v>4.8</v>
+      </c>
+      <c r="BI192">
+        <v>1.25</v>
+      </c>
+      <c r="BJ192">
+        <v>3.45</v>
+      </c>
+      <c r="BK192">
+        <v>1.43</v>
+      </c>
+      <c r="BL192">
+        <v>2.55</v>
+      </c>
+      <c r="BM192">
+        <v>1.68</v>
+      </c>
+      <c r="BN192">
+        <v>2.02</v>
+      </c>
+      <c r="BO192">
+        <v>2.04</v>
+      </c>
+      <c r="BP192">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7480324</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45753.4375</v>
+      </c>
+      <c r="F193">
+        <v>32</v>
+      </c>
+      <c r="G193" t="s">
+        <v>70</v>
+      </c>
+      <c r="H193" t="s">
+        <v>72</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <v>1</v>
+      </c>
+      <c r="N193">
+        <v>1</v>
+      </c>
+      <c r="O193" t="s">
+        <v>82</v>
+      </c>
+      <c r="P193" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q193">
+        <v>2.25</v>
+      </c>
+      <c r="R193">
+        <v>2.25</v>
+      </c>
+      <c r="S193">
+        <v>5</v>
+      </c>
+      <c r="T193">
+        <v>1.36</v>
+      </c>
+      <c r="U193">
+        <v>3</v>
+      </c>
+      <c r="V193">
+        <v>2.75</v>
+      </c>
+      <c r="W193">
+        <v>1.4</v>
+      </c>
+      <c r="X193">
+        <v>7</v>
+      </c>
+      <c r="Y193">
+        <v>1.1</v>
+      </c>
+      <c r="Z193">
+        <v>1.66</v>
+      </c>
+      <c r="AA193">
+        <v>3.83</v>
+      </c>
+      <c r="AB193">
+        <v>4.8</v>
+      </c>
+      <c r="AC193">
+        <v>1.05</v>
+      </c>
+      <c r="AD193">
+        <v>9.5</v>
+      </c>
+      <c r="AE193">
+        <v>1.25</v>
+      </c>
+      <c r="AF193">
+        <v>3.7</v>
+      </c>
+      <c r="AG193">
+        <v>1.82</v>
+      </c>
+      <c r="AH193">
+        <v>1.92</v>
+      </c>
+      <c r="AI193">
+        <v>1.8</v>
+      </c>
+      <c r="AJ193">
+        <v>1.95</v>
+      </c>
+      <c r="AK193">
+        <v>1.18</v>
+      </c>
+      <c r="AL193">
+        <v>1.25</v>
+      </c>
+      <c r="AM193">
+        <v>2.1</v>
+      </c>
+      <c r="AN193">
+        <v>1.6</v>
+      </c>
+      <c r="AO193">
+        <v>1.44</v>
+      </c>
+      <c r="AP193">
+        <v>1.5</v>
+      </c>
+      <c r="AQ193">
+        <v>1.53</v>
+      </c>
+      <c r="AR193">
+        <v>1.73</v>
+      </c>
+      <c r="AS193">
+        <v>1.3</v>
+      </c>
+      <c r="AT193">
+        <v>3.03</v>
+      </c>
+      <c r="AU193">
+        <v>8</v>
+      </c>
+      <c r="AV193">
+        <v>4</v>
+      </c>
+      <c r="AW193">
+        <v>7</v>
+      </c>
+      <c r="AX193">
+        <v>4</v>
+      </c>
+      <c r="AY193">
+        <v>18</v>
+      </c>
+      <c r="AZ193">
+        <v>9</v>
+      </c>
+      <c r="BA193">
+        <v>5</v>
+      </c>
+      <c r="BB193">
+        <v>2</v>
+      </c>
+      <c r="BC193">
+        <v>7</v>
+      </c>
+      <c r="BD193">
+        <v>1.34</v>
+      </c>
+      <c r="BE193">
+        <v>7.5</v>
+      </c>
+      <c r="BF193">
+        <v>3.55</v>
+      </c>
+      <c r="BG193">
+        <v>1.19</v>
+      </c>
+      <c r="BH193">
+        <v>4.1</v>
+      </c>
+      <c r="BI193">
+        <v>1.33</v>
+      </c>
+      <c r="BJ193">
+        <v>2.95</v>
+      </c>
+      <c r="BK193">
+        <v>1.54</v>
+      </c>
+      <c r="BL193">
+        <v>2.3</v>
+      </c>
+      <c r="BM193">
+        <v>1.84</v>
+      </c>
+      <c r="BN193">
+        <v>1.84</v>
+      </c>
+      <c r="BO193">
+        <v>2.28</v>
+      </c>
+      <c r="BP193">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Scotland Premiership_20242025.xlsx
@@ -1819,10 +1819,10 @@
         <v>3</v>
       </c>
       <c r="AY2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="AZ2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA2">
         <v>8</v>
@@ -2025,10 +2025,10 @@
         <v>3</v>
       </c>
       <c r="AY3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA3">
         <v>9</v>
@@ -2231,10 +2231,10 @@
         <v>8</v>
       </c>
       <c r="AY4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2437,10 +2437,10 @@
         <v>7</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA5">
         <v>4</v>
@@ -2643,10 +2643,10 @@
         <v>2</v>
       </c>
       <c r="AY6">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="AZ6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA6">
         <v>10</v>
@@ -2849,10 +2849,10 @@
         <v>9</v>
       </c>
       <c r="AY7">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ7">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA7">
         <v>12</v>
@@ -3055,10 +3055,10 @@
         <v>5</v>
       </c>
       <c r="AY8">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA8">
         <v>6</v>
@@ -3261,10 +3261,10 @@
         <v>4</v>
       </c>
       <c r="AY9">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ9">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA9">
         <v>7</v>
@@ -3467,10 +3467,10 @@
         <v>7</v>
       </c>
       <c r="AY10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA10">
         <v>2</v>
@@ -3676,7 +3676,7 @@
         <v>5</v>
       </c>
       <c r="AZ11">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BA11">
         <v>3</v>
@@ -3879,10 +3879,10 @@
         <v>3</v>
       </c>
       <c r="AY12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA12">
         <v>6</v>
@@ -4085,10 +4085,10 @@
         <v>2</v>
       </c>
       <c r="AY13">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA13">
         <v>4</v>
@@ -4291,10 +4291,10 @@
         <v>1</v>
       </c>
       <c r="AY14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA14">
         <v>5</v>
@@ -4500,7 +4500,7 @@
         <v>4</v>
       </c>
       <c r="AZ15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA15">
         <v>2</v>
@@ -4703,10 +4703,10 @@
         <v>1</v>
       </c>
       <c r="AY16">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -4909,10 +4909,10 @@
         <v>5</v>
       </c>
       <c r="AY17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ17">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BA17">
         <v>2</v>
@@ -5115,10 +5115,10 @@
         <v>1</v>
       </c>
       <c r="AY18">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BA18">
         <v>8</v>
@@ -5321,10 +5321,10 @@
         <v>2</v>
       </c>
       <c r="AY19">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA19">
         <v>8</v>
@@ -5527,10 +5527,10 @@
         <v>4</v>
       </c>
       <c r="AY20">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ20">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA20">
         <v>6</v>
@@ -5733,10 +5733,10 @@
         <v>4</v>
       </c>
       <c r="AY21">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ21">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA21">
         <v>4</v>
@@ -5939,10 +5939,10 @@
         <v>2</v>
       </c>
       <c r="AY22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA22">
         <v>1</v>
@@ -6145,10 +6145,10 @@
         <v>5</v>
       </c>
       <c r="AY23">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ23">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA23">
         <v>7</v>
@@ -6351,10 +6351,10 @@
         <v>5</v>
       </c>
       <c r="AY24">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ24">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA24">
         <v>6</v>
@@ -6557,10 +6557,10 @@
         <v>3</v>
       </c>
       <c r="AY25">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA25">
         <v>4</v>
@@ -6763,10 +6763,10 @@
         <v>2</v>
       </c>
       <c r="AY26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA26">
         <v>3</v>
@@ -6969,10 +6969,10 @@
         <v>1</v>
       </c>
       <c r="AY27">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ27">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA27">
         <v>5</v>
@@ -7175,10 +7175,10 @@
         <v>6</v>
       </c>
       <c r="AY28">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ28">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA28">
         <v>3</v>
@@ -7381,10 +7381,10 @@
         <v>2</v>
       </c>
       <c r="AY29">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA29">
         <v>5</v>
@@ -7587,10 +7587,10 @@
         <v>6</v>
       </c>
       <c r="AY30">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ30">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA30">
         <v>6</v>
@@ -7793,10 +7793,10 @@
         <v>2</v>
       </c>
       <c r="AY31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ31">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA31">
         <v>4</v>
@@ -7999,10 +7999,10 @@
         <v>5</v>
       </c>
       <c r="AY32">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA32">
         <v>5</v>
@@ -8205,10 +8205,10 @@
         <v>2</v>
       </c>
       <c r="AY33">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA33">
         <v>1</v>
@@ -8411,19 +8411,19 @@
         <v>2</v>
       </c>
       <c r="AY34">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ34">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA34">
         <v>10</v>
       </c>
       <c r="BB34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC34">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD34">
         <v>1.93</v>
@@ -8617,10 +8617,10 @@
         <v>3</v>
       </c>
       <c r="AY35">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ35">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BA35">
         <v>11</v>
@@ -8823,10 +8823,10 @@
         <v>4</v>
       </c>
       <c r="AY36">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ36">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BA36">
         <v>7</v>
@@ -9029,10 +9029,10 @@
         <v>4</v>
       </c>
       <c r="AY37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ37">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA37">
         <v>9</v>
@@ -9238,7 +9238,7 @@
         <v>6</v>
       </c>
       <c r="AZ38">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA38">
         <v>3</v>
@@ -9441,10 +9441,10 @@
         <v>9</v>
       </c>
       <c r="AY39">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AZ39">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA39">
         <v>4</v>
@@ -9647,10 +9647,10 @@
         <v>9</v>
       </c>
       <c r="AY40">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ40">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="BA40">
         <v>2</v>
@@ -9853,10 +9853,10 @@
         <v>2</v>
       </c>
       <c r="AY41">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ41">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA41">
         <v>10</v>
@@ -10059,10 +10059,10 @@
         <v>4</v>
       </c>
       <c r="AY42">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ42">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA42">
         <v>3</v>
@@ -10265,10 +10265,10 @@
         <v>11</v>
       </c>
       <c r="AY43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ43">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA43">
         <v>1</v>
@@ -10471,10 +10471,10 @@
         <v>6</v>
       </c>
       <c r="AY44">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ44">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA44">
         <v>2</v>
@@ -10677,10 +10677,10 @@
         <v>5</v>
       </c>
       <c r="AY45">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ45">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA45">
         <v>7</v>
@@ -10883,10 +10883,10 @@
         <v>3</v>
       </c>
       <c r="AY46">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ46">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA46">
         <v>5</v>
@@ -11089,10 +11089,10 @@
         <v>1</v>
       </c>
       <c r="AY47">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="AZ47">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA47">
         <v>18</v>
@@ -11295,10 +11295,10 @@
         <v>3</v>
       </c>
       <c r="AY48">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA48">
         <v>1</v>
@@ -11501,10 +11501,10 @@
         <v>4</v>
       </c>
       <c r="AY49">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ49">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA49">
         <v>5</v>
@@ -11707,10 +11707,10 @@
         <v>7</v>
       </c>
       <c r="AY50">
+        <v>10</v>
+      </c>
+      <c r="AZ50">
         <v>12</v>
-      </c>
-      <c r="AZ50">
-        <v>16</v>
       </c>
       <c r="BA50">
         <v>3</v>
@@ -11913,10 +11913,10 @@
         <v>6</v>
       </c>
       <c r="AY51">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ51">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA51">
         <v>1</v>
@@ -12119,10 +12119,10 @@
         <v>10</v>
       </c>
       <c r="AY52">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ52">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BA52">
         <v>2</v>
@@ -12325,10 +12325,10 @@
         <v>3</v>
       </c>
       <c r="AY53">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ53">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA53">
         <v>5</v>
@@ -12531,10 +12531,10 @@
         <v>6</v>
       </c>
       <c r="AY54">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ54">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA54">
         <v>8</v>
@@ -12737,10 +12737,10 @@
         <v>5</v>
       </c>
       <c r="AY55">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ55">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA55">
         <v>1</v>
@@ -12943,10 +12943,10 @@
         <v>5</v>
       </c>
       <c r="AY56">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ56">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA56">
         <v>3</v>
@@ -13149,10 +13149,10 @@
         <v>4</v>
       </c>
       <c r="AY57">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ57">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA57">
         <v>7</v>
@@ -13355,10 +13355,10 @@
         <v>3</v>
       </c>
       <c r="AY58">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA58">
         <v>9</v>
@@ -13561,10 +13561,10 @@
         <v>8</v>
       </c>
       <c r="AY59">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ59">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA59">
         <v>10</v>
@@ -13767,7 +13767,7 @@
         <v>6</v>
       </c>
       <c r="AY60">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ60">
         <v>10</v>
@@ -13973,10 +13973,10 @@
         <v>1</v>
       </c>
       <c r="AY61">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AZ61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA61">
         <v>7</v>
@@ -14179,10 +14179,10 @@
         <v>8</v>
       </c>
       <c r="AY62">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ62">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA62">
         <v>4</v>
@@ -14385,10 +14385,10 @@
         <v>10</v>
       </c>
       <c r="AY63">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AZ63">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA63">
         <v>4</v>
@@ -14591,10 +14591,10 @@
         <v>4</v>
       </c>
       <c r="AY64">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ64">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BA64">
         <v>6</v>
@@ -14797,10 +14797,10 @@
         <v>2</v>
       </c>
       <c r="AY65">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ65">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA65">
         <v>6</v>
@@ -15003,10 +15003,10 @@
         <v>5</v>
       </c>
       <c r="AY66">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ66">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA66">
         <v>13</v>
@@ -15209,10 +15209,10 @@
         <v>6</v>
       </c>
       <c r="AY67">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AZ67">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA67">
         <v>7</v>
@@ -15415,10 +15415,10 @@
         <v>2</v>
       </c>
       <c r="AY68">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ68">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA68">
         <v>3</v>
@@ -15621,10 +15621,10 @@
         <v>4</v>
       </c>
       <c r="AY69">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ69">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA69">
         <v>5</v>
@@ -15827,10 +15827,10 @@
         <v>7</v>
       </c>
       <c r="AY70">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ70">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA70">
         <v>5</v>
@@ -16033,10 +16033,10 @@
         <v>4</v>
       </c>
       <c r="AY71">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ71">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA71">
         <v>7</v>
@@ -16239,10 +16239,10 @@
         <v>2</v>
       </c>
       <c r="AY72">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ72">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA72">
         <v>6</v>
@@ -16445,10 +16445,10 @@
         <v>3</v>
       </c>
       <c r="AY73">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AZ73">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA73">
         <v>9</v>
@@ -16657,13 +16657,13 @@
         <v>-1</v>
       </c>
       <c r="BA74">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="BB74">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BC74">
-        <v>15</v>
+        <v>-1</v>
       </c>
       <c r="BD74">
         <v>2.15</v>
@@ -17481,13 +17481,13 @@
         <v>-1</v>
       </c>
       <c r="BA78">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="BB78">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BC78">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="BD78">
         <v>1.92</v>
@@ -17687,13 +17687,13 @@
         <v>-1</v>
       </c>
       <c r="BA79">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BB79">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BC79">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="BD79">
         <v>3.8</v>
@@ -17887,10 +17887,10 @@
         <v>1</v>
       </c>
       <c r="AY80">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ80">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BA80">
         <v>9</v>
@@ -18093,10 +18093,10 @@
         <v>3</v>
       </c>
       <c r="AY81">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ81">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="BA81">
         <v>4</v>
@@ -18299,10 +18299,10 @@
         <v>5</v>
       </c>
       <c r="AY82">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AZ82">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA82">
         <v>6</v>
@@ -18505,10 +18505,10 @@
         <v>4</v>
       </c>
       <c r="AY83">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ83">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA83">
         <v>3</v>
@@ -18711,7 +18711,7 @@
         <v>1</v>
       </c>
       <c r="AY84">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AZ84">
         <v>3</v>
@@ -18917,10 +18917,10 @@
         <v>4</v>
       </c>
       <c r="AY85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ85">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA85">
         <v>3</v>
@@ -19329,10 +19329,10 @@
         <v>12</v>
       </c>
       <c r="AY87">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AZ87">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BA87">
         <v>4</v>
@@ -19535,10 +19535,10 @@
         <v>0</v>
       </c>
       <c r="AY88">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AZ88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA88">
         <v>7</v>
@@ -19741,10 +19741,10 @@
         <v>5</v>
       </c>
       <c r="AY89">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ89">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA89">
         <v>2</v>
@@ -19947,10 +19947,10 @@
         <v>2</v>
       </c>
       <c r="AY90">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA90">
         <v>6</v>
@@ -20153,10 +20153,10 @@
         <v>4</v>
       </c>
       <c r="AY91">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ91">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA91">
         <v>14</v>
@@ -20359,10 +20359,10 @@
         <v>4</v>
       </c>
       <c r="AY92">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ92">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA92">
         <v>9</v>
@@ -20565,10 +20565,10 @@
         <v>5</v>
       </c>
       <c r="AY93">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ93">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA93">
         <v>6</v>
@@ -20771,10 +20771,10 @@
         <v>4</v>
       </c>
       <c r="AY94">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ94">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA94">
         <v>7</v>
@@ -20977,10 +20977,10 @@
         <v>5</v>
       </c>
       <c r="AY95">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AZ95">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA95">
         <v>8</v>
@@ -21183,10 +21183,10 @@
         <v>6</v>
       </c>
       <c r="AY96">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ96">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA96">
         <v>2</v>
@@ -21389,10 +21389,10 @@
         <v>3</v>
       </c>
       <c r="AY97">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ97">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA97">
         <v>1</v>
@@ -21595,10 +21595,10 @@
         <v>1</v>
       </c>
       <c r="AY98">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ98">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BA98">
         <v>9</v>
@@ -21801,10 +21801,10 @@
         <v>8</v>
       </c>
       <c r="AY99">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ99">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA99">
         <v>3</v>
@@ -22010,7 +22010,7 @@
         <v>5</v>
       </c>
       <c r="AZ100">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA100">
         <v>2</v>
@@ -22213,7 +22213,7 @@
         <v>4</v>
       </c>
       <c r="AY101">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ101">
         <v>6</v>
@@ -22419,10 +22419,10 @@
         <v>5</v>
       </c>
       <c r="AY102">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ102">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA102">
         <v>4</v>
@@ -22625,10 +22625,10 @@
         <v>1</v>
       </c>
       <c r="AY103">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ103">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA103">
         <v>5</v>
@@ -22834,7 +22834,7 @@
         <v>3</v>
       </c>
       <c r="AZ104">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA104">
         <v>3</v>
@@ -23037,7 +23037,7 @@
         <v>6</v>
       </c>
       <c r="AY105">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ105">
         <v>10</v>
@@ -23243,10 +23243,10 @@
         <v>4</v>
       </c>
       <c r="AY106">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ106">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA106">
         <v>6</v>
@@ -23449,10 +23449,10 @@
         <v>4</v>
       </c>
       <c r="AY107">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ107">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA107">
         <v>4</v>
@@ -23655,10 +23655,10 @@
         <v>4</v>
       </c>
       <c r="AY108">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AZ108">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA108">
         <v>7</v>
@@ -23861,10 +23861,10 @@
         <v>9</v>
       </c>
       <c r="AY109">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ109">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BA109">
         <v>5</v>
@@ -24067,10 +24067,10 @@
         <v>2</v>
       </c>
       <c r="AY110">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AZ110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA110">
         <v>6</v>
@@ -24273,10 +24273,10 @@
         <v>9</v>
       </c>
       <c r="AY111">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ111">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BA111">
         <v>7</v>
@@ -24479,10 +24479,10 @@
         <v>4</v>
       </c>
       <c r="AY112">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ112">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA112">
         <v>10</v>
@@ -24685,10 +24685,10 @@
         <v>2</v>
       </c>
       <c r="AY113">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ113">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA113">
         <v>5</v>
@@ -24891,10 +24891,10 @@
         <v>12</v>
       </c>
       <c r="AY114">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ114">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BA114">
         <v>3</v>
@@ -25097,10 +25097,10 @@
         <v>2</v>
       </c>
       <c r="AY115">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ115">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA115">
         <v>5</v>
@@ -25303,7 +25303,7 @@
         <v>2</v>
       </c>
       <c r="AY116">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="AZ116">
         <v>2</v>
@@ -25509,10 +25509,10 @@
         <v>3</v>
       </c>
       <c r="AY117">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ117">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA117">
         <v>9</v>
@@ -25715,10 +25715,10 @@
         <v>2</v>
       </c>
       <c r="AY118">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AZ118">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA118">
         <v>9</v>
@@ -25921,10 +25921,10 @@
         <v>2</v>
       </c>
       <c r="AY119">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ119">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA119">
         <v>12</v>
@@ -26127,10 +26127,10 @@
         <v>1</v>
       </c>
       <c r="AY120">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ120">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BA120">
         <v>4</v>
@@ -26333,7 +26333,7 @@
         <v>3</v>
       </c>
       <c r="AY121">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AZ121">
         <v>5</v>
@@ -26542,7 +26542,7 @@
         <v>6</v>
       </c>
       <c r="AZ122">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA122">
         <v>4</v>
@@ -26745,10 +26745,10 @@
         <v>3</v>
       </c>
       <c r="AY123">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ123">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA123">
         <v>6</v>
@@ -26951,10 +26951,10 @@
         <v>2</v>
       </c>
       <c r="AY124">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ124">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA124">
         <v>10</v>
@@ -27157,10 +27157,10 @@
         <v>5</v>
       </c>
       <c r="AY125">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AZ125">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA125">
         <v>3</v>
@@ -27363,10 +27363,10 @@
         <v>4</v>
       </c>
       <c r="AY126">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ126">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA126">
         <v>5</v>
@@ -27569,10 +27569,10 @@
         <v>3</v>
       </c>
       <c r="AY127">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AZ127">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA127">
         <v>3</v>
@@ -27775,10 +27775,10 @@
         <v>4</v>
       </c>
       <c r="AY128">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AZ128">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA128">
         <v>7</v>
@@ -27981,10 +27981,10 @@
         <v>2</v>
       </c>
       <c r="AY129">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ129">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA129">
         <v>8</v>
@@ -28187,10 +28187,10 @@
         <v>2</v>
       </c>
       <c r="AY130">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ130">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA130">
         <v>12</v>
@@ -28393,10 +28393,10 @@
         <v>3</v>
       </c>
       <c r="AY131">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ131">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA131">
         <v>15</v>
@@ -28599,10 +28599,10 @@
         <v>7</v>
       </c>
       <c r="AY132">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AZ132">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA132">
         <v>3</v>
@@ -28805,10 +28805,10 @@
         <v>4</v>
       </c>
       <c r="AY133">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ133">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="BA133">
         <v>6</v>
@@ -29011,7 +29011,7 @@
         <v>2</v>
       </c>
       <c r="AY134">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ134">
         <v>5</v>
@@ -29217,10 +29217,10 @@
         <v>3</v>
       </c>
       <c r="AY135">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ135">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BA135">
         <v>8</v>
@@ -29423,10 +29423,10 @@
         <v>4</v>
       </c>
       <c r="AY136">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ136">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA136">
         <v>4</v>
@@ -29629,10 +29629,10 @@
         <v>2</v>
       </c>
       <c r="AY137">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AZ137">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA137">
         <v>12</v>
@@ -29838,7 +29838,7 @@
         <v>8</v>
       </c>
       <c r="AZ138">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA138">
         <v>2</v>
@@ -30041,10 +30041,10 @@
         <v>3</v>
       </c>
       <c r="AY139">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AZ139">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA139">
         <v>10</v>
@@ -31071,10 +31071,10 @@
         <v>15</v>
       </c>
       <c r="AY144">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ144">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BA144">
         <v>3</v>
@@ -33543,10 +33543,10 @@
         <v>5</v>
       </c>
       <c r="AY156">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ156">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA156">
         <v>10</v>
@@ -35403,13 +35403,13 @@
         <v>-1</v>
       </c>
       <c r="BA165">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BB165">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="BC165">
-        <v>15</v>
+        <v>-1</v>
       </c>
       <c r="BD165">
         <v>1.8</v>
@@ -38487,10 +38487,10 @@
         <v>5</v>
       </c>
       <c r="AY180">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ180">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA180">
         <v>7</v>
@@ -39105,10 +39105,10 @@
         <v>2</v>
       </c>
       <c r="AY183">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ183">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA183">
         <v>5</v>
@@ -39311,10 +39311,10 @@
         <v>5</v>
       </c>
       <c r="AY184">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ184">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA184">
         <v>4</v>
@@ -39723,10 +39723,10 @@
         <v>10</v>
       </c>
       <c r="AY186">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ186">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA186">
         <v>7</v>
@@ -39929,10 +39929,10 @@
         <v>12</v>
       </c>
       <c r="AY187">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ187">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BA187">
         <v>4</v>
@@ -40135,10 +40135,10 @@
         <v>4</v>
       </c>
       <c r="AY188">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ188">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA188">
         <v>5</v>
@@ -40344,7 +40344,7 @@
         <v>12</v>
       </c>
       <c r="AZ189">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA189">
         <v>8</v>
@@ -40547,10 +40547,10 @@
         <v>4</v>
       </c>
       <c r="AY190">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ190">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA190">
         <v>7</v>
@@ -40753,10 +40753,10 @@
         <v>14</v>
       </c>
       <c r="AY191">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ191">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BA191">
         <v>4</v>
@@ -40959,10 +40959,10 @@
         <v>17</v>
       </c>
       <c r="AY192">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ192">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="BA192">
         <v>4</v>
@@ -41165,10 +41165,10 @@
         <v>4</v>
       </c>
       <c r="AY193">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ193">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA193">
         <v>5</v>
@@ -41371,7 +41371,7 @@
         <v>4</v>
       </c>
       <c r="AY194">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ194">
         <v>6</v>
@@ -41577,10 +41577,10 @@
         <v>10</v>
       </c>
       <c r="AY195">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ195">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA195">
         <v>6</v>
@@ -41783,10 +41783,10 @@
         <v>9</v>
       </c>
       <c r="AY196">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ196">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA196">
         <v>3</v>
@@ -41989,10 +41989,10 @@
         <v>1</v>
       </c>
       <c r="AY197">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ197">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA197">
         <v>6</v>
@@ -42195,10 +42195,10 @@
         <v>7</v>
       </c>
       <c r="AY198">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ198">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA198">
         <v>6</v>
@@ -42401,10 +42401,10 @@
         <v>2</v>
       </c>
       <c r="AY199">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ199">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA199">
         <v>8</v>
@@ -43849,13 +43849,13 @@
         <v>14</v>
       </c>
       <c r="BA206">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB206">
         <v>4</v>
       </c>
       <c r="BC206">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD206">
         <v>1.38</v>
@@ -44873,10 +44873,10 @@
         <v>4</v>
       </c>
       <c r="AY211">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ211">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA211">
         <v>5</v>
@@ -46109,10 +46109,10 @@
         <v>4</v>
       </c>
       <c r="AY217">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AZ217">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA217">
         <v>7</v>
@@ -47345,10 +47345,10 @@
         <v>14</v>
       </c>
       <c r="AY223">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ223">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BA223">
         <v>6</v>
@@ -47757,7 +47757,7 @@
         <v>1</v>
       </c>
       <c r="AY225">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AZ225">
         <v>5</v>
@@ -48169,7 +48169,7 @@
         <v>11</v>
       </c>
       <c r="AY227">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ227">
         <v>20</v>
@@ -48375,7 +48375,7 @@
         <v>6</v>
       </c>
       <c r="AY228">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ228">
         <v>12</v>
@@ -48581,7 +48581,7 @@
         <v>12</v>
       </c>
       <c r="AY229">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ229">
         <v>19</v>
